--- a/nicknames.xlsx
+++ b/nicknames.xlsx
@@ -1,40 +1,440 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>糖豆</t>
+  </si>
+  <si>
+    <t>千寻</t>
+  </si>
+  <si>
+    <t>冷萃</t>
+  </si>
+  <si>
+    <t>青柠</t>
+  </si>
+  <si>
+    <t>犀牛</t>
+  </si>
+  <si>
+    <t>甜茶</t>
+  </si>
+  <si>
+    <t>冰块</t>
+  </si>
+  <si>
+    <t>米酥</t>
+  </si>
+  <si>
+    <t>花鹿</t>
+  </si>
+  <si>
+    <t>海德薇</t>
+  </si>
+  <si>
+    <t>龙葵</t>
+  </si>
+  <si>
+    <t>芭菲</t>
+  </si>
+  <si>
+    <t>欧芹</t>
+  </si>
+  <si>
+    <t>玉米粒</t>
+  </si>
+  <si>
+    <t>美乐多</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,85 +442,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -403,83 +1030,97 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>孙七</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>周八</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>吴九</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>郑十</t>
-        </is>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/nicknames.xlsx
+++ b/nicknames.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$A$6187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$A$7839</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6187" uniqueCount="3927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7839" uniqueCount="4038">
   <si>
     <t>name</t>
   </si>
@@ -11811,6 +11811,339 @@
   </si>
   <si>
     <t>会议运营</t>
+  </si>
+  <si>
+    <t>离歌</t>
+  </si>
+  <si>
+    <t>绿豆芽</t>
+  </si>
+  <si>
+    <t>逍遥仔</t>
+  </si>
+  <si>
+    <t>青让</t>
+  </si>
+  <si>
+    <t>小峰</t>
+  </si>
+  <si>
+    <t>华松</t>
+  </si>
+  <si>
+    <t>陈威</t>
+  </si>
+  <si>
+    <t>夏曦</t>
+  </si>
+  <si>
+    <t>十五</t>
+  </si>
+  <si>
+    <t>丹江</t>
+  </si>
+  <si>
+    <t>麦当</t>
+  </si>
+  <si>
+    <t>白桔</t>
+  </si>
+  <si>
+    <t>似锦</t>
+  </si>
+  <si>
+    <t>运满满</t>
+  </si>
+  <si>
+    <t>栖月</t>
+  </si>
+  <si>
+    <t>木林</t>
+  </si>
+  <si>
+    <t>凌晨</t>
+  </si>
+  <si>
+    <t>北浅</t>
+  </si>
+  <si>
+    <t>白洛</t>
+  </si>
+  <si>
+    <t>一麦</t>
+  </si>
+  <si>
+    <t>北辰</t>
+  </si>
+  <si>
+    <t>千月</t>
+  </si>
+  <si>
+    <t>浮游</t>
+  </si>
+  <si>
+    <t>尪初一</t>
+  </si>
+  <si>
+    <t>宝琴</t>
+  </si>
+  <si>
+    <t>十一月</t>
+  </si>
+  <si>
+    <t>水牛</t>
+  </si>
+  <si>
+    <t>老包</t>
+  </si>
+  <si>
+    <t>甘木</t>
+  </si>
+  <si>
+    <t>季风</t>
+  </si>
+  <si>
+    <t>青戈</t>
+  </si>
+  <si>
+    <t>思妍</t>
+  </si>
+  <si>
+    <t>暮蝶</t>
+  </si>
+  <si>
+    <t>光明</t>
+  </si>
+  <si>
+    <t>靓俊</t>
+  </si>
+  <si>
+    <t>豌豆荚</t>
+  </si>
+  <si>
+    <t>汽水</t>
+  </si>
+  <si>
+    <t>十八</t>
+  </si>
+  <si>
+    <t>序木</t>
+  </si>
+  <si>
+    <t>葱蒜</t>
+  </si>
+  <si>
+    <t>闪光弹</t>
+  </si>
+  <si>
+    <t>咏林</t>
+  </si>
+  <si>
+    <t>机器猫</t>
+  </si>
+  <si>
+    <t>阿兵</t>
+  </si>
+  <si>
+    <t>妙妙屋</t>
+  </si>
+  <si>
+    <t>古灵</t>
+  </si>
+  <si>
+    <t>哆咪</t>
+  </si>
+  <si>
+    <t>茜念</t>
+  </si>
+  <si>
+    <t>美滋滋</t>
+  </si>
+  <si>
+    <t>恒生</t>
+  </si>
+  <si>
+    <t>欣意</t>
+  </si>
+  <si>
+    <t>晚宁</t>
+  </si>
+  <si>
+    <t>文峰</t>
+  </si>
+  <si>
+    <t>风浅</t>
+  </si>
+  <si>
+    <t>芋扣</t>
+  </si>
+  <si>
+    <t>波菜</t>
+  </si>
+  <si>
+    <t>佳夕</t>
+  </si>
+  <si>
+    <t>长沙</t>
+  </si>
+  <si>
+    <t>金翅</t>
+  </si>
+  <si>
+    <t>克龙</t>
+  </si>
+  <si>
+    <t>制造技工岗位招聘</t>
+  </si>
+  <si>
+    <t>布灵</t>
+  </si>
+  <si>
+    <t>优米</t>
+  </si>
+  <si>
+    <t>云梦泽</t>
+  </si>
+  <si>
+    <t>灰太狼</t>
+  </si>
+  <si>
+    <t>芭蕉</t>
+  </si>
+  <si>
+    <t>煜安</t>
+  </si>
+  <si>
+    <t>浮玉</t>
+  </si>
+  <si>
+    <t>金穗</t>
+  </si>
+  <si>
+    <t>紫乐</t>
+  </si>
+  <si>
+    <t>小妖</t>
+  </si>
+  <si>
+    <t>夜合</t>
+  </si>
+  <si>
+    <t>辉夜</t>
+  </si>
+  <si>
+    <t>湘柯</t>
+  </si>
+  <si>
+    <t>浅夏</t>
+  </si>
+  <si>
+    <t>湖海</t>
+  </si>
+  <si>
+    <t>素馨</t>
+  </si>
+  <si>
+    <t>黑鬼</t>
+  </si>
+  <si>
+    <t>代紫</t>
+  </si>
+  <si>
+    <t>蜜橘</t>
+  </si>
+  <si>
+    <t>蓝楹</t>
+  </si>
+  <si>
+    <t>阿昌</t>
+  </si>
+  <si>
+    <t>辉宇</t>
+  </si>
+  <si>
+    <t>千问</t>
+  </si>
+  <si>
+    <t>红布李</t>
+  </si>
+  <si>
+    <t>十里</t>
+  </si>
+  <si>
+    <t>酥七</t>
+  </si>
+  <si>
+    <t>素素</t>
+  </si>
+  <si>
+    <t>禾子</t>
+  </si>
+  <si>
+    <t>易炫</t>
+  </si>
+  <si>
+    <t>安禾</t>
+  </si>
+  <si>
+    <t>木犀</t>
+  </si>
+  <si>
+    <t>拾伍</t>
+  </si>
+  <si>
+    <t>蒜蓉菇</t>
+  </si>
+  <si>
+    <t>孟起</t>
+  </si>
+  <si>
+    <t>雪莲花</t>
+  </si>
+  <si>
+    <t>芬兰</t>
+  </si>
+  <si>
+    <t>宝丽</t>
+  </si>
+  <si>
+    <t>香菇丸</t>
+  </si>
+  <si>
+    <t>蓝妹</t>
+  </si>
+  <si>
+    <t>江河</t>
+  </si>
+  <si>
+    <t>四月</t>
+  </si>
+  <si>
+    <t>小灵通</t>
+  </si>
+  <si>
+    <t>山川</t>
+  </si>
+  <si>
+    <t>山海</t>
+  </si>
+  <si>
+    <t>梁仔</t>
+  </si>
+  <si>
+    <t>韭菜花</t>
+  </si>
+  <si>
+    <t>风曲&amp;蓝带</t>
+  </si>
+  <si>
+    <t>零度-重名@鱼糕</t>
+  </si>
+  <si>
+    <t>雪梨-重名</t>
+  </si>
+  <si>
+    <t>白云边--重名了</t>
   </si>
 </sst>
 </file>
@@ -12424,13 +12757,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -12790,7 +13126,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A6187"/>
+  <dimension ref="A1:A7839"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="19.3166666666667" style="1" customWidth="1"/>
@@ -43731,8 +44067,8268 @@
         <v>3926</v>
       </c>
     </row>
+    <row r="6188" spans="1:1">
+      <c r="A6188" s="3" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="6189" spans="1:1">
+      <c r="A6189" s="3" t="s">
+        <v>3927</v>
+      </c>
+    </row>
+    <row r="6190" spans="1:1">
+      <c r="A6190" s="3" t="s">
+        <v>3928</v>
+      </c>
+    </row>
+    <row r="6191" spans="1:1">
+      <c r="A6191" s="3" t="s">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="6192" spans="1:1">
+      <c r="A6192" s="3" t="s">
+        <v>3930</v>
+      </c>
+    </row>
+    <row r="6193" spans="1:1">
+      <c r="A6193" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="6194" spans="1:1">
+      <c r="A6194" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="6195" spans="1:1">
+      <c r="A6195" s="3" t="s">
+        <v>3933</v>
+      </c>
+    </row>
+    <row r="6196" spans="1:1">
+      <c r="A6196" s="3" t="s">
+        <v>3934</v>
+      </c>
+    </row>
+    <row r="6197" spans="1:1">
+      <c r="A6197" s="3" t="s">
+        <v>3935</v>
+      </c>
+    </row>
+    <row r="6198" spans="1:1">
+      <c r="A6198" s="3" t="s">
+        <v>3936</v>
+      </c>
+    </row>
+    <row r="6199" spans="1:1">
+      <c r="A6199" s="3" t="s">
+        <v>3937</v>
+      </c>
+    </row>
+    <row r="6200" spans="1:1">
+      <c r="A6200" s="3" t="s">
+        <v>3938</v>
+      </c>
+    </row>
+    <row r="6201" spans="1:1">
+      <c r="A6201" s="3" t="s">
+        <v>3939</v>
+      </c>
+    </row>
+    <row r="6202" spans="1:1">
+      <c r="A6202" s="3" t="s">
+        <v>3546</v>
+      </c>
+    </row>
+    <row r="6203" spans="1:1">
+      <c r="A6203" s="3" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="6204" spans="1:1">
+      <c r="A6204" s="3" t="s">
+        <v>3941</v>
+      </c>
+    </row>
+    <row r="6205" spans="1:1">
+      <c r="A6205" s="3" t="s">
+        <v>3942</v>
+      </c>
+    </row>
+    <row r="6206" spans="1:1">
+      <c r="A6206" s="3" t="s">
+        <v>3943</v>
+      </c>
+    </row>
+    <row r="6207" spans="1:1">
+      <c r="A6207" s="3" t="s">
+        <v>3944</v>
+      </c>
+    </row>
+    <row r="6208" spans="1:1">
+      <c r="A6208" s="3" t="s">
+        <v>2962</v>
+      </c>
+    </row>
+    <row r="6209" spans="1:1">
+      <c r="A6209" s="3" t="s">
+        <v>3945</v>
+      </c>
+    </row>
+    <row r="6210" spans="1:1">
+      <c r="A6210" s="3" t="s">
+        <v>3946</v>
+      </c>
+    </row>
+    <row r="6211" spans="1:1">
+      <c r="A6211" s="3" t="s">
+        <v>3947</v>
+      </c>
+    </row>
+    <row r="6212" spans="1:1">
+      <c r="A6212" s="3" t="s">
+        <v>3948</v>
+      </c>
+    </row>
+    <row r="6213" spans="1:1">
+      <c r="A6213" s="3" t="s">
+        <v>3949</v>
+      </c>
+    </row>
+    <row r="6214" spans="1:1">
+      <c r="A6214" s="3" t="s">
+        <v>3950</v>
+      </c>
+    </row>
+    <row r="6215" spans="1:1">
+      <c r="A6215" s="3" t="s">
+        <v>3951</v>
+      </c>
+    </row>
+    <row r="6216" spans="1:1">
+      <c r="A6216" s="3" t="s">
+        <v>3952</v>
+      </c>
+    </row>
+    <row r="6217" spans="1:1">
+      <c r="A6217" s="3" t="s">
+        <v>3953</v>
+      </c>
+    </row>
+    <row r="6218" spans="1:1">
+      <c r="A6218" s="3" t="s">
+        <v>3954</v>
+      </c>
+    </row>
+    <row r="6219" spans="1:1">
+      <c r="A6219" s="3" t="s">
+        <v>3955</v>
+      </c>
+    </row>
+    <row r="6220" spans="1:1">
+      <c r="A6220" s="3" t="s">
+        <v>3956</v>
+      </c>
+    </row>
+    <row r="6221" spans="1:1">
+      <c r="A6221" s="3" t="s">
+        <v>3957</v>
+      </c>
+    </row>
+    <row r="6222" spans="1:1">
+      <c r="A6222" s="3" t="s">
+        <v>3958</v>
+      </c>
+    </row>
+    <row r="6223" spans="1:1">
+      <c r="A6223" s="3" t="s">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="6224" spans="1:1">
+      <c r="A6224" s="3" t="s">
+        <v>3959</v>
+      </c>
+    </row>
+    <row r="6225" spans="1:1">
+      <c r="A6225" s="3" t="s">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="6226" spans="1:1">
+      <c r="A6226" s="3" t="s">
+        <v>3961</v>
+      </c>
+    </row>
+    <row r="6227" spans="1:1">
+      <c r="A6227" s="3" t="s">
+        <v>3962</v>
+      </c>
+    </row>
+    <row r="6228" spans="1:1">
+      <c r="A6228" s="3" t="s">
+        <v>3963</v>
+      </c>
+    </row>
+    <row r="6229" spans="1:1">
+      <c r="A6229" s="3" t="s">
+        <v>3964</v>
+      </c>
+    </row>
+    <row r="6230" spans="1:1">
+      <c r="A6230" s="3" t="s">
+        <v>3965</v>
+      </c>
+    </row>
+    <row r="6231" spans="1:1">
+      <c r="A6231" s="3" t="s">
+        <v>3966</v>
+      </c>
+    </row>
+    <row r="6232" spans="1:1">
+      <c r="A6232" s="3" t="s">
+        <v>3967</v>
+      </c>
+    </row>
+    <row r="6233" spans="1:1">
+      <c r="A6233" s="3" t="s">
+        <v>3968</v>
+      </c>
+    </row>
+    <row r="6234" spans="1:1">
+      <c r="A6234" s="3" t="s">
+        <v>3969</v>
+      </c>
+    </row>
+    <row r="6235" spans="1:1">
+      <c r="A6235" s="3" t="s">
+        <v>3970</v>
+      </c>
+    </row>
+    <row r="6236" spans="1:1">
+      <c r="A6236" s="3" t="s">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="6237" spans="1:1">
+      <c r="A6237" s="3" t="s">
+        <v>3972</v>
+      </c>
+    </row>
+    <row r="6238" spans="1:1">
+      <c r="A6238" s="3" t="s">
+        <v>3973</v>
+      </c>
+    </row>
+    <row r="6239" spans="1:1">
+      <c r="A6239" s="3" t="s">
+        <v>3974</v>
+      </c>
+    </row>
+    <row r="6240" spans="1:1">
+      <c r="A6240" s="3" t="s">
+        <v>3975</v>
+      </c>
+    </row>
+    <row r="6241" spans="1:1">
+      <c r="A6241" s="3" t="s">
+        <v>3976</v>
+      </c>
+    </row>
+    <row r="6242" spans="1:1">
+      <c r="A6242" s="3" t="s">
+        <v>3977</v>
+      </c>
+    </row>
+    <row r="6243" spans="1:1">
+      <c r="A6243" s="3" t="s">
+        <v>3978</v>
+      </c>
+    </row>
+    <row r="6244" spans="1:1">
+      <c r="A6244" s="3" t="s">
+        <v>3979</v>
+      </c>
+    </row>
+    <row r="6245" spans="1:1">
+      <c r="A6245" s="3" t="s">
+        <v>3980</v>
+      </c>
+    </row>
+    <row r="6246" spans="1:1">
+      <c r="A6246" s="3" t="s">
+        <v>3236</v>
+      </c>
+    </row>
+    <row r="6247" spans="1:1">
+      <c r="A6247" s="3" t="s">
+        <v>2886</v>
+      </c>
+    </row>
+    <row r="6248" spans="1:1">
+      <c r="A6248" s="3" t="s">
+        <v>3981</v>
+      </c>
+    </row>
+    <row r="6249" spans="1:1">
+      <c r="A6249" s="3" t="s">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="6250" spans="1:1">
+      <c r="A6250" s="3" t="s">
+        <v>3982</v>
+      </c>
+    </row>
+    <row r="6251" spans="1:1">
+      <c r="A6251" s="3" t="s">
+        <v>3983</v>
+      </c>
+    </row>
+    <row r="6252" spans="1:1">
+      <c r="A6252" s="3" t="s">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="6253" spans="1:1">
+      <c r="A6253" s="3" t="s">
+        <v>3232</v>
+      </c>
+    </row>
+    <row r="6254" spans="1:1">
+      <c r="A6254" s="3" t="s">
+        <v>3985</v>
+      </c>
+    </row>
+    <row r="6255" spans="1:1">
+      <c r="A6255" s="3" t="s">
+        <v>2675</v>
+      </c>
+    </row>
+    <row r="6256" spans="1:1">
+      <c r="A6256" s="3" t="s">
+        <v>3986</v>
+      </c>
+    </row>
+    <row r="6257" spans="1:1">
+      <c r="A6257" s="3" t="s">
+        <v>3987</v>
+      </c>
+    </row>
+    <row r="6258" spans="1:1">
+      <c r="A6258" s="3" t="s">
+        <v>3988</v>
+      </c>
+    </row>
+    <row r="6259" spans="1:1">
+      <c r="A6259" s="3" t="s">
+        <v>3989</v>
+      </c>
+    </row>
+    <row r="6260" spans="1:1">
+      <c r="A6260" s="3" t="s">
+        <v>3990</v>
+      </c>
+    </row>
+    <row r="6261" spans="1:1">
+      <c r="A6261" s="3" t="s">
+        <v>3991</v>
+      </c>
+    </row>
+    <row r="6262" spans="1:1">
+      <c r="A6262" s="3" t="s">
+        <v>3992</v>
+      </c>
+    </row>
+    <row r="6263" spans="1:1">
+      <c r="A6263" s="3" t="s">
+        <v>3993</v>
+      </c>
+    </row>
+    <row r="6264" spans="1:1">
+      <c r="A6264" s="3" t="s">
+        <v>3994</v>
+      </c>
+    </row>
+    <row r="6265" spans="1:1">
+      <c r="A6265" s="3" t="s">
+        <v>3995</v>
+      </c>
+    </row>
+    <row r="6266" spans="1:1">
+      <c r="A6266" s="3" t="s">
+        <v>3996</v>
+      </c>
+    </row>
+    <row r="6267" spans="1:1">
+      <c r="A6267" s="3" t="s">
+        <v>3997</v>
+      </c>
+    </row>
+    <row r="6268" spans="1:1">
+      <c r="A6268" s="3" t="s">
+        <v>3998</v>
+      </c>
+    </row>
+    <row r="6269" spans="1:1">
+      <c r="A6269" s="3" t="s">
+        <v>3999</v>
+      </c>
+    </row>
+    <row r="6270" spans="1:1">
+      <c r="A6270" s="3" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="6271" spans="1:1">
+      <c r="A6271" s="3" t="s">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="6272" spans="1:1">
+      <c r="A6272" s="3" t="s">
+        <v>4002</v>
+      </c>
+    </row>
+    <row r="6273" spans="1:1">
+      <c r="A6273" s="3" t="s">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="6274" spans="1:1">
+      <c r="A6274" s="3" t="s">
+        <v>4004</v>
+      </c>
+    </row>
+    <row r="6275" spans="1:1">
+      <c r="A6275" s="3" t="s">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="6276" spans="1:1">
+      <c r="A6276" s="3" t="s">
+        <v>4006</v>
+      </c>
+    </row>
+    <row r="6277" spans="1:1">
+      <c r="A6277" s="3" t="s">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="6278" spans="1:1">
+      <c r="A6278" s="3" t="s">
+        <v>4008</v>
+      </c>
+    </row>
+    <row r="6279" spans="1:1">
+      <c r="A6279" s="3" t="s">
+        <v>4009</v>
+      </c>
+    </row>
+    <row r="6280" spans="1:1">
+      <c r="A6280" s="3" t="s">
+        <v>4010</v>
+      </c>
+    </row>
+    <row r="6281" spans="1:1">
+      <c r="A6281" s="3" t="s">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="6282" spans="1:1">
+      <c r="A6282" s="3" t="s">
+        <v>4012</v>
+      </c>
+    </row>
+    <row r="6283" spans="1:1">
+      <c r="A6283" s="3" t="s">
+        <v>3199</v>
+      </c>
+    </row>
+    <row r="6284" spans="1:1">
+      <c r="A6284" s="3" t="s">
+        <v>4013</v>
+      </c>
+    </row>
+    <row r="6285" spans="1:1">
+      <c r="A6285" s="3" t="s">
+        <v>4014</v>
+      </c>
+    </row>
+    <row r="6286" spans="1:1">
+      <c r="A6286" s="3" t="s">
+        <v>4015</v>
+      </c>
+    </row>
+    <row r="6287" spans="1:1">
+      <c r="A6287" s="3" t="s">
+        <v>4016</v>
+      </c>
+    </row>
+    <row r="6288" spans="1:1">
+      <c r="A6288" s="3" t="s">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="6289" spans="1:1">
+      <c r="A6289" s="3" t="s">
+        <v>4018</v>
+      </c>
+    </row>
+    <row r="6290" spans="1:1">
+      <c r="A6290" s="3" t="s">
+        <v>4019</v>
+      </c>
+    </row>
+    <row r="6291" spans="1:1">
+      <c r="A6291" s="3" t="s">
+        <v>4020</v>
+      </c>
+    </row>
+    <row r="6292" spans="1:1">
+      <c r="A6292" s="3" t="s">
+        <v>4021</v>
+      </c>
+    </row>
+    <row r="6293" spans="1:1">
+      <c r="A6293" s="3" t="s">
+        <v>3363</v>
+      </c>
+    </row>
+    <row r="6294" spans="1:1">
+      <c r="A6294" s="3" t="s">
+        <v>4022</v>
+      </c>
+    </row>
+    <row r="6295" spans="1:1">
+      <c r="A6295" s="3" t="s">
+        <v>4023</v>
+      </c>
+    </row>
+    <row r="6296" spans="1:1">
+      <c r="A6296" s="3" t="s">
+        <v>4024</v>
+      </c>
+    </row>
+    <row r="6297" spans="1:1">
+      <c r="A6297" s="3" t="s">
+        <v>4025</v>
+      </c>
+    </row>
+    <row r="6298" spans="1:1">
+      <c r="A6298" s="3" t="s">
+        <v>4026</v>
+      </c>
+    </row>
+    <row r="6299" spans="1:1">
+      <c r="A6299" s="3" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="6300" spans="1:1">
+      <c r="A6300" s="3" t="s">
+        <v>4027</v>
+      </c>
+    </row>
+    <row r="6301" spans="1:1">
+      <c r="A6301" s="3" t="s">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="6302" spans="1:1">
+      <c r="A6302" s="3" t="s">
+        <v>4028</v>
+      </c>
+    </row>
+    <row r="6303" spans="1:1">
+      <c r="A6303" s="3" t="s">
+        <v>4029</v>
+      </c>
+    </row>
+    <row r="6304" spans="1:1">
+      <c r="A6304" s="3" t="s">
+        <v>4030</v>
+      </c>
+    </row>
+    <row r="6305" spans="1:1">
+      <c r="A6305" s="3" t="s">
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="6306" spans="1:1">
+      <c r="A6306" s="3" t="s">
+        <v>4031</v>
+      </c>
+    </row>
+    <row r="6307" spans="1:1">
+      <c r="A6307" s="3" t="s">
+        <v>3088</v>
+      </c>
+    </row>
+    <row r="6308" spans="1:1">
+      <c r="A6308" s="3" t="s">
+        <v>3089</v>
+      </c>
+    </row>
+    <row r="6309" spans="1:1">
+      <c r="A6309" s="3" t="s">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="6310" spans="1:1">
+      <c r="A6310" s="3" t="s">
+        <v>3091</v>
+      </c>
+    </row>
+    <row r="6311" spans="1:1">
+      <c r="A6311" s="3" t="s">
+        <v>3092</v>
+      </c>
+    </row>
+    <row r="6312" spans="1:1">
+      <c r="A6312" s="3" t="s">
+        <v>3656</v>
+      </c>
+    </row>
+    <row r="6313" spans="1:1">
+      <c r="A6313" s="3" t="s">
+        <v>3076</v>
+      </c>
+    </row>
+    <row r="6314" spans="1:1">
+      <c r="A6314" s="3" t="s">
+        <v>3077</v>
+      </c>
+    </row>
+    <row r="6315" spans="1:1">
+      <c r="A6315" s="3" t="s">
+        <v>4032</v>
+      </c>
+    </row>
+    <row r="6316" spans="1:1">
+      <c r="A6316" s="3" t="s">
+        <v>2913</v>
+      </c>
+    </row>
+    <row r="6317" spans="1:1">
+      <c r="A6317" s="3" t="s">
+        <v>3079</v>
+      </c>
+    </row>
+    <row r="6318" spans="1:1">
+      <c r="A6318" s="3" t="s">
+        <v>3080</v>
+      </c>
+    </row>
+    <row r="6319" spans="1:1">
+      <c r="A6319" s="3" t="s">
+        <v>3081</v>
+      </c>
+    </row>
+    <row r="6320" spans="1:1">
+      <c r="A6320" s="3" t="s">
+        <v>3082</v>
+      </c>
+    </row>
+    <row r="6321" spans="1:1">
+      <c r="A6321" s="3" t="s">
+        <v>3083</v>
+      </c>
+    </row>
+    <row r="6322" spans="1:1">
+      <c r="A6322" s="3" t="s">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="6323" spans="1:1">
+      <c r="A6323" s="3" t="s">
+        <v>3085</v>
+      </c>
+    </row>
+    <row r="6324" spans="1:1">
+      <c r="A6324" s="3" t="s">
+        <v>3086</v>
+      </c>
+    </row>
+    <row r="6325" spans="1:1">
+      <c r="A6325" s="3" t="s">
+        <v>3087</v>
+      </c>
+    </row>
+    <row r="6326" spans="1:1">
+      <c r="A6326" s="3" t="s">
+        <v>3067</v>
+      </c>
+    </row>
+    <row r="6327" spans="1:1">
+      <c r="A6327" s="3" t="s">
+        <v>3068</v>
+      </c>
+    </row>
+    <row r="6328" spans="1:1">
+      <c r="A6328" s="3" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="6329" spans="1:1">
+      <c r="A6329" s="3" t="s">
+        <v>2938</v>
+      </c>
+    </row>
+    <row r="6330" spans="1:1">
+      <c r="A6330" s="3" t="s">
+        <v>3070</v>
+      </c>
+    </row>
+    <row r="6331" spans="1:1">
+      <c r="A6331" s="3" t="s">
+        <v>3071</v>
+      </c>
+    </row>
+    <row r="6332" spans="1:1">
+      <c r="A6332" s="3" t="s">
+        <v>3072</v>
+      </c>
+    </row>
+    <row r="6333" spans="1:1">
+      <c r="A6333" s="3" t="s">
+        <v>3073</v>
+      </c>
+    </row>
+    <row r="6334" spans="1:1">
+      <c r="A6334" s="3" t="s">
+        <v>3074</v>
+      </c>
+    </row>
+    <row r="6335" spans="1:1">
+      <c r="A6335" s="3" t="s">
+        <v>3075</v>
+      </c>
+    </row>
+    <row r="6336" spans="1:1">
+      <c r="A6336" s="3" t="s">
+        <v>3059</v>
+      </c>
+    </row>
+    <row r="6337" spans="1:1">
+      <c r="A6337" s="3" t="s">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="6338" spans="1:1">
+      <c r="A6338" s="3" t="s">
+        <v>3061</v>
+      </c>
+    </row>
+    <row r="6339" spans="1:1">
+      <c r="A6339" s="3" t="s">
+        <v>3062</v>
+      </c>
+    </row>
+    <row r="6340" spans="1:1">
+      <c r="A6340" s="3" t="s">
+        <v>3063</v>
+      </c>
+    </row>
+    <row r="6341" spans="1:1">
+      <c r="A6341" s="3" t="s">
+        <v>3064</v>
+      </c>
+    </row>
+    <row r="6342" spans="1:1">
+      <c r="A6342" s="3" t="s">
+        <v>3065</v>
+      </c>
+    </row>
+    <row r="6343" spans="1:1">
+      <c r="A6343" s="3" t="s">
+        <v>3066</v>
+      </c>
+    </row>
+    <row r="6344" spans="1:1">
+      <c r="A6344" s="3" t="s">
+        <v>3045</v>
+      </c>
+    </row>
+    <row r="6345" spans="1:1">
+      <c r="A6345" s="3" t="s">
+        <v>3046</v>
+      </c>
+    </row>
+    <row r="6346" spans="1:1">
+      <c r="A6346" s="3" t="s">
+        <v>3047</v>
+      </c>
+    </row>
+    <row r="6347" spans="1:1">
+      <c r="A6347" s="3" t="s">
+        <v>3048</v>
+      </c>
+    </row>
+    <row r="6348" spans="1:1">
+      <c r="A6348" s="3" t="s">
+        <v>3049</v>
+      </c>
+    </row>
+    <row r="6349" spans="1:1">
+      <c r="A6349" s="3" t="s">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="6350" spans="1:1">
+      <c r="A6350" s="3" t="s">
+        <v>3051</v>
+      </c>
+    </row>
+    <row r="6351" spans="1:1">
+      <c r="A6351" s="3" t="s">
+        <v>2931</v>
+      </c>
+    </row>
+    <row r="6352" spans="1:1">
+      <c r="A6352" s="3" t="s">
+        <v>3052</v>
+      </c>
+    </row>
+    <row r="6353" spans="1:1">
+      <c r="A6353" s="3" t="s">
+        <v>3053</v>
+      </c>
+    </row>
+    <row r="6354" spans="1:1">
+      <c r="A6354" s="3" t="s">
+        <v>3054</v>
+      </c>
+    </row>
+    <row r="6355" spans="1:1">
+      <c r="A6355" s="3" t="s">
+        <v>3055</v>
+      </c>
+    </row>
+    <row r="6356" spans="1:1">
+      <c r="A6356" s="3" t="s">
+        <v>3056</v>
+      </c>
+    </row>
+    <row r="6357" spans="1:1">
+      <c r="A6357" s="3" t="s">
+        <v>3057</v>
+      </c>
+    </row>
+    <row r="6358" spans="1:1">
+      <c r="A6358" s="3" t="s">
+        <v>3058</v>
+      </c>
+    </row>
+    <row r="6359" spans="1:1">
+      <c r="A6359" s="3" t="s">
+        <v>3043</v>
+      </c>
+    </row>
+    <row r="6360" spans="1:1">
+      <c r="A6360" s="3" t="s">
+        <v>3038</v>
+      </c>
+    </row>
+    <row r="6361" spans="1:1">
+      <c r="A6361" s="3" t="s">
+        <v>3039</v>
+      </c>
+    </row>
+    <row r="6362" spans="1:1">
+      <c r="A6362" s="3" t="s">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="6363" spans="1:1">
+      <c r="A6363" s="3" t="s">
+        <v>3041</v>
+      </c>
+    </row>
+    <row r="6364" spans="1:1">
+      <c r="A6364" s="3" t="s">
+        <v>3042</v>
+      </c>
+    </row>
+    <row r="6365" spans="1:1">
+      <c r="A6365" s="3" t="s">
+        <v>3037</v>
+      </c>
+    </row>
+    <row r="6366" spans="1:1">
+      <c r="A6366" s="3" t="s">
+        <v>3411</v>
+      </c>
+    </row>
+    <row r="6367" spans="1:1">
+      <c r="A6367" s="3" t="s">
+        <v>3031</v>
+      </c>
+    </row>
+    <row r="6368" spans="1:1">
+      <c r="A6368" s="3" t="s">
+        <v>3032</v>
+      </c>
+    </row>
+    <row r="6369" spans="1:1">
+      <c r="A6369" s="3" t="s">
+        <v>3033</v>
+      </c>
+    </row>
+    <row r="6370" spans="1:1">
+      <c r="A6370" s="3" t="s">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="6371" spans="1:1">
+      <c r="A6371" s="3" t="s">
+        <v>3035</v>
+      </c>
+    </row>
+    <row r="6372" spans="1:1">
+      <c r="A6372" s="3" t="s">
+        <v>3036</v>
+      </c>
+    </row>
+    <row r="6373" spans="1:1">
+      <c r="A6373" s="3" t="s">
+        <v>3028</v>
+      </c>
+    </row>
+    <row r="6374" spans="1:1">
+      <c r="A6374" s="3" t="s">
+        <v>3487</v>
+      </c>
+    </row>
+    <row r="6375" spans="1:1">
+      <c r="A6375" s="3" t="s">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="6376" spans="1:1">
+      <c r="A6376" s="3" t="s">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="6377" spans="1:1">
+      <c r="A6377" s="3" t="s">
+        <v>3026</v>
+      </c>
+    </row>
+    <row r="6378" spans="1:1">
+      <c r="A6378" s="3" t="s">
+        <v>3027</v>
+      </c>
+    </row>
+    <row r="6379" spans="1:1">
+      <c r="A6379" s="3" t="s">
+        <v>3417</v>
+      </c>
+    </row>
+    <row r="6380" spans="1:1">
+      <c r="A6380" s="3" t="s">
+        <v>3029</v>
+      </c>
+    </row>
+    <row r="6381" spans="1:1">
+      <c r="A6381" s="3" t="s">
+        <v>2643</v>
+      </c>
+    </row>
+    <row r="6382" spans="1:1">
+      <c r="A6382" s="3" t="s">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="6383" spans="1:1">
+      <c r="A6383" s="3" t="s">
+        <v>3030</v>
+      </c>
+    </row>
+    <row r="6384" spans="1:1">
+      <c r="A6384" s="3" t="s">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="6385" spans="1:1">
+      <c r="A6385" s="3" t="s">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="6386" spans="1:1">
+      <c r="A6386" s="3" t="s">
+        <v>3022</v>
+      </c>
+    </row>
+    <row r="6387" spans="1:1">
+      <c r="A6387" s="3" t="s">
+        <v>3023</v>
+      </c>
+    </row>
+    <row r="6388" spans="1:1">
+      <c r="A6388" s="3" t="s">
+        <v>3017</v>
+      </c>
+    </row>
+    <row r="6389" spans="1:1">
+      <c r="A6389" s="3" t="s">
+        <v>3018</v>
+      </c>
+    </row>
+    <row r="6390" spans="1:1">
+      <c r="A6390" s="3" t="s">
+        <v>3019</v>
+      </c>
+    </row>
+    <row r="6391" spans="1:1">
+      <c r="A6391" s="3" t="s">
+        <v>3016</v>
+      </c>
+    </row>
+    <row r="6392" spans="1:1">
+      <c r="A6392" s="3" t="s">
+        <v>3013</v>
+      </c>
+    </row>
+    <row r="6393" spans="1:1">
+      <c r="A6393" s="3" t="s">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="6394" spans="1:1">
+      <c r="A6394" s="3" t="s">
+        <v>3015</v>
+      </c>
+    </row>
+    <row r="6395" spans="1:1">
+      <c r="A6395" s="3" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="6396" spans="1:1">
+      <c r="A6396" s="3" t="s">
+        <v>3020</v>
+      </c>
+    </row>
+    <row r="6397" spans="1:1">
+      <c r="A6397" s="3" t="s">
+        <v>2859</v>
+      </c>
+    </row>
+    <row r="6398" spans="1:1">
+      <c r="A6398" s="3" t="s">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="6399" spans="1:1">
+      <c r="A6399" s="3" t="s">
+        <v>2859</v>
+      </c>
+    </row>
+    <row r="6400" spans="1:1">
+      <c r="A6400" s="3" t="s">
+        <v>3003</v>
+      </c>
+    </row>
+    <row r="6401" spans="1:1">
+      <c r="A6401" s="3" t="s">
+        <v>3004</v>
+      </c>
+    </row>
+    <row r="6402" spans="1:1">
+      <c r="A6402" s="3" t="s">
+        <v>3005</v>
+      </c>
+    </row>
+    <row r="6403" spans="1:1">
+      <c r="A6403" s="3" t="s">
+        <v>3006</v>
+      </c>
+    </row>
+    <row r="6404" spans="1:1">
+      <c r="A6404" s="3" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="6405" spans="1:1">
+      <c r="A6405" s="3" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="6406" spans="1:1">
+      <c r="A6406" s="3" t="s">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="6407" spans="1:1">
+      <c r="A6407" s="3" t="s">
+        <v>3010</v>
+      </c>
+    </row>
+    <row r="6408" spans="1:1">
+      <c r="A6408" s="3" t="s">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="6409" spans="1:1">
+      <c r="A6409" s="3" t="s">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="6410" spans="1:1">
+      <c r="A6410" s="3" t="s">
+        <v>2998</v>
+      </c>
+    </row>
+    <row r="6411" spans="1:1">
+      <c r="A6411" s="3" t="s">
+        <v>2999</v>
+      </c>
+    </row>
+    <row r="6412" spans="1:1">
+      <c r="A6412" s="3" t="s">
+        <v>2861</v>
+      </c>
+    </row>
+    <row r="6413" spans="1:1">
+      <c r="A6413" s="3" t="s">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="6414" spans="1:1">
+      <c r="A6414" s="3" t="s">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="6415" spans="1:1">
+      <c r="A6415" s="3" t="s">
+        <v>2982</v>
+      </c>
+    </row>
+    <row r="6416" spans="1:1">
+      <c r="A6416" s="3" t="s">
+        <v>2997</v>
+      </c>
+    </row>
+    <row r="6417" spans="1:1">
+      <c r="A6417" s="3" t="s">
+        <v>2897</v>
+      </c>
+    </row>
+    <row r="6418" spans="1:1">
+      <c r="A6418" s="3" t="s">
+        <v>2612</v>
+      </c>
+    </row>
+    <row r="6419" spans="1:1">
+      <c r="A6419" s="3" t="s">
+        <v>3674</v>
+      </c>
+    </row>
+    <row r="6420" spans="1:1">
+      <c r="A6420" s="3" t="s">
+        <v>2763</v>
+      </c>
+    </row>
+    <row r="6421" spans="1:1">
+      <c r="A6421" s="3" t="s">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="6422" spans="1:1">
+      <c r="A6422" s="3" t="s">
+        <v>2996</v>
+      </c>
+    </row>
+    <row r="6423" spans="1:1">
+      <c r="A6423" s="3" t="s">
+        <v>2993</v>
+      </c>
+    </row>
+    <row r="6424" spans="1:1">
+      <c r="A6424" s="3" t="s">
+        <v>2994</v>
+      </c>
+    </row>
+    <row r="6425" spans="1:1">
+      <c r="A6425" s="3" t="s">
+        <v>2995</v>
+      </c>
+    </row>
+    <row r="6426" spans="1:1">
+      <c r="A6426" s="3" t="s">
+        <v>2987</v>
+      </c>
+    </row>
+    <row r="6427" spans="1:1">
+      <c r="A6427" s="3" t="s">
+        <v>2979</v>
+      </c>
+    </row>
+    <row r="6428" spans="1:1">
+      <c r="A6428" s="3" t="s">
+        <v>2980</v>
+      </c>
+    </row>
+    <row r="6429" spans="1:1">
+      <c r="A6429" s="3" t="s">
+        <v>2981</v>
+      </c>
+    </row>
+    <row r="6430" spans="1:1">
+      <c r="A6430" s="3" t="s">
+        <v>2982</v>
+      </c>
+    </row>
+    <row r="6431" spans="1:1">
+      <c r="A6431" s="3" t="s">
+        <v>2983</v>
+      </c>
+    </row>
+    <row r="6432" spans="1:1">
+      <c r="A6432" s="3" t="s">
+        <v>2984</v>
+      </c>
+    </row>
+    <row r="6433" spans="1:1">
+      <c r="A6433" s="3" t="s">
+        <v>2985</v>
+      </c>
+    </row>
+    <row r="6434" spans="1:1">
+      <c r="A6434" s="3" t="s">
+        <v>2986</v>
+      </c>
+    </row>
+    <row r="6435" spans="1:1">
+      <c r="A6435" s="3" t="s">
+        <v>2849</v>
+      </c>
+    </row>
+    <row r="6436" spans="1:1">
+      <c r="A6436" s="3" t="s">
+        <v>2988</v>
+      </c>
+    </row>
+    <row r="6437" spans="1:1">
+      <c r="A6437" s="3" t="s">
+        <v>2989</v>
+      </c>
+    </row>
+    <row r="6438" spans="1:1">
+      <c r="A6438" s="3" t="s">
+        <v>2990</v>
+      </c>
+    </row>
+    <row r="6439" spans="1:1">
+      <c r="A6439" s="3" t="s">
+        <v>2991</v>
+      </c>
+    </row>
+    <row r="6440" spans="1:1">
+      <c r="A6440" s="3" t="s">
+        <v>2992</v>
+      </c>
+    </row>
+    <row r="6441" spans="1:1">
+      <c r="A6441" s="3" t="s">
+        <v>2743</v>
+      </c>
+    </row>
+    <row r="6442" spans="1:1">
+      <c r="A6442" s="3" t="s">
+        <v>2978</v>
+      </c>
+    </row>
+    <row r="6443" spans="1:1">
+      <c r="A6443" s="3" t="s">
+        <v>2953</v>
+      </c>
+    </row>
+    <row r="6444" spans="1:1">
+      <c r="A6444" s="3" t="s">
+        <v>2977</v>
+      </c>
+    </row>
+    <row r="6445" spans="1:1">
+      <c r="A6445" s="3" t="s">
+        <v>2962</v>
+      </c>
+    </row>
+    <row r="6446" spans="1:1">
+      <c r="A6446" s="3" t="s">
+        <v>2963</v>
+      </c>
+    </row>
+    <row r="6447" spans="1:1">
+      <c r="A6447" s="3" t="s">
+        <v>2964</v>
+      </c>
+    </row>
+    <row r="6448" spans="1:1">
+      <c r="A6448" s="3" t="s">
+        <v>2965</v>
+      </c>
+    </row>
+    <row r="6449" spans="1:1">
+      <c r="A6449" s="3" t="s">
+        <v>2966</v>
+      </c>
+    </row>
+    <row r="6450" spans="1:1">
+      <c r="A6450" s="3" t="s">
+        <v>2967</v>
+      </c>
+    </row>
+    <row r="6451" spans="1:1">
+      <c r="A6451" s="3" t="s">
+        <v>2968</v>
+      </c>
+    </row>
+    <row r="6452" spans="1:1">
+      <c r="A6452" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="6453" spans="1:1">
+      <c r="A6453" s="3" t="s">
+        <v>2970</v>
+      </c>
+    </row>
+    <row r="6454" spans="1:1">
+      <c r="A6454" s="3" t="s">
+        <v>2971</v>
+      </c>
+    </row>
+    <row r="6455" spans="1:1">
+      <c r="A6455" s="3" t="s">
+        <v>2911</v>
+      </c>
+    </row>
+    <row r="6456" spans="1:1">
+      <c r="A6456" s="3" t="s">
+        <v>2972</v>
+      </c>
+    </row>
+    <row r="6457" spans="1:1">
+      <c r="A6457" s="3" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="6458" spans="1:1">
+      <c r="A6458" s="3" t="s">
+        <v>3283</v>
+      </c>
+    </row>
+    <row r="6459" spans="1:1">
+      <c r="A6459" s="3" t="s">
+        <v>3146</v>
+      </c>
+    </row>
+    <row r="6460" spans="1:1">
+      <c r="A6460" s="3" t="s">
+        <v>3853</v>
+      </c>
+    </row>
+    <row r="6461" spans="1:1">
+      <c r="A6461" s="3" t="s">
+        <v>2973</v>
+      </c>
+    </row>
+    <row r="6462" spans="1:1">
+      <c r="A6462" s="3" t="s">
+        <v>2953</v>
+      </c>
+    </row>
+    <row r="6463" spans="1:1">
+      <c r="A6463" s="3" t="s">
+        <v>2954</v>
+      </c>
+    </row>
+    <row r="6464" spans="1:1">
+      <c r="A6464" s="3" t="s">
+        <v>2974</v>
+      </c>
+    </row>
+    <row r="6465" spans="1:1">
+      <c r="A6465" s="3" t="s">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="6466" spans="1:1">
+      <c r="A6466" s="3" t="s">
+        <v>2961</v>
+      </c>
+    </row>
+    <row r="6467" spans="1:1">
+      <c r="A6467" s="3" t="s">
+        <v>2957</v>
+      </c>
+    </row>
+    <row r="6468" spans="1:1">
+      <c r="A6468" s="3" t="s">
+        <v>2958</v>
+      </c>
+    </row>
+    <row r="6469" spans="1:1">
+      <c r="A6469" s="3" t="s">
+        <v>2959</v>
+      </c>
+    </row>
+    <row r="6470" spans="1:1">
+      <c r="A6470" s="3" t="s">
+        <v>2960</v>
+      </c>
+    </row>
+    <row r="6471" spans="1:1">
+      <c r="A6471" s="3" t="s">
+        <v>2976</v>
+      </c>
+    </row>
+    <row r="6472" spans="1:1">
+      <c r="A6472" s="3" t="s">
+        <v>2956</v>
+      </c>
+    </row>
+    <row r="6473" spans="1:1">
+      <c r="A6473" s="3" t="s">
+        <v>3154</v>
+      </c>
+    </row>
+    <row r="6474" spans="1:1">
+      <c r="A6474" s="3" t="s">
+        <v>2955</v>
+      </c>
+    </row>
+    <row r="6475" spans="1:1">
+      <c r="A6475" s="3" t="s">
+        <v>3247</v>
+      </c>
+    </row>
+    <row r="6476" spans="1:1">
+      <c r="A6476" s="3" t="s">
+        <v>2953</v>
+      </c>
+    </row>
+    <row r="6477" spans="1:1">
+      <c r="A6477" s="3" t="s">
+        <v>2954</v>
+      </c>
+    </row>
+    <row r="6478" spans="1:1">
+      <c r="A6478" s="3" t="s">
+        <v>3118</v>
+      </c>
+    </row>
+    <row r="6479" spans="1:1">
+      <c r="A6479" s="3" t="s">
+        <v>3495</v>
+      </c>
+    </row>
+    <row r="6480" spans="1:1">
+      <c r="A6480" s="3" t="s">
+        <v>3234</v>
+      </c>
+    </row>
+    <row r="6481" spans="1:1">
+      <c r="A6481" s="3" t="s">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="6482" spans="1:1">
+      <c r="A6482" s="3" t="s">
+        <v>2938</v>
+      </c>
+    </row>
+    <row r="6483" spans="1:1">
+      <c r="A6483" s="3" t="s">
+        <v>2939</v>
+      </c>
+    </row>
+    <row r="6484" spans="1:1">
+      <c r="A6484" s="3" t="s">
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="6485" spans="1:1">
+      <c r="A6485" s="3" t="s">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="6486" spans="1:1">
+      <c r="A6486" s="3" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="6487" spans="1:1">
+      <c r="A6487" s="3" t="s">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="6488" spans="1:1">
+      <c r="A6488" s="3" t="s">
+        <v>2943</v>
+      </c>
+    </row>
+    <row r="6489" spans="1:1">
+      <c r="A6489" s="3" t="s">
+        <v>2944</v>
+      </c>
+    </row>
+    <row r="6490" spans="1:1">
+      <c r="A6490" s="3" t="s">
+        <v>2945</v>
+      </c>
+    </row>
+    <row r="6491" spans="1:1">
+      <c r="A6491" s="3" t="s">
+        <v>2946</v>
+      </c>
+    </row>
+    <row r="6492" spans="1:1">
+      <c r="A6492" s="3" t="s">
+        <v>2947</v>
+      </c>
+    </row>
+    <row r="6493" spans="1:1">
+      <c r="A6493" s="3" t="s">
+        <v>2948</v>
+      </c>
+    </row>
+    <row r="6494" spans="1:1">
+      <c r="A6494" s="3" t="s">
+        <v>2949</v>
+      </c>
+    </row>
+    <row r="6495" spans="1:1">
+      <c r="A6495" s="3" t="s">
+        <v>2950</v>
+      </c>
+    </row>
+    <row r="6496" spans="1:1">
+      <c r="A6496" s="3" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="6497" spans="1:1">
+      <c r="A6497" s="3" t="s">
+        <v>2952</v>
+      </c>
+    </row>
+    <row r="6498" spans="1:1">
+      <c r="A6498" s="3" t="s">
+        <v>2921</v>
+      </c>
+    </row>
+    <row r="6499" spans="1:1">
+      <c r="A6499" s="3" t="s">
+        <v>2922</v>
+      </c>
+    </row>
+    <row r="6500" spans="1:1">
+      <c r="A6500" s="3" t="s">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="6501" spans="1:1">
+      <c r="A6501" s="3" t="s">
+        <v>2923</v>
+      </c>
+    </row>
+    <row r="6502" spans="1:1">
+      <c r="A6502" s="3" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="6503" spans="1:1">
+      <c r="A6503" s="3" t="s">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="6504" spans="1:1">
+      <c r="A6504" s="3" t="s">
+        <v>2926</v>
+      </c>
+    </row>
+    <row r="6505" spans="1:1">
+      <c r="A6505" s="3" t="s">
+        <v>2927</v>
+      </c>
+    </row>
+    <row r="6506" spans="1:1">
+      <c r="A6506" s="3" t="s">
+        <v>2928</v>
+      </c>
+    </row>
+    <row r="6507" spans="1:1">
+      <c r="A6507" s="3" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="6508" spans="1:1">
+      <c r="A6508" s="3" t="s">
+        <v>2929</v>
+      </c>
+    </row>
+    <row r="6509" spans="1:1">
+      <c r="A6509" s="3" t="s">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="6510" spans="1:1">
+      <c r="A6510" s="3" t="s">
+        <v>2931</v>
+      </c>
+    </row>
+    <row r="6511" spans="1:1">
+      <c r="A6511" s="3" t="s">
+        <v>2932</v>
+      </c>
+    </row>
+    <row r="6512" spans="1:1">
+      <c r="A6512" s="3" t="s">
+        <v>3098</v>
+      </c>
+    </row>
+    <row r="6513" spans="1:1">
+      <c r="A6513" s="3" t="s">
+        <v>2934</v>
+      </c>
+    </row>
+    <row r="6514" spans="1:1">
+      <c r="A6514" s="3" t="s">
+        <v>3430</v>
+      </c>
+    </row>
+    <row r="6515" spans="1:1">
+      <c r="A6515" s="3" t="s">
+        <v>3218</v>
+      </c>
+    </row>
+    <row r="6516" spans="1:1">
+      <c r="A6516" s="3" t="s">
+        <v>2935</v>
+      </c>
+    </row>
+    <row r="6517" spans="1:1">
+      <c r="A6517" s="3" t="s">
+        <v>2936</v>
+      </c>
+    </row>
+    <row r="6518" spans="1:1">
+      <c r="A6518" s="3" t="s">
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="6519" spans="1:1">
+      <c r="A6519" s="3" t="s">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="6520" spans="1:1">
+      <c r="A6520" s="3" t="s">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="6521" spans="1:1">
+      <c r="A6521" s="3" t="s">
+        <v>2917</v>
+      </c>
+    </row>
+    <row r="6522" spans="1:1">
+      <c r="A6522" s="3" t="s">
+        <v>2918</v>
+      </c>
+    </row>
+    <row r="6523" spans="1:1">
+      <c r="A6523" s="3" t="s">
+        <v>2919</v>
+      </c>
+    </row>
+    <row r="6524" spans="1:1">
+      <c r="A6524" s="3" t="s">
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="6525" spans="1:1">
+      <c r="A6525" s="3" t="s">
+        <v>2905</v>
+      </c>
+    </row>
+    <row r="6526" spans="1:1">
+      <c r="A6526" s="3" t="s">
+        <v>2906</v>
+      </c>
+    </row>
+    <row r="6527" spans="1:1">
+      <c r="A6527" s="3" t="s">
+        <v>2907</v>
+      </c>
+    </row>
+    <row r="6528" spans="1:1">
+      <c r="A6528" s="3" t="s">
+        <v>2908</v>
+      </c>
+    </row>
+    <row r="6529" spans="1:1">
+      <c r="A6529" s="3" t="s">
+        <v>2909</v>
+      </c>
+    </row>
+    <row r="6530" spans="1:1">
+      <c r="A6530" s="3" t="s">
+        <v>2910</v>
+      </c>
+    </row>
+    <row r="6531" spans="1:1">
+      <c r="A6531" s="3" t="s">
+        <v>2911</v>
+      </c>
+    </row>
+    <row r="6532" spans="1:1">
+      <c r="A6532" s="3" t="s">
+        <v>2912</v>
+      </c>
+    </row>
+    <row r="6533" spans="1:1">
+      <c r="A6533" s="3" t="s">
+        <v>2913</v>
+      </c>
+    </row>
+    <row r="6534" spans="1:1">
+      <c r="A6534" s="3" t="s">
+        <v>2914</v>
+      </c>
+    </row>
+    <row r="6535" spans="1:1">
+      <c r="A6535" s="3" t="s">
+        <v>2915</v>
+      </c>
+    </row>
+    <row r="6536" spans="1:1">
+      <c r="A6536" s="3" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="6537" spans="1:1">
+      <c r="A6537" s="3" t="s">
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="6538" spans="1:1">
+      <c r="A6538" s="3" t="s">
+        <v>2883</v>
+      </c>
+    </row>
+    <row r="6539" spans="1:1">
+      <c r="A6539" s="3" t="s">
+        <v>2884</v>
+      </c>
+    </row>
+    <row r="6540" spans="1:1">
+      <c r="A6540" s="3" t="s">
+        <v>2885</v>
+      </c>
+    </row>
+    <row r="6541" spans="1:1">
+      <c r="A6541" s="3" t="s">
+        <v>2886</v>
+      </c>
+    </row>
+    <row r="6542" spans="1:1">
+      <c r="A6542" s="3" t="s">
+        <v>2887</v>
+      </c>
+    </row>
+    <row r="6543" spans="1:1">
+      <c r="A6543" s="3" t="s">
+        <v>2888</v>
+      </c>
+    </row>
+    <row r="6544" spans="1:1">
+      <c r="A6544" s="3" t="s">
+        <v>2889</v>
+      </c>
+    </row>
+    <row r="6545" spans="1:1">
+      <c r="A6545" s="3" t="s">
+        <v>2890</v>
+      </c>
+    </row>
+    <row r="6546" spans="1:1">
+      <c r="A6546" s="3" t="s">
+        <v>2891</v>
+      </c>
+    </row>
+    <row r="6547" spans="1:1">
+      <c r="A6547" s="3" t="s">
+        <v>2892</v>
+      </c>
+    </row>
+    <row r="6548" spans="1:1">
+      <c r="A6548" s="3" t="s">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="6549" spans="1:1">
+      <c r="A6549" s="3" t="s">
+        <v>2894</v>
+      </c>
+    </row>
+    <row r="6550" spans="1:1">
+      <c r="A6550" s="3" t="s">
+        <v>2807</v>
+      </c>
+    </row>
+    <row r="6551" spans="1:1">
+      <c r="A6551" s="3" t="s">
+        <v>2895</v>
+      </c>
+    </row>
+    <row r="6552" spans="1:1">
+      <c r="A6552" s="3" t="s">
+        <v>2896</v>
+      </c>
+    </row>
+    <row r="6553" spans="1:1">
+      <c r="A6553" s="3" t="s">
+        <v>2897</v>
+      </c>
+    </row>
+    <row r="6554" spans="1:1">
+      <c r="A6554" s="3" t="s">
+        <v>2773</v>
+      </c>
+    </row>
+    <row r="6555" spans="1:1">
+      <c r="A6555" s="3" t="s">
+        <v>2898</v>
+      </c>
+    </row>
+    <row r="6556" spans="1:1">
+      <c r="A6556" s="3" t="s">
+        <v>2899</v>
+      </c>
+    </row>
+    <row r="6557" spans="1:1">
+      <c r="A6557" s="3" t="s">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="6558" spans="1:1">
+      <c r="A6558" s="3" t="s">
+        <v>2901</v>
+      </c>
+    </row>
+    <row r="6559" spans="1:1">
+      <c r="A6559" s="3" t="s">
+        <v>2902</v>
+      </c>
+    </row>
+    <row r="6560" spans="1:1">
+      <c r="A6560" s="3" t="s">
+        <v>2903</v>
+      </c>
+    </row>
+    <row r="6561" spans="1:1">
+      <c r="A6561" s="3" t="s">
+        <v>2904</v>
+      </c>
+    </row>
+    <row r="6562" spans="1:1">
+      <c r="A6562" s="3" t="s">
+        <v>2881</v>
+      </c>
+    </row>
+    <row r="6563" spans="1:1">
+      <c r="A6563" s="3" t="s">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="6564" spans="1:1">
+      <c r="A6564" s="3" t="s">
+        <v>3465</v>
+      </c>
+    </row>
+    <row r="6565" spans="1:1">
+      <c r="A6565" s="3" t="s">
+        <v>2878</v>
+      </c>
+    </row>
+    <row r="6566" spans="1:1">
+      <c r="A6566" s="3" t="s">
+        <v>2809</v>
+      </c>
+    </row>
+    <row r="6567" spans="1:1">
+      <c r="A6567" s="3" t="s">
+        <v>2802</v>
+      </c>
+    </row>
+    <row r="6568" spans="1:1">
+      <c r="A6568" s="3" t="s">
+        <v>2867</v>
+      </c>
+    </row>
+    <row r="6569" spans="1:1">
+      <c r="A6569" s="3" t="s">
+        <v>2868</v>
+      </c>
+    </row>
+    <row r="6570" spans="1:1">
+      <c r="A6570" s="3" t="s">
+        <v>2869</v>
+      </c>
+    </row>
+    <row r="6571" spans="1:1">
+      <c r="A6571" s="3" t="s">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="6572" spans="1:1">
+      <c r="A6572" s="3" t="s">
+        <v>2871</v>
+      </c>
+    </row>
+    <row r="6573" spans="1:1">
+      <c r="A6573" s="3" t="s">
+        <v>2872</v>
+      </c>
+    </row>
+    <row r="6574" spans="1:1">
+      <c r="A6574" s="3" t="s">
+        <v>2873</v>
+      </c>
+    </row>
+    <row r="6575" spans="1:1">
+      <c r="A6575" s="3" t="s">
+        <v>2874</v>
+      </c>
+    </row>
+    <row r="6576" spans="1:1">
+      <c r="A6576" s="3" t="s">
+        <v>2875</v>
+      </c>
+    </row>
+    <row r="6577" spans="1:1">
+      <c r="A6577" s="3" t="s">
+        <v>3360</v>
+      </c>
+    </row>
+    <row r="6578" spans="1:1">
+      <c r="A6578" s="3" t="s">
+        <v>2876</v>
+      </c>
+    </row>
+    <row r="6579" spans="1:1">
+      <c r="A6579" s="3" t="s">
+        <v>2877</v>
+      </c>
+    </row>
+    <row r="6580" spans="1:1">
+      <c r="A6580" s="3" t="s">
+        <v>3276</v>
+      </c>
+    </row>
+    <row r="6581" spans="1:1">
+      <c r="A6581" s="3" t="s">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="6582" spans="1:1">
+      <c r="A6582" s="3" t="s">
+        <v>2862</v>
+      </c>
+    </row>
+    <row r="6583" spans="1:1">
+      <c r="A6583" s="3" t="s">
+        <v>2863</v>
+      </c>
+    </row>
+    <row r="6584" spans="1:1">
+      <c r="A6584" s="3" t="s">
+        <v>2861</v>
+      </c>
+    </row>
+    <row r="6585" spans="1:1">
+      <c r="A6585" s="3" t="s">
+        <v>2852</v>
+      </c>
+    </row>
+    <row r="6586" spans="1:1">
+      <c r="A6586" s="3" t="s">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="6587" spans="1:1">
+      <c r="A6587" s="3" t="s">
+        <v>2865</v>
+      </c>
+    </row>
+    <row r="6588" spans="1:1">
+      <c r="A6588" s="3" t="s">
+        <v>2859</v>
+      </c>
+    </row>
+    <row r="6589" spans="1:1">
+      <c r="A6589" s="3" t="s">
+        <v>2860</v>
+      </c>
+    </row>
+    <row r="6590" spans="1:1">
+      <c r="A6590" s="3" t="s">
+        <v>3218</v>
+      </c>
+    </row>
+    <row r="6591" spans="1:1">
+      <c r="A6591" s="3" t="s">
+        <v>2849</v>
+      </c>
+    </row>
+    <row r="6592" spans="1:1">
+      <c r="A6592" s="3" t="s">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="6593" spans="1:1">
+      <c r="A6593" s="3" t="s">
+        <v>2851</v>
+      </c>
+    </row>
+    <row r="6594" spans="1:1">
+      <c r="A6594" s="3" t="s">
+        <v>2852</v>
+      </c>
+    </row>
+    <row r="6595" spans="1:1">
+      <c r="A6595" s="3" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="6596" spans="1:1">
+      <c r="A6596" s="3" t="s">
+        <v>3430</v>
+      </c>
+    </row>
+    <row r="6597" spans="1:1">
+      <c r="A6597" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="6598" spans="1:1">
+      <c r="A6598" s="3" t="s">
+        <v>2855</v>
+      </c>
+    </row>
+    <row r="6599" spans="1:1">
+      <c r="A6599" s="3" t="s">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="6600" spans="1:1">
+      <c r="A6600" s="3" t="s">
+        <v>2857</v>
+      </c>
+    </row>
+    <row r="6601" spans="1:1">
+      <c r="A6601" s="3" t="s">
+        <v>2858</v>
+      </c>
+    </row>
+    <row r="6602" spans="1:1">
+      <c r="A6602" s="3" t="s">
+        <v>3335</v>
+      </c>
+    </row>
+    <row r="6603" spans="1:1">
+      <c r="A6603" s="3" t="s">
+        <v>2846</v>
+      </c>
+    </row>
+    <row r="6604" spans="1:1">
+      <c r="A6604" s="3" t="s">
+        <v>2847</v>
+      </c>
+    </row>
+    <row r="6605" spans="1:1">
+      <c r="A6605" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="6606" spans="1:1">
+      <c r="A6606" s="3" t="s">
+        <v>2844</v>
+      </c>
+    </row>
+    <row r="6607" spans="1:1">
+      <c r="A6607" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="6608" spans="1:1">
+      <c r="A6608" s="3" t="s">
+        <v>2841</v>
+      </c>
+    </row>
+    <row r="6609" spans="1:1">
+      <c r="A6609" s="3" t="s">
+        <v>2842</v>
+      </c>
+    </row>
+    <row r="6610" spans="1:1">
+      <c r="A6610" s="3" t="s">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="6611" spans="1:1">
+      <c r="A6611" s="3" t="s">
+        <v>2840</v>
+      </c>
+    </row>
+    <row r="6612" spans="1:1">
+      <c r="A6612" s="3" t="s">
+        <v>2801</v>
+      </c>
+    </row>
+    <row r="6613" spans="1:1">
+      <c r="A6613" s="3" t="s">
+        <v>3218</v>
+      </c>
+    </row>
+    <row r="6614" spans="1:1">
+      <c r="A6614" s="3" t="s">
+        <v>2839</v>
+      </c>
+    </row>
+    <row r="6615" spans="1:1">
+      <c r="A6615" s="3" t="s">
+        <v>3410</v>
+      </c>
+    </row>
+    <row r="6616" spans="1:1">
+      <c r="A6616" s="3" t="s">
+        <v>3313</v>
+      </c>
+    </row>
+    <row r="6617" spans="1:1">
+      <c r="A6617" s="3" t="s">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="6618" spans="1:1">
+      <c r="A6618" s="3" t="s">
+        <v>3389</v>
+      </c>
+    </row>
+    <row r="6619" spans="1:1">
+      <c r="A6619" s="3" t="s">
+        <v>2838</v>
+      </c>
+    </row>
+    <row r="6620" spans="1:1">
+      <c r="A6620" s="3" t="s">
+        <v>2834</v>
+      </c>
+    </row>
+    <row r="6621" spans="1:1">
+      <c r="A6621" s="3" t="s">
+        <v>2835</v>
+      </c>
+    </row>
+    <row r="6622" spans="1:1">
+      <c r="A6622" s="3" t="s">
+        <v>2836</v>
+      </c>
+    </row>
+    <row r="6623" spans="1:1">
+      <c r="A6623" s="3" t="s">
+        <v>2837</v>
+      </c>
+    </row>
+    <row r="6624" spans="1:1">
+      <c r="A6624" s="3" t="s">
+        <v>3111</v>
+      </c>
+    </row>
+    <row r="6625" spans="1:1">
+      <c r="A6625" s="3" t="s">
+        <v>3238</v>
+      </c>
+    </row>
+    <row r="6626" spans="1:1">
+      <c r="A6626" s="3" t="s">
+        <v>2819</v>
+      </c>
+    </row>
+    <row r="6627" spans="1:1">
+      <c r="A6627" s="3" t="s">
+        <v>2820</v>
+      </c>
+    </row>
+    <row r="6628" spans="1:1">
+      <c r="A6628" s="3" t="s">
+        <v>3686</v>
+      </c>
+    </row>
+    <row r="6629" spans="1:1">
+      <c r="A6629" s="3" t="s">
+        <v>3410</v>
+      </c>
+    </row>
+    <row r="6630" spans="1:1">
+      <c r="A6630" s="3" t="s">
+        <v>3196</v>
+      </c>
+    </row>
+    <row r="6631" spans="1:1">
+      <c r="A6631" s="3" t="s">
+        <v>2822</v>
+      </c>
+    </row>
+    <row r="6632" spans="1:1">
+      <c r="A6632" s="3" t="s">
+        <v>2823</v>
+      </c>
+    </row>
+    <row r="6633" spans="1:1">
+      <c r="A6633" s="3" t="s">
+        <v>2824</v>
+      </c>
+    </row>
+    <row r="6634" spans="1:1">
+      <c r="A6634" s="3" t="s">
+        <v>2825</v>
+      </c>
+    </row>
+    <row r="6635" spans="1:1">
+      <c r="A6635" s="3" t="s">
+        <v>2826</v>
+      </c>
+    </row>
+    <row r="6636" spans="1:1">
+      <c r="A6636" s="3" t="s">
+        <v>3556</v>
+      </c>
+    </row>
+    <row r="6637" spans="1:1">
+      <c r="A6637" s="3" t="s">
+        <v>2827</v>
+      </c>
+    </row>
+    <row r="6638" spans="1:1">
+      <c r="A6638" s="3" t="s">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="6639" spans="1:1">
+      <c r="A6639" s="3" t="s">
+        <v>2829</v>
+      </c>
+    </row>
+    <row r="6640" spans="1:1">
+      <c r="A6640" s="3" t="s">
+        <v>2830</v>
+      </c>
+    </row>
+    <row r="6641" spans="1:1">
+      <c r="A6641" s="3" t="s">
+        <v>2831</v>
+      </c>
+    </row>
+    <row r="6642" spans="1:1">
+      <c r="A6642" s="3" t="s">
+        <v>2832</v>
+      </c>
+    </row>
+    <row r="6643" spans="1:1">
+      <c r="A6643" s="3" t="s">
+        <v>2833</v>
+      </c>
+    </row>
+    <row r="6644" spans="1:1">
+      <c r="A6644" s="3" t="s">
+        <v>2817</v>
+      </c>
+    </row>
+    <row r="6645" spans="1:1">
+      <c r="A6645" s="3" t="s">
+        <v>2818</v>
+      </c>
+    </row>
+    <row r="6646" spans="1:1">
+      <c r="A6646" s="3" t="s">
+        <v>2814</v>
+      </c>
+    </row>
+    <row r="6647" spans="1:1">
+      <c r="A6647" s="3" t="s">
+        <v>2815</v>
+      </c>
+    </row>
+    <row r="6648" spans="1:1">
+      <c r="A6648" s="3" t="s">
+        <v>2816</v>
+      </c>
+    </row>
+    <row r="6649" spans="1:1">
+      <c r="A6649" s="3" t="s">
+        <v>2811</v>
+      </c>
+    </row>
+    <row r="6650" spans="1:1">
+      <c r="A6650" s="3" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="6651" spans="1:1">
+      <c r="A6651" s="3" t="s">
+        <v>2806</v>
+      </c>
+    </row>
+    <row r="6652" spans="1:1">
+      <c r="A6652" s="3" t="s">
+        <v>2807</v>
+      </c>
+    </row>
+    <row r="6653" spans="1:1">
+      <c r="A6653" s="3" t="s">
+        <v>2808</v>
+      </c>
+    </row>
+    <row r="6654" spans="1:1">
+      <c r="A6654" s="3" t="s">
+        <v>2809</v>
+      </c>
+    </row>
+    <row r="6655" spans="1:1">
+      <c r="A6655" s="3" t="s">
+        <v>2810</v>
+      </c>
+    </row>
+    <row r="6656" spans="1:1">
+      <c r="A6656" s="3" t="s">
+        <v>2812</v>
+      </c>
+    </row>
+    <row r="6657" spans="1:1">
+      <c r="A6657" s="3" t="s">
+        <v>2813</v>
+      </c>
+    </row>
+    <row r="6658" spans="1:1">
+      <c r="A6658" s="3" t="s">
+        <v>2796</v>
+      </c>
+    </row>
+    <row r="6659" spans="1:1">
+      <c r="A6659" s="3" t="s">
+        <v>2798</v>
+      </c>
+    </row>
+    <row r="6660" spans="1:1">
+      <c r="A6660" s="3" t="s">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="6661" spans="1:1">
+      <c r="A6661" s="3" t="s">
+        <v>2793</v>
+      </c>
+    </row>
+    <row r="6662" spans="1:1">
+      <c r="A6662" s="3" t="s">
+        <v>2761</v>
+      </c>
+    </row>
+    <row r="6663" spans="1:1">
+      <c r="A6663" s="3" t="s">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="6664" spans="1:1">
+      <c r="A6664" s="3" t="s">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="6665" spans="1:1">
+      <c r="A6665" s="3" t="s">
+        <v>2794</v>
+      </c>
+    </row>
+    <row r="6666" spans="1:1">
+      <c r="A6666" s="3" t="s">
+        <v>2795</v>
+      </c>
+    </row>
+    <row r="6667" spans="1:1">
+      <c r="A6667" s="3" t="s">
+        <v>4033</v>
+      </c>
+    </row>
+    <row r="6668" spans="1:1">
+      <c r="A6668" s="3" t="s">
+        <v>2797</v>
+      </c>
+    </row>
+    <row r="6669" spans="1:1">
+      <c r="A6669" s="3" t="s">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="6670" spans="1:1">
+      <c r="A6670" s="3" t="s">
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="6671" spans="1:1">
+      <c r="A6671" s="3" t="s">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="6672" spans="1:1">
+      <c r="A6672" s="3" t="s">
+        <v>2801</v>
+      </c>
+    </row>
+    <row r="6673" spans="1:1">
+      <c r="A6673" s="3" t="s">
+        <v>2802</v>
+      </c>
+    </row>
+    <row r="6674" spans="1:1">
+      <c r="A6674" s="3" t="s">
+        <v>3134</v>
+      </c>
+    </row>
+    <row r="6675" spans="1:1">
+      <c r="A6675" s="3" t="s">
+        <v>2804</v>
+      </c>
+    </row>
+    <row r="6676" spans="1:1">
+      <c r="A6676" s="3" t="s">
+        <v>2805</v>
+      </c>
+    </row>
+    <row r="6677" spans="1:1">
+      <c r="A6677" s="3" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="6678" spans="1:1">
+      <c r="A6678" s="3" t="s">
+        <v>4033</v>
+      </c>
+    </row>
+    <row r="6679" spans="1:1">
+      <c r="A6679" s="3" t="s">
+        <v>2788</v>
+      </c>
+    </row>
+    <row r="6680" spans="1:1">
+      <c r="A6680" s="3" t="s">
+        <v>2789</v>
+      </c>
+    </row>
+    <row r="6681" spans="1:1">
+      <c r="A6681" s="3" t="s">
+        <v>2790</v>
+      </c>
+    </row>
+    <row r="6682" spans="1:1">
+      <c r="A6682" s="3" t="s">
+        <v>2791</v>
+      </c>
+    </row>
+    <row r="6683" spans="1:1">
+      <c r="A6683" s="3" t="s">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="6684" spans="1:1">
+      <c r="A6684" s="3" t="s">
+        <v>2782</v>
+      </c>
+    </row>
+    <row r="6685" spans="1:1">
+      <c r="A6685" s="3" t="s">
+        <v>2783</v>
+      </c>
+    </row>
+    <row r="6686" spans="1:1">
+      <c r="A6686" s="3" t="s">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="6687" spans="1:1">
+      <c r="A6687" s="3" t="s">
+        <v>2785</v>
+      </c>
+    </row>
+    <row r="6688" spans="1:1">
+      <c r="A6688" s="3" t="s">
+        <v>2786</v>
+      </c>
+    </row>
+    <row r="6689" spans="1:1">
+      <c r="A6689" s="3" t="s">
+        <v>2787</v>
+      </c>
+    </row>
+    <row r="6690" spans="1:1">
+      <c r="A6690" s="3" t="s">
+        <v>2777</v>
+      </c>
+    </row>
+    <row r="6691" spans="1:1">
+      <c r="A6691" s="3" t="s">
+        <v>2778</v>
+      </c>
+    </row>
+    <row r="6692" spans="1:1">
+      <c r="A6692" s="3" t="s">
+        <v>2779</v>
+      </c>
+    </row>
+    <row r="6693" spans="1:1">
+      <c r="A6693" s="3" t="s">
+        <v>2778</v>
+      </c>
+    </row>
+    <row r="6694" spans="1:1">
+      <c r="A6694" s="3" t="s">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="6695" spans="1:1">
+      <c r="A6695" s="3" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="6696" spans="1:1">
+      <c r="A6696" s="3" t="s">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="6697" spans="1:1">
+      <c r="A6697" s="3" t="s">
+        <v>2776</v>
+      </c>
+    </row>
+    <row r="6698" spans="1:1">
+      <c r="A6698" s="3" t="s">
+        <v>2771</v>
+      </c>
+    </row>
+    <row r="6699" spans="1:1">
+      <c r="A6699" s="3" t="s">
+        <v>2772</v>
+      </c>
+    </row>
+    <row r="6700" spans="1:1">
+      <c r="A6700" s="3" t="s">
+        <v>2773</v>
+      </c>
+    </row>
+    <row r="6701" spans="1:1">
+      <c r="A6701" s="3" t="s">
+        <v>2774</v>
+      </c>
+    </row>
+    <row r="6702" spans="1:1">
+      <c r="A6702" s="3" t="s">
+        <v>2768</v>
+      </c>
+    </row>
+    <row r="6703" spans="1:1">
+      <c r="A6703" s="3" t="s">
+        <v>2769</v>
+      </c>
+    </row>
+    <row r="6704" spans="1:1">
+      <c r="A6704" s="3" t="s">
+        <v>3324</v>
+      </c>
+    </row>
+    <row r="6705" spans="1:1">
+      <c r="A6705" s="3" t="s">
+        <v>2763</v>
+      </c>
+    </row>
+    <row r="6706" spans="1:1">
+      <c r="A6706" s="3" t="s">
+        <v>2764</v>
+      </c>
+    </row>
+    <row r="6707" spans="1:1">
+      <c r="A6707" s="3" t="s">
+        <v>2765</v>
+      </c>
+    </row>
+    <row r="6708" spans="1:1">
+      <c r="A6708" s="3" t="s">
+        <v>2766</v>
+      </c>
+    </row>
+    <row r="6709" spans="1:1">
+      <c r="A6709" s="3" t="s">
+        <v>2767</v>
+      </c>
+    </row>
+    <row r="6710" spans="1:1">
+      <c r="A6710" s="3" t="s">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="6711" spans="1:1">
+      <c r="A6711" s="3" t="s">
+        <v>2761</v>
+      </c>
+    </row>
+    <row r="6712" spans="1:1">
+      <c r="A6712" s="3" t="s">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="6713" spans="1:1">
+      <c r="A6713" s="3" t="s">
+        <v>2759</v>
+      </c>
+    </row>
+    <row r="6714" spans="1:1">
+      <c r="A6714" s="3" t="s">
+        <v>2749</v>
+      </c>
+    </row>
+    <row r="6715" spans="1:1">
+      <c r="A6715" s="3" t="s">
+        <v>2754</v>
+      </c>
+    </row>
+    <row r="6716" spans="1:1">
+      <c r="A6716" s="3" t="s">
+        <v>2755</v>
+      </c>
+    </row>
+    <row r="6717" spans="1:1">
+      <c r="A6717" s="3" t="s">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="6718" spans="1:1">
+      <c r="A6718" s="3" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="6719" spans="1:1">
+      <c r="A6719" s="3" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="6720" spans="1:1">
+      <c r="A6720" s="3" t="s">
+        <v>2758</v>
+      </c>
+    </row>
+    <row r="6721" spans="1:1">
+      <c r="A6721" s="3" t="s">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="6722" spans="1:1">
+      <c r="A6722" s="3" t="s">
+        <v>2751</v>
+      </c>
+    </row>
+    <row r="6723" spans="1:1">
+      <c r="A6723" s="3" t="s">
+        <v>2752</v>
+      </c>
+    </row>
+    <row r="6724" spans="1:1">
+      <c r="A6724" s="3" t="s">
+        <v>2753</v>
+      </c>
+    </row>
+    <row r="6725" spans="1:1">
+      <c r="A6725" s="3" t="s">
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="6726" spans="1:1">
+      <c r="A6726" s="3" t="s">
+        <v>2748</v>
+      </c>
+    </row>
+    <row r="6727" spans="1:1">
+      <c r="A6727" s="3" t="s">
+        <v>2749</v>
+      </c>
+    </row>
+    <row r="6728" spans="1:1">
+      <c r="A6728" s="3" t="s">
+        <v>2744</v>
+      </c>
+    </row>
+    <row r="6729" spans="1:1">
+      <c r="A6729" s="3" t="s">
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="6730" spans="1:1">
+      <c r="A6730" s="3" t="s">
+        <v>2746</v>
+      </c>
+    </row>
+    <row r="6731" spans="1:1">
+      <c r="A6731" s="3" t="s">
+        <v>2747</v>
+      </c>
+    </row>
+    <row r="6732" spans="1:1">
+      <c r="A6732" s="3" t="s">
+        <v>2743</v>
+      </c>
+    </row>
+    <row r="6733" spans="1:1">
+      <c r="A6733" s="3" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="6734" spans="1:1">
+      <c r="A6734" s="3" t="s">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="6735" spans="1:1">
+      <c r="A6735" s="3" t="s">
+        <v>2742</v>
+      </c>
+    </row>
+    <row r="6736" spans="1:1">
+      <c r="A6736" s="3" t="s">
+        <v>2738</v>
+      </c>
+    </row>
+    <row r="6737" spans="1:1">
+      <c r="A6737" s="3" t="s">
+        <v>2739</v>
+      </c>
+    </row>
+    <row r="6738" spans="1:1">
+      <c r="A6738" s="3" t="s">
+        <v>2740</v>
+      </c>
+    </row>
+    <row r="6739" spans="1:1">
+      <c r="A6739" s="3" t="s">
+        <v>2736</v>
+      </c>
+    </row>
+    <row r="6740" spans="1:1">
+      <c r="A6740" s="3" t="s">
+        <v>2737</v>
+      </c>
+    </row>
+    <row r="6741" spans="1:1">
+      <c r="A6741" s="3" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="6742" spans="1:1">
+      <c r="A6742" s="3" t="s">
+        <v>2730</v>
+      </c>
+    </row>
+    <row r="6743" spans="1:1">
+      <c r="A6743" s="3" t="s">
+        <v>2731</v>
+      </c>
+    </row>
+    <row r="6744" spans="1:1">
+      <c r="A6744" s="3" t="s">
+        <v>2732</v>
+      </c>
+    </row>
+    <row r="6745" spans="1:1">
+      <c r="A6745" s="3" t="s">
+        <v>2729</v>
+      </c>
+    </row>
+    <row r="6746" spans="1:1">
+      <c r="A6746" s="3" t="s">
+        <v>2733</v>
+      </c>
+    </row>
+    <row r="6747" spans="1:1">
+      <c r="A6747" s="3" t="s">
+        <v>2734</v>
+      </c>
+    </row>
+    <row r="6748" spans="1:1">
+      <c r="A6748" s="3" t="s">
+        <v>2735</v>
+      </c>
+    </row>
+    <row r="6749" spans="1:1">
+      <c r="A6749" s="3" t="s">
+        <v>2728</v>
+      </c>
+    </row>
+    <row r="6750" spans="1:1">
+      <c r="A6750" s="3" t="s">
+        <v>2720</v>
+      </c>
+    </row>
+    <row r="6751" spans="1:1">
+      <c r="A6751" s="3" t="s">
+        <v>2721</v>
+      </c>
+    </row>
+    <row r="6752" spans="1:1">
+      <c r="A6752" s="3" t="s">
+        <v>2722</v>
+      </c>
+    </row>
+    <row r="6753" spans="1:1">
+      <c r="A6753" s="3" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="6754" spans="1:1">
+      <c r="A6754" s="3" t="s">
+        <v>2724</v>
+      </c>
+    </row>
+    <row r="6755" spans="1:1">
+      <c r="A6755" s="3" t="s">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="6756" spans="1:1">
+      <c r="A6756" s="3" t="s">
+        <v>2726</v>
+      </c>
+    </row>
+    <row r="6757" spans="1:1">
+      <c r="A6757" s="3" t="s">
+        <v>3233</v>
+      </c>
+    </row>
+    <row r="6758" spans="1:1">
+      <c r="A6758" s="3" t="s">
+        <v>2727</v>
+      </c>
+    </row>
+    <row r="6759" spans="1:1">
+      <c r="A6759" s="3" t="s">
+        <v>2718</v>
+      </c>
+    </row>
+    <row r="6760" spans="1:1">
+      <c r="A6760" s="3" t="s">
+        <v>2719</v>
+      </c>
+    </row>
+    <row r="6761" spans="1:1">
+      <c r="A6761" s="3" t="s">
+        <v>3464</v>
+      </c>
+    </row>
+    <row r="6762" spans="1:1">
+      <c r="A6762" s="3" t="s">
+        <v>3474</v>
+      </c>
+    </row>
+    <row r="6763" spans="1:1">
+      <c r="A6763" s="3" t="s">
+        <v>2713</v>
+      </c>
+    </row>
+    <row r="6764" spans="1:1">
+      <c r="A6764" s="3" t="s">
+        <v>3460</v>
+      </c>
+    </row>
+    <row r="6765" spans="1:1">
+      <c r="A6765" s="3" t="s">
+        <v>2714</v>
+      </c>
+    </row>
+    <row r="6766" spans="1:1">
+      <c r="A6766" s="3" t="s">
+        <v>2715</v>
+      </c>
+    </row>
+    <row r="6767" spans="1:1">
+      <c r="A6767" s="3" t="s">
+        <v>2716</v>
+      </c>
+    </row>
+    <row r="6768" spans="1:1">
+      <c r="A6768" s="3" t="s">
+        <v>2717</v>
+      </c>
+    </row>
+    <row r="6769" spans="1:1">
+      <c r="A6769" s="3" t="s">
+        <v>2712</v>
+      </c>
+    </row>
+    <row r="6770" spans="1:1">
+      <c r="A6770" s="3" t="s">
+        <v>2710</v>
+      </c>
+    </row>
+    <row r="6771" spans="1:1">
+      <c r="A6771" s="3" t="s">
+        <v>2711</v>
+      </c>
+    </row>
+    <row r="6772" spans="1:1">
+      <c r="A6772" s="3" t="s">
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="6773" spans="1:1">
+      <c r="A6773" s="3" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="6774" spans="1:1">
+      <c r="A6774" s="3" t="s">
+        <v>2707</v>
+      </c>
+    </row>
+    <row r="6775" spans="1:1">
+      <c r="A6775" s="3" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="6776" spans="1:1">
+      <c r="A6776" s="3" t="s">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="6777" spans="1:1">
+      <c r="A6777" s="3" t="s">
+        <v>2705</v>
+      </c>
+    </row>
+    <row r="6778" spans="1:1">
+      <c r="A6778" s="3" t="s">
+        <v>2704</v>
+      </c>
+    </row>
+    <row r="6779" spans="1:1">
+      <c r="A6779" s="3" t="s">
+        <v>2703</v>
+      </c>
+    </row>
+    <row r="6780" spans="1:1">
+      <c r="A6780" s="3" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="6781" spans="1:1">
+      <c r="A6781" s="3" t="s">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="6782" spans="1:1">
+      <c r="A6782" s="3" t="s">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="6783" spans="1:1">
+      <c r="A6783" s="3" t="s">
+        <v>2701</v>
+      </c>
+    </row>
+    <row r="6784" spans="1:1">
+      <c r="A6784" s="3" t="s">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="6785" spans="1:1">
+      <c r="A6785" s="3" t="s">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="6786" spans="1:1">
+      <c r="A6786" s="3" t="s">
+        <v>2698</v>
+      </c>
+    </row>
+    <row r="6787" spans="1:1">
+      <c r="A6787" s="3" t="s">
+        <v>2697</v>
+      </c>
+    </row>
+    <row r="6788" spans="1:1">
+      <c r="A6788" s="3" t="s">
+        <v>2696</v>
+      </c>
+    </row>
+    <row r="6789" spans="1:1">
+      <c r="A6789" s="3" t="s">
+        <v>2695</v>
+      </c>
+    </row>
+    <row r="6790" spans="1:1">
+      <c r="A6790" s="3" t="s">
+        <v>2698</v>
+      </c>
+    </row>
+    <row r="6791" spans="1:1">
+      <c r="A6791" s="3" t="s">
+        <v>2665</v>
+      </c>
+    </row>
+    <row r="6792" spans="1:1">
+      <c r="A6792" s="3" t="s">
+        <v>3519</v>
+      </c>
+    </row>
+    <row r="6793" spans="1:1">
+      <c r="A6793" s="3" t="s">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="6794" spans="1:1">
+      <c r="A6794" s="3" t="s">
+        <v>2687</v>
+      </c>
+    </row>
+    <row r="6795" spans="1:1">
+      <c r="A6795" s="3" t="s">
+        <v>2686</v>
+      </c>
+    </row>
+    <row r="6796" spans="1:1">
+      <c r="A6796" s="3" t="s">
+        <v>2685</v>
+      </c>
+    </row>
+    <row r="6797" spans="1:1">
+      <c r="A6797" s="3" t="s">
+        <v>2688</v>
+      </c>
+    </row>
+    <row r="6798" spans="1:1">
+      <c r="A6798" s="3" t="s">
+        <v>2684</v>
+      </c>
+    </row>
+    <row r="6799" spans="1:1">
+      <c r="A6799" s="3" t="s">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="6800" spans="1:1">
+      <c r="A6800" s="3" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="6801" spans="1:1">
+      <c r="A6801" s="3" t="s">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="6802" spans="1:1">
+      <c r="A6802" s="3" t="s">
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="6803" spans="1:1">
+      <c r="A6803" s="3" t="s">
+        <v>2680</v>
+      </c>
+    </row>
+    <row r="6804" spans="1:1">
+      <c r="A6804" s="3" t="s">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="6805" spans="1:1">
+      <c r="A6805" s="3" t="s">
+        <v>2679</v>
+      </c>
+    </row>
+    <row r="6806" spans="1:1">
+      <c r="A6806" s="3" t="s">
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="6807" spans="1:1">
+      <c r="A6807" s="3" t="s">
+        <v>2677</v>
+      </c>
+    </row>
+    <row r="6808" spans="1:1">
+      <c r="A6808" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="6809" spans="1:1">
+      <c r="A6809" s="3" t="s">
+        <v>2675</v>
+      </c>
+    </row>
+    <row r="6810" spans="1:1">
+      <c r="A6810" s="3" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="6811" spans="1:1">
+      <c r="A6811" s="3" t="s">
+        <v>2673</v>
+      </c>
+    </row>
+    <row r="6812" spans="1:1">
+      <c r="A6812" s="3" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="6813" spans="1:1">
+      <c r="A6813" s="3" t="s">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="6814" spans="1:1">
+      <c r="A6814" s="3" t="s">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="6815" spans="1:1">
+      <c r="A6815" s="3" t="s">
+        <v>2669</v>
+      </c>
+    </row>
+    <row r="6816" spans="1:1">
+      <c r="A6816" s="3" t="s">
+        <v>2668</v>
+      </c>
+    </row>
+    <row r="6817" spans="1:1">
+      <c r="A6817" s="3" t="s">
+        <v>2667</v>
+      </c>
+    </row>
+    <row r="6818" spans="1:1">
+      <c r="A6818" s="3" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="6819" spans="1:1">
+      <c r="A6819" s="3" t="s">
+        <v>2665</v>
+      </c>
+    </row>
+    <row r="6820" spans="1:1">
+      <c r="A6820" s="3" t="s">
+        <v>2664</v>
+      </c>
+    </row>
+    <row r="6821" spans="1:1">
+      <c r="A6821" s="3" t="s">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="6822" spans="1:1">
+      <c r="A6822" s="3" t="s">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="6823" spans="1:1">
+      <c r="A6823" s="3" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="6824" spans="1:1">
+      <c r="A6824" s="3" t="s">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="6825" spans="1:1">
+      <c r="A6825" s="3" t="s">
+        <v>3371</v>
+      </c>
+    </row>
+    <row r="6826" spans="1:1">
+      <c r="A6826" s="3" t="s">
+        <v>2659</v>
+      </c>
+    </row>
+    <row r="6827" spans="1:1">
+      <c r="A6827" s="3" t="s">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="6828" spans="1:1">
+      <c r="A6828" s="3" t="s">
+        <v>2658</v>
+      </c>
+    </row>
+    <row r="6829" spans="1:1">
+      <c r="A6829" s="3" t="s">
+        <v>2657</v>
+      </c>
+    </row>
+    <row r="6830" spans="1:1">
+      <c r="A6830" s="3" t="s">
+        <v>2656</v>
+      </c>
+    </row>
+    <row r="6831" spans="1:1">
+      <c r="A6831" s="3" t="s">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="6832" spans="1:1">
+      <c r="A6832" s="3" t="s">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="6833" spans="1:1">
+      <c r="A6833" s="3" t="s">
+        <v>3206</v>
+      </c>
+    </row>
+    <row r="6834" spans="1:1">
+      <c r="A6834" s="3" t="s">
+        <v>2654</v>
+      </c>
+    </row>
+    <row r="6835" spans="1:1">
+      <c r="A6835" s="3" t="s">
+        <v>2652</v>
+      </c>
+    </row>
+    <row r="6836" spans="1:1">
+      <c r="A6836" s="3" t="s">
+        <v>2651</v>
+      </c>
+    </row>
+    <row r="6837" spans="1:1">
+      <c r="A6837" s="3" t="s">
+        <v>2647</v>
+      </c>
+    </row>
+    <row r="6838" spans="1:1">
+      <c r="A6838" s="3" t="s">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="6839" spans="1:1">
+      <c r="A6839" s="3" t="s">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="6840" spans="1:1">
+      <c r="A6840" s="3" t="s">
+        <v>2653</v>
+      </c>
+    </row>
+    <row r="6841" spans="1:1">
+      <c r="A6841" s="3" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="6842" spans="1:1">
+      <c r="A6842" s="3" t="s">
+        <v>3310</v>
+      </c>
+    </row>
+    <row r="6843" spans="1:1">
+      <c r="A6843" s="3" t="s">
+        <v>2646</v>
+      </c>
+    </row>
+    <row r="6844" spans="1:1">
+      <c r="A6844" s="3" t="s">
+        <v>4034</v>
+      </c>
+    </row>
+    <row r="6845" spans="1:1">
+      <c r="A6845" s="3" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="6846" spans="1:1">
+      <c r="A6846" s="3" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="6847" spans="1:1">
+      <c r="A6847" s="3" t="s">
+        <v>2643</v>
+      </c>
+    </row>
+    <row r="6848" spans="1:1">
+      <c r="A6848" s="3" t="s">
+        <v>2642</v>
+      </c>
+    </row>
+    <row r="6849" spans="1:1">
+      <c r="A6849" s="3" t="s">
+        <v>2641</v>
+      </c>
+    </row>
+    <row r="6850" spans="1:1">
+      <c r="A6850" s="3" t="s">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="6851" spans="1:1">
+      <c r="A6851" s="3" t="s">
+        <v>2639</v>
+      </c>
+    </row>
+    <row r="6852" spans="1:1">
+      <c r="A6852" s="3" t="s">
+        <v>2638</v>
+      </c>
+    </row>
+    <row r="6853" spans="1:1">
+      <c r="A6853" s="3" t="s">
+        <v>2636</v>
+      </c>
+    </row>
+    <row r="6854" spans="1:1">
+      <c r="A6854" s="3" t="s">
+        <v>2637</v>
+      </c>
+    </row>
+    <row r="6855" spans="1:1">
+      <c r="A6855" s="3" t="s">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="6856" spans="1:1">
+      <c r="A6856" s="3" t="s">
+        <v>3096</v>
+      </c>
+    </row>
+    <row r="6857" spans="1:1">
+      <c r="A6857" s="3" t="s">
+        <v>3097</v>
+      </c>
+    </row>
+    <row r="6858" spans="1:1">
+      <c r="A6858" s="3" t="s">
+        <v>3098</v>
+      </c>
+    </row>
+    <row r="6859" spans="1:1">
+      <c r="A6859" s="3" t="s">
+        <v>3099</v>
+      </c>
+    </row>
+    <row r="6860" spans="1:1">
+      <c r="A6860" s="3" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="6861" spans="1:1">
+      <c r="A6861" s="3" t="s">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="6862" spans="1:1">
+      <c r="A6862" s="3" t="s">
+        <v>3101</v>
+      </c>
+    </row>
+    <row r="6863" spans="1:1">
+      <c r="A6863" s="3" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="6864" spans="1:1">
+      <c r="A6864" s="3" t="s">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="6865" spans="1:1">
+      <c r="A6865" s="3" t="s">
+        <v>3103</v>
+      </c>
+    </row>
+    <row r="6866" spans="1:1">
+      <c r="A6866" s="3" t="s">
+        <v>3104</v>
+      </c>
+    </row>
+    <row r="6867" spans="1:1">
+      <c r="A6867" s="3" t="s">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="6868" spans="1:1">
+      <c r="A6868" s="3" t="s">
+        <v>3106</v>
+      </c>
+    </row>
+    <row r="6869" spans="1:1">
+      <c r="A6869" s="3" t="s">
+        <v>3107</v>
+      </c>
+    </row>
+    <row r="6870" spans="1:1">
+      <c r="A6870" s="3" t="s">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="6871" spans="1:1">
+      <c r="A6871" s="3" t="s">
+        <v>3109</v>
+      </c>
+    </row>
+    <row r="6872" spans="1:1">
+      <c r="A6872" s="3" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="6873" spans="1:1">
+      <c r="A6873" s="3" t="s">
+        <v>3111</v>
+      </c>
+    </row>
+    <row r="6874" spans="1:1">
+      <c r="A6874" s="3" t="s">
+        <v>3112</v>
+      </c>
+    </row>
+    <row r="6875" spans="1:1">
+      <c r="A6875" s="3" t="s">
+        <v>3113</v>
+      </c>
+    </row>
+    <row r="6876" spans="1:1">
+      <c r="A6876" s="3" t="s">
+        <v>3114</v>
+      </c>
+    </row>
+    <row r="6877" spans="1:1">
+      <c r="A6877" s="3" t="s">
+        <v>3115</v>
+      </c>
+    </row>
+    <row r="6878" spans="1:1">
+      <c r="A6878" s="3" t="s">
+        <v>3116</v>
+      </c>
+    </row>
+    <row r="6879" spans="1:1">
+      <c r="A6879" s="3" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="6880" spans="1:1">
+      <c r="A6880" s="3" t="s">
+        <v>3118</v>
+      </c>
+    </row>
+    <row r="6881" spans="1:1">
+      <c r="A6881" s="3" t="s">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="6882" spans="1:1">
+      <c r="A6882" s="3" t="s">
+        <v>3119</v>
+      </c>
+    </row>
+    <row r="6883" spans="1:1">
+      <c r="A6883" s="3" t="s">
+        <v>3359</v>
+      </c>
+    </row>
+    <row r="6884" spans="1:1">
+      <c r="A6884" s="3" t="s">
+        <v>3126</v>
+      </c>
+    </row>
+    <row r="6885" spans="1:1">
+      <c r="A6885" s="3" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="6886" spans="1:1">
+      <c r="A6886" s="3" t="s">
+        <v>3122</v>
+      </c>
+    </row>
+    <row r="6887" spans="1:1">
+      <c r="A6887" s="3" t="s">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="6888" spans="1:1">
+      <c r="A6888" s="3" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="6889" spans="1:1">
+      <c r="A6889" s="3" t="s">
+        <v>3124</v>
+      </c>
+    </row>
+    <row r="6890" spans="1:1">
+      <c r="A6890" s="3" t="s">
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="6891" spans="1:1">
+      <c r="A6891" s="3" t="s">
+        <v>3126</v>
+      </c>
+    </row>
+    <row r="6892" spans="1:1">
+      <c r="A6892" s="3" t="s">
+        <v>3127</v>
+      </c>
+    </row>
+    <row r="6893" spans="1:1">
+      <c r="A6893" s="3" t="s">
+        <v>3128</v>
+      </c>
+    </row>
+    <row r="6894" spans="1:1">
+      <c r="A6894" s="3" t="s">
+        <v>3129</v>
+      </c>
+    </row>
+    <row r="6895" spans="1:1">
+      <c r="A6895" s="3" t="s">
+        <v>3307</v>
+      </c>
+    </row>
+    <row r="6896" spans="1:1">
+      <c r="A6896" s="3" t="s">
+        <v>3130</v>
+      </c>
+    </row>
+    <row r="6897" spans="1:1">
+      <c r="A6897" s="3" t="s">
+        <v>3131</v>
+      </c>
+    </row>
+    <row r="6898" spans="1:1">
+      <c r="A6898" s="3" t="s">
+        <v>3648</v>
+      </c>
+    </row>
+    <row r="6899" spans="1:1">
+      <c r="A6899" s="3" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="6900" spans="1:1">
+      <c r="A6900" s="3" t="s">
+        <v>3133</v>
+      </c>
+    </row>
+    <row r="6901" spans="1:1">
+      <c r="A6901" s="3" t="s">
+        <v>3134</v>
+      </c>
+    </row>
+    <row r="6902" spans="1:1">
+      <c r="A6902" s="3" t="s">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="6903" spans="1:1">
+      <c r="A6903" s="3" t="s">
+        <v>3132</v>
+      </c>
+    </row>
+    <row r="6904" spans="1:1">
+      <c r="A6904" s="3" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="6905" spans="1:1">
+      <c r="A6905" s="3" t="s">
+        <v>3158</v>
+      </c>
+    </row>
+    <row r="6906" spans="1:1">
+      <c r="A6906" s="3" t="s">
+        <v>3158</v>
+      </c>
+    </row>
+    <row r="6907" spans="1:1">
+      <c r="A6907" s="3" t="s">
+        <v>3135</v>
+      </c>
+    </row>
+    <row r="6908" spans="1:1">
+      <c r="A6908" s="3" t="s">
+        <v>3136</v>
+      </c>
+    </row>
+    <row r="6909" spans="1:1">
+      <c r="A6909" s="3" t="s">
+        <v>3137</v>
+      </c>
+    </row>
+    <row r="6910" spans="1:1">
+      <c r="A6910" s="3" t="s">
+        <v>3138</v>
+      </c>
+    </row>
+    <row r="6911" spans="1:1">
+      <c r="A6911" s="3" t="s">
+        <v>3139</v>
+      </c>
+    </row>
+    <row r="6912" spans="1:1">
+      <c r="A6912" s="3" t="s">
+        <v>3140</v>
+      </c>
+    </row>
+    <row r="6913" spans="1:1">
+      <c r="A6913" s="3" t="s">
+        <v>3141</v>
+      </c>
+    </row>
+    <row r="6914" spans="1:1">
+      <c r="A6914" s="3" t="s">
+        <v>3142</v>
+      </c>
+    </row>
+    <row r="6915" spans="1:1">
+      <c r="A6915" s="3" t="s">
+        <v>3143</v>
+      </c>
+    </row>
+    <row r="6916" spans="1:1">
+      <c r="A6916" s="3" t="s">
+        <v>3144</v>
+      </c>
+    </row>
+    <row r="6917" spans="1:1">
+      <c r="A6917" s="3" t="s">
+        <v>3145</v>
+      </c>
+    </row>
+    <row r="6918" spans="1:1">
+      <c r="A6918" s="3" t="s">
+        <v>3146</v>
+      </c>
+    </row>
+    <row r="6919" spans="1:1">
+      <c r="A6919" s="3" t="s">
+        <v>3151</v>
+      </c>
+    </row>
+    <row r="6920" spans="1:1">
+      <c r="A6920" s="3" t="s">
+        <v>3147</v>
+      </c>
+    </row>
+    <row r="6921" spans="1:1">
+      <c r="A6921" s="3" t="s">
+        <v>3148</v>
+      </c>
+    </row>
+    <row r="6922" spans="1:1">
+      <c r="A6922" s="3" t="s">
+        <v>3152</v>
+      </c>
+    </row>
+    <row r="6923" spans="1:1">
+      <c r="A6923" s="3" t="s">
+        <v>3149</v>
+      </c>
+    </row>
+    <row r="6924" spans="1:1">
+      <c r="A6924" s="3" t="s">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="6925" spans="1:1">
+      <c r="A6925" s="3" t="s">
+        <v>3153</v>
+      </c>
+    </row>
+    <row r="6926" spans="1:1">
+      <c r="A6926" s="3" t="s">
+        <v>2318</v>
+      </c>
+    </row>
+    <row r="6927" spans="1:1">
+      <c r="A6927" s="3" t="s">
+        <v>3154</v>
+      </c>
+    </row>
+    <row r="6928" spans="1:1">
+      <c r="A6928" s="3" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="6929" spans="1:1">
+      <c r="A6929" s="3" t="s">
+        <v>3156</v>
+      </c>
+    </row>
+    <row r="6930" spans="1:1">
+      <c r="A6930" s="3" t="s">
+        <v>3155</v>
+      </c>
+    </row>
+    <row r="6931" spans="1:1">
+      <c r="A6931" s="3" t="s">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="6932" spans="1:1">
+      <c r="A6932" s="3" t="s">
+        <v>3365</v>
+      </c>
+    </row>
+    <row r="6933" spans="1:1">
+      <c r="A6933" s="3" t="s">
+        <v>3157</v>
+      </c>
+    </row>
+    <row r="6934" spans="1:1">
+      <c r="A6934" s="3" t="s">
+        <v>3158</v>
+      </c>
+    </row>
+    <row r="6935" spans="1:1">
+      <c r="A6935" s="3" t="s">
+        <v>3499</v>
+      </c>
+    </row>
+    <row r="6936" spans="1:1">
+      <c r="A6936" s="3" t="s">
+        <v>3159</v>
+      </c>
+    </row>
+    <row r="6937" spans="1:1">
+      <c r="A6937" s="3" t="s">
+        <v>3160</v>
+      </c>
+    </row>
+    <row r="6938" spans="1:1">
+      <c r="A6938" s="3" t="s">
+        <v>3507</v>
+      </c>
+    </row>
+    <row r="6939" spans="1:1">
+      <c r="A6939" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="6940" spans="1:1">
+      <c r="A6940" s="3" t="s">
+        <v>3161</v>
+      </c>
+    </row>
+    <row r="6941" spans="1:1">
+      <c r="A6941" s="3" t="s">
+        <v>3162</v>
+      </c>
+    </row>
+    <row r="6942" spans="1:1">
+      <c r="A6942" s="3" t="s">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="6943" spans="1:1">
+      <c r="A6943" s="3" t="s">
+        <v>3605</v>
+      </c>
+    </row>
+    <row r="6944" spans="1:1">
+      <c r="A6944" s="3" t="s">
+        <v>3494</v>
+      </c>
+    </row>
+    <row r="6945" spans="1:1">
+      <c r="A6945" s="3" t="s">
+        <v>3163</v>
+      </c>
+    </row>
+    <row r="6946" spans="1:1">
+      <c r="A6946" s="3" t="s">
+        <v>3164</v>
+      </c>
+    </row>
+    <row r="6947" spans="1:1">
+      <c r="A6947" s="3" t="s">
+        <v>3165</v>
+      </c>
+    </row>
+    <row r="6948" spans="1:1">
+      <c r="A6948" s="3" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="6949" spans="1:1">
+      <c r="A6949" s="3" t="s">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="6950" spans="1:1">
+      <c r="A6950" s="3" t="s">
+        <v>3532</v>
+      </c>
+    </row>
+    <row r="6951" spans="1:1">
+      <c r="A6951" s="3" t="s">
+        <v>3166</v>
+      </c>
+    </row>
+    <row r="6952" spans="1:1">
+      <c r="A6952" s="3" t="s">
+        <v>3169</v>
+      </c>
+    </row>
+    <row r="6953" spans="1:1">
+      <c r="A6953" s="3" t="s">
+        <v>3167</v>
+      </c>
+    </row>
+    <row r="6954" spans="1:1">
+      <c r="A6954" s="3" t="s">
+        <v>3168</v>
+      </c>
+    </row>
+    <row r="6955" spans="1:1">
+      <c r="A6955" s="3" t="s">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="6956" spans="1:1">
+      <c r="A6956" s="3" t="s">
+        <v>3171</v>
+      </c>
+    </row>
+    <row r="6957" spans="1:1">
+      <c r="A6957" s="3" t="s">
+        <v>3194</v>
+      </c>
+    </row>
+    <row r="6958" spans="1:1">
+      <c r="A6958" s="3" t="s">
+        <v>3618</v>
+      </c>
+    </row>
+    <row r="6959" spans="1:1">
+      <c r="A6959" s="3" t="s">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="6960" spans="1:1">
+      <c r="A6960" s="3" t="s">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="6961" spans="1:1">
+      <c r="A6961" s="3" t="s">
+        <v>3176</v>
+      </c>
+    </row>
+    <row r="6962" spans="1:1">
+      <c r="A6962" s="3" t="s">
+        <v>3177</v>
+      </c>
+    </row>
+    <row r="6963" spans="1:1">
+      <c r="A6963" s="3" t="s">
+        <v>3170</v>
+      </c>
+    </row>
+    <row r="6964" spans="1:1">
+      <c r="A6964" s="3" t="s">
+        <v>3175</v>
+      </c>
+    </row>
+    <row r="6965" spans="1:1">
+      <c r="A6965" s="3" t="s">
+        <v>3174</v>
+      </c>
+    </row>
+    <row r="6966" spans="1:1">
+      <c r="A6966" s="3" t="s">
+        <v>3173</v>
+      </c>
+    </row>
+    <row r="6967" spans="1:1">
+      <c r="A6967" s="3" t="s">
+        <v>3185</v>
+      </c>
+    </row>
+    <row r="6968" spans="1:1">
+      <c r="A6968" s="3" t="s">
+        <v>3178</v>
+      </c>
+    </row>
+    <row r="6969" spans="1:1">
+      <c r="A6969" s="3" t="s">
+        <v>3172</v>
+      </c>
+    </row>
+    <row r="6970" spans="1:1">
+      <c r="A6970" s="3" t="s">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="6971" spans="1:1">
+      <c r="A6971" s="3" t="s">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="6972" spans="1:1">
+      <c r="A6972" s="3" t="s">
+        <v>3179</v>
+      </c>
+    </row>
+    <row r="6973" spans="1:1">
+      <c r="A6973" s="3" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="6974" spans="1:1">
+      <c r="A6974" s="3" t="s">
+        <v>3187</v>
+      </c>
+    </row>
+    <row r="6975" spans="1:1">
+      <c r="A6975" s="3" t="s">
+        <v>3183</v>
+      </c>
+    </row>
+    <row r="6976" spans="1:1">
+      <c r="A6976" s="3" t="s">
+        <v>3181</v>
+      </c>
+    </row>
+    <row r="6977" spans="1:1">
+      <c r="A6977" s="3" t="s">
+        <v>3180</v>
+      </c>
+    </row>
+    <row r="6978" spans="1:1">
+      <c r="A6978" s="3" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="6979" spans="1:1">
+      <c r="A6979" s="3" t="s">
+        <v>3186</v>
+      </c>
+    </row>
+    <row r="6980" spans="1:1">
+      <c r="A6980" s="3" t="s">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="6981" spans="1:1">
+      <c r="A6981" s="3" t="s">
+        <v>3182</v>
+      </c>
+    </row>
+    <row r="6982" spans="1:1">
+      <c r="A6982" s="3" t="s">
+        <v>3185</v>
+      </c>
+    </row>
+    <row r="6983" spans="1:1">
+      <c r="A6983" s="3" t="s">
+        <v>3197</v>
+      </c>
+    </row>
+    <row r="6984" spans="1:1">
+      <c r="A6984" s="3" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="6985" spans="1:1">
+      <c r="A6985" s="3" t="s">
+        <v>3195</v>
+      </c>
+    </row>
+    <row r="6986" spans="1:1">
+      <c r="A6986" s="3" t="s">
+        <v>3193</v>
+      </c>
+    </row>
+    <row r="6987" spans="1:1">
+      <c r="A6987" s="3" t="s">
+        <v>3298</v>
+      </c>
+    </row>
+    <row r="6988" spans="1:1">
+      <c r="A6988" s="3" t="s">
+        <v>3335</v>
+      </c>
+    </row>
+    <row r="6989" spans="1:1">
+      <c r="A6989" s="3" t="s">
+        <v>3219</v>
+      </c>
+    </row>
+    <row r="6990" spans="1:1">
+      <c r="A6990" s="3" t="s">
+        <v>3194</v>
+      </c>
+    </row>
+    <row r="6991" spans="1:1">
+      <c r="A6991" s="3" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="6992" spans="1:1">
+      <c r="A6992" s="3" t="s">
+        <v>3196</v>
+      </c>
+    </row>
+    <row r="6993" spans="1:1">
+      <c r="A6993" s="3" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="6994" spans="1:1">
+      <c r="A6994" s="3" t="s">
+        <v>3198</v>
+      </c>
+    </row>
+    <row r="6995" spans="1:1">
+      <c r="A6995" s="3" t="s">
+        <v>3199</v>
+      </c>
+    </row>
+    <row r="6996" spans="1:1">
+      <c r="A6996" s="3" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="6997" spans="1:1">
+      <c r="A6997" s="3" t="s">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="6998" spans="1:1">
+      <c r="A6998" s="3" t="s">
+        <v>3201</v>
+      </c>
+    </row>
+    <row r="6999" spans="1:1">
+      <c r="A6999" s="3" t="s">
+        <v>3202</v>
+      </c>
+    </row>
+    <row r="7000" spans="1:1">
+      <c r="A7000" s="3" t="s">
+        <v>3205</v>
+      </c>
+    </row>
+    <row r="7001" spans="1:1">
+      <c r="A7001" s="3" t="s">
+        <v>3203</v>
+      </c>
+    </row>
+    <row r="7002" spans="1:1">
+      <c r="A7002" s="3" t="s">
+        <v>3204</v>
+      </c>
+    </row>
+    <row r="7003" spans="1:1">
+      <c r="A7003" s="3" t="s">
+        <v>3221</v>
+      </c>
+    </row>
+    <row r="7004" spans="1:1">
+      <c r="A7004" s="3" t="s">
+        <v>3208</v>
+      </c>
+    </row>
+    <row r="7005" spans="1:1">
+      <c r="A7005" s="3" t="s">
+        <v>3209</v>
+      </c>
+    </row>
+    <row r="7006" spans="1:1">
+      <c r="A7006" s="3" t="s">
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="7007" spans="1:1">
+      <c r="A7007" s="3" t="s">
+        <v>3061</v>
+      </c>
+    </row>
+    <row r="7008" spans="1:1">
+      <c r="A7008" s="3" t="s">
+        <v>3211</v>
+      </c>
+    </row>
+    <row r="7009" spans="1:1">
+      <c r="A7009" s="3" t="s">
+        <v>3212</v>
+      </c>
+    </row>
+    <row r="7010" spans="1:1">
+      <c r="A7010" s="3" t="s">
+        <v>3206</v>
+      </c>
+    </row>
+    <row r="7011" spans="1:1">
+      <c r="A7011" s="3" t="s">
+        <v>3219</v>
+      </c>
+    </row>
+    <row r="7012" spans="1:1">
+      <c r="A7012" s="3" t="s">
+        <v>3217</v>
+      </c>
+    </row>
+    <row r="7013" spans="1:1">
+      <c r="A7013" s="3" t="s">
+        <v>3218</v>
+      </c>
+    </row>
+    <row r="7014" spans="1:1">
+      <c r="A7014" s="3" t="s">
+        <v>3213</v>
+      </c>
+    </row>
+    <row r="7015" spans="1:1">
+      <c r="A7015" s="3" t="s">
+        <v>3216</v>
+      </c>
+    </row>
+    <row r="7016" spans="1:1">
+      <c r="A7016" s="3" t="s">
+        <v>3214</v>
+      </c>
+    </row>
+    <row r="7017" spans="1:1">
+      <c r="A7017" s="3" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="7018" spans="1:1">
+      <c r="A7018" s="3" t="s">
+        <v>3463</v>
+      </c>
+    </row>
+    <row r="7019" spans="1:1">
+      <c r="A7019" s="3" t="s">
+        <v>3207</v>
+      </c>
+    </row>
+    <row r="7020" spans="1:1">
+      <c r="A7020" s="3" t="s">
+        <v>3215</v>
+      </c>
+    </row>
+    <row r="7021" spans="1:1">
+      <c r="A7021" s="3" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="7022" spans="1:1">
+      <c r="A7022" s="3" t="s">
+        <v>3220</v>
+      </c>
+    </row>
+    <row r="7023" spans="1:1">
+      <c r="A7023" s="3" t="s">
+        <v>3222</v>
+      </c>
+    </row>
+    <row r="7024" spans="1:1">
+      <c r="A7024" s="3" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="7025" spans="1:1">
+      <c r="A7025" s="3" t="s">
+        <v>3224</v>
+      </c>
+    </row>
+    <row r="7026" spans="1:1">
+      <c r="A7026" s="3" t="s">
+        <v>3225</v>
+      </c>
+    </row>
+    <row r="7027" spans="1:1">
+      <c r="A7027" s="3" t="s">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="7028" spans="1:1">
+      <c r="A7028" s="3" t="s">
+        <v>3227</v>
+      </c>
+    </row>
+    <row r="7029" spans="1:1">
+      <c r="A7029" s="3" t="s">
+        <v>3226</v>
+      </c>
+    </row>
+    <row r="7030" spans="1:1">
+      <c r="A7030" s="3" t="s">
+        <v>3228</v>
+      </c>
+    </row>
+    <row r="7031" spans="1:1">
+      <c r="A7031" s="3" t="s">
+        <v>3230</v>
+      </c>
+    </row>
+    <row r="7032" spans="1:1">
+      <c r="A7032" s="3" t="s">
+        <v>3229</v>
+      </c>
+    </row>
+    <row r="7033" spans="1:1">
+      <c r="A7033" s="3" t="s">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="7034" spans="1:1">
+      <c r="A7034" s="3" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="7035" spans="1:1">
+      <c r="A7035" s="3" t="s">
+        <v>3231</v>
+      </c>
+    </row>
+    <row r="7036" spans="1:1">
+      <c r="A7036" s="3" t="s">
+        <v>3232</v>
+      </c>
+    </row>
+    <row r="7037" spans="1:1">
+      <c r="A7037" s="3" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="7038" spans="1:1">
+      <c r="A7038" s="3" t="s">
+        <v>3233</v>
+      </c>
+    </row>
+    <row r="7039" spans="1:1">
+      <c r="A7039" s="3" t="s">
+        <v>3234</v>
+      </c>
+    </row>
+    <row r="7040" spans="1:1">
+      <c r="A7040" s="3" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="7041" spans="1:1">
+      <c r="A7041" s="3" t="s">
+        <v>3236</v>
+      </c>
+    </row>
+    <row r="7042" spans="1:1">
+      <c r="A7042" s="3" t="s">
+        <v>3237</v>
+      </c>
+    </row>
+    <row r="7043" spans="1:1">
+      <c r="A7043" s="3" t="s">
+        <v>3683</v>
+      </c>
+    </row>
+    <row r="7044" spans="1:1">
+      <c r="A7044" s="3" t="s">
+        <v>3603</v>
+      </c>
+    </row>
+    <row r="7045" spans="1:1">
+      <c r="A7045" s="3" t="s">
+        <v>3238</v>
+      </c>
+    </row>
+    <row r="7046" spans="1:1">
+      <c r="A7046" s="3" t="s">
+        <v>3239</v>
+      </c>
+    </row>
+    <row r="7047" spans="1:1">
+      <c r="A7047" s="3" t="s">
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="7048" spans="1:1">
+      <c r="A7048" s="3" t="s">
+        <v>3247</v>
+      </c>
+    </row>
+    <row r="7049" spans="1:1">
+      <c r="A7049" s="3" t="s">
+        <v>3241</v>
+      </c>
+    </row>
+    <row r="7050" spans="1:1">
+      <c r="A7050" s="3" t="s">
+        <v>3246</v>
+      </c>
+    </row>
+    <row r="7051" spans="1:1">
+      <c r="A7051" s="3" t="s">
+        <v>3242</v>
+      </c>
+    </row>
+    <row r="7052" spans="1:1">
+      <c r="A7052" s="3" t="s">
+        <v>3325</v>
+      </c>
+    </row>
+    <row r="7053" spans="1:1">
+      <c r="A7053" s="3" t="s">
+        <v>3243</v>
+      </c>
+    </row>
+    <row r="7054" spans="1:1">
+      <c r="A7054" s="3" t="s">
+        <v>3244</v>
+      </c>
+    </row>
+    <row r="7055" spans="1:1">
+      <c r="A7055" s="3" t="s">
+        <v>3245</v>
+      </c>
+    </row>
+    <row r="7056" spans="1:1">
+      <c r="A7056" s="3" t="s">
+        <v>3248</v>
+      </c>
+    </row>
+    <row r="7057" spans="1:1">
+      <c r="A7057" s="3" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="7058" spans="1:1">
+      <c r="A7058" s="3" t="s">
+        <v>3252</v>
+      </c>
+    </row>
+    <row r="7059" spans="1:1">
+      <c r="A7059" s="3" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="7060" spans="1:1">
+      <c r="A7060" s="3" t="s">
+        <v>3251</v>
+      </c>
+    </row>
+    <row r="7061" spans="1:1">
+      <c r="A7061" s="3" t="s">
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="7062" spans="1:1">
+      <c r="A7062" s="3" t="s">
+        <v>3253</v>
+      </c>
+    </row>
+    <row r="7063" spans="1:1">
+      <c r="A7063" s="3" t="s">
+        <v>3254</v>
+      </c>
+    </row>
+    <row r="7064" spans="1:1">
+      <c r="A7064" s="3" t="s">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="7065" spans="1:1">
+      <c r="A7065" s="3" t="s">
+        <v>3249</v>
+      </c>
+    </row>
+    <row r="7066" spans="1:1">
+      <c r="A7066" s="3" t="s">
+        <v>3556</v>
+      </c>
+    </row>
+    <row r="7067" spans="1:1">
+      <c r="A7067" s="3" t="s">
+        <v>3255</v>
+      </c>
+    </row>
+    <row r="7068" spans="1:1">
+      <c r="A7068" s="3" t="s">
+        <v>3256</v>
+      </c>
+    </row>
+    <row r="7069" spans="1:1">
+      <c r="A7069" s="3" t="s">
+        <v>3257</v>
+      </c>
+    </row>
+    <row r="7070" spans="1:1">
+      <c r="A7070" s="3" t="s">
+        <v>3258</v>
+      </c>
+    </row>
+    <row r="7071" spans="1:1">
+      <c r="A7071" s="3" t="s">
+        <v>3263</v>
+      </c>
+    </row>
+    <row r="7072" spans="1:1">
+      <c r="A7072" s="3" t="s">
+        <v>3264</v>
+      </c>
+    </row>
+    <row r="7073" spans="1:1">
+      <c r="A7073" s="3" t="s">
+        <v>3262</v>
+      </c>
+    </row>
+    <row r="7074" spans="1:1">
+      <c r="A7074" s="3" t="s">
+        <v>2883</v>
+      </c>
+    </row>
+    <row r="7075" spans="1:1">
+      <c r="A7075" s="3" t="s">
+        <v>3261</v>
+      </c>
+    </row>
+    <row r="7076" spans="1:1">
+      <c r="A7076" s="3" t="s">
+        <v>3260</v>
+      </c>
+    </row>
+    <row r="7077" spans="1:1">
+      <c r="A7077" s="3" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="7078" spans="1:1">
+      <c r="A7078" s="3" t="s">
+        <v>3267</v>
+      </c>
+    </row>
+    <row r="7079" spans="1:1">
+      <c r="A7079" s="3" t="s">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="7080" spans="1:1">
+      <c r="A7080" s="3" t="s">
+        <v>3348</v>
+      </c>
+    </row>
+    <row r="7081" spans="1:1">
+      <c r="A7081" s="3" t="s">
+        <v>3265</v>
+      </c>
+    </row>
+    <row r="7082" spans="1:1">
+      <c r="A7082" s="3" t="s">
+        <v>3269</v>
+      </c>
+    </row>
+    <row r="7083" spans="1:1">
+      <c r="A7083" s="3" t="s">
+        <v>3266</v>
+      </c>
+    </row>
+    <row r="7084" spans="1:1">
+      <c r="A7084" s="3" t="s">
+        <v>3268</v>
+      </c>
+    </row>
+    <row r="7085" spans="1:1">
+      <c r="A7085" s="3" t="s">
+        <v>3629</v>
+      </c>
+    </row>
+    <row r="7086" spans="1:1">
+      <c r="A7086" s="3" t="s">
+        <v>3275</v>
+      </c>
+    </row>
+    <row r="7087" spans="1:1">
+      <c r="A7087" s="3" t="s">
+        <v>3270</v>
+      </c>
+    </row>
+    <row r="7088" spans="1:1">
+      <c r="A7088" s="3" t="s">
+        <v>3273</v>
+      </c>
+    </row>
+    <row r="7089" spans="1:1">
+      <c r="A7089" s="3" t="s">
+        <v>3278</v>
+      </c>
+    </row>
+    <row r="7090" spans="1:1">
+      <c r="A7090" s="3" t="s">
+        <v>3276</v>
+      </c>
+    </row>
+    <row r="7091" spans="1:1">
+      <c r="A7091" s="3" t="s">
+        <v>3277</v>
+      </c>
+    </row>
+    <row r="7092" spans="1:1">
+      <c r="A7092" s="3" t="s">
+        <v>3274</v>
+      </c>
+    </row>
+    <row r="7093" spans="1:1">
+      <c r="A7093" s="3" t="s">
+        <v>3271</v>
+      </c>
+    </row>
+    <row r="7094" spans="1:1">
+      <c r="A7094" s="3" t="s">
+        <v>3272</v>
+      </c>
+    </row>
+    <row r="7095" spans="1:1">
+      <c r="A7095" s="3" t="s">
+        <v>3280</v>
+      </c>
+    </row>
+    <row r="7096" spans="1:1">
+      <c r="A7096" s="3" t="s">
+        <v>3281</v>
+      </c>
+    </row>
+    <row r="7097" spans="1:1">
+      <c r="A7097" s="3" t="s">
+        <v>3282</v>
+      </c>
+    </row>
+    <row r="7098" spans="1:1">
+      <c r="A7098" s="3" t="s">
+        <v>3374</v>
+      </c>
+    </row>
+    <row r="7099" spans="1:1">
+      <c r="A7099" s="3" t="s">
+        <v>3571</v>
+      </c>
+    </row>
+    <row r="7100" spans="1:1">
+      <c r="A7100" s="3" t="s">
+        <v>3285</v>
+      </c>
+    </row>
+    <row r="7101" spans="1:1">
+      <c r="A7101" s="3" t="s">
+        <v>3284</v>
+      </c>
+    </row>
+    <row r="7102" spans="1:1">
+      <c r="A7102" s="3" t="s">
+        <v>3283</v>
+      </c>
+    </row>
+    <row r="7103" spans="1:1">
+      <c r="A7103" s="3" t="s">
+        <v>3287</v>
+      </c>
+    </row>
+    <row r="7104" spans="1:1">
+      <c r="A7104" s="3" t="s">
+        <v>3288</v>
+      </c>
+    </row>
+    <row r="7105" spans="1:1">
+      <c r="A7105" s="3" t="s">
+        <v>3289</v>
+      </c>
+    </row>
+    <row r="7106" spans="1:1">
+      <c r="A7106" s="3" t="s">
+        <v>3292</v>
+      </c>
+    </row>
+    <row r="7107" spans="1:1">
+      <c r="A7107" s="3" t="s">
+        <v>3291</v>
+      </c>
+    </row>
+    <row r="7108" spans="1:1">
+      <c r="A7108" s="3" t="s">
+        <v>3290</v>
+      </c>
+    </row>
+    <row r="7109" spans="1:1">
+      <c r="A7109" s="3" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="7110" spans="1:1">
+      <c r="A7110" s="3" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="7111" spans="1:1">
+      <c r="A7111" s="3" t="s">
+        <v>3296</v>
+      </c>
+    </row>
+    <row r="7112" spans="1:1">
+      <c r="A7112" s="3" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="7113" spans="1:1">
+      <c r="A7113" s="3" t="s">
+        <v>3293</v>
+      </c>
+    </row>
+    <row r="7114" spans="1:1">
+      <c r="A7114" s="3" t="s">
+        <v>3298</v>
+      </c>
+    </row>
+    <row r="7115" spans="1:1">
+      <c r="A7115" s="3" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="7116" spans="1:1">
+      <c r="A7116" s="3" t="s">
+        <v>3294</v>
+      </c>
+    </row>
+    <row r="7117" spans="1:1">
+      <c r="A7117" s="3" t="s">
+        <v>3299</v>
+      </c>
+    </row>
+    <row r="7118" spans="1:1">
+      <c r="A7118" s="3" t="s">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="7119" spans="1:1">
+      <c r="A7119" s="3" t="s">
+        <v>3301</v>
+      </c>
+    </row>
+    <row r="7120" spans="1:1">
+      <c r="A7120" s="3" t="s">
+        <v>3302</v>
+      </c>
+    </row>
+    <row r="7121" spans="1:1">
+      <c r="A7121" s="3" t="s">
+        <v>3303</v>
+      </c>
+    </row>
+    <row r="7122" spans="1:1">
+      <c r="A7122" s="3" t="s">
+        <v>3304</v>
+      </c>
+    </row>
+    <row r="7123" spans="1:1">
+      <c r="A7123" s="3" t="s">
+        <v>3311</v>
+      </c>
+    </row>
+    <row r="7124" spans="1:1">
+      <c r="A7124" s="3" t="s">
+        <v>3306</v>
+      </c>
+    </row>
+    <row r="7125" spans="1:1">
+      <c r="A7125" s="3" t="s">
+        <v>3308</v>
+      </c>
+    </row>
+    <row r="7126" spans="1:1">
+      <c r="A7126" s="3" t="s">
+        <v>3585</v>
+      </c>
+    </row>
+    <row r="7127" spans="1:1">
+      <c r="A7127" s="3" t="s">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="7128" spans="1:1">
+      <c r="A7128" s="3" t="s">
+        <v>3307</v>
+      </c>
+    </row>
+    <row r="7129" spans="1:1">
+      <c r="A7129" s="3" t="s">
+        <v>3310</v>
+      </c>
+    </row>
+    <row r="7130" spans="1:1">
+      <c r="A7130" s="3" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="7131" spans="1:1">
+      <c r="A7131" s="3" t="s">
+        <v>3305</v>
+      </c>
+    </row>
+    <row r="7132" spans="1:1">
+      <c r="A7132" s="3" t="s">
+        <v>3309</v>
+      </c>
+    </row>
+    <row r="7133" spans="1:1">
+      <c r="A7133" s="3" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="7134" spans="1:1">
+      <c r="A7134" s="3" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="7135" spans="1:1">
+      <c r="A7135" s="3" t="s">
+        <v>3312</v>
+      </c>
+    </row>
+    <row r="7136" spans="1:1">
+      <c r="A7136" s="3" t="s">
+        <v>3313</v>
+      </c>
+    </row>
+    <row r="7137" spans="1:1">
+      <c r="A7137" s="3" t="s">
+        <v>3314</v>
+      </c>
+    </row>
+    <row r="7138" spans="1:1">
+      <c r="A7138" s="3" t="s">
+        <v>3316</v>
+      </c>
+    </row>
+    <row r="7139" spans="1:1">
+      <c r="A7139" s="3" t="s">
+        <v>3317</v>
+      </c>
+    </row>
+    <row r="7140" spans="1:1">
+      <c r="A7140" s="3" t="s">
+        <v>3315</v>
+      </c>
+    </row>
+    <row r="7141" spans="1:1">
+      <c r="A7141" s="3" t="s">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="7142" spans="1:1">
+      <c r="A7142" s="3" t="s">
+        <v>3319</v>
+      </c>
+    </row>
+    <row r="7143" spans="1:1">
+      <c r="A7143" s="3" t="s">
+        <v>3320</v>
+      </c>
+    </row>
+    <row r="7144" spans="1:1">
+      <c r="A7144" s="3" t="s">
+        <v>3322</v>
+      </c>
+    </row>
+    <row r="7145" spans="1:1">
+      <c r="A7145" s="3" t="s">
+        <v>3321</v>
+      </c>
+    </row>
+    <row r="7146" spans="1:1">
+      <c r="A7146" s="3" t="s">
+        <v>3324</v>
+      </c>
+    </row>
+    <row r="7147" spans="1:1">
+      <c r="A7147" s="3" t="s">
+        <v>3328</v>
+      </c>
+    </row>
+    <row r="7148" spans="1:1">
+      <c r="A7148" s="3" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="7149" spans="1:1">
+      <c r="A7149" s="3" t="s">
+        <v>3323</v>
+      </c>
+    </row>
+    <row r="7150" spans="1:1">
+      <c r="A7150" s="3" t="s">
+        <v>3325</v>
+      </c>
+    </row>
+    <row r="7151" spans="1:1">
+      <c r="A7151" s="3" t="s">
+        <v>3329</v>
+      </c>
+    </row>
+    <row r="7152" spans="1:1">
+      <c r="A7152" s="3" t="s">
+        <v>3326</v>
+      </c>
+    </row>
+    <row r="7153" spans="1:1">
+      <c r="A7153" s="3" t="s">
+        <v>3327</v>
+      </c>
+    </row>
+    <row r="7154" spans="1:1">
+      <c r="A7154" s="3" t="s">
+        <v>3590</v>
+      </c>
+    </row>
+    <row r="7155" spans="1:1">
+      <c r="A7155" s="3" t="s">
+        <v>3332</v>
+      </c>
+    </row>
+    <row r="7156" spans="1:1">
+      <c r="A7156" s="3" t="s">
+        <v>3331</v>
+      </c>
+    </row>
+    <row r="7157" spans="1:1">
+      <c r="A7157" s="3" t="s">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="7158" spans="1:1">
+      <c r="A7158" s="3" t="s">
+        <v>3334</v>
+      </c>
+    </row>
+    <row r="7159" spans="1:1">
+      <c r="A7159" s="3" t="s">
+        <v>2884</v>
+      </c>
+    </row>
+    <row r="7160" spans="1:1">
+      <c r="A7160" s="3" t="s">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="7161" spans="1:1">
+      <c r="A7161" s="3" t="s">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="7162" spans="1:1">
+      <c r="A7162" s="3" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="7163" spans="1:1">
+      <c r="A7163" s="3" t="s">
+        <v>3336</v>
+      </c>
+    </row>
+    <row r="7164" spans="1:1">
+      <c r="A7164" s="3" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="7165" spans="1:1">
+      <c r="A7165" s="3" t="s">
+        <v>3337</v>
+      </c>
+    </row>
+    <row r="7166" spans="1:1">
+      <c r="A7166" s="3" t="s">
+        <v>3339</v>
+      </c>
+    </row>
+    <row r="7167" spans="1:1">
+      <c r="A7167" s="3" t="s">
+        <v>3338</v>
+      </c>
+    </row>
+    <row r="7168" spans="1:1">
+      <c r="A7168" s="3" t="s">
+        <v>3335</v>
+      </c>
+    </row>
+    <row r="7169" spans="1:1">
+      <c r="A7169" s="3" t="s">
+        <v>2302</v>
+      </c>
+    </row>
+    <row r="7170" spans="1:1">
+      <c r="A7170" s="3" t="s">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="7171" spans="1:1">
+      <c r="A7171" s="3" t="s">
+        <v>3341</v>
+      </c>
+    </row>
+    <row r="7172" spans="1:1">
+      <c r="A7172" s="3" t="s">
+        <v>3342</v>
+      </c>
+    </row>
+    <row r="7173" spans="1:1">
+      <c r="A7173" s="3" t="s">
+        <v>3343</v>
+      </c>
+    </row>
+    <row r="7174" spans="1:1">
+      <c r="A7174" s="3" t="s">
+        <v>3344</v>
+      </c>
+    </row>
+    <row r="7175" spans="1:1">
+      <c r="A7175" s="3" t="s">
+        <v>3345</v>
+      </c>
+    </row>
+    <row r="7176" spans="1:1">
+      <c r="A7176" s="3" t="s">
+        <v>3346</v>
+      </c>
+    </row>
+    <row r="7177" spans="1:1">
+      <c r="A7177" s="3" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="7178" spans="1:1">
+      <c r="A7178" s="3" t="s">
+        <v>3347</v>
+      </c>
+    </row>
+    <row r="7179" spans="1:1">
+      <c r="A7179" s="3" t="s">
+        <v>3348</v>
+      </c>
+    </row>
+    <row r="7180" spans="1:1">
+      <c r="A7180" s="3" t="s">
+        <v>3349</v>
+      </c>
+    </row>
+    <row r="7181" spans="1:1">
+      <c r="A7181" s="3" t="s">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="7182" spans="1:1">
+      <c r="A7182" s="3" t="s">
+        <v>3351</v>
+      </c>
+    </row>
+    <row r="7183" spans="1:1">
+      <c r="A7183" s="3" t="s">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="7184" spans="1:1">
+      <c r="A7184" s="3" t="s">
+        <v>3353</v>
+      </c>
+    </row>
+    <row r="7185" spans="1:1">
+      <c r="A7185" s="3" t="s">
+        <v>2278</v>
+      </c>
+    </row>
+    <row r="7186" spans="1:1">
+      <c r="A7186" s="3" t="s">
+        <v>3352</v>
+      </c>
+    </row>
+    <row r="7187" spans="1:1">
+      <c r="A7187" s="3" t="s">
+        <v>3354</v>
+      </c>
+    </row>
+    <row r="7188" spans="1:1">
+      <c r="A7188" s="3" t="s">
+        <v>3356</v>
+      </c>
+    </row>
+    <row r="7189" spans="1:1">
+      <c r="A7189" s="3" t="s">
+        <v>3357</v>
+      </c>
+    </row>
+    <row r="7190" spans="1:1">
+      <c r="A7190" s="3" t="s">
+        <v>3358</v>
+      </c>
+    </row>
+    <row r="7191" spans="1:1">
+      <c r="A7191" s="3" t="s">
+        <v>3355</v>
+      </c>
+    </row>
+    <row r="7192" spans="1:1">
+      <c r="A7192" s="3" t="s">
+        <v>3359</v>
+      </c>
+    </row>
+    <row r="7193" spans="1:1">
+      <c r="A7193" s="3" t="s">
+        <v>3360</v>
+      </c>
+    </row>
+    <row r="7194" spans="1:1">
+      <c r="A7194" s="3" t="s">
+        <v>3361</v>
+      </c>
+    </row>
+    <row r="7195" spans="1:1">
+      <c r="A7195" s="3" t="s">
+        <v>3362</v>
+      </c>
+    </row>
+    <row r="7196" spans="1:1">
+      <c r="A7196" s="3" t="s">
+        <v>3363</v>
+      </c>
+    </row>
+    <row r="7197" spans="1:1">
+      <c r="A7197" s="3" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="7198" spans="1:1">
+      <c r="A7198" s="3" t="s">
+        <v>2898</v>
+      </c>
+    </row>
+    <row r="7199" spans="1:1">
+      <c r="A7199" s="3" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="7200" spans="1:1">
+      <c r="A7200" s="3" t="s">
+        <v>3364</v>
+      </c>
+    </row>
+    <row r="7201" spans="1:1">
+      <c r="A7201" s="3" t="s">
+        <v>3408</v>
+      </c>
+    </row>
+    <row r="7202" spans="1:1">
+      <c r="A7202" s="3" t="s">
+        <v>2894</v>
+      </c>
+    </row>
+    <row r="7203" spans="1:1">
+      <c r="A7203" s="3" t="s">
+        <v>3365</v>
+      </c>
+    </row>
+    <row r="7204" spans="1:1">
+      <c r="A7204" s="3" t="s">
+        <v>2305</v>
+      </c>
+    </row>
+    <row r="7205" spans="1:1">
+      <c r="A7205" s="3" t="s">
+        <v>3656</v>
+      </c>
+    </row>
+    <row r="7206" spans="1:1">
+      <c r="A7206" s="3" t="s">
+        <v>3367</v>
+      </c>
+    </row>
+    <row r="7207" spans="1:1">
+      <c r="A7207" s="3" t="s">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="7208" spans="1:1">
+      <c r="A7208" s="3" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="7209" spans="1:1">
+      <c r="A7209" s="3" t="s">
+        <v>3368</v>
+      </c>
+    </row>
+    <row r="7210" spans="1:1">
+      <c r="A7210" s="3" t="s">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="7211" spans="1:1">
+      <c r="A7211" s="3" t="s">
+        <v>3369</v>
+      </c>
+    </row>
+    <row r="7212" spans="1:1">
+      <c r="A7212" s="3" t="s">
+        <v>3370</v>
+      </c>
+    </row>
+    <row r="7213" spans="1:1">
+      <c r="A7213" s="3" t="s">
+        <v>3371</v>
+      </c>
+    </row>
+    <row r="7214" spans="1:1">
+      <c r="A7214" s="3" t="s">
+        <v>3372</v>
+      </c>
+    </row>
+    <row r="7215" spans="1:1">
+      <c r="A7215" s="3" t="s">
+        <v>2271</v>
+      </c>
+    </row>
+    <row r="7216" spans="1:1">
+      <c r="A7216" s="3" t="s">
+        <v>3373</v>
+      </c>
+    </row>
+    <row r="7217" spans="1:1">
+      <c r="A7217" s="3" t="s">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="7218" spans="1:1">
+      <c r="A7218" s="3" t="s">
+        <v>3376</v>
+      </c>
+    </row>
+    <row r="7219" spans="1:1">
+      <c r="A7219" s="3" t="s">
+        <v>3377</v>
+      </c>
+    </row>
+    <row r="7220" spans="1:1">
+      <c r="A7220" s="3" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="7221" spans="1:1">
+      <c r="A7221" s="3" t="s">
+        <v>3374</v>
+      </c>
+    </row>
+    <row r="7222" spans="1:1">
+      <c r="A7222" s="3" t="s">
+        <v>3378</v>
+      </c>
+    </row>
+    <row r="7223" spans="1:1">
+      <c r="A7223" s="3" t="s">
+        <v>3380</v>
+      </c>
+    </row>
+    <row r="7224" spans="1:1">
+      <c r="A7224" s="3" t="s">
+        <v>3379</v>
+      </c>
+    </row>
+    <row r="7225" spans="1:1">
+      <c r="A7225" s="3" t="s">
+        <v>2318</v>
+      </c>
+    </row>
+    <row r="7226" spans="1:1">
+      <c r="A7226" s="3" t="s">
+        <v>3381</v>
+      </c>
+    </row>
+    <row r="7227" spans="1:1">
+      <c r="A7227" s="3" t="s">
+        <v>3382</v>
+      </c>
+    </row>
+    <row r="7228" spans="1:1">
+      <c r="A7228" s="3" t="s">
+        <v>3383</v>
+      </c>
+    </row>
+    <row r="7229" spans="1:1">
+      <c r="A7229" s="3" t="s">
+        <v>3384</v>
+      </c>
+    </row>
+    <row r="7230" spans="1:1">
+      <c r="A7230" s="3" t="s">
+        <v>3386</v>
+      </c>
+    </row>
+    <row r="7231" spans="1:1">
+      <c r="A7231" s="3" t="s">
+        <v>3385</v>
+      </c>
+    </row>
+    <row r="7232" spans="1:1">
+      <c r="A7232" s="3" t="s">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="7233" spans="1:1">
+      <c r="A7233" s="3" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="7234" spans="1:1">
+      <c r="A7234" s="3" t="s">
+        <v>3387</v>
+      </c>
+    </row>
+    <row r="7235" spans="1:1">
+      <c r="A7235" s="3" t="s">
+        <v>3388</v>
+      </c>
+    </row>
+    <row r="7236" spans="1:1">
+      <c r="A7236" s="3" t="s">
+        <v>3389</v>
+      </c>
+    </row>
+    <row r="7237" spans="1:1">
+      <c r="A7237" s="3" t="s">
+        <v>3390</v>
+      </c>
+    </row>
+    <row r="7238" spans="1:1">
+      <c r="A7238" s="3" t="s">
+        <v>3391</v>
+      </c>
+    </row>
+    <row r="7239" spans="1:1">
+      <c r="A7239" s="3" t="s">
+        <v>3392</v>
+      </c>
+    </row>
+    <row r="7240" spans="1:1">
+      <c r="A7240" s="3" t="s">
+        <v>3622</v>
+      </c>
+    </row>
+    <row r="7241" spans="1:1">
+      <c r="A7241" s="3" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="7242" spans="1:1">
+      <c r="A7242" s="3" t="s">
+        <v>3393</v>
+      </c>
+    </row>
+    <row r="7243" spans="1:1">
+      <c r="A7243" s="3" t="s">
+        <v>3394</v>
+      </c>
+    </row>
+    <row r="7244" spans="1:1">
+      <c r="A7244" s="3" t="s">
+        <v>3396</v>
+      </c>
+    </row>
+    <row r="7245" spans="1:1">
+      <c r="A7245" s="3" t="s">
+        <v>3395</v>
+      </c>
+    </row>
+    <row r="7246" spans="1:1">
+      <c r="A7246" s="3" t="s">
+        <v>3401</v>
+      </c>
+    </row>
+    <row r="7247" spans="1:1">
+      <c r="A7247" s="3" t="s">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="7248" spans="1:1">
+      <c r="A7248" s="3" t="s">
+        <v>3399</v>
+      </c>
+    </row>
+    <row r="7249" spans="1:1">
+      <c r="A7249" s="3" t="s">
+        <v>3398</v>
+      </c>
+    </row>
+    <row r="7250" spans="1:1">
+      <c r="A7250" s="3" t="s">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="7251" spans="1:1">
+      <c r="A7251" s="3" t="s">
+        <v>3397</v>
+      </c>
+    </row>
+    <row r="7252" spans="1:1">
+      <c r="A7252" s="3" t="s">
+        <v>3402</v>
+      </c>
+    </row>
+    <row r="7253" spans="1:1">
+      <c r="A7253" s="3" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="7254" spans="1:1">
+      <c r="A7254" s="3" t="s">
+        <v>3404</v>
+      </c>
+    </row>
+    <row r="7255" spans="1:1">
+      <c r="A7255" s="3" t="s">
+        <v>3405</v>
+      </c>
+    </row>
+    <row r="7256" spans="1:1">
+      <c r="A7256" s="3" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="7257" spans="1:1">
+      <c r="A7257" s="3" t="s">
+        <v>3406</v>
+      </c>
+    </row>
+    <row r="7258" spans="1:1">
+      <c r="A7258" s="3" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="7259" spans="1:1">
+      <c r="A7259" s="3" t="s">
+        <v>3407</v>
+      </c>
+    </row>
+    <row r="7260" spans="1:1">
+      <c r="A7260" s="3" t="s">
+        <v>3408</v>
+      </c>
+    </row>
+    <row r="7261" spans="1:1">
+      <c r="A7261" s="3" t="s">
+        <v>3409</v>
+      </c>
+    </row>
+    <row r="7262" spans="1:1">
+      <c r="A7262" s="3" t="s">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="7263" spans="1:1">
+      <c r="A7263" s="3" t="s">
+        <v>3410</v>
+      </c>
+    </row>
+    <row r="7264" spans="1:1">
+      <c r="A7264" s="3" t="s">
+        <v>3411</v>
+      </c>
+    </row>
+    <row r="7265" spans="1:1">
+      <c r="A7265" s="3" t="s">
+        <v>3412</v>
+      </c>
+    </row>
+    <row r="7266" spans="1:1">
+      <c r="A7266" s="3" t="s">
+        <v>3413</v>
+      </c>
+    </row>
+    <row r="7267" spans="1:1">
+      <c r="A7267" s="3" t="s">
+        <v>3414</v>
+      </c>
+    </row>
+    <row r="7268" spans="1:1">
+      <c r="A7268" s="3" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="7269" spans="1:1">
+      <c r="A7269" s="3" t="s">
+        <v>3416</v>
+      </c>
+    </row>
+    <row r="7270" spans="1:1">
+      <c r="A7270" s="3" t="s">
+        <v>3417</v>
+      </c>
+    </row>
+    <row r="7271" spans="1:1">
+      <c r="A7271" s="3" t="s">
+        <v>3418</v>
+      </c>
+    </row>
+    <row r="7272" spans="1:1">
+      <c r="A7272" s="3" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="7273" spans="1:1">
+      <c r="A7273" s="3" t="s">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="7274" spans="1:1">
+      <c r="A7274" s="3" t="s">
+        <v>3421</v>
+      </c>
+    </row>
+    <row r="7275" spans="1:1">
+      <c r="A7275" s="3" t="s">
+        <v>3419</v>
+      </c>
+    </row>
+    <row r="7276" spans="1:1">
+      <c r="A7276" s="3" t="s">
+        <v>3422</v>
+      </c>
+    </row>
+    <row r="7277" spans="1:1">
+      <c r="A7277" s="3" t="s">
+        <v>3423</v>
+      </c>
+    </row>
+    <row r="7278" spans="1:1">
+      <c r="A7278" s="3" t="s">
+        <v>3424</v>
+      </c>
+    </row>
+    <row r="7279" spans="1:1">
+      <c r="A7279" s="3" t="s">
+        <v>3425</v>
+      </c>
+    </row>
+    <row r="7280" spans="1:1">
+      <c r="A7280" s="3" t="s">
+        <v>3426</v>
+      </c>
+    </row>
+    <row r="7281" spans="1:1">
+      <c r="A7281" s="3" t="s">
+        <v>3427</v>
+      </c>
+    </row>
+    <row r="7282" spans="1:1">
+      <c r="A7282" s="3" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="7283" spans="1:1">
+      <c r="A7283" s="3" t="s">
+        <v>3428</v>
+      </c>
+    </row>
+    <row r="7284" spans="1:1">
+      <c r="A7284" s="3" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="7285" spans="1:1">
+      <c r="A7285" s="3" t="s">
+        <v>3429</v>
+      </c>
+    </row>
+    <row r="7286" spans="1:1">
+      <c r="A7286" s="3" t="s">
+        <v>3430</v>
+      </c>
+    </row>
+    <row r="7287" spans="1:1">
+      <c r="A7287" s="3" t="s">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="7288" spans="1:1">
+      <c r="A7288" s="3" t="s">
+        <v>2318</v>
+      </c>
+    </row>
+    <row r="7289" spans="1:1">
+      <c r="A7289" s="3" t="s">
+        <v>3431</v>
+      </c>
+    </row>
+    <row r="7290" spans="1:1">
+      <c r="A7290" s="3" t="s">
+        <v>3432</v>
+      </c>
+    </row>
+    <row r="7291" spans="1:1">
+      <c r="A7291" s="3" t="s">
+        <v>2296</v>
+      </c>
+    </row>
+    <row r="7292" spans="1:1">
+      <c r="A7292" s="3" t="s">
+        <v>3433</v>
+      </c>
+    </row>
+    <row r="7293" spans="1:1">
+      <c r="A7293" s="3" t="s">
+        <v>3434</v>
+      </c>
+    </row>
+    <row r="7294" spans="1:1">
+      <c r="A7294" s="3" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="7295" spans="1:1">
+      <c r="A7295" s="3" t="s">
+        <v>3435</v>
+      </c>
+    </row>
+    <row r="7296" spans="1:1">
+      <c r="A7296" s="3" t="s">
+        <v>3436</v>
+      </c>
+    </row>
+    <row r="7297" spans="1:1">
+      <c r="A7297" s="3" t="s">
+        <v>3056</v>
+      </c>
+    </row>
+    <row r="7298" spans="1:1">
+      <c r="A7298" s="3" t="s">
+        <v>3437</v>
+      </c>
+    </row>
+    <row r="7299" spans="1:1">
+      <c r="A7299" s="3" t="s">
+        <v>3438</v>
+      </c>
+    </row>
+    <row r="7300" spans="1:1">
+      <c r="A7300" s="3" t="s">
+        <v>3439</v>
+      </c>
+    </row>
+    <row r="7301" spans="1:1">
+      <c r="A7301" s="3" t="s">
+        <v>3440</v>
+      </c>
+    </row>
+    <row r="7302" spans="1:1">
+      <c r="A7302" s="3" t="s">
+        <v>3441</v>
+      </c>
+    </row>
+    <row r="7303" spans="1:1">
+      <c r="A7303" s="3" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="7304" spans="1:1">
+      <c r="A7304" s="3" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="7305" spans="1:1">
+      <c r="A7305" s="3" t="s">
+        <v>3442</v>
+      </c>
+    </row>
+    <row r="7306" spans="1:1">
+      <c r="A7306" s="3" t="s">
+        <v>3443</v>
+      </c>
+    </row>
+    <row r="7307" spans="1:1">
+      <c r="A7307" s="3" t="s">
+        <v>3444</v>
+      </c>
+    </row>
+    <row r="7308" spans="1:1">
+      <c r="A7308" s="3" t="s">
+        <v>3445</v>
+      </c>
+    </row>
+    <row r="7309" spans="1:1">
+      <c r="A7309" s="3" t="s">
+        <v>3577</v>
+      </c>
+    </row>
+    <row r="7310" spans="1:1">
+      <c r="A7310" s="3" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="7311" spans="1:1">
+      <c r="A7311" s="3" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="7312" spans="1:1">
+      <c r="A7312" s="3" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="7313" spans="1:1">
+      <c r="A7313" s="3" t="s">
+        <v>3446</v>
+      </c>
+    </row>
+    <row r="7314" spans="1:1">
+      <c r="A7314" s="3" t="s">
+        <v>3447</v>
+      </c>
+    </row>
+    <row r="7315" spans="1:1">
+      <c r="A7315" s="3" t="s">
+        <v>3448</v>
+      </c>
+    </row>
+    <row r="7316" spans="1:1">
+      <c r="A7316" s="3" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="7317" spans="1:1">
+      <c r="A7317" s="3" t="s">
+        <v>3449</v>
+      </c>
+    </row>
+    <row r="7318" spans="1:1">
+      <c r="A7318" s="3" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="7319" spans="1:1">
+      <c r="A7319" s="3" t="s">
+        <v>3450</v>
+      </c>
+    </row>
+    <row r="7320" spans="1:1">
+      <c r="A7320" s="3" t="s">
+        <v>3451</v>
+      </c>
+    </row>
+    <row r="7321" spans="1:1">
+      <c r="A7321" s="3" t="s">
+        <v>3452</v>
+      </c>
+    </row>
+    <row r="7322" spans="1:1">
+      <c r="A7322" s="3" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="7323" spans="1:1">
+      <c r="A7323" s="3" t="s">
+        <v>3453</v>
+      </c>
+    </row>
+    <row r="7324" spans="1:1">
+      <c r="A7324" s="3" t="s">
+        <v>3454</v>
+      </c>
+    </row>
+    <row r="7325" spans="1:1">
+      <c r="A7325" s="3" t="s">
+        <v>3455</v>
+      </c>
+    </row>
+    <row r="7326" spans="1:1">
+      <c r="A7326" s="3" t="s">
+        <v>3683</v>
+      </c>
+    </row>
+    <row r="7327" spans="1:1">
+      <c r="A7327" s="3" t="s">
+        <v>3456</v>
+      </c>
+    </row>
+    <row r="7328" spans="1:1">
+      <c r="A7328" s="3" t="s">
+        <v>3457</v>
+      </c>
+    </row>
+    <row r="7329" spans="1:1">
+      <c r="A7329" s="3" t="s">
+        <v>3458</v>
+      </c>
+    </row>
+    <row r="7330" spans="1:1">
+      <c r="A7330" s="3" t="s">
+        <v>3459</v>
+      </c>
+    </row>
+    <row r="7331" spans="1:1">
+      <c r="A7331" s="3" t="s">
+        <v>3460</v>
+      </c>
+    </row>
+    <row r="7332" spans="1:1">
+      <c r="A7332" s="3" t="s">
+        <v>3461</v>
+      </c>
+    </row>
+    <row r="7333" spans="1:1">
+      <c r="A7333" s="3" t="s">
+        <v>3462</v>
+      </c>
+    </row>
+    <row r="7334" spans="1:1">
+      <c r="A7334" s="3" t="s">
+        <v>3463</v>
+      </c>
+    </row>
+    <row r="7335" spans="1:1">
+      <c r="A7335" s="3" t="s">
+        <v>3464</v>
+      </c>
+    </row>
+    <row r="7336" spans="1:1">
+      <c r="A7336" s="3" t="s">
+        <v>3465</v>
+      </c>
+    </row>
+    <row r="7337" spans="1:1">
+      <c r="A7337" s="3" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="7338" spans="1:1">
+      <c r="A7338" s="3" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="7339" spans="1:1">
+      <c r="A7339" s="3" t="s">
+        <v>3466</v>
+      </c>
+    </row>
+    <row r="7340" spans="1:1">
+      <c r="A7340" s="3" t="s">
+        <v>3470</v>
+      </c>
+    </row>
+    <row r="7341" spans="1:1">
+      <c r="A7341" s="3" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="7342" spans="1:1">
+      <c r="A7342" s="3" t="s">
+        <v>3469</v>
+      </c>
+    </row>
+    <row r="7343" spans="1:1">
+      <c r="A7343" s="3" t="s">
+        <v>3468</v>
+      </c>
+    </row>
+    <row r="7344" spans="1:1">
+      <c r="A7344" s="3" t="s">
+        <v>3467</v>
+      </c>
+    </row>
+    <row r="7345" spans="1:1">
+      <c r="A7345" s="3" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="7346" spans="1:1">
+      <c r="A7346" s="3" t="s">
+        <v>3471</v>
+      </c>
+    </row>
+    <row r="7347" spans="1:1">
+      <c r="A7347" s="3" t="s">
+        <v>3472</v>
+      </c>
+    </row>
+    <row r="7348" spans="1:1">
+      <c r="A7348" s="3" t="s">
+        <v>3473</v>
+      </c>
+    </row>
+    <row r="7349" spans="1:1">
+      <c r="A7349" s="3" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="7350" spans="1:1">
+      <c r="A7350" s="3" t="s">
+        <v>3474</v>
+      </c>
+    </row>
+    <row r="7351" spans="1:1">
+      <c r="A7351" s="3" t="s">
+        <v>3475</v>
+      </c>
+    </row>
+    <row r="7352" spans="1:1">
+      <c r="A7352" s="3" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="7353" spans="1:1">
+      <c r="A7353" s="3" t="s">
+        <v>3476</v>
+      </c>
+    </row>
+    <row r="7354" spans="1:1">
+      <c r="A7354" s="3" t="s">
+        <v>3479</v>
+      </c>
+    </row>
+    <row r="7355" spans="1:1">
+      <c r="A7355" s="3" t="s">
+        <v>3478</v>
+      </c>
+    </row>
+    <row r="7356" spans="1:1">
+      <c r="A7356" s="3" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="7357" spans="1:1">
+      <c r="A7357" s="3" t="s">
+        <v>3480</v>
+      </c>
+    </row>
+    <row r="7358" spans="1:1">
+      <c r="A7358" s="3" t="s">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="7359" spans="1:1">
+      <c r="A7359" s="3" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="7360" spans="1:1">
+      <c r="A7360" s="3" t="s">
+        <v>3481</v>
+      </c>
+    </row>
+    <row r="7361" spans="1:1">
+      <c r="A7361" s="3" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="7362" spans="1:1">
+      <c r="A7362" s="3" t="s">
+        <v>3483</v>
+      </c>
+    </row>
+    <row r="7363" spans="1:1">
+      <c r="A7363" s="3" t="s">
+        <v>3484</v>
+      </c>
+    </row>
+    <row r="7364" spans="1:1">
+      <c r="A7364" s="3" t="s">
+        <v>3482</v>
+      </c>
+    </row>
+    <row r="7365" spans="1:1">
+      <c r="A7365" s="3" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="7366" spans="1:1">
+      <c r="A7366" s="3" t="s">
+        <v>3583</v>
+      </c>
+    </row>
+    <row r="7367" spans="1:1">
+      <c r="A7367" s="3" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="7368" spans="1:1">
+      <c r="A7368" s="3" t="s">
+        <v>3486</v>
+      </c>
+    </row>
+    <row r="7369" spans="1:1">
+      <c r="A7369" s="3" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="7370" spans="1:1">
+      <c r="A7370" s="3" t="s">
+        <v>3551</v>
+      </c>
+    </row>
+    <row r="7371" spans="1:1">
+      <c r="A7371" s="3" t="s">
+        <v>3487</v>
+      </c>
+    </row>
+    <row r="7372" spans="1:1">
+      <c r="A7372" s="3" t="s">
+        <v>3488</v>
+      </c>
+    </row>
+    <row r="7373" spans="1:1">
+      <c r="A7373" s="3" t="s">
+        <v>3489</v>
+      </c>
+    </row>
+    <row r="7374" spans="1:1">
+      <c r="A7374" s="3" t="s">
+        <v>3667</v>
+      </c>
+    </row>
+    <row r="7375" spans="1:1">
+      <c r="A7375" s="3" t="s">
+        <v>3490</v>
+      </c>
+    </row>
+    <row r="7376" spans="1:1">
+      <c r="A7376" s="3" t="s">
+        <v>3491</v>
+      </c>
+    </row>
+    <row r="7377" spans="1:1">
+      <c r="A7377" s="3" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="7378" spans="1:1">
+      <c r="A7378" s="3" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="7379" spans="1:1">
+      <c r="A7379" s="3" t="s">
+        <v>3493</v>
+      </c>
+    </row>
+    <row r="7380" spans="1:1">
+      <c r="A7380" s="3" t="s">
+        <v>3492</v>
+      </c>
+    </row>
+    <row r="7381" spans="1:1">
+      <c r="A7381" s="3" t="s">
+        <v>3494</v>
+      </c>
+    </row>
+    <row r="7382" spans="1:1">
+      <c r="A7382" s="3" t="s">
+        <v>3495</v>
+      </c>
+    </row>
+    <row r="7383" spans="1:1">
+      <c r="A7383" s="3" t="s">
+        <v>2319</v>
+      </c>
+    </row>
+    <row r="7384" spans="1:1">
+      <c r="A7384" s="3" t="s">
+        <v>3497</v>
+      </c>
+    </row>
+    <row r="7385" spans="1:1">
+      <c r="A7385" s="3" t="s">
+        <v>3496</v>
+      </c>
+    </row>
+    <row r="7386" spans="1:1">
+      <c r="A7386" s="3" t="s">
+        <v>3499</v>
+      </c>
+    </row>
+    <row r="7387" spans="1:1">
+      <c r="A7387" s="3" t="s">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="7388" spans="1:1">
+      <c r="A7388" s="3" t="s">
+        <v>3501</v>
+      </c>
+    </row>
+    <row r="7389" spans="1:1">
+      <c r="A7389" s="3" t="s">
+        <v>3502</v>
+      </c>
+    </row>
+    <row r="7390" spans="1:1">
+      <c r="A7390" s="3" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="7391" spans="1:1">
+      <c r="A7391" s="3" t="s">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="7392" spans="1:1">
+      <c r="A7392" s="3" t="s">
+        <v>3498</v>
+      </c>
+    </row>
+    <row r="7393" spans="1:1">
+      <c r="A7393" s="3" t="s">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="7394" spans="1:1">
+      <c r="A7394" s="3" t="s">
+        <v>3503</v>
+      </c>
+    </row>
+    <row r="7395" spans="1:1">
+      <c r="A7395" s="3" t="s">
+        <v>3504</v>
+      </c>
+    </row>
+    <row r="7396" spans="1:1">
+      <c r="A7396" s="3" t="s">
+        <v>3505</v>
+      </c>
+    </row>
+    <row r="7397" spans="1:1">
+      <c r="A7397" s="3" t="s">
+        <v>3506</v>
+      </c>
+    </row>
+    <row r="7398" spans="1:1">
+      <c r="A7398" s="3" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="7399" spans="1:1">
+      <c r="A7399" s="3" t="s">
+        <v>3507</v>
+      </c>
+    </row>
+    <row r="7400" spans="1:1">
+      <c r="A7400" s="3" t="s">
+        <v>3508</v>
+      </c>
+    </row>
+    <row r="7401" spans="1:1">
+      <c r="A7401" s="3" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="7402" spans="1:1">
+      <c r="A7402" s="3" t="s">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="7403" spans="1:1">
+      <c r="A7403" s="3" t="s">
+        <v>3509</v>
+      </c>
+    </row>
+    <row r="7404" spans="1:1">
+      <c r="A7404" s="3" t="s">
+        <v>3511</v>
+      </c>
+    </row>
+    <row r="7405" spans="1:1">
+      <c r="A7405" s="3" t="s">
+        <v>3512</v>
+      </c>
+    </row>
+    <row r="7406" spans="1:1">
+      <c r="A7406" s="3" t="s">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="7407" spans="1:1">
+      <c r="A7407" s="3" t="s">
+        <v>3510</v>
+      </c>
+    </row>
+    <row r="7408" spans="1:1">
+      <c r="A7408" s="3" t="s">
+        <v>3515</v>
+      </c>
+    </row>
+    <row r="7409" spans="1:1">
+      <c r="A7409" s="3" t="s">
+        <v>3514</v>
+      </c>
+    </row>
+    <row r="7410" spans="1:1">
+      <c r="A7410" s="3" t="s">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="7411" spans="1:1">
+      <c r="A7411" s="3" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="7412" spans="1:1">
+      <c r="A7412" s="3" t="s">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="7413" spans="1:1">
+      <c r="A7413" s="3" t="s">
+        <v>3517</v>
+      </c>
+    </row>
+    <row r="7414" spans="1:1">
+      <c r="A7414" s="3" t="s">
+        <v>3518</v>
+      </c>
+    </row>
+    <row r="7415" spans="1:1">
+      <c r="A7415" s="3" t="s">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="7416" spans="1:1">
+      <c r="A7416" s="3" t="s">
+        <v>3516</v>
+      </c>
+    </row>
+    <row r="7417" spans="1:1">
+      <c r="A7417" s="3" t="s">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="7418" spans="1:1">
+      <c r="A7418" s="3" t="s">
+        <v>3519</v>
+      </c>
+    </row>
+    <row r="7419" spans="1:1">
+      <c r="A7419" s="3" t="s">
+        <v>3521</v>
+      </c>
+    </row>
+    <row r="7420" spans="1:1">
+      <c r="A7420" s="3" t="s">
+        <v>3522</v>
+      </c>
+    </row>
+    <row r="7421" spans="1:1">
+      <c r="A7421" s="3" t="s">
+        <v>3520</v>
+      </c>
+    </row>
+    <row r="7422" spans="1:1">
+      <c r="A7422" s="3" t="s">
+        <v>3523</v>
+      </c>
+    </row>
+    <row r="7423" spans="1:1">
+      <c r="A7423" s="3" t="s">
+        <v>3524</v>
+      </c>
+    </row>
+    <row r="7424" spans="1:1">
+      <c r="A7424" s="3" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="7425" spans="1:1">
+      <c r="A7425" s="3" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="7426" spans="1:1">
+      <c r="A7426" s="3" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="7427" spans="1:1">
+      <c r="A7427" s="3" t="s">
+        <v>3525</v>
+      </c>
+    </row>
+    <row r="7428" spans="1:1">
+      <c r="A7428" s="3" t="s">
+        <v>3526</v>
+      </c>
+    </row>
+    <row r="7429" spans="1:1">
+      <c r="A7429" s="3" t="s">
+        <v>3527</v>
+      </c>
+    </row>
+    <row r="7430" spans="1:1">
+      <c r="A7430" s="3" t="s">
+        <v>3528</v>
+      </c>
+    </row>
+    <row r="7431" spans="1:1">
+      <c r="A7431" s="3" t="s">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="7432" spans="1:1">
+      <c r="A7432" s="3" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="7433" spans="1:1">
+      <c r="A7433" s="3" t="s">
+        <v>3529</v>
+      </c>
+    </row>
+    <row r="7434" spans="1:1">
+      <c r="A7434" s="3" t="s">
+        <v>3530</v>
+      </c>
+    </row>
+    <row r="7435" spans="1:1">
+      <c r="A7435" s="3" t="s">
+        <v>3531</v>
+      </c>
+    </row>
+    <row r="7436" spans="1:1">
+      <c r="A7436" s="3" t="s">
+        <v>3532</v>
+      </c>
+    </row>
+    <row r="7437" spans="1:1">
+      <c r="A7437" s="3" t="s">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="7438" spans="1:1">
+      <c r="A7438" s="3" t="s">
+        <v>3533</v>
+      </c>
+    </row>
+    <row r="7439" spans="1:1">
+      <c r="A7439" s="3" t="s">
+        <v>3534</v>
+      </c>
+    </row>
+    <row r="7440" spans="1:1">
+      <c r="A7440" s="3" t="s">
+        <v>3537</v>
+      </c>
+    </row>
+    <row r="7441" spans="1:1">
+      <c r="A7441" s="3" t="s">
+        <v>3536</v>
+      </c>
+    </row>
+    <row r="7442" spans="1:1">
+      <c r="A7442" s="3" t="s">
+        <v>3535</v>
+      </c>
+    </row>
+    <row r="7443" spans="1:1">
+      <c r="A7443" s="3" t="s">
+        <v>3538</v>
+      </c>
+    </row>
+    <row r="7444" spans="1:1">
+      <c r="A7444" s="3" t="s">
+        <v>3539</v>
+      </c>
+    </row>
+    <row r="7445" spans="1:1">
+      <c r="A7445" s="3" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="7446" spans="1:1">
+      <c r="A7446" s="3" t="s">
+        <v>3540</v>
+      </c>
+    </row>
+    <row r="7447" spans="1:1">
+      <c r="A7447" s="3" t="s">
+        <v>3541</v>
+      </c>
+    </row>
+    <row r="7448" spans="1:1">
+      <c r="A7448" s="3" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="7449" spans="1:1">
+      <c r="A7449" s="3" t="s">
+        <v>3542</v>
+      </c>
+    </row>
+    <row r="7450" spans="1:1">
+      <c r="A7450" s="3" t="s">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="7451" spans="1:1">
+      <c r="A7451" s="3" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="7452" spans="1:1">
+      <c r="A7452" s="3" t="s">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="7453" spans="1:1">
+      <c r="A7453" s="3" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="7454" spans="1:1">
+      <c r="A7454" s="3" t="s">
+        <v>3544</v>
+      </c>
+    </row>
+    <row r="7455" spans="1:1">
+      <c r="A7455" s="3" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="7456" spans="1:1">
+      <c r="A7456" s="3" t="s">
+        <v>3545</v>
+      </c>
+    </row>
+    <row r="7457" spans="1:1">
+      <c r="A7457" s="3" t="s">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="7458" spans="1:1">
+      <c r="A7458" s="3" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="7459" spans="1:1">
+      <c r="A7459" s="3" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="7460" spans="1:1">
+      <c r="A7460" s="3" t="s">
+        <v>3546</v>
+      </c>
+    </row>
+    <row r="7461" spans="1:1">
+      <c r="A7461" s="3" t="s">
+        <v>3547</v>
+      </c>
+    </row>
+    <row r="7462" spans="1:1">
+      <c r="A7462" s="3" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="7463" spans="1:1">
+      <c r="A7463" s="3" t="s">
+        <v>3548</v>
+      </c>
+    </row>
+    <row r="7464" spans="1:1">
+      <c r="A7464" s="3" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="7465" spans="1:1">
+      <c r="A7465" s="3" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="7466" spans="1:1">
+      <c r="A7466" s="3" t="s">
+        <v>4035</v>
+      </c>
+    </row>
+    <row r="7467" spans="1:1">
+      <c r="A7467" s="3" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="7468" spans="1:1">
+      <c r="A7468" s="3" t="s">
+        <v>3549</v>
+      </c>
+    </row>
+    <row r="7469" spans="1:1">
+      <c r="A7469" s="3" t="s">
+        <v>2587</v>
+      </c>
+    </row>
+    <row r="7470" spans="1:1">
+      <c r="A7470" s="3" t="s">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="7471" spans="1:1">
+      <c r="A7471" s="3" t="s">
+        <v>3551</v>
+      </c>
+    </row>
+    <row r="7472" spans="1:1">
+      <c r="A7472" s="3" t="s">
+        <v>3550</v>
+      </c>
+    </row>
+    <row r="7473" spans="1:1">
+      <c r="A7473" s="3" t="s">
+        <v>3552</v>
+      </c>
+    </row>
+    <row r="7474" spans="1:1">
+      <c r="A7474" s="3" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="7475" spans="1:1">
+      <c r="A7475" s="3" t="s">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="7476" spans="1:1">
+      <c r="A7476" s="3" t="s">
+        <v>3553</v>
+      </c>
+    </row>
+    <row r="7477" spans="1:1">
+      <c r="A7477" s="3" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="7478" spans="1:1">
+      <c r="A7478" s="3" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="7479" spans="1:1">
+      <c r="A7479" s="3" t="s">
+        <v>3555</v>
+      </c>
+    </row>
+    <row r="7480" spans="1:1">
+      <c r="A7480" s="3" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="7481" spans="1:1">
+      <c r="A7481" s="3" t="s">
+        <v>3554</v>
+      </c>
+    </row>
+    <row r="7482" spans="1:1">
+      <c r="A7482" s="3" t="s">
+        <v>4036</v>
+      </c>
+    </row>
+    <row r="7483" spans="1:1">
+      <c r="A7483" s="3" t="s">
+        <v>3556</v>
+      </c>
+    </row>
+    <row r="7484" spans="1:1">
+      <c r="A7484" s="3" t="s">
+        <v>3557</v>
+      </c>
+    </row>
+    <row r="7485" spans="1:1">
+      <c r="A7485" s="3" t="s">
+        <v>3558</v>
+      </c>
+    </row>
+    <row r="7486" spans="1:1">
+      <c r="A7486" s="3" t="s">
+        <v>3560</v>
+      </c>
+    </row>
+    <row r="7487" spans="1:1">
+      <c r="A7487" s="3" t="s">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="7488" spans="1:1">
+      <c r="A7488" s="3" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="7489" spans="1:1">
+      <c r="A7489" s="3" t="s">
+        <v>3559</v>
+      </c>
+    </row>
+    <row r="7490" spans="1:1">
+      <c r="A7490" s="3" t="s">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="7491" spans="1:1">
+      <c r="A7491" s="3" t="s">
+        <v>3561</v>
+      </c>
+    </row>
+    <row r="7492" spans="1:1">
+      <c r="A7492" s="3" t="s">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="7493" spans="1:1">
+      <c r="A7493" s="3" t="s">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="7494" spans="1:1">
+      <c r="A7494" s="3" t="s">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="7495" spans="1:1">
+      <c r="A7495" s="3" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="7496" spans="1:1">
+      <c r="A7496" s="3" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="7497" spans="1:1">
+      <c r="A7497" s="3" t="s">
+        <v>3562</v>
+      </c>
+    </row>
+    <row r="7498" spans="1:1">
+      <c r="A7498" s="3" t="s">
+        <v>3563</v>
+      </c>
+    </row>
+    <row r="7499" spans="1:1">
+      <c r="A7499" s="3" t="s">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="7500" spans="1:1">
+      <c r="A7500" s="3" t="s">
+        <v>3566</v>
+      </c>
+    </row>
+    <row r="7501" spans="1:1">
+      <c r="A7501" s="3" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="7502" spans="1:1">
+      <c r="A7502" s="3" t="s">
+        <v>3564</v>
+      </c>
+    </row>
+    <row r="7503" spans="1:1">
+      <c r="A7503" s="3" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="7504" spans="1:1">
+      <c r="A7504" s="3" t="s">
+        <v>3565</v>
+      </c>
+    </row>
+    <row r="7505" spans="1:1">
+      <c r="A7505" s="3" t="s">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="7506" spans="1:1">
+      <c r="A7506" s="3" t="s">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="7507" spans="1:1">
+      <c r="A7507" s="3" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="7508" spans="1:1">
+      <c r="A7508" s="3" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="7509" spans="1:1">
+      <c r="A7509" s="3" t="s">
+        <v>3567</v>
+      </c>
+    </row>
+    <row r="7510" spans="1:1">
+      <c r="A7510" s="3" t="s">
+        <v>3568</v>
+      </c>
+    </row>
+    <row r="7511" spans="1:1">
+      <c r="A7511" s="3" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="7512" spans="1:1">
+      <c r="A7512" s="3" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="7513" spans="1:1">
+      <c r="A7513" s="3" t="s">
+        <v>3569</v>
+      </c>
+    </row>
+    <row r="7514" spans="1:1">
+      <c r="A7514" s="3" t="s">
+        <v>3570</v>
+      </c>
+    </row>
+    <row r="7515" spans="1:1">
+      <c r="A7515" s="3" t="s">
+        <v>3572</v>
+      </c>
+    </row>
+    <row r="7516" spans="1:1">
+      <c r="A7516" s="3" t="s">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="7517" spans="1:1">
+      <c r="A7517" s="3" t="s">
+        <v>3571</v>
+      </c>
+    </row>
+    <row r="7518" spans="1:1">
+      <c r="A7518" s="3" t="s">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="7519" spans="1:1">
+      <c r="A7519" s="3" t="s">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="7520" spans="1:1">
+      <c r="A7520" s="3" t="s">
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="7521" spans="1:1">
+      <c r="A7521" s="3" t="s">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="7522" spans="1:1">
+      <c r="A7522" s="3" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="7523" spans="1:1">
+      <c r="A7523" s="3" t="s">
+        <v>3574</v>
+      </c>
+    </row>
+    <row r="7524" spans="1:1">
+      <c r="A7524" s="3" t="s">
+        <v>3573</v>
+      </c>
+    </row>
+    <row r="7525" spans="1:1">
+      <c r="A7525" s="3" t="s">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="7526" spans="1:1">
+      <c r="A7526" s="3" t="s">
+        <v>4037</v>
+      </c>
+    </row>
+    <row r="7527" spans="1:1">
+      <c r="A7527" s="3" t="s">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="7528" spans="1:1">
+      <c r="A7528" s="3" t="s">
+        <v>3576</v>
+      </c>
+    </row>
+    <row r="7529" spans="1:1">
+      <c r="A7529" s="3" t="s">
+        <v>3577</v>
+      </c>
+    </row>
+    <row r="7530" spans="1:1">
+      <c r="A7530" s="3" t="s">
+        <v>3578</v>
+      </c>
+    </row>
+    <row r="7531" spans="1:1">
+      <c r="A7531" s="3" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="7532" spans="1:1">
+      <c r="A7532" s="3" t="s">
+        <v>3579</v>
+      </c>
+    </row>
+    <row r="7533" spans="1:1">
+      <c r="A7533" s="3" t="s">
+        <v>3580</v>
+      </c>
+    </row>
+    <row r="7534" spans="1:1">
+      <c r="A7534" s="3" t="s">
+        <v>3581</v>
+      </c>
+    </row>
+    <row r="7535" spans="1:1">
+      <c r="A7535" s="3" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="7536" spans="1:1">
+      <c r="A7536" s="3" t="s">
+        <v>3583</v>
+      </c>
+    </row>
+    <row r="7537" spans="1:1">
+      <c r="A7537" s="3" t="s">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="7538" spans="1:1">
+      <c r="A7538" s="3" t="s">
+        <v>3582</v>
+      </c>
+    </row>
+    <row r="7539" spans="1:1">
+      <c r="A7539" s="3" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="7540" spans="1:1">
+      <c r="A7540" s="3" t="s">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="7541" spans="1:1">
+      <c r="A7541" s="3" t="s">
+        <v>3585</v>
+      </c>
+    </row>
+    <row r="7542" spans="1:1">
+      <c r="A7542" s="3" t="s">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="7543" spans="1:1">
+      <c r="A7543" s="3" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="7544" spans="1:1">
+      <c r="A7544" s="3" t="s">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="7545" spans="1:1">
+      <c r="A7545" s="3" t="s">
+        <v>3586</v>
+      </c>
+    </row>
+    <row r="7546" spans="1:1">
+      <c r="A7546" s="3" t="s">
+        <v>2693</v>
+      </c>
+    </row>
+    <row r="7547" spans="1:1">
+      <c r="A7547" s="3" t="s">
+        <v>3587</v>
+      </c>
+    </row>
+    <row r="7548" spans="1:1">
+      <c r="A7548" s="3" t="s">
+        <v>3588</v>
+      </c>
+    </row>
+    <row r="7549" spans="1:1">
+      <c r="A7549" s="3" t="s">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="7550" spans="1:1">
+      <c r="A7550" s="3" t="s">
+        <v>3589</v>
+      </c>
+    </row>
+    <row r="7551" spans="1:1">
+      <c r="A7551" s="3" t="s">
+        <v>3591</v>
+      </c>
+    </row>
+    <row r="7552" spans="1:1">
+      <c r="A7552" s="3" t="s">
+        <v>3592</v>
+      </c>
+    </row>
+    <row r="7553" spans="1:1">
+      <c r="A7553" s="3" t="s">
+        <v>3593</v>
+      </c>
+    </row>
+    <row r="7554" spans="1:1">
+      <c r="A7554" s="3" t="s">
+        <v>3595</v>
+      </c>
+    </row>
+    <row r="7555" spans="1:1">
+      <c r="A7555" s="3" t="s">
+        <v>3594</v>
+      </c>
+    </row>
+    <row r="7556" spans="1:1">
+      <c r="A7556" s="3" t="s">
+        <v>3596</v>
+      </c>
+    </row>
+    <row r="7557" spans="1:1">
+      <c r="A7557" s="3" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="7558" spans="1:1">
+      <c r="A7558" s="3" t="s">
+        <v>3597</v>
+      </c>
+    </row>
+    <row r="7559" spans="1:1">
+      <c r="A7559" s="3" t="s">
+        <v>3598</v>
+      </c>
+    </row>
+    <row r="7560" spans="1:1">
+      <c r="A7560" s="3" t="s">
+        <v>3599</v>
+      </c>
+    </row>
+    <row r="7561" spans="1:1">
+      <c r="A7561" s="3" t="s">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="7562" spans="1:1">
+      <c r="A7562" s="3" t="s">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="7563" spans="1:1">
+      <c r="A7563" s="3" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="7564" spans="1:1">
+      <c r="A7564" s="3" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="7565" spans="1:1">
+      <c r="A7565" s="3" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="7566" spans="1:1">
+      <c r="A7566" s="3" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="7567" spans="1:1">
+      <c r="A7567" s="3" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="7568" spans="1:1">
+      <c r="A7568" s="3" t="s">
+        <v>3602</v>
+      </c>
+    </row>
+    <row r="7569" spans="1:1">
+      <c r="A7569" s="3" t="s">
+        <v>3603</v>
+      </c>
+    </row>
+    <row r="7570" spans="1:1">
+      <c r="A7570" s="3" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="7571" spans="1:1">
+      <c r="A7571" s="3" t="s">
+        <v>2474</v>
+      </c>
+    </row>
+    <row r="7572" spans="1:1">
+      <c r="A7572" s="3" t="s">
+        <v>3604</v>
+      </c>
+    </row>
+    <row r="7573" spans="1:1">
+      <c r="A7573" s="3" t="s">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="7574" spans="1:1">
+      <c r="A7574" s="3" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="7575" spans="1:1">
+      <c r="A7575" s="3" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="7576" spans="1:1">
+      <c r="A7576" s="3" t="s">
+        <v>3605</v>
+      </c>
+    </row>
+    <row r="7577" spans="1:1">
+      <c r="A7577" s="3" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="7578" spans="1:1">
+      <c r="A7578" s="3" t="s">
+        <v>3606</v>
+      </c>
+    </row>
+    <row r="7579" spans="1:1">
+      <c r="A7579" s="3" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="7580" spans="1:1">
+      <c r="A7580" s="3" t="s">
+        <v>3608</v>
+      </c>
+    </row>
+    <row r="7581" spans="1:1">
+      <c r="A7581" s="3" t="s">
+        <v>3613</v>
+      </c>
+    </row>
+    <row r="7582" spans="1:1">
+      <c r="A7582" s="3" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="7583" spans="1:1">
+      <c r="A7583" s="3" t="s">
+        <v>3612</v>
+      </c>
+    </row>
+    <row r="7584" spans="1:1">
+      <c r="A7584" s="3" t="s">
+        <v>2692</v>
+      </c>
+    </row>
+    <row r="7585" spans="1:1">
+      <c r="A7585" s="3" t="s">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="7586" spans="1:1">
+      <c r="A7586" s="3" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="7587" spans="1:1">
+      <c r="A7587" s="3" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="7588" spans="1:1">
+      <c r="A7588" s="3" t="s">
+        <v>3615</v>
+      </c>
+    </row>
+    <row r="7589" spans="1:1">
+      <c r="A7589" s="3" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="7590" spans="1:1">
+      <c r="A7590" s="3" t="s">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="7591" spans="1:1">
+      <c r="A7591" s="3" t="s">
+        <v>3616</v>
+      </c>
+    </row>
+    <row r="7592" spans="1:1">
+      <c r="A7592" s="3" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="7593" spans="1:1">
+      <c r="A7593" s="3" t="s">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="7594" spans="1:1">
+      <c r="A7594" s="3" t="s">
+        <v>3617</v>
+      </c>
+    </row>
+    <row r="7595" spans="1:1">
+      <c r="A7595" s="3" t="s">
+        <v>2293</v>
+      </c>
+    </row>
+    <row r="7596" spans="1:1">
+      <c r="A7596" s="3" t="s">
+        <v>3618</v>
+      </c>
+    </row>
+    <row r="7597" spans="1:1">
+      <c r="A7597" s="3" t="s">
+        <v>3619</v>
+      </c>
+    </row>
+    <row r="7598" spans="1:1">
+      <c r="A7598" s="3" t="s">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="7599" spans="1:1">
+      <c r="A7599" s="3" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="7600" spans="1:1">
+      <c r="A7600" s="3" t="s">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="7601" spans="1:1">
+      <c r="A7601" s="3" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="7602" spans="1:1">
+      <c r="A7602" s="3" t="s">
+        <v>3620</v>
+      </c>
+    </row>
+    <row r="7603" spans="1:1">
+      <c r="A7603" s="3" t="s">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="7604" spans="1:1">
+      <c r="A7604" s="3" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="7605" spans="1:1">
+      <c r="A7605" s="3" t="s">
+        <v>3621</v>
+      </c>
+    </row>
+    <row r="7606" spans="1:1">
+      <c r="A7606" s="3" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="7607" spans="1:1">
+      <c r="A7607" s="3" t="s">
+        <v>3623</v>
+      </c>
+    </row>
+    <row r="7608" spans="1:1">
+      <c r="A7608" s="3" t="s">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="7609" spans="1:1">
+      <c r="A7609" s="3" t="s">
+        <v>3624</v>
+      </c>
+    </row>
+    <row r="7610" spans="1:1">
+      <c r="A7610" s="3" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="7611" spans="1:1">
+      <c r="A7611" s="3" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="7612" spans="1:1">
+      <c r="A7612" s="3" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="7613" spans="1:1">
+      <c r="A7613" s="3" t="s">
+        <v>3626</v>
+      </c>
+    </row>
+    <row r="7614" spans="1:1">
+      <c r="A7614" s="3" t="s">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="7615" spans="1:1">
+      <c r="A7615" s="3" t="s">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="7616" spans="1:1">
+      <c r="A7616" s="3" t="s">
+        <v>3627</v>
+      </c>
+    </row>
+    <row r="7617" spans="1:1">
+      <c r="A7617" s="3" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="7618" spans="1:1">
+      <c r="A7618" s="3" t="s">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="7619" spans="1:1">
+      <c r="A7619" s="3" t="s">
+        <v>3628</v>
+      </c>
+    </row>
+    <row r="7620" spans="1:1">
+      <c r="A7620" s="3" t="s">
+        <v>3630</v>
+      </c>
+    </row>
+    <row r="7621" spans="1:1">
+      <c r="A7621" s="3" t="s">
+        <v>3632</v>
+      </c>
+    </row>
+    <row r="7622" spans="1:1">
+      <c r="A7622" s="3" t="s">
+        <v>3631</v>
+      </c>
+    </row>
+    <row r="7623" spans="1:1">
+      <c r="A7623" s="3" t="s">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="7624" spans="1:1">
+      <c r="A7624" s="3" t="s">
+        <v>3629</v>
+      </c>
+    </row>
+    <row r="7625" spans="1:1">
+      <c r="A7625" s="3" t="s">
+        <v>3633</v>
+      </c>
+    </row>
+    <row r="7626" spans="1:1">
+      <c r="A7626" s="3" t="s">
+        <v>3634</v>
+      </c>
+    </row>
+    <row r="7627" spans="1:1">
+      <c r="A7627" s="3" t="s">
+        <v>3635</v>
+      </c>
+    </row>
+    <row r="7628" spans="1:1">
+      <c r="A7628" s="3" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="7629" spans="1:1">
+      <c r="A7629" s="3" t="s">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="7630" spans="1:1">
+      <c r="A7630" s="3" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="7631" spans="1:1">
+      <c r="A7631" s="3" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="7632" spans="1:1">
+      <c r="A7632" s="3" t="s">
+        <v>3636</v>
+      </c>
+    </row>
+    <row r="7633" spans="1:1">
+      <c r="A7633" s="3" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="7634" spans="1:1">
+      <c r="A7634" s="3" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="7635" spans="1:1">
+      <c r="A7635" s="3" t="s">
+        <v>3637</v>
+      </c>
+    </row>
+    <row r="7636" spans="1:1">
+      <c r="A7636" s="3" t="s">
+        <v>3638</v>
+      </c>
+    </row>
+    <row r="7637" spans="1:1">
+      <c r="A7637" s="3" t="s">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="7638" spans="1:1">
+      <c r="A7638" s="3" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="7639" spans="1:1">
+      <c r="A7639" s="3" t="s">
+        <v>3643</v>
+      </c>
+    </row>
+    <row r="7640" spans="1:1">
+      <c r="A7640" s="3" t="s">
+        <v>3645</v>
+      </c>
+    </row>
+    <row r="7641" spans="1:1">
+      <c r="A7641" s="3" t="s">
+        <v>3641</v>
+      </c>
+    </row>
+    <row r="7642" spans="1:1">
+      <c r="A7642" s="3" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="7643" spans="1:1">
+      <c r="A7643" s="3" t="s">
+        <v>3644</v>
+      </c>
+    </row>
+    <row r="7644" spans="1:1">
+      <c r="A7644" s="3" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="7645" spans="1:1">
+      <c r="A7645" s="3" t="s">
+        <v>3642</v>
+      </c>
+    </row>
+    <row r="7646" spans="1:1">
+      <c r="A7646" s="3" t="s">
+        <v>3646</v>
+      </c>
+    </row>
+    <row r="7647" spans="1:1">
+      <c r="A7647" s="3" t="s">
+        <v>2517</v>
+      </c>
+    </row>
+    <row r="7648" spans="1:1">
+      <c r="A7648" s="3" t="s">
+        <v>3647</v>
+      </c>
+    </row>
+    <row r="7649" spans="1:1">
+      <c r="A7649" s="3" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="7650" spans="1:1">
+      <c r="A7650" s="3" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="7651" spans="1:1">
+      <c r="A7651" s="3" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="7652" spans="1:1">
+      <c r="A7652" s="3" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="7653" spans="1:1">
+      <c r="A7653" s="3" t="s">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="7654" spans="1:1">
+      <c r="A7654" s="3" t="s">
+        <v>3649</v>
+      </c>
+    </row>
+    <row r="7655" spans="1:1">
+      <c r="A7655" s="3" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="7656" spans="1:1">
+      <c r="A7656" s="3" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="7657" spans="1:1">
+      <c r="A7657" s="3" t="s">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="7658" spans="1:1">
+      <c r="A7658" s="3" t="s">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="7659" spans="1:1">
+      <c r="A7659" s="3" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="7660" spans="1:1">
+      <c r="A7660" s="3" t="s">
+        <v>3651</v>
+      </c>
+    </row>
+    <row r="7661" spans="1:1">
+      <c r="A7661" s="3" t="s">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="7662" spans="1:1">
+      <c r="A7662" s="3" t="s">
+        <v>3652</v>
+      </c>
+    </row>
+    <row r="7663" spans="1:1">
+      <c r="A7663" s="3" t="s">
+        <v>2536</v>
+      </c>
+    </row>
+    <row r="7664" spans="1:1">
+      <c r="A7664" s="3" t="s">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="7665" spans="1:1">
+      <c r="A7665" s="3" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="7666" spans="1:1">
+      <c r="A7666" s="3" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="7667" spans="1:1">
+      <c r="A7667" s="3" t="s">
+        <v>2533</v>
+      </c>
+    </row>
+    <row r="7668" spans="1:1">
+      <c r="A7668" s="3" t="s">
+        <v>3653</v>
+      </c>
+    </row>
+    <row r="7669" spans="1:1">
+      <c r="A7669" s="3" t="s">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="7670" spans="1:1">
+      <c r="A7670" s="3" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="7671" spans="1:1">
+      <c r="A7671" s="3" t="s">
+        <v>2612</v>
+      </c>
+    </row>
+    <row r="7672" spans="1:1">
+      <c r="A7672" s="3" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="7673" spans="1:1">
+      <c r="A7673" s="3" t="s">
+        <v>3654</v>
+      </c>
+    </row>
+    <row r="7674" spans="1:1">
+      <c r="A7674" s="3" t="s">
+        <v>3655</v>
+      </c>
+    </row>
+    <row r="7675" spans="1:1">
+      <c r="A7675" s="3" t="s">
+        <v>3656</v>
+      </c>
+    </row>
+    <row r="7676" spans="1:1">
+      <c r="A7676" s="3" t="s">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="7677" spans="1:1">
+      <c r="A7677" s="3" t="s">
+        <v>3657</v>
+      </c>
+    </row>
+    <row r="7678" spans="1:1">
+      <c r="A7678" s="3" t="s">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="7679" spans="1:1">
+      <c r="A7679" s="3" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="7680" spans="1:1">
+      <c r="A7680" s="3" t="s">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="7681" spans="1:1">
+      <c r="A7681" s="3" t="s">
+        <v>3658</v>
+      </c>
+    </row>
+    <row r="7682" spans="1:1">
+      <c r="A7682" s="3" t="s">
+        <v>3659</v>
+      </c>
+    </row>
+    <row r="7683" spans="1:1">
+      <c r="A7683" s="3" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="7684" spans="1:1">
+      <c r="A7684" s="3" t="s">
+        <v>3660</v>
+      </c>
+    </row>
+    <row r="7685" spans="1:1">
+      <c r="A7685" s="3" t="s">
+        <v>3661</v>
+      </c>
+    </row>
+    <row r="7686" spans="1:1">
+      <c r="A7686" s="3" t="s">
+        <v>3662</v>
+      </c>
+    </row>
+    <row r="7687" spans="1:1">
+      <c r="A7687" s="3" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="7688" spans="1:1">
+      <c r="A7688" s="3" t="s">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="7689" spans="1:1">
+      <c r="A7689" s="3" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="7690" spans="1:1">
+      <c r="A7690" s="3" t="s">
+        <v>3663</v>
+      </c>
+    </row>
+    <row r="7691" spans="1:1">
+      <c r="A7691" s="3" t="s">
+        <v>3664</v>
+      </c>
+    </row>
+    <row r="7692" spans="1:1">
+      <c r="A7692" s="3" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="7693" spans="1:1">
+      <c r="A7693" s="3" t="s">
+        <v>3648</v>
+      </c>
+    </row>
+    <row r="7694" spans="1:1">
+      <c r="A7694" s="3" t="s">
+        <v>3669</v>
+      </c>
+    </row>
+    <row r="7695" spans="1:1">
+      <c r="A7695" s="3" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="7696" spans="1:1">
+      <c r="A7696" s="3" t="s">
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="7697" spans="1:1">
+      <c r="A7697" s="3" t="s">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="7698" spans="1:1">
+      <c r="A7698" s="3" t="s">
+        <v>3668</v>
+      </c>
+    </row>
+    <row r="7699" spans="1:1">
+      <c r="A7699" s="3" t="s">
+        <v>3667</v>
+      </c>
+    </row>
+    <row r="7700" spans="1:1">
+      <c r="A7700" s="3" t="s">
+        <v>3666</v>
+      </c>
+    </row>
+    <row r="7701" spans="1:1">
+      <c r="A7701" s="3" t="s">
+        <v>3665</v>
+      </c>
+    </row>
+    <row r="7702" spans="1:1">
+      <c r="A7702" s="3" t="s">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="7703" spans="1:1">
+      <c r="A7703" s="3" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="7704" spans="1:1">
+      <c r="A7704" s="3" t="s">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="7705" spans="1:1">
+      <c r="A7705" s="3" t="s">
+        <v>3674</v>
+      </c>
+    </row>
+    <row r="7706" spans="1:1">
+      <c r="A7706" s="3" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="7707" spans="1:1">
+      <c r="A7707" s="3" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="7708" spans="1:1">
+      <c r="A7708" s="3" t="s">
+        <v>3673</v>
+      </c>
+    </row>
+    <row r="7709" spans="1:1">
+      <c r="A7709" s="3" t="s">
+        <v>3672</v>
+      </c>
+    </row>
+    <row r="7710" spans="1:1">
+      <c r="A7710" s="3" t="s">
+        <v>3671</v>
+      </c>
+    </row>
+    <row r="7711" spans="1:1">
+      <c r="A7711" s="3" t="s">
+        <v>3670</v>
+      </c>
+    </row>
+    <row r="7712" spans="1:1">
+      <c r="A7712" s="3" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="7713" spans="1:1">
+      <c r="A7713" s="3" t="s">
+        <v>3675</v>
+      </c>
+    </row>
+    <row r="7714" spans="1:1">
+      <c r="A7714" s="3" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="7715" spans="1:1">
+      <c r="A7715" s="3" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="7716" spans="1:1">
+      <c r="A7716" s="3" t="s">
+        <v>3678</v>
+      </c>
+    </row>
+    <row r="7717" spans="1:1">
+      <c r="A7717" s="3" t="s">
+        <v>3677</v>
+      </c>
+    </row>
+    <row r="7718" spans="1:1">
+      <c r="A7718" s="3" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="7719" spans="1:1">
+      <c r="A7719" s="3" t="s">
+        <v>3676</v>
+      </c>
+    </row>
+    <row r="7720" spans="1:1">
+      <c r="A7720" s="3" t="s">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="7721" spans="1:1">
+      <c r="A7721" s="3" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="7722" spans="1:1">
+      <c r="A7722" s="3" t="s">
+        <v>3680</v>
+      </c>
+    </row>
+    <row r="7723" spans="1:1">
+      <c r="A7723" s="3" t="s">
+        <v>3679</v>
+      </c>
+    </row>
+    <row r="7724" spans="1:1">
+      <c r="A7724" s="3" t="s">
+        <v>3681</v>
+      </c>
+    </row>
+    <row r="7725" spans="1:1">
+      <c r="A7725" s="3" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="7726" spans="1:1">
+      <c r="A7726" s="3" t="s">
+        <v>3683</v>
+      </c>
+    </row>
+    <row r="7727" spans="1:1">
+      <c r="A7727" s="3" t="s">
+        <v>3682</v>
+      </c>
+    </row>
+    <row r="7728" spans="1:1">
+      <c r="A7728" s="3" t="s">
+        <v>3685</v>
+      </c>
+    </row>
+    <row r="7729" spans="1:1">
+      <c r="A7729" s="3" t="s">
+        <v>3684</v>
+      </c>
+    </row>
+    <row r="7730" spans="1:1">
+      <c r="A7730" s="3" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="7731" spans="1:1">
+      <c r="A7731" s="3" t="s">
+        <v>3686</v>
+      </c>
+    </row>
+    <row r="7732" spans="1:1">
+      <c r="A7732" s="3" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="7733" spans="1:1">
+      <c r="A7733" s="3" t="s">
+        <v>3687</v>
+      </c>
+    </row>
+    <row r="7734" spans="1:1">
+      <c r="A7734" s="3" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="7735" spans="1:1">
+      <c r="A7735" s="3" t="s">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="7736" spans="1:1">
+      <c r="A7736" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7737" spans="1:1">
+      <c r="A7737" s="3" t="s">
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="7738" spans="1:1">
+      <c r="A7738" s="3" t="s">
+        <v>3689</v>
+      </c>
+    </row>
+    <row r="7739" spans="1:1">
+      <c r="A7739" s="3" t="s">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="7740" spans="1:1">
+      <c r="A7740" s="3" t="s">
+        <v>3688</v>
+      </c>
+    </row>
+    <row r="7741" spans="1:1">
+      <c r="A7741" s="3" t="s">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="7742" spans="1:1">
+      <c r="A7742" s="3" t="s">
+        <v>3690</v>
+      </c>
+    </row>
+    <row r="7743" spans="1:1">
+      <c r="A7743" s="3" t="s">
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="7744" spans="1:1">
+      <c r="A7744" s="3" t="s">
+        <v>3691</v>
+      </c>
+    </row>
+    <row r="7745" spans="1:1">
+      <c r="A7745" s="3" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="7746" spans="1:1">
+      <c r="A7746" s="3" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="7747" spans="1:1">
+      <c r="A7747" s="3" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="7748" spans="1:1">
+      <c r="A7748" s="3" t="s">
+        <v>3692</v>
+      </c>
+    </row>
+    <row r="7749" spans="1:1">
+      <c r="A7749" s="3" t="s">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="7750" spans="1:1">
+      <c r="A7750" s="3" t="s">
+        <v>3695</v>
+      </c>
+    </row>
+    <row r="7751" spans="1:1">
+      <c r="A7751" s="3" t="s">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="7752" spans="1:1">
+      <c r="A7752" s="3" t="s">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="7753" spans="1:1">
+      <c r="A7753" s="3" t="s">
+        <v>3693</v>
+      </c>
+    </row>
+    <row r="7754" spans="1:1">
+      <c r="A7754" s="3" t="s">
+        <v>3694</v>
+      </c>
+    </row>
+    <row r="7755" spans="1:1">
+      <c r="A7755" s="3" t="s">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="7756" spans="1:1">
+      <c r="A7756" s="3" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="7757" spans="1:1">
+      <c r="A7757" s="3" t="s">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="7758" spans="1:1">
+      <c r="A7758" s="3" t="s">
+        <v>3697</v>
+      </c>
+    </row>
+    <row r="7759" spans="1:1">
+      <c r="A7759" s="3" t="s">
+        <v>3696</v>
+      </c>
+    </row>
+    <row r="7760" spans="1:1">
+      <c r="A7760" s="3" t="s">
+        <v>2542</v>
+      </c>
+    </row>
+    <row r="7761" spans="1:1">
+      <c r="A7761" s="3" t="s">
+        <v>3698</v>
+      </c>
+    </row>
+    <row r="7762" spans="1:1">
+      <c r="A7762" s="3" t="s">
+        <v>3699</v>
+      </c>
+    </row>
+    <row r="7763" spans="1:1">
+      <c r="A7763" s="3" t="s">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="7764" spans="1:1">
+      <c r="A7764" s="3" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="7765" spans="1:1">
+      <c r="A7765" s="3" t="s">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="7766" spans="1:1">
+      <c r="A7766" s="3" t="s">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="7767" spans="1:1">
+      <c r="A7767" s="3" t="s">
+        <v>3701</v>
+      </c>
+    </row>
+    <row r="7768" spans="1:1">
+      <c r="A7768" s="3" t="s">
+        <v>3702</v>
+      </c>
+    </row>
+    <row r="7769" spans="1:1">
+      <c r="A7769" s="3" t="s">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="7770" spans="1:1">
+      <c r="A7770" s="3" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="7771" spans="1:1">
+      <c r="A7771" s="3" t="s">
+        <v>3704</v>
+      </c>
+    </row>
+    <row r="7772" spans="1:1">
+      <c r="A7772" s="3" t="s">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="7773" spans="1:1">
+      <c r="A7773" s="3" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="7774" spans="1:1">
+      <c r="A7774" s="3" t="s">
+        <v>3707</v>
+      </c>
+    </row>
+    <row r="7775" spans="1:1">
+      <c r="A7775" s="3" t="s">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="7776" spans="1:1">
+      <c r="A7776" s="3" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="7777" spans="1:1">
+      <c r="A7777" s="3" t="s">
+        <v>3709</v>
+      </c>
+    </row>
+    <row r="7778" spans="1:1">
+      <c r="A7778" s="3" t="s">
+        <v>3775</v>
+      </c>
+    </row>
+    <row r="7779" spans="1:1">
+      <c r="A7779" s="3" t="s">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="7780" spans="1:1">
+      <c r="A7780" s="3" t="s">
+        <v>3770</v>
+      </c>
+    </row>
+    <row r="7781" spans="1:1">
+      <c r="A7781" s="3" t="s">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="7782" spans="1:1">
+      <c r="A7782" s="3" t="s">
+        <v>3769</v>
+      </c>
+    </row>
+    <row r="7783" spans="1:1">
+      <c r="A7783" s="3" t="s">
+        <v>3768</v>
+      </c>
+    </row>
+    <row r="7784" spans="1:1">
+      <c r="A7784" s="3" t="s">
+        <v>3766</v>
+      </c>
+    </row>
+    <row r="7785" spans="1:1">
+      <c r="A7785" s="3" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="7786" spans="1:1">
+      <c r="A7786" s="3" t="s">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="7787" spans="1:1">
+      <c r="A7787" s="3" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="7788" spans="1:1">
+      <c r="A7788" s="3" t="s">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="7789" spans="1:1">
+      <c r="A7789" s="3" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="7790" spans="1:1">
+      <c r="A7790" s="3" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="7791" spans="1:1">
+      <c r="A7791" s="3" t="s">
+        <v>3705</v>
+      </c>
+    </row>
+    <row r="7792" spans="1:1">
+      <c r="A7792" s="3" t="s">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="7793" spans="1:1">
+      <c r="A7793" s="3" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="7794" spans="1:1">
+      <c r="A7794" s="3" t="s">
+        <v>3866</v>
+      </c>
+    </row>
+    <row r="7795" spans="1:1">
+      <c r="A7795" s="3" t="s">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="7796" spans="1:1">
+      <c r="A7796" s="3" t="s">
+        <v>3765</v>
+      </c>
+    </row>
+    <row r="7797" spans="1:1">
+      <c r="A7797" s="3" t="s">
+        <v>3813</v>
+      </c>
+    </row>
+    <row r="7798" spans="1:1">
+      <c r="A7798" s="3" t="s">
+        <v>3764</v>
+      </c>
+    </row>
+    <row r="7799" spans="1:1">
+      <c r="A7799" s="3" t="s">
+        <v>2543</v>
+      </c>
+    </row>
+    <row r="7800" spans="1:1">
+      <c r="A7800" s="3" t="s">
+        <v>3762</v>
+      </c>
+    </row>
+    <row r="7801" spans="1:1">
+      <c r="A7801" s="3" t="s">
+        <v>3756</v>
+      </c>
+    </row>
+    <row r="7802" spans="1:1">
+      <c r="A7802" s="3" t="s">
+        <v>3868</v>
+      </c>
+    </row>
+    <row r="7803" spans="1:1">
+      <c r="A7803" s="3" t="s">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="7804" spans="1:1">
+      <c r="A7804" s="3" t="s">
+        <v>3753</v>
+      </c>
+    </row>
+    <row r="7805" spans="1:1">
+      <c r="A7805" s="3" t="s">
+        <v>3771</v>
+      </c>
+    </row>
+    <row r="7806" spans="1:1">
+      <c r="A7806" s="3" t="s">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="7807" spans="1:1">
+      <c r="A7807" s="3" t="s">
+        <v>3863</v>
+      </c>
+    </row>
+    <row r="7808" spans="1:1">
+      <c r="A7808" s="3" t="s">
+        <v>2595</v>
+      </c>
+    </row>
+    <row r="7809" spans="1:1">
+      <c r="A7809" s="3" t="s">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="7810" spans="1:1">
+      <c r="A7810" s="3" t="s">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="7811" spans="1:1">
+      <c r="A7811" s="3" t="s">
+        <v>3749</v>
+      </c>
+    </row>
+    <row r="7812" spans="1:1">
+      <c r="A7812" s="3" t="s">
+        <v>2593</v>
+      </c>
+    </row>
+    <row r="7813" spans="1:1">
+      <c r="A7813" s="3" t="s">
+        <v>2592</v>
+      </c>
+    </row>
+    <row r="7814" spans="1:1">
+      <c r="A7814" s="3" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="7815" spans="1:1">
+      <c r="A7815" s="3" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="7816" spans="1:1">
+      <c r="A7816" s="3" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="7817" spans="1:1">
+      <c r="A7817" s="3" t="s">
+        <v>3737</v>
+      </c>
+    </row>
+    <row r="7818" spans="1:1">
+      <c r="A7818" s="3" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="7819" spans="1:1">
+      <c r="A7819" s="3" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="7820" spans="1:1">
+      <c r="A7820" s="3" t="s">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="7821" spans="1:1">
+      <c r="A7821" s="3" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="7822" spans="1:1">
+      <c r="A7822" s="3" t="s">
+        <v>2548</v>
+      </c>
+    </row>
+    <row r="7823" spans="1:1">
+      <c r="A7823" s="3" t="s">
+        <v>3720</v>
+      </c>
+    </row>
+    <row r="7824" spans="1:1">
+      <c r="A7824" s="3" t="s">
+        <v>3719</v>
+      </c>
+    </row>
+    <row r="7825" spans="1:1">
+      <c r="A7825" s="3" t="s">
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="7826" spans="1:1">
+      <c r="A7826" s="3" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="7827" spans="1:1">
+      <c r="A7827" s="3" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="7828" spans="1:1">
+      <c r="A7828" s="3" t="s">
+        <v>3718</v>
+      </c>
+    </row>
+    <row r="7829" spans="1:1">
+      <c r="A7829" s="3" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="7830" spans="1:1">
+      <c r="A7830" s="3" t="s">
+        <v>3717</v>
+      </c>
+    </row>
+    <row r="7831" spans="1:1">
+      <c r="A7831" s="3" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="7832" spans="1:1">
+      <c r="A7832" s="3" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="7833" spans="1:1">
+      <c r="A7833" s="3" t="s">
+        <v>3713</v>
+      </c>
+    </row>
+    <row r="7834" spans="1:1">
+      <c r="A7834" s="3" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="7835" spans="1:1">
+      <c r="A7835" s="3" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="7836" spans="1:1">
+      <c r="A7836" s="3" t="s">
+        <v>3712</v>
+      </c>
+    </row>
+    <row r="7837" spans="1:1">
+      <c r="A7837" s="3" t="s">
+        <v>3711</v>
+      </c>
+    </row>
+    <row r="7838" spans="1:1">
+      <c r="A7838" s="3" t="s">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="7839" spans="1:1">
+      <c r="A7839" s="3" t="s">
+        <v>2467</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:A6187" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:A7839" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A$1:A$1048576">

--- a/nicknames.xlsx
+++ b/nicknames.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7839" uniqueCount="4038">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8207" uniqueCount="4227">
   <si>
     <t>name</t>
   </si>
@@ -12137,13 +12137,580 @@
     <t>风曲&amp;蓝带</t>
   </si>
   <si>
-    <t>零度-重名@鱼糕</t>
-  </si>
-  <si>
-    <t>雪梨-重名</t>
-  </si>
-  <si>
-    <t>白云边--重名了</t>
+    <t>芙芙</t>
+  </si>
+  <si>
+    <t>秋豚</t>
+  </si>
+  <si>
+    <t>耿鬼</t>
+  </si>
+  <si>
+    <t>米花糖</t>
+  </si>
+  <si>
+    <t>锅贴</t>
+  </si>
+  <si>
+    <t>乐檬</t>
+  </si>
+  <si>
+    <t>赛百味</t>
+  </si>
+  <si>
+    <t>归楚</t>
+  </si>
+  <si>
+    <t>萨拉米</t>
+  </si>
+  <si>
+    <t>伯约</t>
+  </si>
+  <si>
+    <t>奶龙</t>
+  </si>
+  <si>
+    <t>碱水面</t>
+  </si>
+  <si>
+    <t>籽棉</t>
+  </si>
+  <si>
+    <t>百岁兰</t>
+  </si>
+  <si>
+    <t>贝橙</t>
+  </si>
+  <si>
+    <t>抹茶拿铁</t>
+  </si>
+  <si>
+    <t>三笠</t>
+  </si>
+  <si>
+    <t>洛可</t>
+  </si>
+  <si>
+    <t>观风</t>
+  </si>
+  <si>
+    <t>空桑</t>
+  </si>
+  <si>
+    <t>卡莉</t>
+  </si>
+  <si>
+    <t>金丝猴</t>
+  </si>
+  <si>
+    <t>伯劳</t>
+  </si>
+  <si>
+    <t>沙枣</t>
+  </si>
+  <si>
+    <t>卷叶</t>
+  </si>
+  <si>
+    <t>钟离</t>
+  </si>
+  <si>
+    <t>晴川</t>
+  </si>
+  <si>
+    <t>峨眉峰</t>
+  </si>
+  <si>
+    <t>有鱼</t>
+  </si>
+  <si>
+    <t>悠悠</t>
+  </si>
+  <si>
+    <t>璐璐</t>
+  </si>
+  <si>
+    <t>小七</t>
+  </si>
+  <si>
+    <t>闪电松鼠</t>
+  </si>
+  <si>
+    <t>星星酱</t>
+  </si>
+  <si>
+    <t>派派</t>
+  </si>
+  <si>
+    <t>邦尼</t>
+  </si>
+  <si>
+    <t>妮可</t>
+  </si>
+  <si>
+    <t>兵长</t>
+  </si>
+  <si>
+    <t>黑豹</t>
+  </si>
+  <si>
+    <t>十安</t>
+  </si>
+  <si>
+    <t>土豆猫</t>
+  </si>
+  <si>
+    <t>落羽杉</t>
+  </si>
+  <si>
+    <t>鸣人</t>
+  </si>
+  <si>
+    <t>花花</t>
+  </si>
+  <si>
+    <t>怀瑾</t>
+  </si>
+  <si>
+    <t>拓芙</t>
+  </si>
+  <si>
+    <t>阮丰</t>
+  </si>
+  <si>
+    <t>猫咪</t>
+  </si>
+  <si>
+    <t>顾清寒</t>
+  </si>
+  <si>
+    <t>碗仔翅</t>
+  </si>
+  <si>
+    <t>新荷</t>
+  </si>
+  <si>
+    <t>白晶菊</t>
+  </si>
+  <si>
+    <t>雏田</t>
+  </si>
+  <si>
+    <t>树根</t>
+  </si>
+  <si>
+    <t>金渐层</t>
+  </si>
+  <si>
+    <t>大夫</t>
+  </si>
+  <si>
+    <t>柴犬</t>
+  </si>
+  <si>
+    <t>齐静春</t>
+  </si>
+  <si>
+    <t>海角柠檬</t>
+  </si>
+  <si>
+    <t>土笋冻</t>
+  </si>
+  <si>
+    <t>鱼仔</t>
+  </si>
+  <si>
+    <t>蜜柚</t>
+  </si>
+  <si>
+    <t>百草</t>
+  </si>
+  <si>
+    <t>英二</t>
+  </si>
+  <si>
+    <t>橙花</t>
+  </si>
+  <si>
+    <t>银时</t>
+  </si>
+  <si>
+    <t>阿兰</t>
+  </si>
+  <si>
+    <t>Deniz Sarikaya</t>
+  </si>
+  <si>
+    <t>凤尾竹</t>
+  </si>
+  <si>
+    <t>木暮</t>
+  </si>
+  <si>
+    <t>美心</t>
+  </si>
+  <si>
+    <t>肉片</t>
+  </si>
+  <si>
+    <t>冰瓜</t>
+  </si>
+  <si>
+    <t>加应子</t>
+  </si>
+  <si>
+    <t>莱因哈特</t>
+  </si>
+  <si>
+    <t>莉可</t>
+  </si>
+  <si>
+    <t>邃武</t>
+  </si>
+  <si>
+    <t>白柳</t>
+  </si>
+  <si>
+    <t>老猫</t>
+  </si>
+  <si>
+    <t>珊迪</t>
+  </si>
+  <si>
+    <t>芬奇</t>
+  </si>
+  <si>
+    <t>阿年</t>
+  </si>
+  <si>
+    <t>一米</t>
+  </si>
+  <si>
+    <t>剑兰</t>
+  </si>
+  <si>
+    <t>桐人</t>
+  </si>
+  <si>
+    <t>香葱赤虾</t>
+  </si>
+  <si>
+    <t>檀竹</t>
+  </si>
+  <si>
+    <t>达菲</t>
+  </si>
+  <si>
+    <t>呀土豆</t>
+  </si>
+  <si>
+    <t>赛文</t>
+  </si>
+  <si>
+    <t>墨染</t>
+  </si>
+  <si>
+    <t>小樱</t>
+  </si>
+  <si>
+    <t>英子</t>
+  </si>
+  <si>
+    <t>Lorenzo Segarra</t>
+  </si>
+  <si>
+    <t>片仔癀</t>
+  </si>
+  <si>
+    <t>塔尔米</t>
+  </si>
+  <si>
+    <t>Mathilde Berchon</t>
+  </si>
+  <si>
+    <t>Patrick Roeffen</t>
+  </si>
+  <si>
+    <t>草果</t>
+  </si>
+  <si>
+    <t>海白</t>
+  </si>
+  <si>
+    <t>望春</t>
+  </si>
+  <si>
+    <t>苏眉</t>
+  </si>
+  <si>
+    <t>苏式面</t>
+  </si>
+  <si>
+    <t>大粽</t>
+  </si>
+  <si>
+    <t>紫竹</t>
+  </si>
+  <si>
+    <t>朱橘</t>
+  </si>
+  <si>
+    <t>Kevin Stiehl</t>
+  </si>
+  <si>
+    <t>Thomas Breitkreutz</t>
+  </si>
+  <si>
+    <t>鑫仔</t>
+  </si>
+  <si>
+    <t>灯火</t>
+  </si>
+  <si>
+    <t>小朱</t>
+  </si>
+  <si>
+    <t>印度</t>
+  </si>
+  <si>
+    <t>叮当</t>
+  </si>
+  <si>
+    <t>夏雪</t>
+  </si>
+  <si>
+    <t>米芝</t>
+  </si>
+  <si>
+    <t>槐安</t>
+  </si>
+  <si>
+    <t>云飞扬</t>
+  </si>
+  <si>
+    <t>颜如玉</t>
+  </si>
+  <si>
+    <t>大悦</t>
+  </si>
+  <si>
+    <t>树苗</t>
+  </si>
+  <si>
+    <t>柳絮</t>
+  </si>
+  <si>
+    <t>破风</t>
+  </si>
+  <si>
+    <t>斑桂</t>
+  </si>
+  <si>
+    <t>明湘</t>
+  </si>
+  <si>
+    <t>暮春</t>
+  </si>
+  <si>
+    <t>辰风</t>
+  </si>
+  <si>
+    <t>方圆</t>
+  </si>
+  <si>
+    <t>九条</t>
+  </si>
+  <si>
+    <t>东香</t>
+  </si>
+  <si>
+    <t>犀鸟</t>
+  </si>
+  <si>
+    <t>义涛</t>
+  </si>
+  <si>
+    <t>刚果</t>
+  </si>
+  <si>
+    <t>海蓝宝</t>
+  </si>
+  <si>
+    <t>雨林</t>
+  </si>
+  <si>
+    <t>美阳阳</t>
+  </si>
+  <si>
+    <t>月兔</t>
+  </si>
+  <si>
+    <t>羊习习</t>
+  </si>
+  <si>
+    <t>小料</t>
+  </si>
+  <si>
+    <t>故里</t>
+  </si>
+  <si>
+    <t>米斗</t>
+  </si>
+  <si>
+    <t>软白沙</t>
+  </si>
+  <si>
+    <t>熵增</t>
+  </si>
+  <si>
+    <t>辰月</t>
+  </si>
+  <si>
+    <t>云烟</t>
+  </si>
+  <si>
+    <t>玉团</t>
+  </si>
+  <si>
+    <t>南时枳</t>
+  </si>
+  <si>
+    <t>左柚</t>
+  </si>
+  <si>
+    <t>扎西</t>
+  </si>
+  <si>
+    <t>四喜丸子</t>
+  </si>
+  <si>
+    <t>鹈鹕</t>
+  </si>
+  <si>
+    <t>陌然</t>
+  </si>
+  <si>
+    <t>冻柠檬</t>
+  </si>
+  <si>
+    <t>星露</t>
+  </si>
+  <si>
+    <t>龙舞</t>
+  </si>
+  <si>
+    <t>云衫</t>
+  </si>
+  <si>
+    <t>嘉禾</t>
+  </si>
+  <si>
+    <t>五只羊</t>
+  </si>
+  <si>
+    <t>白玉菇</t>
+  </si>
+  <si>
+    <t>清歌</t>
+  </si>
+  <si>
+    <t>玉欢</t>
+  </si>
+  <si>
+    <t>玉叶</t>
+  </si>
+  <si>
+    <t>赞赞</t>
+  </si>
+  <si>
+    <t>粘豆包</t>
+  </si>
+  <si>
+    <t>甘棠</t>
+  </si>
+  <si>
+    <t>凯迪</t>
+  </si>
+  <si>
+    <t>小橙子</t>
+  </si>
+  <si>
+    <t>三水</t>
+  </si>
+  <si>
+    <t>上迪</t>
+  </si>
+  <si>
+    <t>橘菇</t>
+  </si>
+  <si>
+    <t>洛奇亚</t>
+  </si>
+  <si>
+    <t>云臻</t>
+  </si>
+  <si>
+    <t>江南</t>
+  </si>
+  <si>
+    <t>祥云</t>
+  </si>
+  <si>
+    <t>绮年</t>
+  </si>
+  <si>
+    <t>零号</t>
+  </si>
+  <si>
+    <t>楚河</t>
+  </si>
+  <si>
+    <t>长安</t>
+  </si>
+  <si>
+    <t>天烨</t>
+  </si>
+  <si>
+    <t>白妍</t>
+  </si>
+  <si>
+    <t>老登</t>
+  </si>
+  <si>
+    <t>初阳</t>
+  </si>
+  <si>
+    <t>春风</t>
+  </si>
+  <si>
+    <t>龙川</t>
+  </si>
+  <si>
+    <t>婷婷子</t>
+  </si>
+  <si>
+    <t>鲑鱼</t>
+  </si>
+  <si>
+    <t>可待</t>
+  </si>
+  <si>
+    <t>崂山</t>
+  </si>
+  <si>
+    <t>南下</t>
+  </si>
+  <si>
+    <t>鸡米</t>
+  </si>
+  <si>
+    <t>梧桐山</t>
+  </si>
+  <si>
+    <t>白胡椒</t>
+  </si>
+  <si>
+    <t>贝贝</t>
   </si>
 </sst>
 </file>
@@ -12757,7 +13324,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -12767,6 +13334,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -13126,7 +13696,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A7839"/>
+  <dimension ref="A1:A8207"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="19.3166666666667" style="1" customWidth="1"/>
@@ -50459,7 +51029,7 @@
     </row>
     <row r="7466" spans="1:1">
       <c r="A7466" s="3" t="s">
-        <v>4035</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="7467" spans="1:1">
@@ -50539,7 +51109,7 @@
     </row>
     <row r="7482" spans="1:1">
       <c r="A7482" s="3" t="s">
-        <v>4036</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="7483" spans="1:1">
@@ -50759,7 +51329,7 @@
     </row>
     <row r="7526" spans="1:1">
       <c r="A7526" s="3" t="s">
-        <v>4037</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="7527" spans="1:1">
@@ -52325,6 +52895,1846 @@
     <row r="7839" spans="1:1">
       <c r="A7839" s="3" t="s">
         <v>2467</v>
+      </c>
+    </row>
+    <row r="7840" spans="1:1">
+      <c r="A7840" s="4" t="s">
+        <v>4035</v>
+      </c>
+    </row>
+    <row r="7841" spans="1:1">
+      <c r="A7841" s="4" t="s">
+        <v>4036</v>
+      </c>
+    </row>
+    <row r="7842" spans="1:1">
+      <c r="A7842" s="4" t="s">
+        <v>4037</v>
+      </c>
+    </row>
+    <row r="7843" spans="1:1">
+      <c r="A7843" s="4" t="s">
+        <v>4038</v>
+      </c>
+    </row>
+    <row r="7844" spans="1:1">
+      <c r="A7844" s="4" t="s">
+        <v>4039</v>
+      </c>
+    </row>
+    <row r="7845" spans="1:1">
+      <c r="A7845" s="4" t="s">
+        <v>4040</v>
+      </c>
+    </row>
+    <row r="7846" spans="1:1">
+      <c r="A7846" s="4" t="s">
+        <v>4041</v>
+      </c>
+    </row>
+    <row r="7847" spans="1:1">
+      <c r="A7847" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7848" spans="1:1">
+      <c r="A7848" s="4" t="s">
+        <v>4042</v>
+      </c>
+    </row>
+    <row r="7849" spans="1:1">
+      <c r="A7849" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7850" spans="1:1">
+      <c r="A7850" s="4" t="s">
+        <v>4043</v>
+      </c>
+    </row>
+    <row r="7851" spans="1:1">
+      <c r="A7851" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7852" spans="1:1">
+      <c r="A7852" s="4" t="s">
+        <v>4044</v>
+      </c>
+    </row>
+    <row r="7853" spans="1:1">
+      <c r="A7853" s="4" t="s">
+        <v>4045</v>
+      </c>
+    </row>
+    <row r="7854" spans="1:1">
+      <c r="A7854" s="4" t="s">
+        <v>4046</v>
+      </c>
+    </row>
+    <row r="7855" spans="1:1">
+      <c r="A7855" s="4" t="s">
+        <v>4047</v>
+      </c>
+    </row>
+    <row r="7856" spans="1:1">
+      <c r="A7856" s="4" t="s">
+        <v>4048</v>
+      </c>
+    </row>
+    <row r="7857" spans="1:1">
+      <c r="A7857" s="4" t="s">
+        <v>4049</v>
+      </c>
+    </row>
+    <row r="7858" spans="1:1">
+      <c r="A7858" s="4" t="s">
+        <v>4050</v>
+      </c>
+    </row>
+    <row r="7859" spans="1:1">
+      <c r="A7859" s="4" t="s">
+        <v>4051</v>
+      </c>
+    </row>
+    <row r="7860" spans="1:1">
+      <c r="A7860" s="4" t="s">
+        <v>4052</v>
+      </c>
+    </row>
+    <row r="7861" spans="1:1">
+      <c r="A7861" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="7862" spans="1:1">
+      <c r="A7862" s="4" t="s">
+        <v>4053</v>
+      </c>
+    </row>
+    <row r="7863" spans="1:1">
+      <c r="A7863" s="4" t="s">
+        <v>4054</v>
+      </c>
+    </row>
+    <row r="7864" spans="1:1">
+      <c r="A7864" s="4" t="s">
+        <v>4055</v>
+      </c>
+    </row>
+    <row r="7865" spans="1:1">
+      <c r="A7865" s="4" t="s">
+        <v>4056</v>
+      </c>
+    </row>
+    <row r="7866" spans="1:1">
+      <c r="A7866" s="4" t="s">
+        <v>4057</v>
+      </c>
+    </row>
+    <row r="7867" spans="1:1">
+      <c r="A7867" s="4" t="s">
+        <v>4058</v>
+      </c>
+    </row>
+    <row r="7868" spans="1:1">
+      <c r="A7868" s="4" t="s">
+        <v>4059</v>
+      </c>
+    </row>
+    <row r="7869" spans="1:1">
+      <c r="A7869" s="4" t="s">
+        <v>4060</v>
+      </c>
+    </row>
+    <row r="7870" spans="1:1">
+      <c r="A7870" s="4" t="s">
+        <v>4061</v>
+      </c>
+    </row>
+    <row r="7871" spans="1:1">
+      <c r="A7871" s="4" t="s">
+        <v>4062</v>
+      </c>
+    </row>
+    <row r="7872" spans="1:1">
+      <c r="A7872" s="4" t="s">
+        <v>4063</v>
+      </c>
+    </row>
+    <row r="7873" spans="1:1">
+      <c r="A7873" s="4" t="s">
+        <v>4064</v>
+      </c>
+    </row>
+    <row r="7874" spans="1:1">
+      <c r="A7874" s="4" t="s">
+        <v>4065</v>
+      </c>
+    </row>
+    <row r="7875" spans="1:1">
+      <c r="A7875" s="4" t="s">
+        <v>4066</v>
+      </c>
+    </row>
+    <row r="7876" spans="1:1">
+      <c r="A7876" s="4" t="s">
+        <v>4067</v>
+      </c>
+    </row>
+    <row r="7877" spans="1:1">
+      <c r="A7877" s="4" t="s">
+        <v>4068</v>
+      </c>
+    </row>
+    <row r="7878" spans="1:1">
+      <c r="A7878" s="4" t="s">
+        <v>4069</v>
+      </c>
+    </row>
+    <row r="7879" spans="1:1">
+      <c r="A7879" s="4" t="s">
+        <v>4070</v>
+      </c>
+    </row>
+    <row r="7880" spans="1:1">
+      <c r="A7880" s="4" t="s">
+        <v>4071</v>
+      </c>
+    </row>
+    <row r="7881" spans="1:1">
+      <c r="A7881" s="4" t="s">
+        <v>4072</v>
+      </c>
+    </row>
+    <row r="7882" spans="1:1">
+      <c r="A7882" s="4" t="s">
+        <v>4073</v>
+      </c>
+    </row>
+    <row r="7883" spans="1:1">
+      <c r="A7883" s="4" t="s">
+        <v>4074</v>
+      </c>
+    </row>
+    <row r="7884" spans="1:1">
+      <c r="A7884" s="4" t="s">
+        <v>4075</v>
+      </c>
+    </row>
+    <row r="7885" spans="1:1">
+      <c r="A7885" s="4" t="s">
+        <v>4076</v>
+      </c>
+    </row>
+    <row r="7886" spans="1:1">
+      <c r="A7886" s="4" t="s">
+        <v>4077</v>
+      </c>
+    </row>
+    <row r="7887" spans="1:1">
+      <c r="A7887" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7888" spans="1:1">
+      <c r="A7888" s="4" t="s">
+        <v>4078</v>
+      </c>
+    </row>
+    <row r="7889" spans="1:1">
+      <c r="A7889" s="4" t="s">
+        <v>4079</v>
+      </c>
+    </row>
+    <row r="7890" spans="1:1">
+      <c r="A7890" s="4" t="s">
+        <v>4080</v>
+      </c>
+    </row>
+    <row r="7891" spans="1:1">
+      <c r="A7891" s="4" t="s">
+        <v>4081</v>
+      </c>
+    </row>
+    <row r="7892" spans="1:1">
+      <c r="A7892" s="4" t="s">
+        <v>4082</v>
+      </c>
+    </row>
+    <row r="7893" spans="1:1">
+      <c r="A7893" s="4" t="s">
+        <v>4083</v>
+      </c>
+    </row>
+    <row r="7894" spans="1:1">
+      <c r="A7894" s="4" t="s">
+        <v>4084</v>
+      </c>
+    </row>
+    <row r="7895" spans="1:1">
+      <c r="A7895" s="4" t="s">
+        <v>4085</v>
+      </c>
+    </row>
+    <row r="7896" spans="1:1">
+      <c r="A7896" s="4" t="s">
+        <v>4086</v>
+      </c>
+    </row>
+    <row r="7897" spans="1:1">
+      <c r="A7897" s="4" t="s">
+        <v>4087</v>
+      </c>
+    </row>
+    <row r="7898" spans="1:1">
+      <c r="A7898" s="4" t="s">
+        <v>4088</v>
+      </c>
+    </row>
+    <row r="7899" spans="1:1">
+      <c r="A7899" s="4" t="s">
+        <v>4089</v>
+      </c>
+    </row>
+    <row r="7900" spans="1:1">
+      <c r="A7900" s="4" t="s">
+        <v>4090</v>
+      </c>
+    </row>
+    <row r="7901" spans="1:1">
+      <c r="A7901" s="4" t="s">
+        <v>4091</v>
+      </c>
+    </row>
+    <row r="7902" spans="1:1">
+      <c r="A7902" s="4" t="s">
+        <v>4092</v>
+      </c>
+    </row>
+    <row r="7903" spans="1:1">
+      <c r="A7903" s="4" t="s">
+        <v>4093</v>
+      </c>
+    </row>
+    <row r="7904" spans="1:1">
+      <c r="A7904" s="4" t="s">
+        <v>4094</v>
+      </c>
+    </row>
+    <row r="7905" spans="1:1">
+      <c r="A7905" s="4" t="s">
+        <v>4095</v>
+      </c>
+    </row>
+    <row r="7906" spans="1:1">
+      <c r="A7906" s="4" t="s">
+        <v>4096</v>
+      </c>
+    </row>
+    <row r="7907" spans="1:1">
+      <c r="A7907" s="4" t="s">
+        <v>4097</v>
+      </c>
+    </row>
+    <row r="7908" spans="1:1">
+      <c r="A7908" s="4" t="s">
+        <v>4098</v>
+      </c>
+    </row>
+    <row r="7909" spans="1:1">
+      <c r="A7909" s="4" t="s">
+        <v>4099</v>
+      </c>
+    </row>
+    <row r="7910" spans="1:1">
+      <c r="A7910" s="4" t="s">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="7911" spans="1:1">
+      <c r="A7911" s="4" t="s">
+        <v>4101</v>
+      </c>
+    </row>
+    <row r="7912" spans="1:1">
+      <c r="A7912" s="4" t="s">
+        <v>4102</v>
+      </c>
+    </row>
+    <row r="7913" spans="1:1">
+      <c r="A7913" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7914" spans="1:1">
+      <c r="A7914" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7915" spans="1:1">
+      <c r="A7915" s="4" t="s">
+        <v>4103</v>
+      </c>
+    </row>
+    <row r="7916" spans="1:1">
+      <c r="A7916" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7917" spans="1:1">
+      <c r="A7917" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7918" spans="1:1">
+      <c r="A7918" s="4" t="s">
+        <v>4104</v>
+      </c>
+    </row>
+    <row r="7919" spans="1:1">
+      <c r="A7919" s="4" t="s">
+        <v>4105</v>
+      </c>
+    </row>
+    <row r="7920" spans="1:1">
+      <c r="A7920" s="4" t="s">
+        <v>4106</v>
+      </c>
+    </row>
+    <row r="7921" spans="1:1">
+      <c r="A7921" s="4" t="s">
+        <v>4107</v>
+      </c>
+    </row>
+    <row r="7922" spans="1:1">
+      <c r="A7922" s="4" t="s">
+        <v>4108</v>
+      </c>
+    </row>
+    <row r="7923" spans="1:1">
+      <c r="A7923" s="4" t="s">
+        <v>4109</v>
+      </c>
+    </row>
+    <row r="7924" spans="1:1">
+      <c r="A7924" s="4" t="s">
+        <v>4110</v>
+      </c>
+    </row>
+    <row r="7925" spans="1:1">
+      <c r="A7925" s="4" t="s">
+        <v>4111</v>
+      </c>
+    </row>
+    <row r="7926" spans="1:1">
+      <c r="A7926" s="4" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="7927" spans="1:1">
+      <c r="A7927" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7928" spans="1:1">
+      <c r="A7928" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7929" spans="1:1">
+      <c r="A7929" s="4" t="s">
+        <v>4112</v>
+      </c>
+    </row>
+    <row r="7930" spans="1:1">
+      <c r="A7930" s="4" t="s">
+        <v>4113</v>
+      </c>
+    </row>
+    <row r="7931" spans="1:1">
+      <c r="A7931" s="4" t="s">
+        <v>4114</v>
+      </c>
+    </row>
+    <row r="7932" spans="1:1">
+      <c r="A7932" s="4" t="s">
+        <v>4115</v>
+      </c>
+    </row>
+    <row r="7933" spans="1:1">
+      <c r="A7933" s="4" t="s">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="7934" spans="1:1">
+      <c r="A7934" s="4" t="s">
+        <v>4117</v>
+      </c>
+    </row>
+    <row r="7935" spans="1:1">
+      <c r="A7935" s="4" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="7936" spans="1:1">
+      <c r="A7936" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7937" spans="1:1">
+      <c r="A7937" s="4" t="s">
+        <v>4118</v>
+      </c>
+    </row>
+    <row r="7938" spans="1:1">
+      <c r="A7938" s="4" t="s">
+        <v>4119</v>
+      </c>
+    </row>
+    <row r="7939" spans="1:1">
+      <c r="A7939" s="4" t="s">
+        <v>4120</v>
+      </c>
+    </row>
+    <row r="7940" spans="1:1">
+      <c r="A7940" s="4" t="s">
+        <v>4121</v>
+      </c>
+    </row>
+    <row r="7941" spans="1:1">
+      <c r="A7941" s="4" t="s">
+        <v>4122</v>
+      </c>
+    </row>
+    <row r="7942" spans="1:1">
+      <c r="A7942" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7943" spans="1:1">
+      <c r="A7943" s="4" t="s">
+        <v>4123</v>
+      </c>
+    </row>
+    <row r="7944" spans="1:1">
+      <c r="A7944" s="4" t="s">
+        <v>4124</v>
+      </c>
+    </row>
+    <row r="7945" spans="1:1">
+      <c r="A7945" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7946" spans="1:1">
+      <c r="A7946" s="4" t="s">
+        <v>4125</v>
+      </c>
+    </row>
+    <row r="7947" spans="1:1">
+      <c r="A7947" s="4" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="7948" spans="1:1">
+      <c r="A7948" s="4" t="s">
+        <v>4126</v>
+      </c>
+    </row>
+    <row r="7949" spans="1:1">
+      <c r="A7949" s="4" t="s">
+        <v>4127</v>
+      </c>
+    </row>
+    <row r="7950" spans="1:1">
+      <c r="A7950" s="4" t="s">
+        <v>4128</v>
+      </c>
+    </row>
+    <row r="7951" spans="1:1">
+      <c r="A7951" s="4" t="s">
+        <v>4129</v>
+      </c>
+    </row>
+    <row r="7952" spans="1:1">
+      <c r="A7952" s="4" t="s">
+        <v>4130</v>
+      </c>
+    </row>
+    <row r="7953" spans="1:1">
+      <c r="A7953" s="4" t="s">
+        <v>4131</v>
+      </c>
+    </row>
+    <row r="7954" spans="1:1">
+      <c r="A7954" s="4" t="s">
+        <v>4132</v>
+      </c>
+    </row>
+    <row r="7955" spans="1:1">
+      <c r="A7955" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7956" spans="1:1">
+      <c r="A7956" s="4" t="s">
+        <v>4133</v>
+      </c>
+    </row>
+    <row r="7957" spans="1:1">
+      <c r="A7957" s="4" t="s">
+        <v>4134</v>
+      </c>
+    </row>
+    <row r="7958" spans="1:1">
+      <c r="A7958" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7959" spans="1:1">
+      <c r="A7959" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7960" spans="1:1">
+      <c r="A7960" s="4" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="7961" spans="1:1">
+      <c r="A7961" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7962" spans="1:1">
+      <c r="A7962" s="4" t="s">
+        <v>4135</v>
+      </c>
+    </row>
+    <row r="7963" spans="1:1">
+      <c r="A7963" s="4" t="s">
+        <v>4136</v>
+      </c>
+    </row>
+    <row r="7964" spans="1:1">
+      <c r="A7964" s="4" t="s">
+        <v>4137</v>
+      </c>
+    </row>
+    <row r="7965" spans="1:1">
+      <c r="A7965" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7966" spans="1:1">
+      <c r="A7966" s="4" t="s">
+        <v>4138</v>
+      </c>
+    </row>
+    <row r="7967" spans="1:1">
+      <c r="A7967" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7968" spans="1:1">
+      <c r="A7968" s="4" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="7969" spans="1:1">
+      <c r="A7969" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7970" spans="1:1">
+      <c r="A7970" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7971" spans="1:1">
+      <c r="A7971" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7972" spans="1:1">
+      <c r="A7972" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7973" spans="1:1">
+      <c r="A7973" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7974" spans="1:1">
+      <c r="A7974" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7975" spans="1:1">
+      <c r="A7975" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7976" spans="1:1">
+      <c r="A7976" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7977" spans="1:1">
+      <c r="A7977" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7978" spans="1:1">
+      <c r="A7978" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7979" spans="1:1">
+      <c r="A7979" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7980" spans="1:1">
+      <c r="A7980" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7981" spans="1:1">
+      <c r="A7981" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7982" spans="1:1">
+      <c r="A7982" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7983" spans="1:1">
+      <c r="A7983" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7984" spans="1:1">
+      <c r="A7984" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7985" spans="1:1">
+      <c r="A7985" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7986" spans="1:1">
+      <c r="A7986" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7987" spans="1:1">
+      <c r="A7987" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7988" spans="1:1">
+      <c r="A7988" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7989" spans="1:1">
+      <c r="A7989" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7990" spans="1:1">
+      <c r="A7990" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7991" spans="1:1">
+      <c r="A7991" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7992" spans="1:1">
+      <c r="A7992" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7993" spans="1:1">
+      <c r="A7993" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7994" spans="1:1">
+      <c r="A7994" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7995" spans="1:1">
+      <c r="A7995" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7996" spans="1:1">
+      <c r="A7996" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7997" spans="1:1">
+      <c r="A7997" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7998" spans="1:1">
+      <c r="A7998" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7999" spans="1:1">
+      <c r="A7999" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8000" spans="1:1">
+      <c r="A8000" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8001" spans="1:1">
+      <c r="A8001" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8002" spans="1:1">
+      <c r="A8002" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8003" spans="1:1">
+      <c r="A8003" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8004" spans="1:1">
+      <c r="A8004" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8005" spans="1:1">
+      <c r="A8005" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8006" spans="1:1">
+      <c r="A8006" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8007" spans="1:1">
+      <c r="A8007" s="4" t="s">
+        <v>4139</v>
+      </c>
+    </row>
+    <row r="8008" spans="1:1">
+      <c r="A8008" s="4" t="s">
+        <v>4140</v>
+      </c>
+    </row>
+    <row r="8009" spans="1:1">
+      <c r="A8009" s="4" t="s">
+        <v>4141</v>
+      </c>
+    </row>
+    <row r="8010" spans="1:1">
+      <c r="A8010" s="4" t="s">
+        <v>4142</v>
+      </c>
+    </row>
+    <row r="8011" spans="1:1">
+      <c r="A8011" s="4" t="s">
+        <v>4143</v>
+      </c>
+    </row>
+    <row r="8012" spans="1:1">
+      <c r="A8012" s="4" t="s">
+        <v>4144</v>
+      </c>
+    </row>
+    <row r="8013" spans="1:1">
+      <c r="A8013" s="4" t="s">
+        <v>3835</v>
+      </c>
+    </row>
+    <row r="8014" spans="1:1">
+      <c r="A8014" s="4" t="s">
+        <v>4145</v>
+      </c>
+    </row>
+    <row r="8015" spans="1:1">
+      <c r="A8015" s="4" t="s">
+        <v>4146</v>
+      </c>
+    </row>
+    <row r="8016" spans="1:1">
+      <c r="A8016" s="4" t="s">
+        <v>4147</v>
+      </c>
+    </row>
+    <row r="8017" spans="1:1">
+      <c r="A8017" s="4" t="s">
+        <v>4148</v>
+      </c>
+    </row>
+    <row r="8018" spans="1:1">
+      <c r="A8018" s="4" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="8019" spans="1:1">
+      <c r="A8019" s="4" t="s">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="8020" spans="1:1">
+      <c r="A8020" s="4" t="s">
+        <v>4151</v>
+      </c>
+    </row>
+    <row r="8021" spans="1:1">
+      <c r="A8021" s="4" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="8022" spans="1:1">
+      <c r="A8022" s="4" t="s">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="8023" spans="1:1">
+      <c r="A8023" s="4" t="s">
+        <v>3317</v>
+      </c>
+    </row>
+    <row r="8024" spans="1:1">
+      <c r="A8024" s="4" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="8025" spans="1:1">
+      <c r="A8025" s="4" t="s">
+        <v>4154</v>
+      </c>
+    </row>
+    <row r="8026" spans="1:1">
+      <c r="A8026" s="4" t="s">
+        <v>3162</v>
+      </c>
+    </row>
+    <row r="8027" spans="1:1">
+      <c r="A8027" s="4" t="s">
+        <v>4155</v>
+      </c>
+    </row>
+    <row r="8028" spans="1:1">
+      <c r="A8028" s="4" t="s">
+        <v>4156</v>
+      </c>
+    </row>
+    <row r="8029" spans="1:1">
+      <c r="A8029" s="4" t="s">
+        <v>4157</v>
+      </c>
+    </row>
+    <row r="8030" spans="1:1">
+      <c r="A8030" s="4" t="s">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="8031" spans="1:1">
+      <c r="A8031" s="4" t="s">
+        <v>4159</v>
+      </c>
+    </row>
+    <row r="8032" spans="1:1">
+      <c r="A8032" s="4" t="s">
+        <v>4160</v>
+      </c>
+    </row>
+    <row r="8033" spans="1:1">
+      <c r="A8033" s="4" t="s">
+        <v>4161</v>
+      </c>
+    </row>
+    <row r="8034" spans="1:1">
+      <c r="A8034" s="4" t="s">
+        <v>4162</v>
+      </c>
+    </row>
+    <row r="8035" spans="1:1">
+      <c r="A8035" s="4" t="s">
+        <v>4163</v>
+      </c>
+    </row>
+    <row r="8036" spans="1:1">
+      <c r="A8036" s="4" t="s">
+        <v>4164</v>
+      </c>
+    </row>
+    <row r="8037" spans="1:1">
+      <c r="A8037" s="4" t="s">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="8038" spans="1:1">
+      <c r="A8038" s="4" t="s">
+        <v>4166</v>
+      </c>
+    </row>
+    <row r="8039" spans="1:1">
+      <c r="A8039" s="4" t="s">
+        <v>3219</v>
+      </c>
+    </row>
+    <row r="8040" spans="1:1">
+      <c r="A8040" s="4" t="s">
+        <v>4167</v>
+      </c>
+    </row>
+    <row r="8041" spans="1:1">
+      <c r="A8041" s="4" t="s">
+        <v>4168</v>
+      </c>
+    </row>
+    <row r="8042" spans="1:1">
+      <c r="A8042" s="4" t="s">
+        <v>4169</v>
+      </c>
+    </row>
+    <row r="8043" spans="1:1">
+      <c r="A8043" s="4" t="s">
+        <v>4170</v>
+      </c>
+    </row>
+    <row r="8044" spans="1:1">
+      <c r="A8044" s="4" t="s">
+        <v>4171</v>
+      </c>
+    </row>
+    <row r="8045" spans="1:1">
+      <c r="A8045" s="4" t="s">
+        <v>2962</v>
+      </c>
+    </row>
+    <row r="8046" spans="1:1">
+      <c r="A8046" s="4" t="s">
+        <v>4172</v>
+      </c>
+    </row>
+    <row r="8047" spans="1:1">
+      <c r="A8047" s="4" t="s">
+        <v>4173</v>
+      </c>
+    </row>
+    <row r="8048" spans="1:1">
+      <c r="A8048" s="4" t="s">
+        <v>4174</v>
+      </c>
+    </row>
+    <row r="8049" spans="1:1">
+      <c r="A8049" s="4" t="s">
+        <v>4175</v>
+      </c>
+    </row>
+    <row r="8050" spans="1:1">
+      <c r="A8050" s="4" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="8051" spans="1:1">
+      <c r="A8051" s="4" t="s">
+        <v>2810</v>
+      </c>
+    </row>
+    <row r="8052" spans="1:1">
+      <c r="A8052" s="4" t="s">
+        <v>4176</v>
+      </c>
+    </row>
+    <row r="8053" spans="1:1">
+      <c r="A8053" s="4" t="s">
+        <v>4177</v>
+      </c>
+    </row>
+    <row r="8054" spans="1:1">
+      <c r="A8054" s="4" t="s">
+        <v>3216</v>
+      </c>
+    </row>
+    <row r="8055" spans="1:1">
+      <c r="A8055" s="4" t="s">
+        <v>4178</v>
+      </c>
+    </row>
+    <row r="8056" spans="1:1">
+      <c r="A8056" s="4" t="s">
+        <v>4179</v>
+      </c>
+    </row>
+    <row r="8057" spans="1:1">
+      <c r="A8057" s="4" t="s">
+        <v>4180</v>
+      </c>
+    </row>
+    <row r="8058" spans="1:1">
+      <c r="A8058" s="4" t="s">
+        <v>4181</v>
+      </c>
+    </row>
+    <row r="8059" spans="1:1">
+      <c r="A8059" s="4" t="s">
+        <v>4182</v>
+      </c>
+    </row>
+    <row r="8060" spans="1:1">
+      <c r="A8060" s="4" t="s">
+        <v>2886</v>
+      </c>
+    </row>
+    <row r="8061" spans="1:1">
+      <c r="A8061" s="4" t="s">
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="8062" spans="1:1">
+      <c r="A8062" s="4" t="s">
+        <v>4183</v>
+      </c>
+    </row>
+    <row r="8063" spans="1:1">
+      <c r="A8063" s="4" t="s">
+        <v>4184</v>
+      </c>
+    </row>
+    <row r="8064" spans="1:1">
+      <c r="A8064" s="4" t="s">
+        <v>4185</v>
+      </c>
+    </row>
+    <row r="8065" spans="1:1">
+      <c r="A8065" s="4" t="s">
+        <v>4186</v>
+      </c>
+    </row>
+    <row r="8066" spans="1:1">
+      <c r="A8066" s="4" t="s">
+        <v>4187</v>
+      </c>
+    </row>
+    <row r="8067" spans="1:1">
+      <c r="A8067" s="4" t="s">
+        <v>4188</v>
+      </c>
+    </row>
+    <row r="8068" spans="1:1">
+      <c r="A8068" s="4" t="s">
+        <v>4189</v>
+      </c>
+    </row>
+    <row r="8069" spans="1:1">
+      <c r="A8069" s="4" t="s">
+        <v>4190</v>
+      </c>
+    </row>
+    <row r="8070" spans="1:1">
+      <c r="A8070" s="4" t="s">
+        <v>4191</v>
+      </c>
+    </row>
+    <row r="8071" spans="1:1">
+      <c r="A8071" s="4" t="s">
+        <v>4192</v>
+      </c>
+    </row>
+    <row r="8072" spans="1:1">
+      <c r="A8072" s="4" t="s">
+        <v>4193</v>
+      </c>
+    </row>
+    <row r="8073" spans="1:1">
+      <c r="A8073" s="4" t="s">
+        <v>3312</v>
+      </c>
+    </row>
+    <row r="8074" spans="1:1">
+      <c r="A8074" s="4" t="s">
+        <v>4194</v>
+      </c>
+    </row>
+    <row r="8075" spans="1:1">
+      <c r="A8075" s="4" t="s">
+        <v>4195</v>
+      </c>
+    </row>
+    <row r="8076" spans="1:1">
+      <c r="A8076" s="4" t="s">
+        <v>4196</v>
+      </c>
+    </row>
+    <row r="8077" spans="1:1">
+      <c r="A8077" s="4" t="s">
+        <v>4197</v>
+      </c>
+    </row>
+    <row r="8078" spans="1:1">
+      <c r="A8078" s="4" t="s">
+        <v>4198</v>
+      </c>
+    </row>
+    <row r="8079" spans="1:1">
+      <c r="A8079" s="4" t="s">
+        <v>4199</v>
+      </c>
+    </row>
+    <row r="8080" spans="1:1">
+      <c r="A8080" s="4" t="s">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="8081" spans="1:1">
+      <c r="A8081" s="4" t="s">
+        <v>4201</v>
+      </c>
+    </row>
+    <row r="8082" spans="1:1">
+      <c r="A8082" s="4" t="s">
+        <v>4202</v>
+      </c>
+    </row>
+    <row r="8083" spans="1:1">
+      <c r="A8083" s="4" t="s">
+        <v>4203</v>
+      </c>
+    </row>
+    <row r="8084" spans="1:1">
+      <c r="A8084" s="4" t="s">
+        <v>4204</v>
+      </c>
+    </row>
+    <row r="8085" spans="1:1">
+      <c r="A8085" s="4" t="s">
+        <v>4205</v>
+      </c>
+    </row>
+    <row r="8086" spans="1:1">
+      <c r="A8086" s="4" t="s">
+        <v>4206</v>
+      </c>
+    </row>
+    <row r="8087" spans="1:1">
+      <c r="A8087" s="4" t="s">
+        <v>4207</v>
+      </c>
+    </row>
+    <row r="8088" spans="1:1">
+      <c r="A8088" s="4" t="s">
+        <v>4208</v>
+      </c>
+    </row>
+    <row r="8089" spans="1:1">
+      <c r="A8089" s="4" t="s">
+        <v>4209</v>
+      </c>
+    </row>
+    <row r="8090" spans="1:1">
+      <c r="A8090" s="4" t="s">
+        <v>4210</v>
+      </c>
+    </row>
+    <row r="8091" spans="1:1">
+      <c r="A8091" s="4" t="s">
+        <v>4211</v>
+      </c>
+    </row>
+    <row r="8092" spans="1:1">
+      <c r="A8092" s="4" t="s">
+        <v>4212</v>
+      </c>
+    </row>
+    <row r="8093" spans="1:1">
+      <c r="A8093" s="4" t="s">
+        <v>4213</v>
+      </c>
+    </row>
+    <row r="8094" spans="1:1">
+      <c r="A8094" s="4" t="s">
+        <v>4214</v>
+      </c>
+    </row>
+    <row r="8095" spans="1:1">
+      <c r="A8095" s="4" t="s">
+        <v>4215</v>
+      </c>
+    </row>
+    <row r="8096" spans="1:1">
+      <c r="A8096" s="4" t="s">
+        <v>4216</v>
+      </c>
+    </row>
+    <row r="8097" spans="1:1">
+      <c r="A8097" s="4" t="s">
+        <v>4217</v>
+      </c>
+    </row>
+    <row r="8098" spans="1:1">
+      <c r="A8098" s="4" t="s">
+        <v>4218</v>
+      </c>
+    </row>
+    <row r="8099" spans="1:1">
+      <c r="A8099" s="4" t="s">
+        <v>4219</v>
+      </c>
+    </row>
+    <row r="8100" spans="1:1">
+      <c r="A8100" s="4" t="s">
+        <v>4220</v>
+      </c>
+    </row>
+    <row r="8101" spans="1:1">
+      <c r="A8101" s="4" t="s">
+        <v>4221</v>
+      </c>
+    </row>
+    <row r="8102" spans="1:1">
+      <c r="A8102" s="4" t="s">
+        <v>4222</v>
+      </c>
+    </row>
+    <row r="8103" spans="1:1">
+      <c r="A8103" s="4" t="s">
+        <v>4223</v>
+      </c>
+    </row>
+    <row r="8104" spans="1:1">
+      <c r="A8104" s="4" t="s">
+        <v>4224</v>
+      </c>
+    </row>
+    <row r="8105" spans="1:1">
+      <c r="A8105" s="4" t="s">
+        <v>3927</v>
+      </c>
+    </row>
+    <row r="8106" spans="1:1">
+      <c r="A8106" s="4" t="s">
+        <v>3928</v>
+      </c>
+    </row>
+    <row r="8107" spans="1:1">
+      <c r="A8107" s="4" t="s">
+        <v>4225</v>
+      </c>
+    </row>
+    <row r="8108" spans="1:1">
+      <c r="A8108" s="4" t="s">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="8109" spans="1:1">
+      <c r="A8109" s="4" t="s">
+        <v>3930</v>
+      </c>
+    </row>
+    <row r="8110" spans="1:1">
+      <c r="A8110" s="4" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="8111" spans="1:1">
+      <c r="A8111" s="4" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="8112" spans="1:1">
+      <c r="A8112" s="4" t="s">
+        <v>3492</v>
+      </c>
+    </row>
+    <row r="8113" spans="1:1">
+      <c r="A8113" s="4" t="s">
+        <v>3934</v>
+      </c>
+    </row>
+    <row r="8114" spans="1:1">
+      <c r="A8114" s="4" t="s">
+        <v>2716</v>
+      </c>
+    </row>
+    <row r="8115" spans="1:1">
+      <c r="A8115" s="4" t="s">
+        <v>3935</v>
+      </c>
+    </row>
+    <row r="8116" spans="1:1">
+      <c r="A8116" s="4" t="s">
+        <v>3936</v>
+      </c>
+    </row>
+    <row r="8117" spans="1:1">
+      <c r="A8117" s="4" t="s">
+        <v>4226</v>
+      </c>
+    </row>
+    <row r="8118" spans="1:1">
+      <c r="A8118" s="4" t="s">
+        <v>3937</v>
+      </c>
+    </row>
+    <row r="8119" spans="1:1">
+      <c r="A8119" s="4" t="s">
+        <v>3938</v>
+      </c>
+    </row>
+    <row r="8120" spans="1:1">
+      <c r="A8120" s="4" t="s">
+        <v>3939</v>
+      </c>
+    </row>
+    <row r="8121" spans="1:1">
+      <c r="A8121" s="4" t="s">
+        <v>3546</v>
+      </c>
+    </row>
+    <row r="8122" spans="1:1">
+      <c r="A8122" s="4" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="8123" spans="1:1">
+      <c r="A8123" s="4" t="s">
+        <v>3941</v>
+      </c>
+    </row>
+    <row r="8124" spans="1:1">
+      <c r="A8124" s="4" t="s">
+        <v>3942</v>
+      </c>
+    </row>
+    <row r="8125" spans="1:1">
+      <c r="A8125" s="4" t="s">
+        <v>3943</v>
+      </c>
+    </row>
+    <row r="8126" spans="1:1">
+      <c r="A8126" s="4" t="s">
+        <v>3944</v>
+      </c>
+    </row>
+    <row r="8127" spans="1:1">
+      <c r="A8127" s="4" t="s">
+        <v>2962</v>
+      </c>
+    </row>
+    <row r="8128" spans="1:1">
+      <c r="A8128" s="4" t="s">
+        <v>3945</v>
+      </c>
+    </row>
+    <row r="8129" spans="1:1">
+      <c r="A8129" s="4" t="s">
+        <v>3946</v>
+      </c>
+    </row>
+    <row r="8130" spans="1:1">
+      <c r="A8130" s="4" t="s">
+        <v>3947</v>
+      </c>
+    </row>
+    <row r="8131" spans="1:1">
+      <c r="A8131" s="4" t="s">
+        <v>3948</v>
+      </c>
+    </row>
+    <row r="8132" spans="1:1">
+      <c r="A8132" s="4" t="s">
+        <v>3949</v>
+      </c>
+    </row>
+    <row r="8133" spans="1:1">
+      <c r="A8133" s="4" t="s">
+        <v>3950</v>
+      </c>
+    </row>
+    <row r="8134" spans="1:1">
+      <c r="A8134" s="4" t="s">
+        <v>3951</v>
+      </c>
+    </row>
+    <row r="8135" spans="1:1">
+      <c r="A8135" s="4" t="s">
+        <v>3952</v>
+      </c>
+    </row>
+    <row r="8136" spans="1:1">
+      <c r="A8136" s="4" t="s">
+        <v>3953</v>
+      </c>
+    </row>
+    <row r="8137" spans="1:1">
+      <c r="A8137" s="4" t="s">
+        <v>3954</v>
+      </c>
+    </row>
+    <row r="8138" spans="1:1">
+      <c r="A8138" s="4" t="s">
+        <v>3955</v>
+      </c>
+    </row>
+    <row r="8139" spans="1:1">
+      <c r="A8139" s="4" t="s">
+        <v>3956</v>
+      </c>
+    </row>
+    <row r="8140" spans="1:1">
+      <c r="A8140" s="4" t="s">
+        <v>3957</v>
+      </c>
+    </row>
+    <row r="8141" spans="1:1">
+      <c r="A8141" s="4" t="s">
+        <v>3958</v>
+      </c>
+    </row>
+    <row r="8142" spans="1:1">
+      <c r="A8142" s="4" t="s">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="8143" spans="1:1">
+      <c r="A8143" s="4" t="s">
+        <v>3959</v>
+      </c>
+    </row>
+    <row r="8144" spans="1:1">
+      <c r="A8144" s="4" t="s">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="8145" spans="1:1">
+      <c r="A8145" s="4" t="s">
+        <v>3961</v>
+      </c>
+    </row>
+    <row r="8146" spans="1:1">
+      <c r="A8146" s="4" t="s">
+        <v>3962</v>
+      </c>
+    </row>
+    <row r="8147" spans="1:1">
+      <c r="A8147" s="4" t="s">
+        <v>3963</v>
+      </c>
+    </row>
+    <row r="8148" spans="1:1">
+      <c r="A8148" s="4" t="s">
+        <v>3964</v>
+      </c>
+    </row>
+    <row r="8149" spans="1:1">
+      <c r="A8149" s="4" t="s">
+        <v>3965</v>
+      </c>
+    </row>
+    <row r="8150" spans="1:1">
+      <c r="A8150" s="4" t="s">
+        <v>3966</v>
+      </c>
+    </row>
+    <row r="8151" spans="1:1">
+      <c r="A8151" s="4" t="s">
+        <v>3967</v>
+      </c>
+    </row>
+    <row r="8152" spans="1:1">
+      <c r="A8152" s="4" t="s">
+        <v>3968</v>
+      </c>
+    </row>
+    <row r="8153" spans="1:1">
+      <c r="A8153" s="4" t="s">
+        <v>3969</v>
+      </c>
+    </row>
+    <row r="8154" spans="1:1">
+      <c r="A8154" s="4" t="s">
+        <v>3970</v>
+      </c>
+    </row>
+    <row r="8155" spans="1:1">
+      <c r="A8155" s="4" t="s">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="8156" spans="1:1">
+      <c r="A8156" s="4" t="s">
+        <v>3972</v>
+      </c>
+    </row>
+    <row r="8157" spans="1:1">
+      <c r="A8157" s="4" t="s">
+        <v>3973</v>
+      </c>
+    </row>
+    <row r="8158" spans="1:1">
+      <c r="A8158" s="4" t="s">
+        <v>3974</v>
+      </c>
+    </row>
+    <row r="8159" spans="1:1">
+      <c r="A8159" s="4" t="s">
+        <v>3975</v>
+      </c>
+    </row>
+    <row r="8160" spans="1:1">
+      <c r="A8160" s="4" t="s">
+        <v>3976</v>
+      </c>
+    </row>
+    <row r="8161" spans="1:1">
+      <c r="A8161" s="4" t="s">
+        <v>3977</v>
+      </c>
+    </row>
+    <row r="8162" spans="1:1">
+      <c r="A8162" s="4" t="s">
+        <v>3978</v>
+      </c>
+    </row>
+    <row r="8163" spans="1:1">
+      <c r="A8163" s="4" t="s">
+        <v>3979</v>
+      </c>
+    </row>
+    <row r="8164" spans="1:1">
+      <c r="A8164" s="4" t="s">
+        <v>3980</v>
+      </c>
+    </row>
+    <row r="8165" spans="1:1">
+      <c r="A8165" s="4" t="s">
+        <v>3236</v>
+      </c>
+    </row>
+    <row r="8166" spans="1:1">
+      <c r="A8166" s="4" t="s">
+        <v>2886</v>
+      </c>
+    </row>
+    <row r="8167" spans="1:1">
+      <c r="A8167" s="4" t="s">
+        <v>3981</v>
+      </c>
+    </row>
+    <row r="8168" spans="1:1">
+      <c r="A8168" s="4" t="s">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="8169" spans="1:1">
+      <c r="A8169" s="4" t="s">
+        <v>3982</v>
+      </c>
+    </row>
+    <row r="8170" spans="1:1">
+      <c r="A8170" s="4" t="s">
+        <v>3983</v>
+      </c>
+    </row>
+    <row r="8171" spans="1:1">
+      <c r="A8171" s="4" t="s">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="8172" spans="1:1">
+      <c r="A8172" s="4" t="s">
+        <v>3232</v>
+      </c>
+    </row>
+    <row r="8173" spans="1:1">
+      <c r="A8173" s="4" t="s">
+        <v>3985</v>
+      </c>
+    </row>
+    <row r="8174" spans="1:1">
+      <c r="A8174" s="4" t="s">
+        <v>2675</v>
+      </c>
+    </row>
+    <row r="8175" spans="1:1">
+      <c r="A8175" s="4" t="s">
+        <v>3986</v>
+      </c>
+    </row>
+    <row r="8176" spans="1:1">
+      <c r="A8176" s="4" t="s">
+        <v>3987</v>
+      </c>
+    </row>
+    <row r="8177" spans="1:1">
+      <c r="A8177" s="4" t="s">
+        <v>3988</v>
+      </c>
+    </row>
+    <row r="8178" spans="1:1">
+      <c r="A8178" s="4" t="s">
+        <v>3989</v>
+      </c>
+    </row>
+    <row r="8179" spans="1:1">
+      <c r="A8179" s="4" t="s">
+        <v>3990</v>
+      </c>
+    </row>
+    <row r="8180" spans="1:1">
+      <c r="A8180" s="4" t="s">
+        <v>3991</v>
+      </c>
+    </row>
+    <row r="8181" spans="1:1">
+      <c r="A8181" s="4" t="s">
+        <v>3992</v>
+      </c>
+    </row>
+    <row r="8182" spans="1:1">
+      <c r="A8182" s="4" t="s">
+        <v>3993</v>
+      </c>
+    </row>
+    <row r="8183" spans="1:1">
+      <c r="A8183" s="4" t="s">
+        <v>3994</v>
+      </c>
+    </row>
+    <row r="8184" spans="1:1">
+      <c r="A8184" s="4" t="s">
+        <v>3995</v>
+      </c>
+    </row>
+    <row r="8185" spans="1:1">
+      <c r="A8185" s="4" t="s">
+        <v>3996</v>
+      </c>
+    </row>
+    <row r="8186" spans="1:1">
+      <c r="A8186" s="4" t="s">
+        <v>3997</v>
+      </c>
+    </row>
+    <row r="8187" spans="1:1">
+      <c r="A8187" s="4" t="s">
+        <v>3998</v>
+      </c>
+    </row>
+    <row r="8188" spans="1:1">
+      <c r="A8188" s="4" t="s">
+        <v>3999</v>
+      </c>
+    </row>
+    <row r="8189" spans="1:1">
+      <c r="A8189" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="8190" spans="1:1">
+      <c r="A8190" s="4" t="s">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="8191" spans="1:1">
+      <c r="A8191" s="4" t="s">
+        <v>4002</v>
+      </c>
+    </row>
+    <row r="8192" spans="1:1">
+      <c r="A8192" s="4" t="s">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="8193" spans="1:1">
+      <c r="A8193" s="4" t="s">
+        <v>4004</v>
+      </c>
+    </row>
+    <row r="8194" spans="1:1">
+      <c r="A8194" s="4" t="s">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="8195" spans="1:1">
+      <c r="A8195" s="4" t="s">
+        <v>4006</v>
+      </c>
+    </row>
+    <row r="8196" spans="1:1">
+      <c r="A8196" s="4" t="s">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="8197" spans="1:1">
+      <c r="A8197" s="4" t="s">
+        <v>4008</v>
+      </c>
+    </row>
+    <row r="8198" spans="1:1">
+      <c r="A8198" s="4" t="s">
+        <v>4009</v>
+      </c>
+    </row>
+    <row r="8199" spans="1:1">
+      <c r="A8199" s="4" t="s">
+        <v>4010</v>
+      </c>
+    </row>
+    <row r="8200" spans="1:1">
+      <c r="A8200" s="4" t="s">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="8201" spans="1:1">
+      <c r="A8201" s="4" t="s">
+        <v>4012</v>
+      </c>
+    </row>
+    <row r="8202" spans="1:1">
+      <c r="A8202" s="4" t="s">
+        <v>3199</v>
+      </c>
+    </row>
+    <row r="8203" spans="1:1">
+      <c r="A8203" s="4" t="s">
+        <v>4013</v>
+      </c>
+    </row>
+    <row r="8204" spans="1:1">
+      <c r="A8204" s="4" t="s">
+        <v>4014</v>
+      </c>
+    </row>
+    <row r="8205" spans="1:1">
+      <c r="A8205" s="4" t="s">
+        <v>4015</v>
+      </c>
+    </row>
+    <row r="8206" spans="1:1">
+      <c r="A8206" s="4" t="s">
+        <v>4016</v>
+      </c>
+    </row>
+    <row r="8207" spans="1:1">
+      <c r="A8207" s="4" t="s">
+        <v>4017</v>
       </c>
     </row>
   </sheetData>

--- a/nicknames.xlsx
+++ b/nicknames.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$A$7839</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$A$8207</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8207" uniqueCount="4227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8517" uniqueCount="4363">
   <si>
     <t>name</t>
   </si>
@@ -12711,6 +12711,414 @@
   </si>
   <si>
     <t>贝贝</t>
+  </si>
+  <si>
+    <t>烤鸭</t>
+  </si>
+  <si>
+    <t>可可纳</t>
+  </si>
+  <si>
+    <t>青柏</t>
+  </si>
+  <si>
+    <t>馄饨</t>
+  </si>
+  <si>
+    <t>蘅芜</t>
+  </si>
+  <si>
+    <t>玄粟</t>
+  </si>
+  <si>
+    <t>老啤</t>
+  </si>
+  <si>
+    <t>布欧</t>
+  </si>
+  <si>
+    <t>梓树</t>
+  </si>
+  <si>
+    <t>青梨</t>
+  </si>
+  <si>
+    <t>滑马</t>
+  </si>
+  <si>
+    <t>哪吒</t>
+  </si>
+  <si>
+    <t>飞鸟</t>
+  </si>
+  <si>
+    <t>黛西</t>
+  </si>
+  <si>
+    <t>嘉月</t>
+  </si>
+  <si>
+    <t>艾达</t>
+  </si>
+  <si>
+    <t>鸭脚木</t>
+  </si>
+  <si>
+    <t>扭扭糖</t>
+  </si>
+  <si>
+    <t>快乐星猫</t>
+  </si>
+  <si>
+    <t>爬山虎</t>
+  </si>
+  <si>
+    <t>瓦松</t>
+  </si>
+  <si>
+    <t>芋薯</t>
+  </si>
+  <si>
+    <t>橙子桃</t>
+  </si>
+  <si>
+    <t>艾尼路</t>
+  </si>
+  <si>
+    <t>卡卡</t>
+  </si>
+  <si>
+    <t>圆圈</t>
+  </si>
+  <si>
+    <t>阿莫克</t>
+  </si>
+  <si>
+    <t>猪脚粉</t>
+  </si>
+  <si>
+    <t>夏饭</t>
+  </si>
+  <si>
+    <t>苍狼</t>
+  </si>
+  <si>
+    <t>鱼尾</t>
+  </si>
+  <si>
+    <t>芒草</t>
+  </si>
+  <si>
+    <t>子青</t>
+  </si>
+  <si>
+    <t>大猫</t>
+  </si>
+  <si>
+    <t>椰子蟹</t>
+  </si>
+  <si>
+    <t>观澜</t>
+  </si>
+  <si>
+    <t>仔姜</t>
+  </si>
+  <si>
+    <t>白掌</t>
+  </si>
+  <si>
+    <t>格鲁特</t>
+  </si>
+  <si>
+    <t>仲夏</t>
+  </si>
+  <si>
+    <t>芙莉莲</t>
+  </si>
+  <si>
+    <t>南风</t>
+  </si>
+  <si>
+    <t>猫呦</t>
+  </si>
+  <si>
+    <t>拉布</t>
+  </si>
+  <si>
+    <t>寻木</t>
+  </si>
+  <si>
+    <t>寒露</t>
+  </si>
+  <si>
+    <t>馓子</t>
+  </si>
+  <si>
+    <t>玄离</t>
+  </si>
+  <si>
+    <t>河狸</t>
+  </si>
+  <si>
+    <t>凤梨酥</t>
+  </si>
+  <si>
+    <t>Figgy Wu</t>
+  </si>
+  <si>
+    <t>Hoihoi Chen</t>
+  </si>
+  <si>
+    <t>希言</t>
+  </si>
+  <si>
+    <t>加柠</t>
+  </si>
+  <si>
+    <t>兮叶</t>
+  </si>
+  <si>
+    <t>老铲</t>
+  </si>
+  <si>
+    <t>青榕</t>
+  </si>
+  <si>
+    <t>星萤</t>
+  </si>
+  <si>
+    <t>布隆</t>
+  </si>
+  <si>
+    <t>小舟</t>
+  </si>
+  <si>
+    <t>岚岚</t>
+  </si>
+  <si>
+    <t>梓木</t>
+  </si>
+  <si>
+    <t>德克士</t>
+  </si>
+  <si>
+    <t>皮克斯</t>
+  </si>
+  <si>
+    <t>波吉</t>
+  </si>
+  <si>
+    <t>Dr. Pepper</t>
+  </si>
+  <si>
+    <t>燕回</t>
+  </si>
+  <si>
+    <t>露可</t>
+  </si>
+  <si>
+    <t>鼠尾草</t>
+  </si>
+  <si>
+    <t>椰子水</t>
+  </si>
+  <si>
+    <t>熊大</t>
+  </si>
+  <si>
+    <t>带土</t>
+  </si>
+  <si>
+    <t>糖芋</t>
+  </si>
+  <si>
+    <t>焖饼</t>
+  </si>
+  <si>
+    <t>米澄</t>
+  </si>
+  <si>
+    <t>立夏</t>
+  </si>
+  <si>
+    <t>挽风</t>
+  </si>
+  <si>
+    <t>青蘅</t>
+  </si>
+  <si>
+    <t>摩西</t>
+  </si>
+  <si>
+    <t>糯米团子</t>
+  </si>
+  <si>
+    <t>吉伊</t>
+  </si>
+  <si>
+    <t>岩仓玲音</t>
+  </si>
+  <si>
+    <t>拓森</t>
+  </si>
+  <si>
+    <t>迪迪裤</t>
+  </si>
+  <si>
+    <t>玉兰</t>
+  </si>
+  <si>
+    <t>指环王</t>
+  </si>
+  <si>
+    <t>大马猴</t>
+  </si>
+  <si>
+    <t>赤道樱草</t>
+  </si>
+  <si>
+    <t>鱼干</t>
+  </si>
+  <si>
+    <t>鱼鱼</t>
+  </si>
+  <si>
+    <t>源稚生</t>
+  </si>
+  <si>
+    <t>脆脆冰</t>
+  </si>
+  <si>
+    <t>鲁本王</t>
+  </si>
+  <si>
+    <t>赤练</t>
+  </si>
+  <si>
+    <t>冰禾</t>
+  </si>
+  <si>
+    <t>赤兔</t>
+  </si>
+  <si>
+    <t>仙桃</t>
+  </si>
+  <si>
+    <t>东篱</t>
+  </si>
+  <si>
+    <t>小千</t>
+  </si>
+  <si>
+    <t>龙柏</t>
+  </si>
+  <si>
+    <t>鱼掌</t>
+  </si>
+  <si>
+    <t>弧光</t>
+  </si>
+  <si>
+    <t>米钱</t>
+  </si>
+  <si>
+    <t>竹里</t>
+  </si>
+  <si>
+    <t>望潮</t>
+  </si>
+  <si>
+    <t>观夏</t>
+  </si>
+  <si>
+    <t>胡蜂</t>
+  </si>
+  <si>
+    <t>云松</t>
+  </si>
+  <si>
+    <t>蛋烘糕</t>
+  </si>
+  <si>
+    <t>乌尔苏拉</t>
+  </si>
+  <si>
+    <t>青石</t>
+  </si>
+  <si>
+    <t>维克</t>
+  </si>
+  <si>
+    <t>米菲</t>
+  </si>
+  <si>
+    <t>小暑</t>
+  </si>
+  <si>
+    <t>粥粥</t>
+  </si>
+  <si>
+    <t>精卫</t>
+  </si>
+  <si>
+    <t>弘毅</t>
+  </si>
+  <si>
+    <t>洛克斯</t>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+  </si>
+  <si>
+    <t>迦蓝</t>
+  </si>
+  <si>
+    <t>瓦力</t>
+  </si>
+  <si>
+    <t>赤羚</t>
+  </si>
+  <si>
+    <t>麦糯</t>
+  </si>
+  <si>
+    <t>路明非</t>
+  </si>
+  <si>
+    <t>左乐</t>
+  </si>
+  <si>
+    <t>子昭</t>
+  </si>
+  <si>
+    <t>岩蜂</t>
+  </si>
+  <si>
+    <t>蓝白</t>
+  </si>
+  <si>
+    <t>东锦</t>
+  </si>
+  <si>
+    <t>鱼籽</t>
+  </si>
+  <si>
+    <t>黄鹤</t>
+  </si>
+  <si>
+    <t>莴笋</t>
+  </si>
+  <si>
+    <t>虹猫</t>
+  </si>
+  <si>
+    <t>星禾</t>
+  </si>
+  <si>
+    <t>兰茜</t>
+  </si>
+  <si>
+    <t>春和</t>
   </si>
 </sst>
 </file>
@@ -13324,7 +13732,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -13334,6 +13742,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -13696,7 +14107,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A8207"/>
+  <dimension ref="A1:A8518"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="19.3166666666667" style="1" customWidth="1"/>
@@ -54737,8 +55148,1561 @@
         <v>4017</v>
       </c>
     </row>
+    <row r="8208" spans="1:1">
+      <c r="A8208" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8209" spans="1:1">
+      <c r="A8209" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8210" spans="1:1">
+      <c r="A8210" s="5" t="s">
+        <v>4227</v>
+      </c>
+    </row>
+    <row r="8211" spans="1:1">
+      <c r="A8211" s="5" t="s">
+        <v>4228</v>
+      </c>
+    </row>
+    <row r="8212" spans="1:1">
+      <c r="A8212" s="5" t="s">
+        <v>4229</v>
+      </c>
+    </row>
+    <row r="8213" spans="1:1">
+      <c r="A8213" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8214" spans="1:1">
+      <c r="A8214" s="5" t="s">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="8215" spans="1:1">
+      <c r="A8215" s="5" t="s">
+        <v>4231</v>
+      </c>
+    </row>
+    <row r="8216" spans="1:1">
+      <c r="A8216" s="5" t="s">
+        <v>4232</v>
+      </c>
+    </row>
+    <row r="8217" spans="1:1">
+      <c r="A8217" s="5" t="s">
+        <v>4233</v>
+      </c>
+    </row>
+    <row r="8218" spans="1:1">
+      <c r="A8218" s="5" t="s">
+        <v>4234</v>
+      </c>
+    </row>
+    <row r="8219" spans="1:1">
+      <c r="A8219" s="5" t="s">
+        <v>4235</v>
+      </c>
+    </row>
+    <row r="8220" spans="1:1">
+      <c r="A8220" s="5" t="s">
+        <v>4236</v>
+      </c>
+    </row>
+    <row r="8221" spans="1:1">
+      <c r="A8221" s="5" t="s">
+        <v>4237</v>
+      </c>
+    </row>
+    <row r="8222" spans="1:1">
+      <c r="A8222" s="5" t="s">
+        <v>4238</v>
+      </c>
+    </row>
+    <row r="8223" spans="1:1">
+      <c r="A8223" s="5" t="s">
+        <v>4239</v>
+      </c>
+    </row>
+    <row r="8224" spans="1:1">
+      <c r="A8224" s="5" t="s">
+        <v>4240</v>
+      </c>
+    </row>
+    <row r="8225" spans="1:1">
+      <c r="A8225" s="5" t="s">
+        <v>4241</v>
+      </c>
+    </row>
+    <row r="8226" spans="1:1">
+      <c r="A8226" s="5" t="s">
+        <v>4242</v>
+      </c>
+    </row>
+    <row r="8227" spans="1:1">
+      <c r="A8227" s="5" t="s">
+        <v>4243</v>
+      </c>
+    </row>
+    <row r="8228" spans="1:1">
+      <c r="A8228" s="5" t="s">
+        <v>4244</v>
+      </c>
+    </row>
+    <row r="8229" spans="1:1">
+      <c r="A8229" s="5" t="s">
+        <v>4245</v>
+      </c>
+    </row>
+    <row r="8230" spans="1:1">
+      <c r="A8230" s="5" t="s">
+        <v>4246</v>
+      </c>
+    </row>
+    <row r="8231" spans="1:1">
+      <c r="A8231" s="5" t="s">
+        <v>4247</v>
+      </c>
+    </row>
+    <row r="8232" spans="1:1">
+      <c r="A8232" s="5" t="s">
+        <v>4248</v>
+      </c>
+    </row>
+    <row r="8233" spans="1:1">
+      <c r="A8233" s="5" t="s">
+        <v>4249</v>
+      </c>
+    </row>
+    <row r="8234" spans="1:1">
+      <c r="A8234" s="5" t="s">
+        <v>4250</v>
+      </c>
+    </row>
+    <row r="8235" spans="1:1">
+      <c r="A8235" s="5" t="s">
+        <v>4251</v>
+      </c>
+    </row>
+    <row r="8236" spans="1:1">
+      <c r="A8236" s="5" t="s">
+        <v>4252</v>
+      </c>
+    </row>
+    <row r="8237" spans="1:1">
+      <c r="A8237" s="5" t="s">
+        <v>4253</v>
+      </c>
+    </row>
+    <row r="8238" spans="1:1">
+      <c r="A8238" s="5" t="s">
+        <v>4254</v>
+      </c>
+    </row>
+    <row r="8239" spans="1:1">
+      <c r="A8239" s="5" t="s">
+        <v>4255</v>
+      </c>
+    </row>
+    <row r="8240" spans="1:1">
+      <c r="A8240" s="5" t="s">
+        <v>4256</v>
+      </c>
+    </row>
+    <row r="8241" spans="1:1">
+      <c r="A8241" s="5" t="s">
+        <v>4257</v>
+      </c>
+    </row>
+    <row r="8242" spans="1:1">
+      <c r="A8242" s="5" t="s">
+        <v>4258</v>
+      </c>
+    </row>
+    <row r="8243" spans="1:1">
+      <c r="A8243" s="5" t="s">
+        <v>4035</v>
+      </c>
+    </row>
+    <row r="8244" spans="1:1">
+      <c r="A8244" s="5" t="s">
+        <v>4259</v>
+      </c>
+    </row>
+    <row r="8245" spans="1:1">
+      <c r="A8245" s="5" t="s">
+        <v>4260</v>
+      </c>
+    </row>
+    <row r="8246" spans="1:1">
+      <c r="A8246" s="5" t="s">
+        <v>4261</v>
+      </c>
+    </row>
+    <row r="8247" spans="1:1">
+      <c r="A8247" s="5" t="s">
+        <v>4262</v>
+      </c>
+    </row>
+    <row r="8248" spans="1:1">
+      <c r="A8248" s="5" t="s">
+        <v>4263</v>
+      </c>
+    </row>
+    <row r="8249" spans="1:1">
+      <c r="A8249" s="5" t="s">
+        <v>4264</v>
+      </c>
+    </row>
+    <row r="8250" spans="1:1">
+      <c r="A8250" s="5" t="s">
+        <v>4265</v>
+      </c>
+    </row>
+    <row r="8251" spans="1:1">
+      <c r="A8251" s="5" t="s">
+        <v>4266</v>
+      </c>
+    </row>
+    <row r="8252" spans="1:1">
+      <c r="A8252" s="5" t="s">
+        <v>4267</v>
+      </c>
+    </row>
+    <row r="8253" spans="1:1">
+      <c r="A8253" s="5" t="s">
+        <v>4268</v>
+      </c>
+    </row>
+    <row r="8254" spans="1:1">
+      <c r="A8254" s="5" t="s">
+        <v>4269</v>
+      </c>
+    </row>
+    <row r="8255" spans="1:1">
+      <c r="A8255" s="5" t="s">
+        <v>4270</v>
+      </c>
+    </row>
+    <row r="8256" spans="1:1">
+      <c r="A8256" s="5" t="s">
+        <v>4271</v>
+      </c>
+    </row>
+    <row r="8257" spans="1:1">
+      <c r="A8257" s="5" t="s">
+        <v>4272</v>
+      </c>
+    </row>
+    <row r="8258" spans="1:1">
+      <c r="A8258" s="5" t="s">
+        <v>4273</v>
+      </c>
+    </row>
+    <row r="8259" spans="1:1">
+      <c r="A8259" s="5" t="s">
+        <v>4274</v>
+      </c>
+    </row>
+    <row r="8260" spans="1:1">
+      <c r="A8260" s="5" t="s">
+        <v>4275</v>
+      </c>
+    </row>
+    <row r="8261" spans="1:1">
+      <c r="A8261" s="5" t="s">
+        <v>4276</v>
+      </c>
+    </row>
+    <row r="8262" spans="1:1">
+      <c r="A8262" s="5" t="s">
+        <v>4277</v>
+      </c>
+    </row>
+    <row r="8263" spans="1:1">
+      <c r="A8263" s="5" t="s">
+        <v>4278</v>
+      </c>
+    </row>
+    <row r="8264" spans="1:1">
+      <c r="A8264" s="5" t="s">
+        <v>4279</v>
+      </c>
+    </row>
+    <row r="8265" spans="1:1">
+      <c r="A8265" s="5" t="s">
+        <v>4280</v>
+      </c>
+    </row>
+    <row r="8266" spans="1:1">
+      <c r="A8266" s="5" t="s">
+        <v>4281</v>
+      </c>
+    </row>
+    <row r="8267" spans="1:1">
+      <c r="A8267" s="5" t="s">
+        <v>4282</v>
+      </c>
+    </row>
+    <row r="8268" spans="1:1">
+      <c r="A8268" s="5" t="s">
+        <v>4283</v>
+      </c>
+    </row>
+    <row r="8269" spans="1:1">
+      <c r="A8269" s="5" t="s">
+        <v>4284</v>
+      </c>
+    </row>
+    <row r="8270" spans="1:1">
+      <c r="A8270" s="5" t="s">
+        <v>4285</v>
+      </c>
+    </row>
+    <row r="8271" spans="1:1">
+      <c r="A8271" s="5" t="s">
+        <v>4286</v>
+      </c>
+    </row>
+    <row r="8272" spans="1:1">
+      <c r="A8272" s="5" t="s">
+        <v>4287</v>
+      </c>
+    </row>
+    <row r="8273" spans="1:1">
+      <c r="A8273" s="5" t="s">
+        <v>4288</v>
+      </c>
+    </row>
+    <row r="8274" spans="1:1">
+      <c r="A8274" s="5" t="s">
+        <v>4289</v>
+      </c>
+    </row>
+    <row r="8275" spans="1:1">
+      <c r="A8275" s="5" t="s">
+        <v>4290</v>
+      </c>
+    </row>
+    <row r="8276" spans="1:1">
+      <c r="A8276" s="5" t="s">
+        <v>4291</v>
+      </c>
+    </row>
+    <row r="8277" spans="1:1">
+      <c r="A8277" s="5" t="s">
+        <v>4292</v>
+      </c>
+    </row>
+    <row r="8278" spans="1:1">
+      <c r="A8278" s="5" t="s">
+        <v>4293</v>
+      </c>
+    </row>
+    <row r="8279" spans="1:1">
+      <c r="A8279" s="5" t="s">
+        <v>4294</v>
+      </c>
+    </row>
+    <row r="8280" spans="1:1">
+      <c r="A8280" s="5" t="s">
+        <v>4295</v>
+      </c>
+    </row>
+    <row r="8281" spans="1:1">
+      <c r="A8281" s="5" t="s">
+        <v>4036</v>
+      </c>
+    </row>
+    <row r="8282" spans="1:1">
+      <c r="A8282" s="5" t="s">
+        <v>4296</v>
+      </c>
+    </row>
+    <row r="8283" spans="1:1">
+      <c r="A8283" s="5" t="s">
+        <v>4297</v>
+      </c>
+    </row>
+    <row r="8284" spans="1:1">
+      <c r="A8284" s="5" t="s">
+        <v>4298</v>
+      </c>
+    </row>
+    <row r="8285" spans="1:1">
+      <c r="A8285" s="5" t="s">
+        <v>4299</v>
+      </c>
+    </row>
+    <row r="8286" spans="1:1">
+      <c r="A8286" s="5" t="s">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="8287" spans="1:1">
+      <c r="A8287" s="5" t="s">
+        <v>4301</v>
+      </c>
+    </row>
+    <row r="8288" spans="1:1">
+      <c r="A8288" s="5" t="s">
+        <v>4302</v>
+      </c>
+    </row>
+    <row r="8289" spans="1:1">
+      <c r="A8289" s="5" t="s">
+        <v>4303</v>
+      </c>
+    </row>
+    <row r="8290" spans="1:1">
+      <c r="A8290" s="5" t="s">
+        <v>4304</v>
+      </c>
+    </row>
+    <row r="8291" spans="1:1">
+      <c r="A8291" s="5" t="s">
+        <v>4305</v>
+      </c>
+    </row>
+    <row r="8292" spans="1:1">
+      <c r="A8292" s="5" t="s">
+        <v>4306</v>
+      </c>
+    </row>
+    <row r="8293" spans="1:1">
+      <c r="A8293" s="5" t="s">
+        <v>4307</v>
+      </c>
+    </row>
+    <row r="8294" spans="1:1">
+      <c r="A8294" s="5" t="s">
+        <v>4308</v>
+      </c>
+    </row>
+    <row r="8295" spans="1:1">
+      <c r="A8295" s="5" t="s">
+        <v>4309</v>
+      </c>
+    </row>
+    <row r="8296" spans="1:1">
+      <c r="A8296" s="5" t="s">
+        <v>4310</v>
+      </c>
+    </row>
+    <row r="8297" spans="1:1">
+      <c r="A8297" s="5" t="s">
+        <v>4311</v>
+      </c>
+    </row>
+    <row r="8298" spans="1:1">
+      <c r="A8298" s="5" t="s">
+        <v>4312</v>
+      </c>
+    </row>
+    <row r="8299" spans="1:1">
+      <c r="A8299" s="5" t="s">
+        <v>4313</v>
+      </c>
+    </row>
+    <row r="8300" spans="1:1">
+      <c r="A8300" s="5" t="s">
+        <v>4314</v>
+      </c>
+    </row>
+    <row r="8301" spans="1:1">
+      <c r="A8301" s="5" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="8302" spans="1:1">
+      <c r="A8302" s="5" t="s">
+        <v>4316</v>
+      </c>
+    </row>
+    <row r="8303" spans="1:1">
+      <c r="A8303" s="5" t="s">
+        <v>4317</v>
+      </c>
+    </row>
+    <row r="8304" spans="1:1">
+      <c r="A8304" s="5" t="s">
+        <v>4318</v>
+      </c>
+    </row>
+    <row r="8305" spans="1:1">
+      <c r="A8305" s="5" t="s">
+        <v>4319</v>
+      </c>
+    </row>
+    <row r="8306" spans="1:1">
+      <c r="A8306" s="5" t="s">
+        <v>4320</v>
+      </c>
+    </row>
+    <row r="8307" spans="1:1">
+      <c r="A8307" s="5" t="s">
+        <v>4321</v>
+      </c>
+    </row>
+    <row r="8308" spans="1:1">
+      <c r="A8308" s="5" t="s">
+        <v>4322</v>
+      </c>
+    </row>
+    <row r="8309" spans="1:1">
+      <c r="A8309" s="5" t="s">
+        <v>4323</v>
+      </c>
+    </row>
+    <row r="8310" spans="1:1">
+      <c r="A8310" s="5" t="s">
+        <v>4324</v>
+      </c>
+    </row>
+    <row r="8311" spans="1:1">
+      <c r="A8311" s="5" t="s">
+        <v>4325</v>
+      </c>
+    </row>
+    <row r="8312" spans="1:1">
+      <c r="A8312" s="5" t="s">
+        <v>4326</v>
+      </c>
+    </row>
+    <row r="8313" spans="1:1">
+      <c r="A8313" s="5" t="s">
+        <v>4327</v>
+      </c>
+    </row>
+    <row r="8314" spans="1:1">
+      <c r="A8314" s="5" t="s">
+        <v>4328</v>
+      </c>
+    </row>
+    <row r="8315" spans="1:1">
+      <c r="A8315" s="5" t="s">
+        <v>4329</v>
+      </c>
+    </row>
+    <row r="8316" spans="1:1">
+      <c r="A8316" s="5" t="s">
+        <v>4038</v>
+      </c>
+    </row>
+    <row r="8317" spans="1:1">
+      <c r="A8317" s="5" t="s">
+        <v>4330</v>
+      </c>
+    </row>
+    <row r="8318" spans="1:1">
+      <c r="A8318" s="5" t="s">
+        <v>4331</v>
+      </c>
+    </row>
+    <row r="8319" spans="1:1">
+      <c r="A8319" s="5" t="s">
+        <v>4332</v>
+      </c>
+    </row>
+    <row r="8320" spans="1:1">
+      <c r="A8320" s="5" t="s">
+        <v>4333</v>
+      </c>
+    </row>
+    <row r="8321" spans="1:1">
+      <c r="A8321" s="5" t="s">
+        <v>4334</v>
+      </c>
+    </row>
+    <row r="8322" spans="1:1">
+      <c r="A8322" s="5" t="s">
+        <v>4335</v>
+      </c>
+    </row>
+    <row r="8323" spans="1:1">
+      <c r="A8323" s="5" t="s">
+        <v>4336</v>
+      </c>
+    </row>
+    <row r="8324" spans="1:1">
+      <c r="A8324" s="5" t="s">
+        <v>4337</v>
+      </c>
+    </row>
+    <row r="8325" spans="1:1">
+      <c r="A8325" s="5" t="s">
+        <v>4338</v>
+      </c>
+    </row>
+    <row r="8326" spans="1:1">
+      <c r="A8326" s="5" t="s">
+        <v>4339</v>
+      </c>
+    </row>
+    <row r="8327" spans="1:1">
+      <c r="A8327" s="5" t="s">
+        <v>4340</v>
+      </c>
+    </row>
+    <row r="8328" spans="1:1">
+      <c r="A8328" s="5" t="s">
+        <v>4039</v>
+      </c>
+    </row>
+    <row r="8329" spans="1:1">
+      <c r="A8329" s="5" t="s">
+        <v>4341</v>
+      </c>
+    </row>
+    <row r="8330" spans="1:1">
+      <c r="A8330" s="5" t="s">
+        <v>4342</v>
+      </c>
+    </row>
+    <row r="8331" spans="1:1">
+      <c r="A8331" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8332" spans="1:1">
+      <c r="A8332" s="5" t="s">
+        <v>4343</v>
+      </c>
+    </row>
+    <row r="8333" spans="1:1">
+      <c r="A8333" s="5" t="s">
+        <v>4344</v>
+      </c>
+    </row>
+    <row r="8334" spans="1:1">
+      <c r="A8334" s="5" t="s">
+        <v>4345</v>
+      </c>
+    </row>
+    <row r="8335" spans="1:1">
+      <c r="A8335" s="5" t="s">
+        <v>4346</v>
+      </c>
+    </row>
+    <row r="8336" spans="1:1">
+      <c r="A8336" s="5" t="s">
+        <v>4347</v>
+      </c>
+    </row>
+    <row r="8337" spans="1:1">
+      <c r="A8337" s="5" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="8338" spans="1:1">
+      <c r="A8338" s="5" t="s">
+        <v>4349</v>
+      </c>
+    </row>
+    <row r="8339" spans="1:1">
+      <c r="A8339" s="5" t="s">
+        <v>4350</v>
+      </c>
+    </row>
+    <row r="8340" spans="1:1">
+      <c r="A8340" s="5" t="s">
+        <v>4351</v>
+      </c>
+    </row>
+    <row r="8341" spans="1:1">
+      <c r="A8341" s="5" t="s">
+        <v>4352</v>
+      </c>
+    </row>
+    <row r="8342" spans="1:1">
+      <c r="A8342" s="5" t="s">
+        <v>4353</v>
+      </c>
+    </row>
+    <row r="8343" spans="1:1">
+      <c r="A8343" s="5" t="s">
+        <v>4354</v>
+      </c>
+    </row>
+    <row r="8344" spans="1:1">
+      <c r="A8344" s="5" t="s">
+        <v>4046</v>
+      </c>
+    </row>
+    <row r="8345" spans="1:1">
+      <c r="A8345" s="5" t="s">
+        <v>4041</v>
+      </c>
+    </row>
+    <row r="8346" spans="1:1">
+      <c r="A8346" s="5" t="s">
+        <v>4355</v>
+      </c>
+    </row>
+    <row r="8347" spans="1:1">
+      <c r="A8347" s="5" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="8348" spans="1:1">
+      <c r="A8348" s="5" t="s">
+        <v>4356</v>
+      </c>
+    </row>
+    <row r="8349" spans="1:1">
+      <c r="A8349" s="5" t="s">
+        <v>4357</v>
+      </c>
+    </row>
+    <row r="8350" spans="1:1">
+      <c r="A8350" s="5" t="s">
+        <v>4358</v>
+      </c>
+    </row>
+    <row r="8351" spans="1:1">
+      <c r="A8351" s="5" t="s">
+        <v>4359</v>
+      </c>
+    </row>
+    <row r="8352" spans="1:1">
+      <c r="A8352" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8353" spans="1:1">
+      <c r="A8353" s="5" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="8354" spans="1:1">
+      <c r="A8354" s="5" t="s">
+        <v>3544</v>
+      </c>
+    </row>
+    <row r="8355" spans="1:1">
+      <c r="A8355" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8356" spans="1:1">
+      <c r="A8356" s="5" t="s">
+        <v>3573</v>
+      </c>
+    </row>
+    <row r="8357" spans="1:1">
+      <c r="A8357" s="5" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="8358" spans="1:1">
+      <c r="A8358" s="5"/>
+    </row>
+    <row r="8359" spans="1:1">
+      <c r="A8359" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8360" spans="1:1">
+      <c r="A8360" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8361" spans="1:1">
+      <c r="A8361" s="5" t="s">
+        <v>3384</v>
+      </c>
+    </row>
+    <row r="8362" spans="1:1">
+      <c r="A8362" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8363" spans="1:1">
+      <c r="A8363" s="5" t="s">
+        <v>2807</v>
+      </c>
+    </row>
+    <row r="8364" spans="1:1">
+      <c r="A8364" s="5" t="s">
+        <v>4360</v>
+      </c>
+    </row>
+    <row r="8365" spans="1:1">
+      <c r="A8365" s="5" t="s">
+        <v>3549</v>
+      </c>
+    </row>
+    <row r="8366" spans="1:1">
+      <c r="A8366" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8367" spans="1:1">
+      <c r="A8367" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8368" spans="1:1">
+      <c r="A8368" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8369" spans="1:1">
+      <c r="A8369" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8370" spans="1:1">
+      <c r="A8370" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8371" spans="1:1">
+      <c r="A8371" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8372" spans="1:1">
+      <c r="A8372" s="5" t="s">
+        <v>3859</v>
+      </c>
+    </row>
+    <row r="8373" spans="1:1">
+      <c r="A8373" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8374" spans="1:1">
+      <c r="A8374" s="5" t="s">
+        <v>3702</v>
+      </c>
+    </row>
+    <row r="8375" spans="1:1">
+      <c r="A8375" s="5" t="s">
+        <v>3544</v>
+      </c>
+    </row>
+    <row r="8376" spans="1:1">
+      <c r="A8376" s="5" t="s">
+        <v>3544</v>
+      </c>
+    </row>
+    <row r="8377" spans="1:1">
+      <c r="A8377" s="5" t="s">
+        <v>3544</v>
+      </c>
+    </row>
+    <row r="8378" spans="1:1">
+      <c r="A8378" s="5" t="s">
+        <v>3549</v>
+      </c>
+    </row>
+    <row r="8379" spans="1:1">
+      <c r="A8379" s="5" t="s">
+        <v>3668</v>
+      </c>
+    </row>
+    <row r="8380" spans="1:1">
+      <c r="A8380" s="5" t="s">
+        <v>3668</v>
+      </c>
+    </row>
+    <row r="8381" spans="1:1">
+      <c r="A8381" s="5" t="s">
+        <v>4361</v>
+      </c>
+    </row>
+    <row r="8382" spans="1:1">
+      <c r="A8382" s="5" t="s">
+        <v>4361</v>
+      </c>
+    </row>
+    <row r="8383" spans="1:1">
+      <c r="A8383" s="5" t="s">
+        <v>4361</v>
+      </c>
+    </row>
+    <row r="8384" spans="1:1">
+      <c r="A8384" s="5" t="s">
+        <v>4361</v>
+      </c>
+    </row>
+    <row r="8385" spans="1:1">
+      <c r="A8385" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8386" spans="1:1">
+      <c r="A8386" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8387" spans="1:1">
+      <c r="A8387" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8388" spans="1:1">
+      <c r="A8388" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8389" spans="1:1">
+      <c r="A8389" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8390" spans="1:1">
+      <c r="A8390" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8391" spans="1:1">
+      <c r="A8391" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8392" spans="1:1">
+      <c r="A8392" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8393" spans="1:1">
+      <c r="A8393" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8394" spans="1:1">
+      <c r="A8394" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8395" spans="1:1">
+      <c r="A8395" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8396" spans="1:1">
+      <c r="A8396" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8397" spans="1:1">
+      <c r="A8397" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8398" spans="1:1">
+      <c r="A8398" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8399" spans="1:1">
+      <c r="A8399" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8400" spans="1:1">
+      <c r="A8400" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8401" spans="1:1">
+      <c r="A8401" s="5" t="s">
+        <v>3712</v>
+      </c>
+    </row>
+    <row r="8402" spans="1:1">
+      <c r="A8402" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8403" spans="1:1">
+      <c r="A8403" s="5" t="s">
+        <v>3712</v>
+      </c>
+    </row>
+    <row r="8404" spans="1:1">
+      <c r="A8404" s="5" t="s">
+        <v>3508</v>
+      </c>
+    </row>
+    <row r="8405" spans="1:1">
+      <c r="A8405" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8406" spans="1:1">
+      <c r="A8406" s="5" t="s">
+        <v>2712</v>
+      </c>
+    </row>
+    <row r="8407" spans="1:1">
+      <c r="A8407" s="5" t="s">
+        <v>3557</v>
+      </c>
+    </row>
+    <row r="8408" spans="1:1">
+      <c r="A8408" s="5" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="8409" spans="1:1">
+      <c r="A8409" s="5" t="s">
+        <v>4179</v>
+      </c>
+    </row>
+    <row r="8410" spans="1:1">
+      <c r="A8410" s="5" t="s">
+        <v>3522</v>
+      </c>
+    </row>
+    <row r="8411" spans="1:1">
+      <c r="A8411" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8412" spans="1:1">
+      <c r="A8412" s="5" t="s">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="8413" spans="1:1">
+      <c r="A8413" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8414" spans="1:1">
+      <c r="A8414" s="5" t="s">
+        <v>3749</v>
+      </c>
+    </row>
+    <row r="8415" spans="1:1">
+      <c r="A8415" s="5" t="s">
+        <v>3749</v>
+      </c>
+    </row>
+    <row r="8416" spans="1:1">
+      <c r="A8416" s="5" t="s">
+        <v>3749</v>
+      </c>
+    </row>
+    <row r="8417" spans="1:1">
+      <c r="A8417" s="5" t="s">
+        <v>3668</v>
+      </c>
+    </row>
+    <row r="8418" spans="1:1">
+      <c r="A8418" s="5" t="s">
+        <v>3668</v>
+      </c>
+    </row>
+    <row r="8419" spans="1:1">
+      <c r="A8419" s="5" t="s">
+        <v>3668</v>
+      </c>
+    </row>
+    <row r="8420" spans="1:1">
+      <c r="A8420" s="5" t="s">
+        <v>4180</v>
+      </c>
+    </row>
+    <row r="8421" spans="1:1">
+      <c r="A8421" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8422" spans="1:1">
+      <c r="A8422" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8423" spans="1:1">
+      <c r="A8423" s="5" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="8424" spans="1:1">
+      <c r="A8424" s="5" t="s">
+        <v>3675</v>
+      </c>
+    </row>
+    <row r="8425" spans="1:1">
+      <c r="A8425" s="5" t="s">
+        <v>3991</v>
+      </c>
+    </row>
+    <row r="8426" spans="1:1">
+      <c r="A8426" s="5" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="8427" spans="1:1">
+      <c r="A8427" s="5" t="s">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="8428" spans="1:1">
+      <c r="A8428" s="5" t="s">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="8429" spans="1:1">
+      <c r="A8429" s="5" t="s">
+        <v>3668</v>
+      </c>
+    </row>
+    <row r="8430" spans="1:1">
+      <c r="A8430" s="5" t="s">
+        <v>3668</v>
+      </c>
+    </row>
+    <row r="8431" spans="1:1">
+      <c r="A8431" s="5" t="s">
+        <v>3668</v>
+      </c>
+    </row>
+    <row r="8432" spans="1:1">
+      <c r="A8432" s="5" t="s">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="8433" spans="1:1">
+      <c r="A8433" s="5" t="s">
+        <v>3379</v>
+      </c>
+    </row>
+    <row r="8434" spans="1:1">
+      <c r="A8434" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8435" spans="1:1">
+      <c r="A8435" s="5" t="s">
+        <v>4180</v>
+      </c>
+    </row>
+    <row r="8436" spans="1:1">
+      <c r="A8436" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8437" spans="1:1">
+      <c r="A8437" s="5" t="s">
+        <v>4361</v>
+      </c>
+    </row>
+    <row r="8438" spans="1:1">
+      <c r="A8438" s="5" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="8439" spans="1:1">
+      <c r="A8439" s="5" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="8440" spans="1:1">
+      <c r="A8440" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8441" spans="1:1">
+      <c r="A8441" s="5" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="8442" spans="1:1">
+      <c r="A8442" s="5" t="s">
+        <v>3384</v>
+      </c>
+    </row>
+    <row r="8443" spans="1:1">
+      <c r="A8443" s="5" t="s">
+        <v>3666</v>
+      </c>
+    </row>
+    <row r="8444" spans="1:1">
+      <c r="A8444" s="5" t="s">
+        <v>2737</v>
+      </c>
+    </row>
+    <row r="8445" spans="1:1">
+      <c r="A8445" s="5" t="s">
+        <v>3532</v>
+      </c>
+    </row>
+    <row r="8446" spans="1:1">
+      <c r="A8446" s="5" t="s">
+        <v>3667</v>
+      </c>
+    </row>
+    <row r="8447" spans="1:1">
+      <c r="A8447" s="5" t="s">
+        <v>3334</v>
+      </c>
+    </row>
+    <row r="8448" spans="1:1">
+      <c r="A8448" s="5" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="8449" spans="1:1">
+      <c r="A8449" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8450" spans="1:1">
+      <c r="A8450" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8451" spans="1:1">
+      <c r="A8451" s="5" t="s">
+        <v>3388</v>
+      </c>
+    </row>
+    <row r="8452" spans="1:1">
+      <c r="A8452" s="5" t="s">
+        <v>3829</v>
+      </c>
+    </row>
+    <row r="8453" spans="1:1">
+      <c r="A8453" s="5" t="s">
+        <v>3507</v>
+      </c>
+    </row>
+    <row r="8454" spans="1:1">
+      <c r="A8454" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8455" spans="1:1">
+      <c r="A8455" s="5" t="s">
+        <v>4180</v>
+      </c>
+    </row>
+    <row r="8456" spans="1:1">
+      <c r="A8456" s="5" t="s">
+        <v>2807</v>
+      </c>
+    </row>
+    <row r="8457" spans="1:1">
+      <c r="A8457" s="5" t="s">
+        <v>3299</v>
+      </c>
+    </row>
+    <row r="8458" spans="1:1">
+      <c r="A8458" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8459" spans="1:1">
+      <c r="A8459" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8460" spans="1:1">
+      <c r="A8460" s="5" t="s">
+        <v>3557</v>
+      </c>
+    </row>
+    <row r="8461" spans="1:1">
+      <c r="A8461" s="5" t="s">
+        <v>3557</v>
+      </c>
+    </row>
+    <row r="8462" spans="1:1">
+      <c r="A8462" s="5" t="s">
+        <v>3557</v>
+      </c>
+    </row>
+    <row r="8463" spans="1:1">
+      <c r="A8463" s="5" t="s">
+        <v>3557</v>
+      </c>
+    </row>
+    <row r="8464" spans="1:1">
+      <c r="A8464" s="5" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="8465" spans="1:1">
+      <c r="A8465" s="5" t="s">
+        <v>3391</v>
+      </c>
+    </row>
+    <row r="8466" spans="1:1">
+      <c r="A8466" s="5" t="s">
+        <v>3557</v>
+      </c>
+    </row>
+    <row r="8467" spans="1:1">
+      <c r="A8467" s="5" t="s">
+        <v>3749</v>
+      </c>
+    </row>
+    <row r="8468" spans="1:1">
+      <c r="A8468" s="5" t="s">
+        <v>3749</v>
+      </c>
+    </row>
+    <row r="8469" spans="1:1">
+      <c r="A8469" s="5" t="s">
+        <v>4180</v>
+      </c>
+    </row>
+    <row r="8470" spans="1:1">
+      <c r="A8470" s="5" t="s">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="8471" spans="1:1">
+      <c r="A8471" s="5" t="s">
+        <v>4361</v>
+      </c>
+    </row>
+    <row r="8472" spans="1:1">
+      <c r="A8472" s="5" t="s">
+        <v>3381</v>
+      </c>
+    </row>
+    <row r="8473" spans="1:1">
+      <c r="A8473" s="5" t="s">
+        <v>3668</v>
+      </c>
+    </row>
+    <row r="8474" spans="1:1">
+      <c r="A8474" s="5" t="s">
+        <v>2729</v>
+      </c>
+    </row>
+    <row r="8475" spans="1:1">
+      <c r="A8475" s="5" t="s">
+        <v>3549</v>
+      </c>
+    </row>
+    <row r="8476" spans="1:1">
+      <c r="A8476" s="5" t="s">
+        <v>3549</v>
+      </c>
+    </row>
+    <row r="8477" spans="1:1">
+      <c r="A8477" s="5" t="s">
+        <v>3391</v>
+      </c>
+    </row>
+    <row r="8478" spans="1:1">
+      <c r="A8478" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8479" spans="1:1">
+      <c r="A8479" s="5" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="8480" spans="1:1">
+      <c r="A8480" s="5" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="8481" spans="1:1">
+      <c r="A8481" s="5" t="s">
+        <v>4180</v>
+      </c>
+    </row>
+    <row r="8482" spans="1:1">
+      <c r="A8482" s="5" t="s">
+        <v>4180</v>
+      </c>
+    </row>
+    <row r="8483" spans="1:1">
+      <c r="A8483" s="5" t="s">
+        <v>3412</v>
+      </c>
+    </row>
+    <row r="8484" spans="1:1">
+      <c r="A8484" s="5" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="8485" spans="1:1">
+      <c r="A8485" s="5" t="s">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="8486" spans="1:1">
+      <c r="A8486" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8487" spans="1:1">
+      <c r="A8487" s="5" t="s">
+        <v>4362</v>
+      </c>
+    </row>
+    <row r="8488" spans="1:1">
+      <c r="A8488" s="5" t="s">
+        <v>3992</v>
+      </c>
+    </row>
+    <row r="8489" spans="1:1">
+      <c r="A8489" s="5" t="s">
+        <v>3616</v>
+      </c>
+    </row>
+    <row r="8490" spans="1:1">
+      <c r="A8490" s="5" t="s">
+        <v>3616</v>
+      </c>
+    </row>
+    <row r="8491" spans="1:1">
+      <c r="A8491" s="5" t="s">
+        <v>3668</v>
+      </c>
+    </row>
+    <row r="8492" spans="1:1">
+      <c r="A8492" s="5" t="s">
+        <v>3749</v>
+      </c>
+    </row>
+    <row r="8493" spans="1:1">
+      <c r="A8493" s="5" t="s">
+        <v>3749</v>
+      </c>
+    </row>
+    <row r="8494" spans="1:1">
+      <c r="A8494" s="5" t="s">
+        <v>4361</v>
+      </c>
+    </row>
+    <row r="8495" spans="1:1">
+      <c r="A8495" s="5" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="8496" spans="1:1">
+      <c r="A8496" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8497" spans="1:1">
+      <c r="A8497" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8498" spans="1:1">
+      <c r="A8498" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8499" spans="1:1">
+      <c r="A8499" s="5" t="s">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="8500" spans="1:1">
+      <c r="A8500" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8501" spans="1:1">
+      <c r="A8501" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8502" spans="1:1">
+      <c r="A8502" s="5" t="s">
+        <v>3749</v>
+      </c>
+    </row>
+    <row r="8503" spans="1:1">
+      <c r="A8503" s="5" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="8504" spans="1:1">
+      <c r="A8504" s="5" t="s">
+        <v>3529</v>
+      </c>
+    </row>
+    <row r="8505" spans="1:1">
+      <c r="A8505" s="5" t="s">
+        <v>4361</v>
+      </c>
+    </row>
+    <row r="8506" spans="1:1">
+      <c r="A8506" s="5" t="s">
+        <v>4361</v>
+      </c>
+    </row>
+    <row r="8507" spans="1:1">
+      <c r="A8507" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="8508" spans="1:1">
+      <c r="A8508" s="5" t="s">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="8509" spans="1:1">
+      <c r="A8509" s="5" t="s">
+        <v>4361</v>
+      </c>
+    </row>
+    <row r="8510" spans="1:1">
+      <c r="A8510" s="5" t="s">
+        <v>4361</v>
+      </c>
+    </row>
+    <row r="8511" spans="1:1">
+      <c r="A8511" s="5" t="s">
+        <v>4361</v>
+      </c>
+    </row>
+    <row r="8512" spans="1:1">
+      <c r="A8512" s="5" t="s">
+        <v>2807</v>
+      </c>
+    </row>
+    <row r="8513" spans="1:1">
+      <c r="A8513" s="5" t="s">
+        <v>3299</v>
+      </c>
+    </row>
+    <row r="8514" spans="1:1">
+      <c r="A8514" s="5" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="8515" spans="1:1">
+      <c r="A8515" s="5" t="s">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="8516" spans="1:1">
+      <c r="A8516" s="5" t="s">
+        <v>3668</v>
+      </c>
+    </row>
+    <row r="8517" spans="1:1">
+      <c r="A8517" s="5" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="8518" spans="1:1">
+      <c r="A8518" s="5" t="s">
+        <v>3668</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:A7839" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:A8207" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A$1:A$1048576">

--- a/nicknames.xlsx
+++ b/nicknames.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$A$4359</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4694" uniqueCount="4694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4744" uniqueCount="4744">
   <si>
     <t>name</t>
   </si>
@@ -14112,6 +14112,156 @@
   </si>
   <si>
     <t>桂少</t>
+  </si>
+  <si>
+    <t>曲魂</t>
+  </si>
+  <si>
+    <t>粟粟</t>
+  </si>
+  <si>
+    <t>云枫</t>
+  </si>
+  <si>
+    <t>风车车</t>
+  </si>
+  <si>
+    <t>糖油果子</t>
+  </si>
+  <si>
+    <t>戈薇</t>
+  </si>
+  <si>
+    <t>三丝</t>
+  </si>
+  <si>
+    <t>蕨菜</t>
+  </si>
+  <si>
+    <t>木杉</t>
+  </si>
+  <si>
+    <t>天明</t>
+  </si>
+  <si>
+    <t>肖恩</t>
+  </si>
+  <si>
+    <t>木苏</t>
+  </si>
+  <si>
+    <t>拉布布</t>
+  </si>
+  <si>
+    <t>玄武</t>
+  </si>
+  <si>
+    <t>艾伦</t>
+  </si>
+  <si>
+    <t>兔兔</t>
+  </si>
+  <si>
+    <t>行者</t>
+  </si>
+  <si>
+    <t>艾尔</t>
+  </si>
+  <si>
+    <t>姜薯</t>
+  </si>
+  <si>
+    <t>平仲</t>
+  </si>
+  <si>
+    <t>盖瑞</t>
+  </si>
+  <si>
+    <t>枯叶蝶</t>
+  </si>
+  <si>
+    <t>白松</t>
+  </si>
+  <si>
+    <t>二荆条</t>
+  </si>
+  <si>
+    <t>塔姆</t>
+  </si>
+  <si>
+    <t>鱼汉堡</t>
+  </si>
+  <si>
+    <t>柚挞</t>
+  </si>
+  <si>
+    <t>豚豚</t>
+  </si>
+  <si>
+    <t>荞安</t>
+  </si>
+  <si>
+    <t>水星</t>
+  </si>
+  <si>
+    <t>水竹</t>
+  </si>
+  <si>
+    <t>豆泡</t>
+  </si>
+  <si>
+    <t>苍月草</t>
+  </si>
+  <si>
+    <t>棉凫</t>
+  </si>
+  <si>
+    <t>风隼</t>
+  </si>
+  <si>
+    <t>米娅</t>
+  </si>
+  <si>
+    <t>又青</t>
+  </si>
+  <si>
+    <t>鱼鱼薇</t>
+  </si>
+  <si>
+    <t>玄米</t>
+  </si>
+  <si>
+    <t>擂茶</t>
+  </si>
+  <si>
+    <t>青芃</t>
+  </si>
+  <si>
+    <t>布鲁伊</t>
+  </si>
+  <si>
+    <t>黑揽</t>
+  </si>
+  <si>
+    <t>下小白龙</t>
+  </si>
+  <si>
+    <t>李邓军</t>
+  </si>
+  <si>
+    <t>惠兰</t>
+  </si>
+  <si>
+    <t>行政</t>
+  </si>
+  <si>
+    <t>马前子</t>
+  </si>
+  <si>
+    <t>白衫</t>
+  </si>
+  <si>
+    <t>谭群良</t>
   </si>
 </sst>
 </file>
@@ -14725,7 +14875,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -14734,13 +14884,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -15100,7 +15244,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A8440"/>
+  <dimension ref="A1:A8437"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="19.3166666666667" style="1" customWidth="1"/>
@@ -34452,4279 +34596,4379 @@
       </c>
     </row>
     <row r="3870" spans="1:1">
-      <c r="A3870" s="3" t="s">
+      <c r="A3870" s="2" t="s">
         <v>3869</v>
       </c>
     </row>
     <row r="3871" spans="1:1">
-      <c r="A3871" s="3" t="s">
+      <c r="A3871" s="2" t="s">
         <v>3870</v>
       </c>
     </row>
     <row r="3872" spans="1:1">
-      <c r="A3872" s="3" t="s">
+      <c r="A3872" s="2" t="s">
         <v>3871</v>
       </c>
     </row>
     <row r="3873" spans="1:1">
-      <c r="A3873" s="3" t="s">
+      <c r="A3873" s="2" t="s">
         <v>3872</v>
       </c>
     </row>
     <row r="3874" spans="1:1">
-      <c r="A3874" s="3" t="s">
+      <c r="A3874" s="2" t="s">
         <v>3873</v>
       </c>
     </row>
     <row r="3875" spans="1:1">
-      <c r="A3875" s="3" t="s">
+      <c r="A3875" s="2" t="s">
         <v>3874</v>
       </c>
     </row>
     <row r="3876" spans="1:1">
-      <c r="A3876" s="3" t="s">
+      <c r="A3876" s="2" t="s">
         <v>3875</v>
       </c>
     </row>
     <row r="3877" spans="1:1">
-      <c r="A3877" s="3" t="s">
+      <c r="A3877" s="2" t="s">
         <v>3876</v>
       </c>
     </row>
     <row r="3878" spans="1:1">
-      <c r="A3878" s="3" t="s">
+      <c r="A3878" s="2" t="s">
         <v>3877</v>
       </c>
     </row>
     <row r="3879" spans="1:1">
-      <c r="A3879" s="3" t="s">
+      <c r="A3879" s="2" t="s">
         <v>3878</v>
       </c>
     </row>
     <row r="3880" spans="1:1">
-      <c r="A3880" s="3" t="s">
+      <c r="A3880" s="2" t="s">
         <v>3879</v>
       </c>
     </row>
     <row r="3881" spans="1:1">
-      <c r="A3881" s="3" t="s">
+      <c r="A3881" s="2" t="s">
         <v>3880</v>
       </c>
     </row>
     <row r="3882" spans="1:1">
-      <c r="A3882" s="3" t="s">
+      <c r="A3882" s="2" t="s">
         <v>3881</v>
       </c>
     </row>
     <row r="3883" spans="1:1">
-      <c r="A3883" s="3" t="s">
+      <c r="A3883" s="2" t="s">
         <v>3882</v>
       </c>
     </row>
     <row r="3884" spans="1:1">
-      <c r="A3884" s="3" t="s">
+      <c r="A3884" s="2" t="s">
         <v>3883</v>
       </c>
     </row>
     <row r="3885" spans="1:1">
-      <c r="A3885" s="3" t="s">
+      <c r="A3885" s="2" t="s">
         <v>3884</v>
       </c>
     </row>
     <row r="3886" spans="1:1">
-      <c r="A3886" s="3" t="s">
+      <c r="A3886" s="2" t="s">
         <v>3885</v>
       </c>
     </row>
     <row r="3887" spans="1:1">
-      <c r="A3887" s="3" t="s">
+      <c r="A3887" s="2" t="s">
         <v>3886</v>
       </c>
     </row>
     <row r="3888" spans="1:1">
-      <c r="A3888" s="3" t="s">
+      <c r="A3888" s="2" t="s">
         <v>3887</v>
       </c>
     </row>
     <row r="3889" spans="1:1">
-      <c r="A3889" s="3" t="s">
+      <c r="A3889" s="2" t="s">
         <v>3888</v>
       </c>
     </row>
     <row r="3890" spans="1:1">
-      <c r="A3890" s="3" t="s">
+      <c r="A3890" s="2" t="s">
         <v>3889</v>
       </c>
     </row>
     <row r="3891" spans="1:1">
-      <c r="A3891" s="3" t="s">
+      <c r="A3891" s="2" t="s">
         <v>3890</v>
       </c>
     </row>
     <row r="3892" spans="1:1">
-      <c r="A3892" s="3" t="s">
+      <c r="A3892" s="2" t="s">
         <v>3891</v>
       </c>
     </row>
     <row r="3893" spans="1:1">
-      <c r="A3893" s="3" t="s">
+      <c r="A3893" s="2" t="s">
         <v>3892</v>
       </c>
     </row>
     <row r="3894" spans="1:1">
-      <c r="A3894" s="3" t="s">
+      <c r="A3894" s="2" t="s">
         <v>3893</v>
       </c>
     </row>
     <row r="3895" spans="1:1">
-      <c r="A3895" s="3" t="s">
+      <c r="A3895" s="2" t="s">
         <v>3894</v>
       </c>
     </row>
     <row r="3896" spans="1:1">
-      <c r="A3896" s="3" t="s">
+      <c r="A3896" s="2" t="s">
         <v>3895</v>
       </c>
     </row>
     <row r="3897" spans="1:1">
-      <c r="A3897" s="3" t="s">
+      <c r="A3897" s="2" t="s">
         <v>3896</v>
       </c>
     </row>
     <row r="3898" spans="1:1">
-      <c r="A3898" s="3" t="s">
+      <c r="A3898" s="2" t="s">
         <v>3897</v>
       </c>
     </row>
     <row r="3899" spans="1:1">
-      <c r="A3899" s="3" t="s">
+      <c r="A3899" s="2" t="s">
         <v>3898</v>
       </c>
     </row>
     <row r="3900" spans="1:1">
-      <c r="A3900" s="3" t="s">
+      <c r="A3900" s="2" t="s">
         <v>3899</v>
       </c>
     </row>
     <row r="3901" spans="1:1">
-      <c r="A3901" s="3" t="s">
+      <c r="A3901" s="2" t="s">
         <v>3900</v>
       </c>
     </row>
     <row r="3902" spans="1:1">
-      <c r="A3902" s="3" t="s">
+      <c r="A3902" s="2" t="s">
         <v>3901</v>
       </c>
     </row>
     <row r="3903" spans="1:1">
-      <c r="A3903" s="3" t="s">
+      <c r="A3903" s="2" t="s">
         <v>3902</v>
       </c>
     </row>
     <row r="3904" spans="1:1">
-      <c r="A3904" s="3" t="s">
+      <c r="A3904" s="2" t="s">
         <v>3903</v>
       </c>
     </row>
     <row r="3905" spans="1:1">
-      <c r="A3905" s="3" t="s">
+      <c r="A3905" s="2" t="s">
         <v>3904</v>
       </c>
     </row>
     <row r="3906" spans="1:1">
-      <c r="A3906" s="3" t="s">
+      <c r="A3906" s="2" t="s">
         <v>3905</v>
       </c>
     </row>
     <row r="3907" spans="1:1">
-      <c r="A3907" s="3" t="s">
+      <c r="A3907" s="2" t="s">
         <v>3906</v>
       </c>
     </row>
     <row r="3908" spans="1:1">
-      <c r="A3908" s="3" t="s">
+      <c r="A3908" s="2" t="s">
         <v>3907</v>
       </c>
     </row>
     <row r="3909" spans="1:1">
-      <c r="A3909" s="3" t="s">
+      <c r="A3909" s="2" t="s">
         <v>3908</v>
       </c>
     </row>
     <row r="3910" spans="1:1">
-      <c r="A3910" s="3" t="s">
+      <c r="A3910" s="2" t="s">
         <v>3909</v>
       </c>
     </row>
     <row r="3911" spans="1:1">
-      <c r="A3911" s="3" t="s">
+      <c r="A3911" s="2" t="s">
         <v>3910</v>
       </c>
     </row>
     <row r="3912" spans="1:1">
-      <c r="A3912" s="3" t="s">
+      <c r="A3912" s="2" t="s">
         <v>3911</v>
       </c>
     </row>
     <row r="3913" spans="1:1">
-      <c r="A3913" s="3" t="s">
+      <c r="A3913" s="2" t="s">
         <v>3912</v>
       </c>
     </row>
     <row r="3914" spans="1:1">
-      <c r="A3914" s="3" t="s">
+      <c r="A3914" s="2" t="s">
         <v>3913</v>
       </c>
     </row>
     <row r="3915" spans="1:1">
-      <c r="A3915" s="3" t="s">
+      <c r="A3915" s="2" t="s">
         <v>3914</v>
       </c>
     </row>
     <row r="3916" spans="1:1">
-      <c r="A3916" s="3" t="s">
+      <c r="A3916" s="2" t="s">
         <v>3915</v>
       </c>
     </row>
     <row r="3917" spans="1:1">
-      <c r="A3917" s="3" t="s">
+      <c r="A3917" s="2" t="s">
         <v>3916</v>
       </c>
     </row>
     <row r="3918" spans="1:1">
-      <c r="A3918" s="3" t="s">
+      <c r="A3918" s="2" t="s">
         <v>3917</v>
       </c>
     </row>
     <row r="3919" spans="1:1">
-      <c r="A3919" s="3" t="s">
+      <c r="A3919" s="2" t="s">
         <v>3918</v>
       </c>
     </row>
     <row r="3920" spans="1:1">
-      <c r="A3920" s="3" t="s">
+      <c r="A3920" s="2" t="s">
         <v>3919</v>
       </c>
     </row>
     <row r="3921" spans="1:1">
-      <c r="A3921" s="3" t="s">
+      <c r="A3921" s="2" t="s">
         <v>3920</v>
       </c>
     </row>
     <row r="3922" spans="1:1">
-      <c r="A3922" s="3" t="s">
+      <c r="A3922" s="2" t="s">
         <v>3921</v>
       </c>
     </row>
     <row r="3923" spans="1:1">
-      <c r="A3923" s="3" t="s">
+      <c r="A3923" s="2" t="s">
         <v>3922</v>
       </c>
     </row>
     <row r="3924" spans="1:1">
-      <c r="A3924" s="3" t="s">
+      <c r="A3924" s="2" t="s">
         <v>3923</v>
       </c>
     </row>
     <row r="3925" spans="1:1">
-      <c r="A3925" s="3" t="s">
+      <c r="A3925" s="2" t="s">
         <v>3924</v>
       </c>
     </row>
     <row r="3926" spans="1:1">
-      <c r="A3926" s="3" t="s">
+      <c r="A3926" s="2" t="s">
         <v>3925</v>
       </c>
     </row>
     <row r="3927" spans="1:1">
-      <c r="A3927" s="3" t="s">
+      <c r="A3927" s="2" t="s">
         <v>3926</v>
       </c>
     </row>
     <row r="3928" spans="1:1">
-      <c r="A3928" s="3" t="s">
+      <c r="A3928" s="2" t="s">
         <v>3927</v>
       </c>
     </row>
     <row r="3929" spans="1:1">
-      <c r="A3929" s="3" t="s">
+      <c r="A3929" s="2" t="s">
         <v>3928</v>
       </c>
     </row>
     <row r="3930" spans="1:1">
-      <c r="A3930" s="3" t="s">
+      <c r="A3930" s="2" t="s">
         <v>3929</v>
       </c>
     </row>
     <row r="3931" spans="1:1">
-      <c r="A3931" s="3" t="s">
+      <c r="A3931" s="2" t="s">
         <v>3930</v>
       </c>
     </row>
     <row r="3932" spans="1:1">
-      <c r="A3932" s="3" t="s">
+      <c r="A3932" s="2" t="s">
         <v>3931</v>
       </c>
     </row>
     <row r="3933" spans="1:1">
-      <c r="A3933" s="3" t="s">
+      <c r="A3933" s="2" t="s">
         <v>3932</v>
       </c>
     </row>
     <row r="3934" spans="1:1">
-      <c r="A3934" s="3" t="s">
+      <c r="A3934" s="2" t="s">
         <v>3933</v>
       </c>
     </row>
     <row r="3935" spans="1:1">
-      <c r="A3935" s="3" t="s">
+      <c r="A3935" s="2" t="s">
         <v>3934</v>
       </c>
     </row>
     <row r="3936" spans="1:1">
-      <c r="A3936" s="3" t="s">
+      <c r="A3936" s="2" t="s">
         <v>3935</v>
       </c>
     </row>
     <row r="3937" spans="1:1">
-      <c r="A3937" s="3" t="s">
+      <c r="A3937" s="2" t="s">
         <v>3936</v>
       </c>
     </row>
     <row r="3938" spans="1:1">
-      <c r="A3938" s="3" t="s">
+      <c r="A3938" s="2" t="s">
         <v>3937</v>
       </c>
     </row>
     <row r="3939" spans="1:1">
-      <c r="A3939" s="3" t="s">
+      <c r="A3939" s="2" t="s">
         <v>3938</v>
       </c>
     </row>
     <row r="3940" spans="1:1">
-      <c r="A3940" s="3" t="s">
+      <c r="A3940" s="2" t="s">
         <v>3939</v>
       </c>
     </row>
     <row r="3941" spans="1:1">
-      <c r="A3941" s="3" t="s">
+      <c r="A3941" s="2" t="s">
         <v>3940</v>
       </c>
     </row>
     <row r="3942" spans="1:1">
-      <c r="A3942" s="3" t="s">
+      <c r="A3942" s="2" t="s">
         <v>3941</v>
       </c>
     </row>
     <row r="3943" spans="1:1">
-      <c r="A3943" s="3" t="s">
+      <c r="A3943" s="2" t="s">
         <v>3942</v>
       </c>
     </row>
     <row r="3944" spans="1:1">
-      <c r="A3944" s="3" t="s">
+      <c r="A3944" s="2" t="s">
         <v>3943</v>
       </c>
     </row>
     <row r="3945" spans="1:1">
-      <c r="A3945" s="3" t="s">
+      <c r="A3945" s="2" t="s">
         <v>3944</v>
       </c>
     </row>
     <row r="3946" spans="1:1">
-      <c r="A3946" s="3" t="s">
+      <c r="A3946" s="2" t="s">
         <v>3945</v>
       </c>
     </row>
     <row r="3947" spans="1:1">
-      <c r="A3947" s="3" t="s">
+      <c r="A3947" s="2" t="s">
         <v>3946</v>
       </c>
     </row>
     <row r="3948" spans="1:1">
-      <c r="A3948" s="3" t="s">
+      <c r="A3948" s="2" t="s">
         <v>3947</v>
       </c>
     </row>
     <row r="3949" spans="1:1">
-      <c r="A3949" s="3" t="s">
+      <c r="A3949" s="2" t="s">
         <v>3948</v>
       </c>
     </row>
     <row r="3950" spans="1:1">
-      <c r="A3950" s="3" t="s">
+      <c r="A3950" s="2" t="s">
         <v>3949</v>
       </c>
     </row>
     <row r="3951" spans="1:1">
-      <c r="A3951" s="3" t="s">
+      <c r="A3951" s="2" t="s">
         <v>3950</v>
       </c>
     </row>
     <row r="3952" spans="1:1">
-      <c r="A3952" s="3" t="s">
+      <c r="A3952" s="2" t="s">
         <v>3951</v>
       </c>
     </row>
     <row r="3953" spans="1:1">
-      <c r="A3953" s="3" t="s">
+      <c r="A3953" s="2" t="s">
         <v>3952</v>
       </c>
     </row>
     <row r="3954" spans="1:1">
-      <c r="A3954" s="3" t="s">
+      <c r="A3954" s="2" t="s">
         <v>3953</v>
       </c>
     </row>
     <row r="3955" spans="1:1">
-      <c r="A3955" s="3" t="s">
+      <c r="A3955" s="2" t="s">
         <v>3954</v>
       </c>
     </row>
     <row r="3956" spans="1:1">
-      <c r="A3956" s="3" t="s">
+      <c r="A3956" s="2" t="s">
         <v>3955</v>
       </c>
     </row>
     <row r="3957" spans="1:1">
-      <c r="A3957" s="3" t="s">
+      <c r="A3957" s="2" t="s">
         <v>3956</v>
       </c>
     </row>
     <row r="3958" spans="1:1">
-      <c r="A3958" s="3" t="s">
+      <c r="A3958" s="2" t="s">
         <v>3957</v>
       </c>
     </row>
     <row r="3959" spans="1:1">
-      <c r="A3959" s="3" t="s">
+      <c r="A3959" s="2" t="s">
         <v>3958</v>
       </c>
     </row>
     <row r="3960" spans="1:1">
-      <c r="A3960" s="3" t="s">
+      <c r="A3960" s="2" t="s">
         <v>3959</v>
       </c>
     </row>
     <row r="3961" spans="1:1">
-      <c r="A3961" s="3" t="s">
+      <c r="A3961" s="2" t="s">
         <v>3960</v>
       </c>
     </row>
     <row r="3962" spans="1:1">
-      <c r="A3962" s="3" t="s">
+      <c r="A3962" s="2" t="s">
         <v>3961</v>
       </c>
     </row>
     <row r="3963" spans="1:1">
-      <c r="A3963" s="3" t="s">
+      <c r="A3963" s="2" t="s">
         <v>3962</v>
       </c>
     </row>
     <row r="3964" spans="1:1">
-      <c r="A3964" s="3" t="s">
+      <c r="A3964" s="2" t="s">
         <v>3963</v>
       </c>
     </row>
     <row r="3965" spans="1:1">
-      <c r="A3965" s="3" t="s">
+      <c r="A3965" s="2" t="s">
         <v>3964</v>
       </c>
     </row>
     <row r="3966" spans="1:1">
-      <c r="A3966" s="3" t="s">
+      <c r="A3966" s="2" t="s">
         <v>3965</v>
       </c>
     </row>
     <row r="3967" spans="1:1">
-      <c r="A3967" s="3" t="s">
+      <c r="A3967" s="2" t="s">
         <v>3966</v>
       </c>
     </row>
     <row r="3968" spans="1:1">
-      <c r="A3968" s="3" t="s">
+      <c r="A3968" s="2" t="s">
         <v>3967</v>
       </c>
     </row>
     <row r="3969" spans="1:1">
-      <c r="A3969" s="3" t="s">
+      <c r="A3969" s="2" t="s">
         <v>3968</v>
       </c>
     </row>
     <row r="3970" spans="1:1">
-      <c r="A3970" s="3" t="s">
+      <c r="A3970" s="2" t="s">
         <v>3969</v>
       </c>
     </row>
     <row r="3971" spans="1:1">
-      <c r="A3971" s="3" t="s">
+      <c r="A3971" s="2" t="s">
         <v>3970</v>
       </c>
     </row>
     <row r="3972" spans="1:1">
-      <c r="A3972" s="3" t="s">
+      <c r="A3972" s="2" t="s">
         <v>3971</v>
       </c>
     </row>
     <row r="3973" spans="1:1">
-      <c r="A3973" s="3" t="s">
+      <c r="A3973" s="2" t="s">
         <v>3972</v>
       </c>
     </row>
     <row r="3974" spans="1:1">
-      <c r="A3974" s="3" t="s">
+      <c r="A3974" s="2" t="s">
         <v>3973</v>
       </c>
     </row>
     <row r="3975" spans="1:1">
-      <c r="A3975" s="3" t="s">
+      <c r="A3975" s="2" t="s">
         <v>3974</v>
       </c>
     </row>
     <row r="3976" spans="1:1">
-      <c r="A3976" s="3" t="s">
+      <c r="A3976" s="2" t="s">
         <v>3975</v>
       </c>
     </row>
     <row r="3977" spans="1:1">
-      <c r="A3977" s="3" t="s">
+      <c r="A3977" s="2" t="s">
         <v>3976</v>
       </c>
     </row>
     <row r="3978" spans="1:1">
-      <c r="A3978" s="4" t="s">
+      <c r="A3978" s="2" t="s">
         <v>3977</v>
       </c>
     </row>
     <row r="3979" spans="1:1">
-      <c r="A3979" s="4" t="s">
+      <c r="A3979" s="2" t="s">
         <v>3978</v>
       </c>
     </row>
     <row r="3980" spans="1:1">
-      <c r="A3980" s="4" t="s">
+      <c r="A3980" s="2" t="s">
         <v>3979</v>
       </c>
     </row>
     <row r="3981" spans="1:1">
-      <c r="A3981" s="4" t="s">
+      <c r="A3981" s="2" t="s">
         <v>3980</v>
       </c>
     </row>
     <row r="3982" spans="1:1">
-      <c r="A3982" s="4" t="s">
+      <c r="A3982" s="2" t="s">
         <v>3981</v>
       </c>
     </row>
     <row r="3983" spans="1:1">
-      <c r="A3983" s="4" t="s">
+      <c r="A3983" s="2" t="s">
         <v>3982</v>
       </c>
     </row>
     <row r="3984" spans="1:1">
-      <c r="A3984" s="4" t="s">
+      <c r="A3984" s="2" t="s">
         <v>3983</v>
       </c>
     </row>
     <row r="3985" spans="1:1">
-      <c r="A3985" s="4" t="s">
+      <c r="A3985" s="2" t="s">
         <v>3984</v>
       </c>
     </row>
     <row r="3986" spans="1:1">
-      <c r="A3986" s="4" t="s">
+      <c r="A3986" s="2" t="s">
         <v>3985</v>
       </c>
     </row>
     <row r="3987" spans="1:1">
-      <c r="A3987" s="4" t="s">
+      <c r="A3987" s="2" t="s">
         <v>3986</v>
       </c>
     </row>
     <row r="3988" spans="1:1">
-      <c r="A3988" s="4" t="s">
+      <c r="A3988" s="2" t="s">
         <v>3987</v>
       </c>
     </row>
     <row r="3989" spans="1:1">
-      <c r="A3989" s="4" t="s">
+      <c r="A3989" s="2" t="s">
         <v>3988</v>
       </c>
     </row>
     <row r="3990" spans="1:1">
-      <c r="A3990" s="4" t="s">
+      <c r="A3990" s="2" t="s">
         <v>3989</v>
       </c>
     </row>
     <row r="3991" spans="1:1">
-      <c r="A3991" s="4" t="s">
+      <c r="A3991" s="2" t="s">
         <v>3990</v>
       </c>
     </row>
     <row r="3992" spans="1:1">
-      <c r="A3992" s="4" t="s">
+      <c r="A3992" s="2" t="s">
         <v>3991</v>
       </c>
     </row>
     <row r="3993" spans="1:1">
-      <c r="A3993" s="4" t="s">
+      <c r="A3993" s="2" t="s">
         <v>3992</v>
       </c>
     </row>
     <row r="3994" spans="1:1">
-      <c r="A3994" s="4" t="s">
+      <c r="A3994" s="2" t="s">
         <v>3993</v>
       </c>
     </row>
     <row r="3995" spans="1:1">
-      <c r="A3995" s="4" t="s">
+      <c r="A3995" s="2" t="s">
         <v>3994</v>
       </c>
     </row>
     <row r="3996" spans="1:1">
-      <c r="A3996" s="4" t="s">
+      <c r="A3996" s="2" t="s">
         <v>3995</v>
       </c>
     </row>
     <row r="3997" spans="1:1">
-      <c r="A3997" s="4" t="s">
+      <c r="A3997" s="2" t="s">
         <v>3996</v>
       </c>
     </row>
     <row r="3998" spans="1:1">
-      <c r="A3998" s="4" t="s">
+      <c r="A3998" s="2" t="s">
         <v>3997</v>
       </c>
     </row>
     <row r="3999" spans="1:1">
-      <c r="A3999" s="4" t="s">
+      <c r="A3999" s="2" t="s">
         <v>3998</v>
       </c>
     </row>
     <row r="4000" spans="1:1">
-      <c r="A4000" s="4" t="s">
+      <c r="A4000" s="2" t="s">
         <v>3999</v>
       </c>
     </row>
     <row r="4001" spans="1:1">
-      <c r="A4001" s="4" t="s">
+      <c r="A4001" s="2" t="s">
         <v>4000</v>
       </c>
     </row>
     <row r="4002" spans="1:1">
-      <c r="A4002" s="4" t="s">
+      <c r="A4002" s="2" t="s">
         <v>4001</v>
       </c>
     </row>
     <row r="4003" spans="1:1">
-      <c r="A4003" s="4" t="s">
+      <c r="A4003" s="2" t="s">
         <v>4002</v>
       </c>
     </row>
     <row r="4004" spans="1:1">
-      <c r="A4004" s="4" t="s">
+      <c r="A4004" s="2" t="s">
         <v>4003</v>
       </c>
     </row>
     <row r="4005" spans="1:1">
-      <c r="A4005" s="4" t="s">
+      <c r="A4005" s="2" t="s">
         <v>4004</v>
       </c>
     </row>
     <row r="4006" spans="1:1">
-      <c r="A4006" s="4" t="s">
+      <c r="A4006" s="2" t="s">
         <v>4005</v>
       </c>
     </row>
     <row r="4007" spans="1:1">
-      <c r="A4007" s="4" t="s">
+      <c r="A4007" s="2" t="s">
         <v>4006</v>
       </c>
     </row>
     <row r="4008" spans="1:1">
-      <c r="A4008" s="4" t="s">
+      <c r="A4008" s="2" t="s">
         <v>4007</v>
       </c>
     </row>
     <row r="4009" spans="1:1">
-      <c r="A4009" s="4" t="s">
+      <c r="A4009" s="2" t="s">
         <v>4008</v>
       </c>
     </row>
     <row r="4010" spans="1:1">
-      <c r="A4010" s="4" t="s">
+      <c r="A4010" s="2" t="s">
         <v>4009</v>
       </c>
     </row>
     <row r="4011" spans="1:1">
-      <c r="A4011" s="4" t="s">
+      <c r="A4011" s="2" t="s">
         <v>4010</v>
       </c>
     </row>
     <row r="4012" spans="1:1">
-      <c r="A4012" s="4" t="s">
+      <c r="A4012" s="2" t="s">
         <v>4011</v>
       </c>
     </row>
     <row r="4013" spans="1:1">
-      <c r="A4013" s="4" t="s">
+      <c r="A4013" s="2" t="s">
         <v>4012</v>
       </c>
     </row>
     <row r="4014" spans="1:1">
-      <c r="A4014" s="4" t="s">
+      <c r="A4014" s="2" t="s">
         <v>4013</v>
       </c>
     </row>
     <row r="4015" spans="1:1">
-      <c r="A4015" s="4" t="s">
+      <c r="A4015" s="2" t="s">
         <v>4014</v>
       </c>
     </row>
     <row r="4016" spans="1:1">
-      <c r="A4016" s="4" t="s">
+      <c r="A4016" s="2" t="s">
         <v>4015</v>
       </c>
     </row>
     <row r="4017" spans="1:1">
-      <c r="A4017" s="4" t="s">
+      <c r="A4017" s="2" t="s">
         <v>4016</v>
       </c>
     </row>
     <row r="4018" spans="1:1">
-      <c r="A4018" s="4" t="s">
+      <c r="A4018" s="2" t="s">
         <v>4017</v>
       </c>
     </row>
     <row r="4019" spans="1:1">
-      <c r="A4019" s="4" t="s">
+      <c r="A4019" s="2" t="s">
         <v>4018</v>
       </c>
     </row>
     <row r="4020" spans="1:1">
-      <c r="A4020" s="4" t="s">
+      <c r="A4020" s="2" t="s">
         <v>4019</v>
       </c>
     </row>
     <row r="4021" spans="1:1">
-      <c r="A4021" s="4" t="s">
+      <c r="A4021" s="2" t="s">
         <v>4020</v>
       </c>
     </row>
     <row r="4022" spans="1:1">
-      <c r="A4022" s="4" t="s">
+      <c r="A4022" s="2" t="s">
         <v>4021</v>
       </c>
     </row>
     <row r="4023" spans="1:1">
-      <c r="A4023" s="4" t="s">
+      <c r="A4023" s="2" t="s">
         <v>4022</v>
       </c>
     </row>
     <row r="4024" spans="1:1">
-      <c r="A4024" s="4" t="s">
+      <c r="A4024" s="2" t="s">
         <v>4023</v>
       </c>
     </row>
     <row r="4025" spans="1:1">
-      <c r="A4025" s="4" t="s">
+      <c r="A4025" s="2" t="s">
         <v>4024</v>
       </c>
     </row>
     <row r="4026" spans="1:1">
-      <c r="A4026" s="4" t="s">
+      <c r="A4026" s="2" t="s">
         <v>4025</v>
       </c>
     </row>
     <row r="4027" spans="1:1">
-      <c r="A4027" s="4" t="s">
+      <c r="A4027" s="2" t="s">
         <v>4026</v>
       </c>
     </row>
     <row r="4028" spans="1:1">
-      <c r="A4028" s="4" t="s">
+      <c r="A4028" s="2" t="s">
         <v>4027</v>
       </c>
     </row>
     <row r="4029" spans="1:1">
-      <c r="A4029" s="4" t="s">
+      <c r="A4029" s="2" t="s">
         <v>4028</v>
       </c>
     </row>
     <row r="4030" spans="1:1">
-      <c r="A4030" s="4" t="s">
+      <c r="A4030" s="2" t="s">
         <v>4029</v>
       </c>
     </row>
     <row r="4031" spans="1:1">
-      <c r="A4031" s="4" t="s">
+      <c r="A4031" s="2" t="s">
         <v>4030</v>
       </c>
     </row>
     <row r="4032" spans="1:1">
-      <c r="A4032" s="4" t="s">
+      <c r="A4032" s="2" t="s">
         <v>4031</v>
       </c>
     </row>
     <row r="4033" spans="1:1">
-      <c r="A4033" s="4" t="s">
+      <c r="A4033" s="2" t="s">
         <v>4032</v>
       </c>
     </row>
     <row r="4034" spans="1:1">
-      <c r="A4034" s="4" t="s">
+      <c r="A4034" s="2" t="s">
         <v>4033</v>
       </c>
     </row>
     <row r="4035" spans="1:1">
-      <c r="A4035" s="4" t="s">
+      <c r="A4035" s="2" t="s">
         <v>4034</v>
       </c>
     </row>
     <row r="4036" spans="1:1">
-      <c r="A4036" s="4" t="s">
+      <c r="A4036" s="2" t="s">
         <v>4035</v>
       </c>
     </row>
     <row r="4037" spans="1:1">
-      <c r="A4037" s="4" t="s">
+      <c r="A4037" s="2" t="s">
         <v>4036</v>
       </c>
     </row>
     <row r="4038" spans="1:1">
-      <c r="A4038" s="4" t="s">
+      <c r="A4038" s="2" t="s">
         <v>4037</v>
       </c>
     </row>
     <row r="4039" spans="1:1">
-      <c r="A4039" s="4" t="s">
+      <c r="A4039" s="2" t="s">
         <v>4038</v>
       </c>
     </row>
     <row r="4040" spans="1:1">
-      <c r="A4040" s="4" t="s">
+      <c r="A4040" s="2" t="s">
         <v>4039</v>
       </c>
     </row>
     <row r="4041" spans="1:1">
-      <c r="A4041" s="4" t="s">
+      <c r="A4041" s="2" t="s">
         <v>4040</v>
       </c>
     </row>
     <row r="4042" spans="1:1">
-      <c r="A4042" s="4" t="s">
+      <c r="A4042" s="2" t="s">
         <v>4041</v>
       </c>
     </row>
     <row r="4043" spans="1:1">
-      <c r="A4043" s="4" t="s">
+      <c r="A4043" s="2" t="s">
         <v>4042</v>
       </c>
     </row>
     <row r="4044" spans="1:1">
-      <c r="A4044" s="4" t="s">
+      <c r="A4044" s="2" t="s">
         <v>4043</v>
       </c>
     </row>
     <row r="4045" spans="1:1">
-      <c r="A4045" s="4" t="s">
+      <c r="A4045" s="2" t="s">
         <v>4044</v>
       </c>
     </row>
     <row r="4046" spans="1:1">
-      <c r="A4046" s="4" t="s">
+      <c r="A4046" s="2" t="s">
         <v>4045</v>
       </c>
     </row>
     <row r="4047" spans="1:1">
-      <c r="A4047" s="4" t="s">
+      <c r="A4047" s="2" t="s">
         <v>4046</v>
       </c>
     </row>
     <row r="4048" spans="1:1">
-      <c r="A4048" s="4" t="s">
+      <c r="A4048" s="2" t="s">
         <v>4047</v>
       </c>
     </row>
     <row r="4049" spans="1:1">
-      <c r="A4049" s="4" t="s">
+      <c r="A4049" s="2" t="s">
         <v>4048</v>
       </c>
     </row>
     <row r="4050" spans="1:1">
-      <c r="A4050" s="4" t="s">
+      <c r="A4050" s="2" t="s">
         <v>4049</v>
       </c>
     </row>
     <row r="4051" spans="1:1">
-      <c r="A4051" s="4" t="s">
+      <c r="A4051" s="2" t="s">
         <v>4050</v>
       </c>
     </row>
     <row r="4052" spans="1:1">
-      <c r="A4052" s="4" t="s">
+      <c r="A4052" s="2" t="s">
         <v>4051</v>
       </c>
     </row>
     <row r="4053" spans="1:1">
-      <c r="A4053" s="4" t="s">
+      <c r="A4053" s="2" t="s">
         <v>4052</v>
       </c>
     </row>
     <row r="4054" spans="1:1">
-      <c r="A4054" s="4" t="s">
+      <c r="A4054" s="2" t="s">
         <v>4053</v>
       </c>
     </row>
     <row r="4055" spans="1:1">
-      <c r="A4055" s="4" t="s">
+      <c r="A4055" s="2" t="s">
         <v>4054</v>
       </c>
     </row>
     <row r="4056" spans="1:1">
-      <c r="A4056" s="4" t="s">
+      <c r="A4056" s="2" t="s">
         <v>4055</v>
       </c>
     </row>
     <row r="4057" spans="1:1">
-      <c r="A4057" s="4" t="s">
+      <c r="A4057" s="2" t="s">
         <v>4056</v>
       </c>
     </row>
     <row r="4058" spans="1:1">
-      <c r="A4058" s="4" t="s">
+      <c r="A4058" s="2" t="s">
         <v>4057</v>
       </c>
     </row>
     <row r="4059" spans="1:1">
-      <c r="A4059" s="4" t="s">
+      <c r="A4059" s="2" t="s">
         <v>4058</v>
       </c>
     </row>
     <row r="4060" spans="1:1">
-      <c r="A4060" s="4" t="s">
+      <c r="A4060" s="2" t="s">
         <v>4059</v>
       </c>
     </row>
     <row r="4061" spans="1:1">
-      <c r="A4061" s="4" t="s">
+      <c r="A4061" s="2" t="s">
         <v>4060</v>
       </c>
     </row>
     <row r="4062" spans="1:1">
-      <c r="A4062" s="4" t="s">
+      <c r="A4062" s="2" t="s">
         <v>4061</v>
       </c>
     </row>
     <row r="4063" spans="1:1">
-      <c r="A4063" s="4" t="s">
+      <c r="A4063" s="2" t="s">
         <v>4062</v>
       </c>
     </row>
     <row r="4064" spans="1:1">
-      <c r="A4064" s="4" t="s">
+      <c r="A4064" s="2" t="s">
         <v>4063</v>
       </c>
     </row>
     <row r="4065" spans="1:1">
-      <c r="A4065" s="4" t="s">
+      <c r="A4065" s="2" t="s">
         <v>4064</v>
       </c>
     </row>
     <row r="4066" spans="1:1">
-      <c r="A4066" s="4" t="s">
+      <c r="A4066" s="2" t="s">
         <v>4065</v>
       </c>
     </row>
     <row r="4067" spans="1:1">
-      <c r="A4067" s="4" t="s">
+      <c r="A4067" s="2" t="s">
         <v>4066</v>
       </c>
     </row>
     <row r="4068" spans="1:1">
-      <c r="A4068" s="4" t="s">
+      <c r="A4068" s="2" t="s">
         <v>4067</v>
       </c>
     </row>
     <row r="4069" spans="1:1">
-      <c r="A4069" s="4" t="s">
+      <c r="A4069" s="2" t="s">
         <v>4068</v>
       </c>
     </row>
     <row r="4070" spans="1:1">
-      <c r="A4070" s="4" t="s">
+      <c r="A4070" s="2" t="s">
         <v>4069</v>
       </c>
     </row>
     <row r="4071" spans="1:1">
-      <c r="A4071" s="4" t="s">
+      <c r="A4071" s="2" t="s">
         <v>4070</v>
       </c>
     </row>
     <row r="4072" spans="1:1">
-      <c r="A4072" s="4" t="s">
+      <c r="A4072" s="2" t="s">
         <v>4071</v>
       </c>
     </row>
     <row r="4073" spans="1:1">
-      <c r="A4073" s="4" t="s">
+      <c r="A4073" s="2" t="s">
         <v>4072</v>
       </c>
     </row>
     <row r="4074" spans="1:1">
-      <c r="A4074" s="4" t="s">
+      <c r="A4074" s="2" t="s">
         <v>4073</v>
       </c>
     </row>
     <row r="4075" spans="1:1">
-      <c r="A4075" s="4" t="s">
+      <c r="A4075" s="2" t="s">
         <v>4074</v>
       </c>
     </row>
     <row r="4076" spans="1:1">
-      <c r="A4076" s="4" t="s">
+      <c r="A4076" s="2" t="s">
         <v>4075</v>
       </c>
     </row>
     <row r="4077" spans="1:1">
-      <c r="A4077" s="4" t="s">
+      <c r="A4077" s="2" t="s">
         <v>4076</v>
       </c>
     </row>
     <row r="4078" spans="1:1">
-      <c r="A4078" s="4" t="s">
+      <c r="A4078" s="2" t="s">
         <v>4077</v>
       </c>
     </row>
     <row r="4079" spans="1:1">
-      <c r="A4079" s="4" t="s">
+      <c r="A4079" s="2" t="s">
         <v>4078</v>
       </c>
     </row>
     <row r="4080" spans="1:1">
-      <c r="A4080" s="4" t="s">
+      <c r="A4080" s="2" t="s">
         <v>4079</v>
       </c>
     </row>
     <row r="4081" spans="1:1">
-      <c r="A4081" s="4" t="s">
+      <c r="A4081" s="2" t="s">
         <v>4080</v>
       </c>
     </row>
     <row r="4082" spans="1:1">
-      <c r="A4082" s="4" t="s">
+      <c r="A4082" s="2" t="s">
         <v>4081</v>
       </c>
     </row>
     <row r="4083" spans="1:1">
-      <c r="A4083" s="4" t="s">
+      <c r="A4083" s="2" t="s">
         <v>4082</v>
       </c>
     </row>
     <row r="4084" spans="1:1">
-      <c r="A4084" s="4" t="s">
+      <c r="A4084" s="2" t="s">
         <v>4083</v>
       </c>
     </row>
     <row r="4085" spans="1:1">
-      <c r="A4085" s="4" t="s">
+      <c r="A4085" s="2" t="s">
         <v>4084</v>
       </c>
     </row>
     <row r="4086" spans="1:1">
-      <c r="A4086" s="4" t="s">
+      <c r="A4086" s="2" t="s">
         <v>4085</v>
       </c>
     </row>
     <row r="4087" spans="1:1">
-      <c r="A4087" s="4" t="s">
+      <c r="A4087" s="2" t="s">
         <v>4086</v>
       </c>
     </row>
     <row r="4088" spans="1:1">
-      <c r="A4088" s="4" t="s">
+      <c r="A4088" s="2" t="s">
         <v>4087</v>
       </c>
     </row>
     <row r="4089" spans="1:1">
-      <c r="A4089" s="4" t="s">
+      <c r="A4089" s="2" t="s">
         <v>4088</v>
       </c>
     </row>
     <row r="4090" spans="1:1">
-      <c r="A4090" s="4" t="s">
+      <c r="A4090" s="2" t="s">
         <v>4089</v>
       </c>
     </row>
     <row r="4091" spans="1:1">
-      <c r="A4091" s="4" t="s">
+      <c r="A4091" s="2" t="s">
         <v>4090</v>
       </c>
     </row>
     <row r="4092" spans="1:1">
-      <c r="A4092" s="4" t="s">
+      <c r="A4092" s="2" t="s">
         <v>4091</v>
       </c>
     </row>
     <row r="4093" spans="1:1">
-      <c r="A4093" s="4" t="s">
+      <c r="A4093" s="2" t="s">
         <v>4092</v>
       </c>
     </row>
     <row r="4094" spans="1:1">
-      <c r="A4094" s="4" t="s">
+      <c r="A4094" s="2" t="s">
         <v>4093</v>
       </c>
     </row>
     <row r="4095" spans="1:1">
-      <c r="A4095" s="4" t="s">
+      <c r="A4095" s="2" t="s">
         <v>4094</v>
       </c>
     </row>
     <row r="4096" spans="1:1">
-      <c r="A4096" s="4" t="s">
+      <c r="A4096" s="2" t="s">
         <v>4095</v>
       </c>
     </row>
     <row r="4097" spans="1:1">
-      <c r="A4097" s="4" t="s">
+      <c r="A4097" s="2" t="s">
         <v>4096</v>
       </c>
     </row>
     <row r="4098" spans="1:1">
-      <c r="A4098" s="4" t="s">
+      <c r="A4098" s="2" t="s">
         <v>4097</v>
       </c>
     </row>
     <row r="4099" spans="1:1">
-      <c r="A4099" s="4" t="s">
+      <c r="A4099" s="2" t="s">
         <v>4098</v>
       </c>
     </row>
     <row r="4100" spans="1:1">
-      <c r="A4100" s="4" t="s">
+      <c r="A4100" s="2" t="s">
         <v>4099</v>
       </c>
     </row>
     <row r="4101" spans="1:1">
-      <c r="A4101" s="4" t="s">
+      <c r="A4101" s="2" t="s">
         <v>4100</v>
       </c>
     </row>
     <row r="4102" spans="1:1">
-      <c r="A4102" s="4" t="s">
+      <c r="A4102" s="2" t="s">
         <v>4101</v>
       </c>
     </row>
     <row r="4103" spans="1:1">
-      <c r="A4103" s="4" t="s">
+      <c r="A4103" s="2" t="s">
         <v>4102</v>
       </c>
     </row>
     <row r="4104" spans="1:1">
-      <c r="A4104" s="4" t="s">
+      <c r="A4104" s="2" t="s">
         <v>4103</v>
       </c>
     </row>
     <row r="4105" spans="1:1">
-      <c r="A4105" s="4" t="s">
+      <c r="A4105" s="2" t="s">
         <v>4104</v>
       </c>
     </row>
     <row r="4106" spans="1:1">
-      <c r="A4106" s="4" t="s">
+      <c r="A4106" s="2" t="s">
         <v>4105</v>
       </c>
     </row>
     <row r="4107" spans="1:1">
-      <c r="A4107" s="4" t="s">
+      <c r="A4107" s="2" t="s">
         <v>4106</v>
       </c>
     </row>
     <row r="4108" spans="1:1">
-      <c r="A4108" s="4" t="s">
+      <c r="A4108" s="2" t="s">
         <v>4107</v>
       </c>
     </row>
     <row r="4109" spans="1:1">
-      <c r="A4109" s="4" t="s">
+      <c r="A4109" s="2" t="s">
         <v>4108</v>
       </c>
     </row>
     <row r="4110" spans="1:1">
-      <c r="A4110" s="4" t="s">
+      <c r="A4110" s="2" t="s">
         <v>4109</v>
       </c>
     </row>
     <row r="4111" spans="1:1">
-      <c r="A4111" s="4" t="s">
+      <c r="A4111" s="2" t="s">
         <v>4110</v>
       </c>
     </row>
     <row r="4112" spans="1:1">
-      <c r="A4112" s="4" t="s">
+      <c r="A4112" s="2" t="s">
         <v>4111</v>
       </c>
     </row>
     <row r="4113" spans="1:1">
-      <c r="A4113" s="4" t="s">
+      <c r="A4113" s="2" t="s">
         <v>4112</v>
       </c>
     </row>
     <row r="4114" spans="1:1">
-      <c r="A4114" s="4" t="s">
+      <c r="A4114" s="2" t="s">
         <v>4113</v>
       </c>
     </row>
     <row r="4115" spans="1:1">
-      <c r="A4115" s="4" t="s">
+      <c r="A4115" s="2" t="s">
         <v>4114</v>
       </c>
     </row>
     <row r="4116" spans="1:1">
-      <c r="A4116" s="4" t="s">
+      <c r="A4116" s="2" t="s">
         <v>4115</v>
       </c>
     </row>
     <row r="4117" spans="1:1">
-      <c r="A4117" s="4" t="s">
+      <c r="A4117" s="2" t="s">
         <v>4116</v>
       </c>
     </row>
     <row r="4118" spans="1:1">
-      <c r="A4118" s="4" t="s">
+      <c r="A4118" s="2" t="s">
         <v>4117</v>
       </c>
     </row>
     <row r="4119" spans="1:1">
-      <c r="A4119" s="4" t="s">
+      <c r="A4119" s="2" t="s">
         <v>4118</v>
       </c>
     </row>
     <row r="4120" spans="1:1">
-      <c r="A4120" s="4" t="s">
+      <c r="A4120" s="2" t="s">
         <v>4119</v>
       </c>
     </row>
     <row r="4121" spans="1:1">
-      <c r="A4121" s="4" t="s">
+      <c r="A4121" s="2" t="s">
         <v>4120</v>
       </c>
     </row>
     <row r="4122" spans="1:1">
-      <c r="A4122" s="4" t="s">
+      <c r="A4122" s="2" t="s">
         <v>4121</v>
       </c>
     </row>
     <row r="4123" spans="1:1">
-      <c r="A4123" s="4" t="s">
+      <c r="A4123" s="2" t="s">
         <v>4122</v>
       </c>
     </row>
     <row r="4124" spans="1:1">
-      <c r="A4124" s="4" t="s">
+      <c r="A4124" s="2" t="s">
         <v>4123</v>
       </c>
     </row>
     <row r="4125" spans="1:1">
-      <c r="A4125" s="4" t="s">
+      <c r="A4125" s="2" t="s">
         <v>4124</v>
       </c>
     </row>
     <row r="4126" spans="1:1">
-      <c r="A4126" s="4" t="s">
+      <c r="A4126" s="2" t="s">
         <v>4125</v>
       </c>
     </row>
     <row r="4127" spans="1:1">
-      <c r="A4127" s="4" t="s">
+      <c r="A4127" s="2" t="s">
         <v>4126</v>
       </c>
     </row>
     <row r="4128" spans="1:1">
-      <c r="A4128" s="4" t="s">
+      <c r="A4128" s="2" t="s">
         <v>4127</v>
       </c>
     </row>
     <row r="4129" spans="1:1">
-      <c r="A4129" s="4" t="s">
+      <c r="A4129" s="2" t="s">
         <v>4128</v>
       </c>
     </row>
     <row r="4130" spans="1:1">
-      <c r="A4130" s="4" t="s">
+      <c r="A4130" s="2" t="s">
         <v>4129</v>
       </c>
     </row>
     <row r="4131" spans="1:1">
-      <c r="A4131" s="4" t="s">
+      <c r="A4131" s="2" t="s">
         <v>4130</v>
       </c>
     </row>
     <row r="4132" spans="1:1">
-      <c r="A4132" s="4" t="s">
+      <c r="A4132" s="2" t="s">
         <v>4131</v>
       </c>
     </row>
     <row r="4133" spans="1:1">
-      <c r="A4133" s="4" t="s">
+      <c r="A4133" s="2" t="s">
         <v>4132</v>
       </c>
     </row>
     <row r="4134" spans="1:1">
-      <c r="A4134" s="4" t="s">
+      <c r="A4134" s="2" t="s">
         <v>4133</v>
       </c>
     </row>
     <row r="4135" spans="1:1">
-      <c r="A4135" s="4" t="s">
+      <c r="A4135" s="2" t="s">
         <v>4134</v>
       </c>
     </row>
     <row r="4136" spans="1:1">
-      <c r="A4136" s="4" t="s">
+      <c r="A4136" s="2" t="s">
         <v>4135</v>
       </c>
     </row>
     <row r="4137" spans="1:1">
-      <c r="A4137" s="4" t="s">
+      <c r="A4137" s="2" t="s">
         <v>4136</v>
       </c>
     </row>
     <row r="4138" spans="1:1">
-      <c r="A4138" s="4" t="s">
+      <c r="A4138" s="2" t="s">
         <v>4137</v>
       </c>
     </row>
     <row r="4139" spans="1:1">
-      <c r="A4139" s="4" t="s">
+      <c r="A4139" s="2" t="s">
         <v>4138</v>
       </c>
     </row>
     <row r="4140" spans="1:1">
-      <c r="A4140" s="4" t="s">
+      <c r="A4140" s="2" t="s">
         <v>4139</v>
       </c>
     </row>
     <row r="4141" spans="1:1">
-      <c r="A4141" s="4" t="s">
+      <c r="A4141" s="2" t="s">
         <v>4140</v>
       </c>
     </row>
     <row r="4142" spans="1:1">
-      <c r="A4142" s="4" t="s">
+      <c r="A4142" s="2" t="s">
         <v>4141</v>
       </c>
     </row>
     <row r="4143" spans="1:1">
-      <c r="A4143" s="4" t="s">
+      <c r="A4143" s="2" t="s">
         <v>4142</v>
       </c>
     </row>
     <row r="4144" spans="1:1">
-      <c r="A4144" s="4" t="s">
+      <c r="A4144" s="2" t="s">
         <v>4143</v>
       </c>
     </row>
     <row r="4145" spans="1:1">
-      <c r="A4145" s="4" t="s">
+      <c r="A4145" s="2" t="s">
         <v>4144</v>
       </c>
     </row>
     <row r="4146" spans="1:1">
-      <c r="A4146" s="4" t="s">
+      <c r="A4146" s="2" t="s">
         <v>4145</v>
       </c>
     </row>
     <row r="4147" spans="1:1">
-      <c r="A4147" s="4" t="s">
+      <c r="A4147" s="2" t="s">
         <v>4146</v>
       </c>
     </row>
     <row r="4148" spans="1:1">
-      <c r="A4148" s="4" t="s">
+      <c r="A4148" s="2" t="s">
         <v>4147</v>
       </c>
     </row>
     <row r="4149" spans="1:1">
-      <c r="A4149" s="4" t="s">
+      <c r="A4149" s="2" t="s">
         <v>4148</v>
       </c>
     </row>
     <row r="4150" spans="1:1">
-      <c r="A4150" s="4" t="s">
+      <c r="A4150" s="2" t="s">
         <v>4149</v>
       </c>
     </row>
     <row r="4151" spans="1:1">
-      <c r="A4151" s="4" t="s">
+      <c r="A4151" s="2" t="s">
         <v>4150</v>
       </c>
     </row>
     <row r="4152" spans="1:1">
-      <c r="A4152" s="4" t="s">
+      <c r="A4152" s="2" t="s">
         <v>4151</v>
       </c>
     </row>
     <row r="4153" spans="1:1">
-      <c r="A4153" s="4" t="s">
+      <c r="A4153" s="2" t="s">
         <v>4152</v>
       </c>
     </row>
     <row r="4154" spans="1:1">
-      <c r="A4154" s="4" t="s">
+      <c r="A4154" s="2" t="s">
         <v>4153</v>
       </c>
     </row>
     <row r="4155" spans="1:1">
-      <c r="A4155" s="4" t="s">
+      <c r="A4155" s="2" t="s">
         <v>4154</v>
       </c>
     </row>
     <row r="4156" spans="1:1">
-      <c r="A4156" s="4" t="s">
+      <c r="A4156" s="2" t="s">
         <v>4155</v>
       </c>
     </row>
     <row r="4157" spans="1:1">
-      <c r="A4157" s="4" t="s">
+      <c r="A4157" s="2" t="s">
         <v>4156</v>
       </c>
     </row>
     <row r="4158" spans="1:1">
-      <c r="A4158" s="4" t="s">
+      <c r="A4158" s="2" t="s">
         <v>4157</v>
       </c>
     </row>
     <row r="4159" spans="1:1">
-      <c r="A4159" s="4" t="s">
+      <c r="A4159" s="2" t="s">
         <v>4158</v>
       </c>
     </row>
     <row r="4160" spans="1:1">
-      <c r="A4160" s="4" t="s">
+      <c r="A4160" s="2" t="s">
         <v>4159</v>
       </c>
     </row>
     <row r="4161" spans="1:1">
-      <c r="A4161" s="4" t="s">
+      <c r="A4161" s="2" t="s">
         <v>4160</v>
       </c>
     </row>
     <row r="4162" spans="1:1">
-      <c r="A4162" s="4" t="s">
+      <c r="A4162" s="2" t="s">
         <v>4161</v>
       </c>
     </row>
     <row r="4163" spans="1:1">
-      <c r="A4163" s="4" t="s">
+      <c r="A4163" s="2" t="s">
         <v>4162</v>
       </c>
     </row>
     <row r="4164" spans="1:1">
-      <c r="A4164" s="4" t="s">
+      <c r="A4164" s="2" t="s">
         <v>4163</v>
       </c>
     </row>
     <row r="4165" spans="1:1">
-      <c r="A4165" s="4" t="s">
+      <c r="A4165" s="2" t="s">
         <v>4164</v>
       </c>
     </row>
     <row r="4166" spans="1:1">
-      <c r="A4166" s="4" t="s">
+      <c r="A4166" s="2" t="s">
         <v>4165</v>
       </c>
     </row>
     <row r="4167" spans="1:1">
-      <c r="A4167" s="4" t="s">
+      <c r="A4167" s="2" t="s">
         <v>4166</v>
       </c>
     </row>
     <row r="4168" spans="1:1">
-      <c r="A4168" s="4" t="s">
+      <c r="A4168" s="2" t="s">
         <v>4167</v>
       </c>
     </row>
     <row r="4169" spans="1:1">
-      <c r="A4169" s="4" t="s">
+      <c r="A4169" s="2" t="s">
         <v>4168</v>
       </c>
     </row>
     <row r="4170" spans="1:1">
-      <c r="A4170" s="4" t="s">
+      <c r="A4170" s="2" t="s">
         <v>4169</v>
       </c>
     </row>
     <row r="4171" spans="1:1">
-      <c r="A4171" s="4" t="s">
+      <c r="A4171" s="2" t="s">
         <v>4170</v>
       </c>
     </row>
     <row r="4172" spans="1:1">
-      <c r="A4172" s="4" t="s">
+      <c r="A4172" s="2" t="s">
         <v>4171</v>
       </c>
     </row>
     <row r="4173" spans="1:1">
-      <c r="A4173" s="4" t="s">
+      <c r="A4173" s="2" t="s">
         <v>4172</v>
       </c>
     </row>
     <row r="4174" spans="1:1">
-      <c r="A4174" s="4" t="s">
+      <c r="A4174" s="2" t="s">
         <v>4173</v>
       </c>
     </row>
     <row r="4175" spans="1:1">
-      <c r="A4175" s="4" t="s">
+      <c r="A4175" s="2" t="s">
         <v>4174</v>
       </c>
     </row>
     <row r="4176" spans="1:1">
-      <c r="A4176" s="4" t="s">
+      <c r="A4176" s="2" t="s">
         <v>4175</v>
       </c>
     </row>
     <row r="4177" spans="1:1">
-      <c r="A4177" s="4" t="s">
+      <c r="A4177" s="2" t="s">
         <v>4176</v>
       </c>
     </row>
     <row r="4178" spans="1:1">
-      <c r="A4178" s="4" t="s">
+      <c r="A4178" s="2" t="s">
         <v>4177</v>
       </c>
     </row>
     <row r="4179" spans="1:1">
-      <c r="A4179" s="4" t="s">
+      <c r="A4179" s="2" t="s">
         <v>4178</v>
       </c>
     </row>
     <row r="4180" spans="1:1">
-      <c r="A4180" s="4" t="s">
+      <c r="A4180" s="2" t="s">
         <v>4179</v>
       </c>
     </row>
     <row r="4181" spans="1:1">
-      <c r="A4181" s="4" t="s">
+      <c r="A4181" s="2" t="s">
         <v>4180</v>
       </c>
     </row>
     <row r="4182" spans="1:1">
-      <c r="A4182" s="4" t="s">
+      <c r="A4182" s="2" t="s">
         <v>4181</v>
       </c>
     </row>
     <row r="4183" spans="1:1">
-      <c r="A4183" s="4" t="s">
+      <c r="A4183" s="2" t="s">
         <v>4182</v>
       </c>
     </row>
     <row r="4184" spans="1:1">
-      <c r="A4184" s="4" t="s">
+      <c r="A4184" s="2" t="s">
         <v>4183</v>
       </c>
     </row>
     <row r="4185" spans="1:1">
-      <c r="A4185" s="4" t="s">
+      <c r="A4185" s="2" t="s">
         <v>4184</v>
       </c>
     </row>
     <row r="4186" spans="1:1">
-      <c r="A4186" s="4" t="s">
+      <c r="A4186" s="2" t="s">
         <v>4185</v>
       </c>
     </row>
     <row r="4187" spans="1:1">
-      <c r="A4187" s="4" t="s">
+      <c r="A4187" s="2" t="s">
         <v>4186</v>
       </c>
     </row>
     <row r="4188" spans="1:1">
-      <c r="A4188" s="4" t="s">
+      <c r="A4188" s="2" t="s">
         <v>4187</v>
       </c>
     </row>
     <row r="4189" spans="1:1">
-      <c r="A4189" s="4" t="s">
+      <c r="A4189" s="2" t="s">
         <v>4188</v>
       </c>
     </row>
     <row r="4190" spans="1:1">
-      <c r="A4190" s="4" t="s">
+      <c r="A4190" s="2" t="s">
         <v>4189</v>
       </c>
     </row>
     <row r="4191" spans="1:1">
-      <c r="A4191" s="4" t="s">
+      <c r="A4191" s="2" t="s">
         <v>4190</v>
       </c>
     </row>
     <row r="4192" spans="1:1">
-      <c r="A4192" s="4" t="s">
+      <c r="A4192" s="2" t="s">
         <v>4191</v>
       </c>
     </row>
     <row r="4193" spans="1:1">
-      <c r="A4193" s="4" t="s">
+      <c r="A4193" s="2" t="s">
         <v>4192</v>
       </c>
     </row>
     <row r="4194" spans="1:1">
-      <c r="A4194" s="4" t="s">
+      <c r="A4194" s="2" t="s">
         <v>4193</v>
       </c>
     </row>
     <row r="4195" spans="1:1">
-      <c r="A4195" s="4" t="s">
+      <c r="A4195" s="2" t="s">
         <v>4194</v>
       </c>
     </row>
     <row r="4196" spans="1:1">
-      <c r="A4196" s="4" t="s">
+      <c r="A4196" s="2" t="s">
         <v>4195</v>
       </c>
     </row>
     <row r="4197" spans="1:1">
-      <c r="A4197" s="4" t="s">
+      <c r="A4197" s="2" t="s">
         <v>4196</v>
       </c>
     </row>
     <row r="4198" spans="1:1">
-      <c r="A4198" s="4" t="s">
+      <c r="A4198" s="2" t="s">
         <v>4197</v>
       </c>
     </row>
     <row r="4199" spans="1:1">
-      <c r="A4199" s="4" t="s">
+      <c r="A4199" s="2" t="s">
         <v>4198</v>
       </c>
     </row>
     <row r="4200" spans="1:1">
-      <c r="A4200" s="4" t="s">
+      <c r="A4200" s="2" t="s">
         <v>4199</v>
       </c>
     </row>
     <row r="4201" spans="1:1">
-      <c r="A4201" s="4" t="s">
+      <c r="A4201" s="2" t="s">
         <v>4200</v>
       </c>
     </row>
     <row r="4202" spans="1:1">
-      <c r="A4202" s="4" t="s">
+      <c r="A4202" s="2" t="s">
         <v>4201</v>
       </c>
     </row>
     <row r="4203" spans="1:1">
-      <c r="A4203" s="4" t="s">
+      <c r="A4203" s="2" t="s">
         <v>4202</v>
       </c>
     </row>
     <row r="4204" spans="1:1">
-      <c r="A4204" s="4" t="s">
+      <c r="A4204" s="2" t="s">
         <v>4203</v>
       </c>
     </row>
     <row r="4205" spans="1:1">
-      <c r="A4205" s="4" t="s">
+      <c r="A4205" s="2" t="s">
         <v>4204</v>
       </c>
     </row>
     <row r="4206" spans="1:1">
-      <c r="A4206" s="4" t="s">
+      <c r="A4206" s="2" t="s">
         <v>4205</v>
       </c>
     </row>
     <row r="4207" spans="1:1">
-      <c r="A4207" s="4" t="s">
+      <c r="A4207" s="2" t="s">
         <v>4206</v>
       </c>
     </row>
     <row r="4208" spans="1:1">
-      <c r="A4208" s="4" t="s">
+      <c r="A4208" s="2" t="s">
         <v>4207</v>
       </c>
     </row>
     <row r="4209" spans="1:1">
-      <c r="A4209" s="4" t="s">
+      <c r="A4209" s="2" t="s">
         <v>4208</v>
       </c>
     </row>
     <row r="4210" spans="1:1">
-      <c r="A4210" s="4" t="s">
+      <c r="A4210" s="2" t="s">
         <v>4209</v>
       </c>
     </row>
     <row r="4211" spans="1:1">
-      <c r="A4211" s="4" t="s">
+      <c r="A4211" s="2" t="s">
         <v>4210</v>
       </c>
     </row>
     <row r="4212" spans="1:1">
-      <c r="A4212" s="4" t="s">
+      <c r="A4212" s="2" t="s">
         <v>4211</v>
       </c>
     </row>
     <row r="4213" spans="1:1">
-      <c r="A4213" s="4" t="s">
+      <c r="A4213" s="2" t="s">
         <v>4212</v>
       </c>
     </row>
     <row r="4214" spans="1:1">
-      <c r="A4214" s="4" t="s">
+      <c r="A4214" s="2" t="s">
         <v>4213</v>
       </c>
     </row>
     <row r="4215" spans="1:1">
-      <c r="A4215" s="4" t="s">
+      <c r="A4215" s="2" t="s">
         <v>4214</v>
       </c>
     </row>
     <row r="4216" spans="1:1">
-      <c r="A4216" s="4" t="s">
+      <c r="A4216" s="2" t="s">
         <v>4215</v>
       </c>
     </row>
     <row r="4217" spans="1:1">
-      <c r="A4217" s="4" t="s">
+      <c r="A4217" s="2" t="s">
         <v>4216</v>
       </c>
     </row>
     <row r="4218" spans="1:1">
-      <c r="A4218" s="4" t="s">
+      <c r="A4218" s="2" t="s">
         <v>4217</v>
       </c>
     </row>
     <row r="4219" spans="1:1">
-      <c r="A4219" s="4" t="s">
+      <c r="A4219" s="2" t="s">
         <v>4218</v>
       </c>
     </row>
     <row r="4220" spans="1:1">
-      <c r="A4220" s="4" t="s">
+      <c r="A4220" s="2" t="s">
         <v>4219</v>
       </c>
     </row>
     <row r="4221" spans="1:1">
-      <c r="A4221" s="4" t="s">
+      <c r="A4221" s="2" t="s">
         <v>4220</v>
       </c>
     </row>
     <row r="4222" spans="1:1">
-      <c r="A4222" s="4" t="s">
+      <c r="A4222" s="2" t="s">
         <v>4221</v>
       </c>
     </row>
     <row r="4223" spans="1:1">
-      <c r="A4223" s="4" t="s">
+      <c r="A4223" s="2" t="s">
         <v>4222</v>
       </c>
     </row>
     <row r="4224" spans="1:1">
-      <c r="A4224" s="4" t="s">
+      <c r="A4224" s="2" t="s">
         <v>4223</v>
       </c>
     </row>
     <row r="4225" spans="1:1">
-      <c r="A4225" s="4" t="s">
+      <c r="A4225" s="2" t="s">
         <v>4224</v>
       </c>
     </row>
     <row r="4226" spans="1:1">
-      <c r="A4226" s="4" t="s">
+      <c r="A4226" s="2" t="s">
         <v>4225</v>
       </c>
     </row>
     <row r="4227" spans="1:1">
-      <c r="A4227" s="4" t="s">
+      <c r="A4227" s="2" t="s">
         <v>4226</v>
       </c>
     </row>
     <row r="4228" spans="1:1">
-      <c r="A4228" s="4" t="s">
+      <c r="A4228" s="2" t="s">
         <v>4227</v>
       </c>
     </row>
     <row r="4229" spans="1:1">
-      <c r="A4229" s="4" t="s">
+      <c r="A4229" s="2" t="s">
         <v>4228</v>
       </c>
     </row>
     <row r="4230" spans="1:1">
-      <c r="A4230" s="4" t="s">
+      <c r="A4230" s="2" t="s">
         <v>4229</v>
       </c>
     </row>
     <row r="4231" spans="1:1">
-      <c r="A4231" s="4" t="s">
+      <c r="A4231" s="2" t="s">
         <v>4230</v>
       </c>
     </row>
     <row r="4232" spans="1:1">
-      <c r="A4232" s="4" t="s">
+      <c r="A4232" s="2" t="s">
         <v>4231</v>
       </c>
     </row>
     <row r="4233" spans="1:1">
-      <c r="A4233" s="4" t="s">
+      <c r="A4233" s="2" t="s">
         <v>4232</v>
       </c>
     </row>
     <row r="4234" spans="1:1">
-      <c r="A4234" s="4" t="s">
+      <c r="A4234" s="2" t="s">
         <v>4233</v>
       </c>
     </row>
     <row r="4235" spans="1:1">
-      <c r="A4235" s="4" t="s">
+      <c r="A4235" s="2" t="s">
         <v>4234</v>
       </c>
     </row>
     <row r="4236" spans="1:1">
-      <c r="A4236" s="4" t="s">
+      <c r="A4236" s="2" t="s">
         <v>4235</v>
       </c>
     </row>
     <row r="4237" spans="1:1">
-      <c r="A4237" s="4" t="s">
+      <c r="A4237" s="2" t="s">
         <v>4236</v>
       </c>
     </row>
     <row r="4238" spans="1:1">
-      <c r="A4238" s="4" t="s">
+      <c r="A4238" s="2" t="s">
         <v>4237</v>
       </c>
     </row>
     <row r="4239" spans="1:1">
-      <c r="A4239" s="4" t="s">
+      <c r="A4239" s="2" t="s">
         <v>4238</v>
       </c>
     </row>
     <row r="4240" spans="1:1">
-      <c r="A4240" s="4" t="s">
+      <c r="A4240" s="2" t="s">
         <v>4239</v>
       </c>
     </row>
     <row r="4241" spans="1:1">
-      <c r="A4241" s="4" t="s">
+      <c r="A4241" s="2" t="s">
         <v>4240</v>
       </c>
     </row>
     <row r="4242" spans="1:1">
-      <c r="A4242" s="4" t="s">
+      <c r="A4242" s="2" t="s">
         <v>4241</v>
       </c>
     </row>
     <row r="4243" spans="1:1">
-      <c r="A4243" s="4" t="s">
+      <c r="A4243" s="2" t="s">
         <v>4242</v>
       </c>
     </row>
     <row r="4244" spans="1:1">
-      <c r="A4244" s="4" t="s">
+      <c r="A4244" s="2" t="s">
         <v>4243</v>
       </c>
     </row>
     <row r="4245" spans="1:1">
-      <c r="A4245" s="4" t="s">
+      <c r="A4245" s="2" t="s">
         <v>4244</v>
       </c>
     </row>
     <row r="4246" spans="1:1">
-      <c r="A4246" s="4" t="s">
+      <c r="A4246" s="2" t="s">
         <v>4245</v>
       </c>
     </row>
     <row r="4247" spans="1:1">
-      <c r="A4247" s="4" t="s">
+      <c r="A4247" s="2" t="s">
         <v>4246</v>
       </c>
     </row>
     <row r="4248" spans="1:1">
-      <c r="A4248" s="4" t="s">
+      <c r="A4248" s="2" t="s">
         <v>4247</v>
       </c>
     </row>
     <row r="4249" spans="1:1">
-      <c r="A4249" s="4" t="s">
+      <c r="A4249" s="2" t="s">
         <v>4248</v>
       </c>
     </row>
     <row r="4250" spans="1:1">
-      <c r="A4250" s="4" t="s">
+      <c r="A4250" s="2" t="s">
         <v>4249</v>
       </c>
     </row>
     <row r="4251" spans="1:1">
-      <c r="A4251" s="4" t="s">
+      <c r="A4251" s="2" t="s">
         <v>4250</v>
       </c>
     </row>
     <row r="4252" spans="1:1">
-      <c r="A4252" s="4" t="s">
+      <c r="A4252" s="2" t="s">
         <v>4251</v>
       </c>
     </row>
     <row r="4253" spans="1:1">
-      <c r="A4253" s="4" t="s">
+      <c r="A4253" s="2" t="s">
         <v>4252</v>
       </c>
     </row>
     <row r="4254" spans="1:1">
-      <c r="A4254" s="4" t="s">
+      <c r="A4254" s="2" t="s">
         <v>4253</v>
       </c>
     </row>
     <row r="4255" spans="1:1">
-      <c r="A4255" s="4" t="s">
+      <c r="A4255" s="2" t="s">
         <v>4254</v>
       </c>
     </row>
     <row r="4256" spans="1:1">
-      <c r="A4256" s="4" t="s">
+      <c r="A4256" s="2" t="s">
         <v>4255</v>
       </c>
     </row>
     <row r="4257" spans="1:1">
-      <c r="A4257" s="4" t="s">
+      <c r="A4257" s="2" t="s">
         <v>4256</v>
       </c>
     </row>
     <row r="4258" spans="1:1">
-      <c r="A4258" s="4" t="s">
+      <c r="A4258" s="2" t="s">
         <v>4257</v>
       </c>
     </row>
     <row r="4259" spans="1:1">
-      <c r="A4259" s="4" t="s">
+      <c r="A4259" s="2" t="s">
         <v>4258</v>
       </c>
     </row>
     <row r="4260" spans="1:1">
-      <c r="A4260" s="4" t="s">
+      <c r="A4260" s="2" t="s">
         <v>4259</v>
       </c>
     </row>
     <row r="4261" spans="1:1">
-      <c r="A4261" s="4" t="s">
+      <c r="A4261" s="2" t="s">
         <v>4260</v>
       </c>
     </row>
     <row r="4262" spans="1:1">
-      <c r="A4262" s="4" t="s">
+      <c r="A4262" s="2" t="s">
         <v>4261</v>
       </c>
     </row>
     <row r="4263" spans="1:1">
-      <c r="A4263" s="4" t="s">
+      <c r="A4263" s="2" t="s">
         <v>4262</v>
       </c>
     </row>
     <row r="4264" spans="1:1">
-      <c r="A4264" s="4" t="s">
+      <c r="A4264" s="2" t="s">
         <v>4263</v>
       </c>
     </row>
     <row r="4265" spans="1:1">
-      <c r="A4265" s="4" t="s">
+      <c r="A4265" s="2" t="s">
         <v>4264</v>
       </c>
     </row>
     <row r="4266" spans="1:1">
-      <c r="A4266" s="4" t="s">
+      <c r="A4266" s="2" t="s">
         <v>4265</v>
       </c>
     </row>
     <row r="4267" spans="1:1">
-      <c r="A4267" s="4" t="s">
+      <c r="A4267" s="2" t="s">
         <v>4266</v>
       </c>
     </row>
     <row r="4268" spans="1:1">
-      <c r="A4268" s="4" t="s">
+      <c r="A4268" s="2" t="s">
         <v>4267</v>
       </c>
     </row>
     <row r="4269" spans="1:1">
-      <c r="A4269" s="4" t="s">
+      <c r="A4269" s="2" t="s">
         <v>4268</v>
       </c>
     </row>
     <row r="4270" spans="1:1">
-      <c r="A4270" s="4" t="s">
+      <c r="A4270" s="2" t="s">
         <v>4269</v>
       </c>
     </row>
     <row r="4271" spans="1:1">
-      <c r="A4271" s="4" t="s">
+      <c r="A4271" s="2" t="s">
         <v>4270</v>
       </c>
     </row>
     <row r="4272" spans="1:1">
-      <c r="A4272" s="4" t="s">
+      <c r="A4272" s="2" t="s">
         <v>4271</v>
       </c>
     </row>
     <row r="4273" spans="1:1">
-      <c r="A4273" s="4" t="s">
+      <c r="A4273" s="2" t="s">
         <v>4272</v>
       </c>
     </row>
     <row r="4274" spans="1:1">
-      <c r="A4274" s="4" t="s">
+      <c r="A4274" s="2" t="s">
         <v>4273</v>
       </c>
     </row>
     <row r="4275" spans="1:1">
-      <c r="A4275" s="4" t="s">
+      <c r="A4275" s="2" t="s">
         <v>4274</v>
       </c>
     </row>
     <row r="4276" spans="1:1">
-      <c r="A4276" s="4" t="s">
+      <c r="A4276" s="2" t="s">
         <v>4275</v>
       </c>
     </row>
     <row r="4277" spans="1:1">
-      <c r="A4277" s="4" t="s">
+      <c r="A4277" s="2" t="s">
         <v>4276</v>
       </c>
     </row>
     <row r="4278" spans="1:1">
-      <c r="A4278" s="4" t="s">
+      <c r="A4278" s="2" t="s">
         <v>4277</v>
       </c>
     </row>
     <row r="4279" spans="1:1">
-      <c r="A4279" s="4" t="s">
+      <c r="A4279" s="2" t="s">
         <v>4278</v>
       </c>
     </row>
     <row r="4280" spans="1:1">
-      <c r="A4280" s="4" t="s">
+      <c r="A4280" s="2" t="s">
         <v>4279</v>
       </c>
     </row>
     <row r="4281" spans="1:1">
-      <c r="A4281" s="4" t="s">
+      <c r="A4281" s="2" t="s">
         <v>4280</v>
       </c>
     </row>
     <row r="4282" spans="1:1">
-      <c r="A4282" s="4" t="s">
+      <c r="A4282" s="2" t="s">
         <v>4281</v>
       </c>
     </row>
     <row r="4283" spans="1:1">
-      <c r="A4283" s="4" t="s">
+      <c r="A4283" s="2" t="s">
         <v>4282</v>
       </c>
     </row>
     <row r="4284" spans="1:1">
-      <c r="A4284" s="4" t="s">
+      <c r="A4284" s="2" t="s">
         <v>4283</v>
       </c>
     </row>
     <row r="4285" spans="1:1">
-      <c r="A4285" s="4" t="s">
+      <c r="A4285" s="2" t="s">
         <v>4284</v>
       </c>
     </row>
     <row r="4286" spans="1:1">
-      <c r="A4286" s="4" t="s">
+      <c r="A4286" s="2" t="s">
         <v>4285</v>
       </c>
     </row>
     <row r="4287" spans="1:1">
-      <c r="A4287" s="4" t="s">
+      <c r="A4287" s="2" t="s">
         <v>4286</v>
       </c>
     </row>
     <row r="4288" spans="1:1">
-      <c r="A4288" s="4" t="s">
+      <c r="A4288" s="2" t="s">
         <v>4287</v>
       </c>
     </row>
     <row r="4289" spans="1:1">
-      <c r="A4289" s="4" t="s">
+      <c r="A4289" s="2" t="s">
         <v>4288</v>
       </c>
     </row>
     <row r="4290" spans="1:1">
-      <c r="A4290" s="4" t="s">
+      <c r="A4290" s="2" t="s">
         <v>4289</v>
       </c>
     </row>
     <row r="4291" spans="1:1">
-      <c r="A4291" s="4" t="s">
+      <c r="A4291" s="2" t="s">
         <v>4290</v>
       </c>
     </row>
     <row r="4292" spans="1:1">
-      <c r="A4292" s="4" t="s">
+      <c r="A4292" s="2" t="s">
         <v>4291</v>
       </c>
     </row>
     <row r="4293" spans="1:1">
-      <c r="A4293" s="4" t="s">
+      <c r="A4293" s="2" t="s">
         <v>4292</v>
       </c>
     </row>
     <row r="4294" spans="1:1">
-      <c r="A4294" s="4" t="s">
+      <c r="A4294" s="2" t="s">
         <v>4293</v>
       </c>
     </row>
     <row r="4295" spans="1:1">
-      <c r="A4295" s="4" t="s">
+      <c r="A4295" s="2" t="s">
         <v>4294</v>
       </c>
     </row>
     <row r="4296" spans="1:1">
-      <c r="A4296" s="4" t="s">
+      <c r="A4296" s="2" t="s">
         <v>4295</v>
       </c>
     </row>
     <row r="4297" spans="1:1">
-      <c r="A4297" s="4" t="s">
+      <c r="A4297" s="2" t="s">
         <v>4296</v>
       </c>
     </row>
     <row r="4298" spans="1:1">
-      <c r="A4298" s="4" t="s">
+      <c r="A4298" s="2" t="s">
         <v>4297</v>
       </c>
     </row>
     <row r="4299" spans="1:1">
-      <c r="A4299" s="4" t="s">
+      <c r="A4299" s="2" t="s">
         <v>4298</v>
       </c>
     </row>
     <row r="4300" spans="1:1">
-      <c r="A4300" s="4" t="s">
+      <c r="A4300" s="2" t="s">
         <v>4299</v>
       </c>
     </row>
     <row r="4301" spans="1:1">
-      <c r="A4301" s="4" t="s">
+      <c r="A4301" s="2" t="s">
         <v>4300</v>
       </c>
     </row>
     <row r="4302" spans="1:1">
-      <c r="A4302" s="4" t="s">
+      <c r="A4302" s="2" t="s">
         <v>4301</v>
       </c>
     </row>
     <row r="4303" spans="1:1">
-      <c r="A4303" s="4" t="s">
+      <c r="A4303" s="2" t="s">
         <v>4302</v>
       </c>
     </row>
     <row r="4304" spans="1:1">
-      <c r="A4304" s="4" t="s">
+      <c r="A4304" s="2" t="s">
         <v>4303</v>
       </c>
     </row>
     <row r="4305" spans="1:1">
-      <c r="A4305" s="4" t="s">
+      <c r="A4305" s="2" t="s">
         <v>4304</v>
       </c>
     </row>
     <row r="4306" spans="1:1">
-      <c r="A4306" s="4" t="s">
+      <c r="A4306" s="2" t="s">
         <v>4305</v>
       </c>
     </row>
     <row r="4307" spans="1:1">
-      <c r="A4307" s="4" t="s">
+      <c r="A4307" s="2" t="s">
         <v>4306</v>
       </c>
     </row>
     <row r="4308" spans="1:1">
-      <c r="A4308" s="4" t="s">
+      <c r="A4308" s="2" t="s">
         <v>4307</v>
       </c>
     </row>
     <row r="4309" spans="1:1">
-      <c r="A4309" s="4" t="s">
+      <c r="A4309" s="2" t="s">
         <v>4308</v>
       </c>
     </row>
     <row r="4310" spans="1:1">
-      <c r="A4310" s="4" t="s">
+      <c r="A4310" s="2" t="s">
         <v>4309</v>
       </c>
     </row>
     <row r="4311" spans="1:1">
-      <c r="A4311" s="4" t="s">
+      <c r="A4311" s="2" t="s">
         <v>4310</v>
       </c>
     </row>
     <row r="4312" spans="1:1">
-      <c r="A4312" s="4" t="s">
+      <c r="A4312" s="2" t="s">
         <v>4311</v>
       </c>
     </row>
     <row r="4313" spans="1:1">
-      <c r="A4313" s="4" t="s">
+      <c r="A4313" s="2" t="s">
         <v>4312</v>
       </c>
     </row>
     <row r="4314" spans="1:1">
-      <c r="A4314" s="4" t="s">
+      <c r="A4314" s="2" t="s">
         <v>4313</v>
       </c>
     </row>
     <row r="4315" spans="1:1">
-      <c r="A4315" s="4" t="s">
+      <c r="A4315" s="2" t="s">
         <v>4314</v>
       </c>
     </row>
     <row r="4316" spans="1:1">
-      <c r="A4316" s="4" t="s">
+      <c r="A4316" s="2" t="s">
         <v>4315</v>
       </c>
     </row>
     <row r="4317" spans="1:1">
-      <c r="A4317" s="4" t="s">
+      <c r="A4317" s="2" t="s">
         <v>4316</v>
       </c>
     </row>
     <row r="4318" spans="1:1">
-      <c r="A4318" s="4" t="s">
+      <c r="A4318" s="2" t="s">
         <v>4317</v>
       </c>
     </row>
     <row r="4319" spans="1:1">
-      <c r="A4319" s="4" t="s">
+      <c r="A4319" s="2" t="s">
         <v>4318</v>
       </c>
     </row>
     <row r="4320" spans="1:1">
-      <c r="A4320" s="4" t="s">
+      <c r="A4320" s="2" t="s">
         <v>4319</v>
       </c>
     </row>
     <row r="4321" spans="1:1">
-      <c r="A4321" s="4" t="s">
+      <c r="A4321" s="2" t="s">
         <v>4320</v>
       </c>
     </row>
     <row r="4322" spans="1:1">
-      <c r="A4322" s="4" t="s">
+      <c r="A4322" s="2" t="s">
         <v>4321</v>
       </c>
     </row>
     <row r="4323" spans="1:1">
-      <c r="A4323" s="4" t="s">
+      <c r="A4323" s="2" t="s">
         <v>4322</v>
       </c>
     </row>
     <row r="4324" spans="1:1">
-      <c r="A4324" s="4" t="s">
+      <c r="A4324" s="2" t="s">
         <v>4323</v>
       </c>
     </row>
     <row r="4325" spans="1:1">
-      <c r="A4325" s="4" t="s">
+      <c r="A4325" s="2" t="s">
         <v>4324</v>
       </c>
     </row>
     <row r="4326" spans="1:1">
-      <c r="A4326" s="4" t="s">
+      <c r="A4326" s="2" t="s">
         <v>4325</v>
       </c>
     </row>
     <row r="4327" spans="1:1">
-      <c r="A4327" s="4" t="s">
+      <c r="A4327" s="2" t="s">
         <v>4326</v>
       </c>
     </row>
     <row r="4328" spans="1:1">
-      <c r="A4328" s="4" t="s">
+      <c r="A4328" s="2" t="s">
         <v>4327</v>
       </c>
     </row>
     <row r="4329" spans="1:1">
-      <c r="A4329" s="4" t="s">
+      <c r="A4329" s="2" t="s">
         <v>4328</v>
       </c>
     </row>
     <row r="4330" spans="1:1">
-      <c r="A4330" s="4" t="s">
+      <c r="A4330" s="2" t="s">
         <v>4329</v>
       </c>
     </row>
     <row r="4331" spans="1:1">
-      <c r="A4331" s="4" t="s">
+      <c r="A4331" s="2" t="s">
         <v>4330</v>
       </c>
     </row>
     <row r="4332" spans="1:1">
-      <c r="A4332" s="4" t="s">
+      <c r="A4332" s="2" t="s">
         <v>4331</v>
       </c>
     </row>
     <row r="4333" spans="1:1">
-      <c r="A4333" s="4" t="s">
+      <c r="A4333" s="2" t="s">
         <v>4332</v>
       </c>
     </row>
     <row r="4334" spans="1:1">
-      <c r="A4334" s="4" t="s">
+      <c r="A4334" s="2" t="s">
         <v>4333</v>
       </c>
     </row>
     <row r="4335" spans="1:1">
-      <c r="A4335" s="4" t="s">
+      <c r="A4335" s="2" t="s">
         <v>4334</v>
       </c>
     </row>
     <row r="4336" spans="1:1">
-      <c r="A4336" s="4" t="s">
+      <c r="A4336" s="2" t="s">
         <v>4335</v>
       </c>
     </row>
     <row r="4337" spans="1:1">
-      <c r="A4337" s="4" t="s">
+      <c r="A4337" s="2" t="s">
         <v>4336</v>
       </c>
     </row>
     <row r="4338" spans="1:1">
-      <c r="A4338" s="4" t="s">
+      <c r="A4338" s="2" t="s">
         <v>4337</v>
       </c>
     </row>
     <row r="4339" spans="1:1">
-      <c r="A4339" s="4" t="s">
+      <c r="A4339" s="2" t="s">
         <v>4338</v>
       </c>
     </row>
     <row r="4340" spans="1:1">
-      <c r="A4340" s="4" t="s">
+      <c r="A4340" s="2" t="s">
         <v>4339</v>
       </c>
     </row>
     <row r="4341" spans="1:1">
-      <c r="A4341" s="4" t="s">
+      <c r="A4341" s="2" t="s">
         <v>4340</v>
       </c>
     </row>
     <row r="4342" spans="1:1">
-      <c r="A4342" s="4" t="s">
+      <c r="A4342" s="2" t="s">
         <v>4341</v>
       </c>
     </row>
     <row r="4343" spans="1:1">
-      <c r="A4343" s="4" t="s">
+      <c r="A4343" s="2" t="s">
         <v>4342</v>
       </c>
     </row>
     <row r="4344" spans="1:1">
-      <c r="A4344" s="4" t="s">
+      <c r="A4344" s="2" t="s">
         <v>4343</v>
       </c>
     </row>
     <row r="4345" spans="1:1">
-      <c r="A4345" s="4" t="s">
+      <c r="A4345" s="2" t="s">
         <v>4344</v>
       </c>
     </row>
     <row r="4346" spans="1:1">
-      <c r="A4346" s="4" t="s">
+      <c r="A4346" s="2" t="s">
         <v>4345</v>
       </c>
     </row>
     <row r="4347" spans="1:1">
-      <c r="A4347" s="4" t="s">
+      <c r="A4347" s="2" t="s">
         <v>4346</v>
       </c>
     </row>
     <row r="4348" spans="1:1">
-      <c r="A4348" s="4" t="s">
+      <c r="A4348" s="2" t="s">
         <v>4347</v>
       </c>
     </row>
     <row r="4349" spans="1:1">
-      <c r="A4349" s="4" t="s">
+      <c r="A4349" s="2" t="s">
         <v>4348</v>
       </c>
     </row>
     <row r="4350" spans="1:1">
-      <c r="A4350" s="4" t="s">
+      <c r="A4350" s="2" t="s">
         <v>4349</v>
       </c>
     </row>
     <row r="4351" spans="1:1">
-      <c r="A4351" s="4" t="s">
+      <c r="A4351" s="2" t="s">
         <v>4350</v>
       </c>
     </row>
     <row r="4352" spans="1:1">
-      <c r="A4352" s="4" t="s">
+      <c r="A4352" s="2" t="s">
         <v>4351</v>
       </c>
     </row>
     <row r="4353" spans="1:1">
-      <c r="A4353" s="4" t="s">
+      <c r="A4353" s="2" t="s">
         <v>4352</v>
       </c>
     </row>
     <row r="4354" spans="1:1">
-      <c r="A4354" s="4" t="s">
+      <c r="A4354" s="2" t="s">
         <v>4353</v>
       </c>
     </row>
     <row r="4355" spans="1:1">
-      <c r="A4355" s="4" t="s">
+      <c r="A4355" s="2" t="s">
         <v>4354</v>
       </c>
     </row>
     <row r="4356" spans="1:1">
-      <c r="A4356" s="4" t="s">
+      <c r="A4356" s="2" t="s">
         <v>4355</v>
       </c>
     </row>
     <row r="4357" spans="1:1">
-      <c r="A4357" s="4" t="s">
+      <c r="A4357" s="2" t="s">
         <v>4356</v>
       </c>
     </row>
     <row r="4358" spans="1:1">
-      <c r="A4358" s="4" t="s">
+      <c r="A4358" s="2" t="s">
         <v>4357</v>
       </c>
     </row>
     <row r="4359" spans="1:1">
-      <c r="A4359" s="4" t="s">
+      <c r="A4359" s="2" t="s">
         <v>4358</v>
       </c>
     </row>
     <row r="4360" spans="1:1">
-      <c r="A4360" s="4"/>
+      <c r="A4360" s="2" t="s">
+        <v>4359</v>
+      </c>
     </row>
     <row r="4361" spans="1:1">
-      <c r="A4361" s="4" t="s">
-        <v>4359</v>
+      <c r="A4361" s="2" t="s">
+        <v>4360</v>
       </c>
     </row>
     <row r="4362" spans="1:1">
-      <c r="A4362" s="4" t="s">
-        <v>4360</v>
+      <c r="A4362" s="2" t="s">
+        <v>4361</v>
       </c>
     </row>
     <row r="4363" spans="1:1">
-      <c r="A4363" s="4" t="s">
-        <v>4361</v>
+      <c r="A4363" s="2" t="s">
+        <v>4362</v>
       </c>
     </row>
     <row r="4364" spans="1:1">
-      <c r="A4364" s="5" t="s">
-        <v>4362</v>
+      <c r="A4364" s="2" t="s">
+        <v>4363</v>
       </c>
     </row>
     <row r="4365" spans="1:1">
-      <c r="A4365" s="5" t="s">
-        <v>4363</v>
+      <c r="A4365" s="2" t="s">
+        <v>4364</v>
       </c>
     </row>
     <row r="4366" spans="1:1">
-      <c r="A4366" s="5" t="s">
-        <v>4364</v>
+      <c r="A4366" s="2" t="s">
+        <v>4365</v>
       </c>
     </row>
     <row r="4367" spans="1:1">
-      <c r="A4367" s="5" t="s">
-        <v>4365</v>
+      <c r="A4367" s="2" t="s">
+        <v>4366</v>
       </c>
     </row>
     <row r="4368" spans="1:1">
-      <c r="A4368" s="5" t="s">
-        <v>4366</v>
+      <c r="A4368" s="2" t="s">
+        <v>4367</v>
       </c>
     </row>
     <row r="4369" spans="1:1">
-      <c r="A4369" s="5" t="s">
-        <v>4367</v>
+      <c r="A4369" s="2" t="s">
+        <v>4368</v>
       </c>
     </row>
     <row r="4370" spans="1:1">
-      <c r="A4370" s="5" t="s">
-        <v>4368</v>
+      <c r="A4370" s="2" t="s">
+        <v>4369</v>
       </c>
     </row>
     <row r="4371" spans="1:1">
-      <c r="A4371" s="5" t="s">
-        <v>4369</v>
+      <c r="A4371" s="2" t="s">
+        <v>4370</v>
       </c>
     </row>
     <row r="4372" spans="1:1">
-      <c r="A4372" s="5" t="s">
-        <v>4370</v>
+      <c r="A4372" s="2" t="s">
+        <v>4371</v>
       </c>
     </row>
     <row r="4373" spans="1:1">
-      <c r="A4373" s="5" t="s">
-        <v>4371</v>
+      <c r="A4373" s="2" t="s">
+        <v>4372</v>
       </c>
     </row>
     <row r="4374" spans="1:1">
-      <c r="A4374" s="5" t="s">
-        <v>4372</v>
+      <c r="A4374" s="2" t="s">
+        <v>4373</v>
       </c>
     </row>
     <row r="4375" spans="1:1">
-      <c r="A4375" s="5" t="s">
-        <v>4373</v>
+      <c r="A4375" s="2" t="s">
+        <v>4374</v>
       </c>
     </row>
     <row r="4376" spans="1:1">
-      <c r="A4376" s="5" t="s">
-        <v>4374</v>
+      <c r="A4376" s="2" t="s">
+        <v>4375</v>
       </c>
     </row>
     <row r="4377" spans="1:1">
-      <c r="A4377" s="5" t="s">
-        <v>4375</v>
+      <c r="A4377" s="2" t="s">
+        <v>4376</v>
       </c>
     </row>
     <row r="4378" spans="1:1">
-      <c r="A4378" s="5" t="s">
-        <v>4376</v>
+      <c r="A4378" s="2" t="s">
+        <v>4377</v>
       </c>
     </row>
     <row r="4379" spans="1:1">
-      <c r="A4379" s="5" t="s">
-        <v>4377</v>
+      <c r="A4379" s="2" t="s">
+        <v>4378</v>
       </c>
     </row>
     <row r="4380" spans="1:1">
-      <c r="A4380" s="5" t="s">
-        <v>4378</v>
+      <c r="A4380" s="2" t="s">
+        <v>4379</v>
       </c>
     </row>
     <row r="4381" spans="1:1">
-      <c r="A4381" s="5" t="s">
-        <v>4379</v>
+      <c r="A4381" s="2" t="s">
+        <v>4380</v>
       </c>
     </row>
     <row r="4382" spans="1:1">
-      <c r="A4382" s="5" t="s">
-        <v>4380</v>
+      <c r="A4382" s="2" t="s">
+        <v>4381</v>
       </c>
     </row>
     <row r="4383" spans="1:1">
-      <c r="A4383" s="5" t="s">
-        <v>4381</v>
+      <c r="A4383" s="2" t="s">
+        <v>4382</v>
       </c>
     </row>
     <row r="4384" spans="1:1">
-      <c r="A4384" s="5" t="s">
-        <v>4382</v>
+      <c r="A4384" s="2" t="s">
+        <v>4383</v>
       </c>
     </row>
     <row r="4385" spans="1:1">
-      <c r="A4385" s="5" t="s">
-        <v>4383</v>
+      <c r="A4385" s="2" t="s">
+        <v>4384</v>
       </c>
     </row>
     <row r="4386" spans="1:1">
-      <c r="A4386" s="5" t="s">
-        <v>4384</v>
+      <c r="A4386" s="2" t="s">
+        <v>4385</v>
       </c>
     </row>
     <row r="4387" spans="1:1">
-      <c r="A4387" s="5" t="s">
-        <v>4385</v>
+      <c r="A4387" s="2" t="s">
+        <v>4386</v>
       </c>
     </row>
     <row r="4388" spans="1:1">
-      <c r="A4388" s="5" t="s">
-        <v>4386</v>
+      <c r="A4388" s="2" t="s">
+        <v>4387</v>
       </c>
     </row>
     <row r="4389" spans="1:1">
-      <c r="A4389" s="5" t="s">
-        <v>4387</v>
+      <c r="A4389" s="2" t="s">
+        <v>4388</v>
       </c>
     </row>
     <row r="4390" spans="1:1">
-      <c r="A4390" s="5" t="s">
-        <v>4388</v>
+      <c r="A4390" s="2" t="s">
+        <v>4389</v>
       </c>
     </row>
     <row r="4391" spans="1:1">
-      <c r="A4391" s="5" t="s">
-        <v>4389</v>
+      <c r="A4391" s="2" t="s">
+        <v>4390</v>
       </c>
     </row>
     <row r="4392" spans="1:1">
-      <c r="A4392" s="5" t="s">
-        <v>4390</v>
+      <c r="A4392" s="2" t="s">
+        <v>4391</v>
       </c>
     </row>
     <row r="4393" spans="1:1">
-      <c r="A4393" s="5" t="s">
-        <v>4391</v>
+      <c r="A4393" s="2" t="s">
+        <v>4392</v>
       </c>
     </row>
     <row r="4394" spans="1:1">
-      <c r="A4394" s="5" t="s">
-        <v>4392</v>
+      <c r="A4394" s="2" t="s">
+        <v>4393</v>
       </c>
     </row>
     <row r="4395" spans="1:1">
-      <c r="A4395" s="5" t="s">
-        <v>4393</v>
+      <c r="A4395" s="2" t="s">
+        <v>4394</v>
       </c>
     </row>
     <row r="4396" spans="1:1">
-      <c r="A4396" s="5" t="s">
-        <v>4394</v>
+      <c r="A4396" s="2" t="s">
+        <v>4395</v>
       </c>
     </row>
     <row r="4397" spans="1:1">
-      <c r="A4397" s="5" t="s">
-        <v>4395</v>
+      <c r="A4397" s="2" t="s">
+        <v>4396</v>
       </c>
     </row>
     <row r="4398" spans="1:1">
-      <c r="A4398" s="5" t="s">
-        <v>4396</v>
+      <c r="A4398" s="2" t="s">
+        <v>4397</v>
       </c>
     </row>
     <row r="4399" spans="1:1">
-      <c r="A4399" s="5" t="s">
-        <v>4397</v>
+      <c r="A4399" s="2" t="s">
+        <v>4398</v>
       </c>
     </row>
     <row r="4400" spans="1:1">
-      <c r="A4400" s="5" t="s">
-        <v>4398</v>
+      <c r="A4400" s="2" t="s">
+        <v>4399</v>
       </c>
     </row>
     <row r="4401" spans="1:1">
-      <c r="A4401" s="5" t="s">
-        <v>4399</v>
+      <c r="A4401" s="2" t="s">
+        <v>4400</v>
       </c>
     </row>
     <row r="4402" spans="1:1">
-      <c r="A4402" s="5" t="s">
-        <v>4400</v>
+      <c r="A4402" s="2" t="s">
+        <v>4401</v>
       </c>
     </row>
     <row r="4403" spans="1:1">
-      <c r="A4403" s="5" t="s">
-        <v>4401</v>
+      <c r="A4403" s="2" t="s">
+        <v>4402</v>
       </c>
     </row>
     <row r="4404" spans="1:1">
-      <c r="A4404" s="5" t="s">
-        <v>4402</v>
+      <c r="A4404" s="2" t="s">
+        <v>4403</v>
       </c>
     </row>
     <row r="4405" spans="1:1">
-      <c r="A4405" s="5" t="s">
-        <v>4403</v>
+      <c r="A4405" s="2" t="s">
+        <v>4404</v>
       </c>
     </row>
     <row r="4406" spans="1:1">
-      <c r="A4406" s="5" t="s">
-        <v>4404</v>
+      <c r="A4406" s="2" t="s">
+        <v>4405</v>
       </c>
     </row>
     <row r="4407" spans="1:1">
-      <c r="A4407" s="5" t="s">
-        <v>4405</v>
+      <c r="A4407" s="2" t="s">
+        <v>4406</v>
       </c>
     </row>
     <row r="4408" spans="1:1">
-      <c r="A4408" s="5" t="s">
-        <v>4406</v>
+      <c r="A4408" s="2" t="s">
+        <v>4407</v>
       </c>
     </row>
     <row r="4409" spans="1:1">
-      <c r="A4409" s="5" t="s">
-        <v>4407</v>
+      <c r="A4409" s="2" t="s">
+        <v>4408</v>
       </c>
     </row>
     <row r="4410" spans="1:1">
-      <c r="A4410" s="5" t="s">
-        <v>4408</v>
+      <c r="A4410" s="2" t="s">
+        <v>4409</v>
       </c>
     </row>
     <row r="4411" spans="1:1">
-      <c r="A4411" s="5" t="s">
-        <v>4409</v>
+      <c r="A4411" s="2" t="s">
+        <v>4410</v>
       </c>
     </row>
     <row r="4412" spans="1:1">
-      <c r="A4412" s="5" t="s">
-        <v>4410</v>
+      <c r="A4412" s="2" t="s">
+        <v>4411</v>
       </c>
     </row>
     <row r="4413" spans="1:1">
-      <c r="A4413" s="5" t="s">
-        <v>4411</v>
+      <c r="A4413" s="2" t="s">
+        <v>4412</v>
       </c>
     </row>
     <row r="4414" spans="1:1">
-      <c r="A4414" s="5" t="s">
-        <v>4412</v>
+      <c r="A4414" s="2" t="s">
+        <v>4413</v>
       </c>
     </row>
     <row r="4415" spans="1:1">
-      <c r="A4415" s="5" t="s">
-        <v>4413</v>
+      <c r="A4415" s="2" t="s">
+        <v>4414</v>
       </c>
     </row>
     <row r="4416" spans="1:1">
-      <c r="A4416" s="5" t="s">
-        <v>4414</v>
+      <c r="A4416" s="2" t="s">
+        <v>4415</v>
       </c>
     </row>
     <row r="4417" spans="1:1">
-      <c r="A4417" s="5" t="s">
-        <v>4415</v>
+      <c r="A4417" s="2" t="s">
+        <v>4416</v>
       </c>
     </row>
     <row r="4418" spans="1:1">
-      <c r="A4418" s="5" t="s">
-        <v>4416</v>
+      <c r="A4418" s="2" t="s">
+        <v>4417</v>
       </c>
     </row>
     <row r="4419" spans="1:1">
-      <c r="A4419" s="5" t="s">
-        <v>4417</v>
+      <c r="A4419" s="2" t="s">
+        <v>4418</v>
       </c>
     </row>
     <row r="4420" spans="1:1">
-      <c r="A4420" s="5" t="s">
-        <v>4418</v>
+      <c r="A4420" s="2" t="s">
+        <v>4419</v>
       </c>
     </row>
     <row r="4421" spans="1:1">
-      <c r="A4421" s="5" t="s">
-        <v>4419</v>
+      <c r="A4421" s="2" t="s">
+        <v>4420</v>
       </c>
     </row>
     <row r="4422" spans="1:1">
-      <c r="A4422" s="5" t="s">
-        <v>4420</v>
+      <c r="A4422" s="2" t="s">
+        <v>4421</v>
       </c>
     </row>
     <row r="4423" spans="1:1">
-      <c r="A4423" s="5" t="s">
-        <v>4421</v>
+      <c r="A4423" s="2" t="s">
+        <v>4422</v>
       </c>
     </row>
     <row r="4424" spans="1:1">
-      <c r="A4424" s="5" t="s">
-        <v>4422</v>
+      <c r="A4424" s="2" t="s">
+        <v>4423</v>
       </c>
     </row>
     <row r="4425" spans="1:1">
-      <c r="A4425" s="5" t="s">
-        <v>4423</v>
+      <c r="A4425" s="2" t="s">
+        <v>4424</v>
       </c>
     </row>
     <row r="4426" spans="1:1">
-      <c r="A4426" s="5" t="s">
-        <v>4424</v>
+      <c r="A4426" s="2" t="s">
+        <v>4425</v>
       </c>
     </row>
     <row r="4427" spans="1:1">
-      <c r="A4427" s="5" t="s">
-        <v>4425</v>
+      <c r="A4427" s="2" t="s">
+        <v>4426</v>
       </c>
     </row>
     <row r="4428" spans="1:1">
-      <c r="A4428" s="5" t="s">
-        <v>4426</v>
+      <c r="A4428" s="2" t="s">
+        <v>4427</v>
       </c>
     </row>
     <row r="4429" spans="1:1">
-      <c r="A4429" s="5" t="s">
-        <v>4427</v>
+      <c r="A4429" s="2" t="s">
+        <v>4428</v>
       </c>
     </row>
     <row r="4430" spans="1:1">
-      <c r="A4430" s="5" t="s">
-        <v>4428</v>
+      <c r="A4430" s="2" t="s">
+        <v>4429</v>
       </c>
     </row>
     <row r="4431" spans="1:1">
-      <c r="A4431" s="5" t="s">
-        <v>4429</v>
+      <c r="A4431" s="2" t="s">
+        <v>4430</v>
       </c>
     </row>
     <row r="4432" spans="1:1">
-      <c r="A4432" s="5" t="s">
-        <v>4430</v>
+      <c r="A4432" s="2" t="s">
+        <v>4431</v>
       </c>
     </row>
     <row r="4433" spans="1:1">
-      <c r="A4433" s="5" t="s">
-        <v>4431</v>
+      <c r="A4433" s="2" t="s">
+        <v>4432</v>
       </c>
     </row>
     <row r="4434" spans="1:1">
-      <c r="A4434" s="5" t="s">
-        <v>4432</v>
+      <c r="A4434" s="2" t="s">
+        <v>4433</v>
       </c>
     </row>
     <row r="4435" spans="1:1">
-      <c r="A4435" s="5" t="s">
-        <v>4433</v>
+      <c r="A4435" s="2" t="s">
+        <v>4434</v>
       </c>
     </row>
     <row r="4436" spans="1:1">
-      <c r="A4436" s="5" t="s">
-        <v>4434</v>
+      <c r="A4436" s="2" t="s">
+        <v>4435</v>
       </c>
     </row>
     <row r="4437" spans="1:1">
-      <c r="A4437" s="5" t="s">
-        <v>4435</v>
+      <c r="A4437" s="2" t="s">
+        <v>4436</v>
       </c>
     </row>
     <row r="4438" spans="1:1">
-      <c r="A4438" s="5" t="s">
-        <v>4436</v>
+      <c r="A4438" s="2" t="s">
+        <v>4437</v>
       </c>
     </row>
     <row r="4439" spans="1:1">
-      <c r="A4439" s="5" t="s">
-        <v>4437</v>
+      <c r="A4439" s="2" t="s">
+        <v>4438</v>
       </c>
     </row>
     <row r="4440" spans="1:1">
-      <c r="A4440" s="5" t="s">
-        <v>4438</v>
+      <c r="A4440" s="2" t="s">
+        <v>4439</v>
       </c>
     </row>
     <row r="4441" spans="1:1">
-      <c r="A4441" s="5" t="s">
-        <v>4439</v>
+      <c r="A4441" s="2" t="s">
+        <v>4440</v>
       </c>
     </row>
     <row r="4442" spans="1:1">
-      <c r="A4442" s="5" t="s">
-        <v>4440</v>
+      <c r="A4442" s="2" t="s">
+        <v>4441</v>
       </c>
     </row>
     <row r="4443" spans="1:1">
-      <c r="A4443" s="5" t="s">
-        <v>4441</v>
+      <c r="A4443" s="2" t="s">
+        <v>4442</v>
       </c>
     </row>
     <row r="4444" spans="1:1">
-      <c r="A4444" s="5" t="s">
-        <v>4442</v>
+      <c r="A4444" s="2" t="s">
+        <v>4443</v>
       </c>
     </row>
     <row r="4445" spans="1:1">
-      <c r="A4445" s="5" t="s">
-        <v>4443</v>
+      <c r="A4445" s="2" t="s">
+        <v>4444</v>
       </c>
     </row>
     <row r="4446" spans="1:1">
-      <c r="A4446" s="5" t="s">
-        <v>4444</v>
+      <c r="A4446" s="2" t="s">
+        <v>4445</v>
       </c>
     </row>
     <row r="4447" spans="1:1">
-      <c r="A4447" s="5" t="s">
-        <v>4445</v>
+      <c r="A4447" s="2" t="s">
+        <v>4446</v>
       </c>
     </row>
     <row r="4448" spans="1:1">
-      <c r="A4448" s="5" t="s">
-        <v>4446</v>
+      <c r="A4448" s="2" t="s">
+        <v>4447</v>
       </c>
     </row>
     <row r="4449" spans="1:1">
-      <c r="A4449" s="5" t="s">
-        <v>4447</v>
+      <c r="A4449" s="2" t="s">
+        <v>4448</v>
       </c>
     </row>
     <row r="4450" spans="1:1">
-      <c r="A4450" s="5" t="s">
-        <v>4448</v>
+      <c r="A4450" s="2" t="s">
+        <v>4449</v>
       </c>
     </row>
     <row r="4451" spans="1:1">
-      <c r="A4451" s="5" t="s">
-        <v>4449</v>
+      <c r="A4451" s="2" t="s">
+        <v>4450</v>
       </c>
     </row>
     <row r="4452" spans="1:1">
-      <c r="A4452" s="5" t="s">
-        <v>4450</v>
+      <c r="A4452" s="2" t="s">
+        <v>4451</v>
       </c>
     </row>
     <row r="4453" spans="1:1">
-      <c r="A4453" s="5" t="s">
-        <v>4451</v>
+      <c r="A4453" s="2" t="s">
+        <v>4452</v>
       </c>
     </row>
     <row r="4454" spans="1:1">
-      <c r="A4454" s="5" t="s">
-        <v>4452</v>
+      <c r="A4454" s="2" t="s">
+        <v>4453</v>
       </c>
     </row>
     <row r="4455" spans="1:1">
-      <c r="A4455" s="5" t="s">
-        <v>4453</v>
+      <c r="A4455" s="2" t="s">
+        <v>4454</v>
       </c>
     </row>
     <row r="4456" spans="1:1">
-      <c r="A4456" s="5" t="s">
-        <v>4454</v>
+      <c r="A4456" s="2" t="s">
+        <v>4455</v>
       </c>
     </row>
     <row r="4457" spans="1:1">
-      <c r="A4457" s="5" t="s">
-        <v>4455</v>
+      <c r="A4457" s="2" t="s">
+        <v>4456</v>
       </c>
     </row>
     <row r="4458" spans="1:1">
-      <c r="A4458" s="5" t="s">
-        <v>4456</v>
+      <c r="A4458" s="2" t="s">
+        <v>4457</v>
       </c>
     </row>
     <row r="4459" spans="1:1">
-      <c r="A4459" s="5" t="s">
-        <v>4457</v>
+      <c r="A4459" s="2" t="s">
+        <v>4458</v>
       </c>
     </row>
     <row r="4460" spans="1:1">
-      <c r="A4460" s="5" t="s">
-        <v>4458</v>
+      <c r="A4460" s="2" t="s">
+        <v>4459</v>
       </c>
     </row>
     <row r="4461" spans="1:1">
-      <c r="A4461" s="5" t="s">
-        <v>4459</v>
+      <c r="A4461" s="2" t="s">
+        <v>4460</v>
       </c>
     </row>
     <row r="4462" spans="1:1">
-      <c r="A4462" s="5" t="s">
-        <v>4460</v>
+      <c r="A4462" s="2" t="s">
+        <v>4461</v>
       </c>
     </row>
     <row r="4463" spans="1:1">
-      <c r="A4463" s="5" t="s">
-        <v>4461</v>
+      <c r="A4463" s="2" t="s">
+        <v>4462</v>
       </c>
     </row>
     <row r="4464" spans="1:1">
-      <c r="A4464" s="5" t="s">
-        <v>4462</v>
+      <c r="A4464" s="2" t="s">
+        <v>4463</v>
       </c>
     </row>
     <row r="4465" spans="1:1">
-      <c r="A4465" s="5" t="s">
-        <v>4463</v>
+      <c r="A4465" s="2" t="s">
+        <v>4464</v>
       </c>
     </row>
     <row r="4466" spans="1:1">
-      <c r="A4466" s="5" t="s">
-        <v>4464</v>
+      <c r="A4466" s="2" t="s">
+        <v>4465</v>
       </c>
     </row>
     <row r="4467" spans="1:1">
-      <c r="A4467" s="5" t="s">
-        <v>4465</v>
+      <c r="A4467" s="2" t="s">
+        <v>4466</v>
       </c>
     </row>
     <row r="4468" spans="1:1">
-      <c r="A4468" s="5" t="s">
-        <v>4466</v>
+      <c r="A4468" s="2" t="s">
+        <v>4467</v>
       </c>
     </row>
     <row r="4469" spans="1:1">
-      <c r="A4469" s="5" t="s">
-        <v>4467</v>
+      <c r="A4469" s="2" t="s">
+        <v>4468</v>
       </c>
     </row>
     <row r="4470" spans="1:1">
-      <c r="A4470" s="5" t="s">
-        <v>4468</v>
+      <c r="A4470" s="2" t="s">
+        <v>4469</v>
       </c>
     </row>
     <row r="4471" spans="1:1">
-      <c r="A4471" s="5" t="s">
-        <v>4469</v>
+      <c r="A4471" s="2" t="s">
+        <v>4470</v>
       </c>
     </row>
     <row r="4472" spans="1:1">
-      <c r="A4472" s="5" t="s">
-        <v>4470</v>
+      <c r="A4472" s="2" t="s">
+        <v>4471</v>
       </c>
     </row>
     <row r="4473" spans="1:1">
-      <c r="A4473" s="5" t="s">
-        <v>4471</v>
+      <c r="A4473" s="2" t="s">
+        <v>4472</v>
       </c>
     </row>
     <row r="4474" spans="1:1">
-      <c r="A4474" s="5" t="s">
-        <v>4472</v>
+      <c r="A4474" s="2" t="s">
+        <v>4473</v>
       </c>
     </row>
     <row r="4475" spans="1:1">
-      <c r="A4475" s="5" t="s">
-        <v>4473</v>
+      <c r="A4475" s="2" t="s">
+        <v>4474</v>
       </c>
     </row>
     <row r="4476" spans="1:1">
-      <c r="A4476" s="5" t="s">
-        <v>4474</v>
+      <c r="A4476" s="2" t="s">
+        <v>4475</v>
       </c>
     </row>
     <row r="4477" spans="1:1">
-      <c r="A4477" s="5" t="s">
-        <v>4475</v>
+      <c r="A4477" s="2" t="s">
+        <v>4476</v>
       </c>
     </row>
     <row r="4478" spans="1:1">
-      <c r="A4478" s="5" t="s">
-        <v>4476</v>
+      <c r="A4478" s="2" t="s">
+        <v>4477</v>
       </c>
     </row>
     <row r="4479" spans="1:1">
-      <c r="A4479" s="5" t="s">
-        <v>4477</v>
+      <c r="A4479" s="2" t="s">
+        <v>4478</v>
       </c>
     </row>
     <row r="4480" spans="1:1">
-      <c r="A4480" s="5" t="s">
-        <v>4478</v>
+      <c r="A4480" s="2" t="s">
+        <v>4479</v>
       </c>
     </row>
     <row r="4481" spans="1:1">
-      <c r="A4481" s="5" t="s">
-        <v>4479</v>
+      <c r="A4481" s="2" t="s">
+        <v>4480</v>
       </c>
     </row>
     <row r="4482" spans="1:1">
-      <c r="A4482" s="5" t="s">
-        <v>4480</v>
+      <c r="A4482" s="2" t="s">
+        <v>4481</v>
       </c>
     </row>
     <row r="4483" spans="1:1">
-      <c r="A4483" s="5" t="s">
-        <v>4481</v>
+      <c r="A4483" s="2" t="s">
+        <v>4482</v>
       </c>
     </row>
     <row r="4484" spans="1:1">
-      <c r="A4484" s="5" t="s">
-        <v>4482</v>
+      <c r="A4484" s="2" t="s">
+        <v>4483</v>
       </c>
     </row>
     <row r="4485" spans="1:1">
-      <c r="A4485" s="5" t="s">
-        <v>4483</v>
+      <c r="A4485" s="2" t="s">
+        <v>4484</v>
       </c>
     </row>
     <row r="4486" spans="1:1">
-      <c r="A4486" s="5" t="s">
-        <v>4484</v>
+      <c r="A4486" s="2" t="s">
+        <v>4485</v>
       </c>
     </row>
     <row r="4487" spans="1:1">
-      <c r="A4487" s="5" t="s">
-        <v>4485</v>
+      <c r="A4487" s="2" t="s">
+        <v>4486</v>
       </c>
     </row>
     <row r="4488" spans="1:1">
-      <c r="A4488" s="5" t="s">
-        <v>4486</v>
+      <c r="A4488" s="2" t="s">
+        <v>4487</v>
       </c>
     </row>
     <row r="4489" spans="1:1">
-      <c r="A4489" s="5" t="s">
-        <v>4487</v>
+      <c r="A4489" s="2" t="s">
+        <v>4488</v>
       </c>
     </row>
     <row r="4490" spans="1:1">
-      <c r="A4490" s="5" t="s">
-        <v>4488</v>
+      <c r="A4490" s="2" t="s">
+        <v>4489</v>
       </c>
     </row>
     <row r="4491" spans="1:1">
-      <c r="A4491" s="5" t="s">
-        <v>4489</v>
+      <c r="A4491" s="2" t="s">
+        <v>4490</v>
       </c>
     </row>
     <row r="4492" spans="1:1">
-      <c r="A4492" s="5" t="s">
-        <v>4490</v>
+      <c r="A4492" s="2" t="s">
+        <v>4491</v>
       </c>
     </row>
     <row r="4493" spans="1:1">
-      <c r="A4493" s="5" t="s">
-        <v>4491</v>
+      <c r="A4493" s="2" t="s">
+        <v>4492</v>
       </c>
     </row>
     <row r="4494" spans="1:1">
-      <c r="A4494" s="5" t="s">
-        <v>4492</v>
+      <c r="A4494" s="2" t="s">
+        <v>4493</v>
       </c>
     </row>
     <row r="4495" spans="1:1">
-      <c r="A4495" s="5" t="s">
-        <v>4493</v>
+      <c r="A4495" s="2" t="s">
+        <v>4494</v>
       </c>
     </row>
     <row r="4496" spans="1:1">
-      <c r="A4496" s="5" t="s">
-        <v>4494</v>
+      <c r="A4496" s="2" t="s">
+        <v>4495</v>
       </c>
     </row>
     <row r="4497" spans="1:1">
-      <c r="A4497" s="5" t="s">
-        <v>4495</v>
+      <c r="A4497" s="2" t="s">
+        <v>4496</v>
       </c>
     </row>
     <row r="4498" spans="1:1">
-      <c r="A4498" s="5" t="s">
-        <v>4496</v>
+      <c r="A4498" s="2" t="s">
+        <v>4497</v>
       </c>
     </row>
     <row r="4499" spans="1:1">
-      <c r="A4499" s="5" t="s">
-        <v>4497</v>
+      <c r="A4499" s="2" t="s">
+        <v>4498</v>
       </c>
     </row>
     <row r="4500" spans="1:1">
-      <c r="A4500" s="5" t="s">
-        <v>4498</v>
+      <c r="A4500" s="2" t="s">
+        <v>4499</v>
       </c>
     </row>
     <row r="4501" spans="1:1">
-      <c r="A4501" s="5" t="s">
-        <v>4499</v>
+      <c r="A4501" s="2" t="s">
+        <v>4500</v>
       </c>
     </row>
     <row r="4502" spans="1:1">
-      <c r="A4502" s="5" t="s">
-        <v>4500</v>
+      <c r="A4502" s="2" t="s">
+        <v>4501</v>
       </c>
     </row>
     <row r="4503" spans="1:1">
-      <c r="A4503" s="5" t="s">
-        <v>4501</v>
+      <c r="A4503" s="2" t="s">
+        <v>4502</v>
       </c>
     </row>
     <row r="4504" spans="1:1">
-      <c r="A4504" s="5" t="s">
-        <v>4502</v>
+      <c r="A4504" s="2" t="s">
+        <v>4503</v>
       </c>
     </row>
     <row r="4505" spans="1:1">
-      <c r="A4505" s="5" t="s">
-        <v>4503</v>
+      <c r="A4505" s="2" t="s">
+        <v>4504</v>
       </c>
     </row>
     <row r="4506" spans="1:1">
-      <c r="A4506" s="5" t="s">
-        <v>4504</v>
+      <c r="A4506" s="2" t="s">
+        <v>4505</v>
       </c>
     </row>
     <row r="4507" spans="1:1">
-      <c r="A4507" s="5" t="s">
-        <v>4505</v>
+      <c r="A4507" s="2" t="s">
+        <v>4506</v>
       </c>
     </row>
     <row r="4508" spans="1:1">
-      <c r="A4508" s="5" t="s">
-        <v>4506</v>
+      <c r="A4508" s="2" t="s">
+        <v>4507</v>
       </c>
     </row>
     <row r="4509" spans="1:1">
-      <c r="A4509" s="5" t="s">
-        <v>4507</v>
+      <c r="A4509" s="2" t="s">
+        <v>4508</v>
       </c>
     </row>
     <row r="4510" spans="1:1">
-      <c r="A4510" s="5" t="s">
-        <v>4508</v>
+      <c r="A4510" s="2" t="s">
+        <v>4509</v>
       </c>
     </row>
     <row r="4511" spans="1:1">
-      <c r="A4511" s="5" t="s">
-        <v>4509</v>
+      <c r="A4511" s="2" t="s">
+        <v>4510</v>
       </c>
     </row>
     <row r="4512" spans="1:1">
-      <c r="A4512" s="5" t="s">
-        <v>4510</v>
+      <c r="A4512" s="2" t="s">
+        <v>4511</v>
       </c>
     </row>
     <row r="4513" spans="1:1">
-      <c r="A4513" s="5" t="s">
-        <v>4511</v>
+      <c r="A4513" s="2" t="s">
+        <v>4512</v>
       </c>
     </row>
     <row r="4514" spans="1:1">
-      <c r="A4514" s="5" t="s">
-        <v>4512</v>
+      <c r="A4514" s="2" t="s">
+        <v>4513</v>
       </c>
     </row>
     <row r="4515" spans="1:1">
-      <c r="A4515" s="5" t="s">
-        <v>4513</v>
+      <c r="A4515" s="2" t="s">
+        <v>4514</v>
       </c>
     </row>
     <row r="4516" spans="1:1">
-      <c r="A4516" s="5" t="s">
-        <v>4514</v>
+      <c r="A4516" s="2" t="s">
+        <v>4515</v>
       </c>
     </row>
     <row r="4517" spans="1:1">
-      <c r="A4517" s="5" t="s">
-        <v>4515</v>
+      <c r="A4517" s="2" t="s">
+        <v>4516</v>
       </c>
     </row>
     <row r="4518" spans="1:1">
-      <c r="A4518" s="5" t="s">
-        <v>4516</v>
+      <c r="A4518" s="2" t="s">
+        <v>4517</v>
       </c>
     </row>
     <row r="4519" spans="1:1">
-      <c r="A4519" s="5" t="s">
-        <v>4517</v>
+      <c r="A4519" s="2" t="s">
+        <v>4518</v>
       </c>
     </row>
     <row r="4520" spans="1:1">
-      <c r="A4520" s="5" t="s">
-        <v>4518</v>
+      <c r="A4520" s="2" t="s">
+        <v>4519</v>
       </c>
     </row>
     <row r="4521" spans="1:1">
-      <c r="A4521" s="5" t="s">
-        <v>4519</v>
+      <c r="A4521" s="2" t="s">
+        <v>4520</v>
       </c>
     </row>
     <row r="4522" spans="1:1">
-      <c r="A4522" s="5" t="s">
-        <v>4520</v>
+      <c r="A4522" s="2" t="s">
+        <v>4521</v>
       </c>
     </row>
     <row r="4523" spans="1:1">
-      <c r="A4523" s="5" t="s">
-        <v>4521</v>
+      <c r="A4523" s="2" t="s">
+        <v>4522</v>
       </c>
     </row>
     <row r="4524" spans="1:1">
-      <c r="A4524" s="5" t="s">
-        <v>4522</v>
+      <c r="A4524" s="2" t="s">
+        <v>4523</v>
       </c>
     </row>
     <row r="4525" spans="1:1">
-      <c r="A4525" s="5" t="s">
-        <v>4523</v>
+      <c r="A4525" s="2" t="s">
+        <v>4524</v>
       </c>
     </row>
     <row r="4526" spans="1:1">
-      <c r="A4526" s="5" t="s">
-        <v>4524</v>
+      <c r="A4526" s="2" t="s">
+        <v>4525</v>
       </c>
     </row>
     <row r="4527" spans="1:1">
-      <c r="A4527" s="5" t="s">
-        <v>4525</v>
+      <c r="A4527" s="2" t="s">
+        <v>4526</v>
       </c>
     </row>
     <row r="4528" spans="1:1">
-      <c r="A4528" s="5" t="s">
-        <v>4526</v>
+      <c r="A4528" s="2" t="s">
+        <v>4527</v>
       </c>
     </row>
     <row r="4529" spans="1:1">
-      <c r="A4529" s="5" t="s">
-        <v>4527</v>
+      <c r="A4529" s="2" t="s">
+        <v>4528</v>
       </c>
     </row>
     <row r="4530" spans="1:1">
-      <c r="A4530" s="5" t="s">
-        <v>4528</v>
+      <c r="A4530" s="2" t="s">
+        <v>4529</v>
       </c>
     </row>
     <row r="4531" spans="1:1">
-      <c r="A4531" s="5" t="s">
-        <v>4529</v>
+      <c r="A4531" s="2" t="s">
+        <v>4530</v>
       </c>
     </row>
     <row r="4532" spans="1:1">
-      <c r="A4532" s="5" t="s">
-        <v>4530</v>
+      <c r="A4532" s="2" t="s">
+        <v>4531</v>
       </c>
     </row>
     <row r="4533" spans="1:1">
-      <c r="A4533" s="5" t="s">
-        <v>4531</v>
+      <c r="A4533" s="2" t="s">
+        <v>4532</v>
       </c>
     </row>
     <row r="4534" spans="1:1">
-      <c r="A4534" s="5" t="s">
-        <v>4532</v>
+      <c r="A4534" s="2" t="s">
+        <v>4533</v>
       </c>
     </row>
     <row r="4535" spans="1:1">
-      <c r="A4535" s="5" t="s">
-        <v>4533</v>
+      <c r="A4535" s="2" t="s">
+        <v>4534</v>
       </c>
     </row>
     <row r="4536" spans="1:1">
-      <c r="A4536" s="5" t="s">
-        <v>4534</v>
+      <c r="A4536" s="2" t="s">
+        <v>4535</v>
       </c>
     </row>
     <row r="4537" spans="1:1">
-      <c r="A4537" s="5" t="s">
-        <v>4535</v>
+      <c r="A4537" s="2" t="s">
+        <v>4536</v>
       </c>
     </row>
     <row r="4538" spans="1:1">
-      <c r="A4538" s="5" t="s">
-        <v>4536</v>
+      <c r="A4538" s="2" t="s">
+        <v>4537</v>
       </c>
     </row>
     <row r="4539" spans="1:1">
-      <c r="A4539" s="5" t="s">
-        <v>4537</v>
+      <c r="A4539" s="2" t="s">
+        <v>4538</v>
       </c>
     </row>
     <row r="4540" spans="1:1">
-      <c r="A4540" s="5" t="s">
-        <v>4538</v>
+      <c r="A4540" s="2" t="s">
+        <v>4539</v>
       </c>
     </row>
     <row r="4541" spans="1:1">
-      <c r="A4541" s="5" t="s">
-        <v>4539</v>
+      <c r="A4541" s="2" t="s">
+        <v>4540</v>
       </c>
     </row>
     <row r="4542" spans="1:1">
-      <c r="A4542" s="5" t="s">
-        <v>4540</v>
+      <c r="A4542" s="2" t="s">
+        <v>4541</v>
       </c>
     </row>
     <row r="4543" spans="1:1">
-      <c r="A4543" s="5" t="s">
-        <v>4541</v>
+      <c r="A4543" s="2" t="s">
+        <v>4542</v>
       </c>
     </row>
     <row r="4544" spans="1:1">
-      <c r="A4544" s="5" t="s">
-        <v>4542</v>
+      <c r="A4544" s="2" t="s">
+        <v>4543</v>
       </c>
     </row>
     <row r="4545" spans="1:1">
-      <c r="A4545" s="5" t="s">
-        <v>4543</v>
+      <c r="A4545" s="2" t="s">
+        <v>4544</v>
       </c>
     </row>
     <row r="4546" spans="1:1">
-      <c r="A4546" s="5" t="s">
-        <v>4544</v>
+      <c r="A4546" s="2" t="s">
+        <v>4545</v>
       </c>
     </row>
     <row r="4547" spans="1:1">
-      <c r="A4547" s="5" t="s">
-        <v>4545</v>
+      <c r="A4547" s="2" t="s">
+        <v>4546</v>
       </c>
     </row>
     <row r="4548" spans="1:1">
-      <c r="A4548" s="5" t="s">
-        <v>4546</v>
+      <c r="A4548" s="2" t="s">
+        <v>4547</v>
       </c>
     </row>
     <row r="4549" spans="1:1">
-      <c r="A4549" s="5" t="s">
-        <v>4547</v>
+      <c r="A4549" s="2" t="s">
+        <v>4548</v>
       </c>
     </row>
     <row r="4550" spans="1:1">
-      <c r="A4550" s="5" t="s">
-        <v>4548</v>
+      <c r="A4550" s="2" t="s">
+        <v>4549</v>
       </c>
     </row>
     <row r="4551" spans="1:1">
-      <c r="A4551" s="5" t="s">
-        <v>4549</v>
+      <c r="A4551" s="2" t="s">
+        <v>4550</v>
       </c>
     </row>
     <row r="4552" spans="1:1">
-      <c r="A4552" s="5" t="s">
-        <v>4550</v>
+      <c r="A4552" s="2" t="s">
+        <v>4551</v>
       </c>
     </row>
     <row r="4553" spans="1:1">
-      <c r="A4553" s="5" t="s">
-        <v>4551</v>
+      <c r="A4553" s="2" t="s">
+        <v>4552</v>
       </c>
     </row>
     <row r="4554" spans="1:1">
-      <c r="A4554" s="5" t="s">
-        <v>4552</v>
+      <c r="A4554" s="2" t="s">
+        <v>4553</v>
       </c>
     </row>
     <row r="4555" spans="1:1">
-      <c r="A4555" s="5" t="s">
-        <v>4553</v>
+      <c r="A4555" s="2" t="s">
+        <v>4554</v>
       </c>
     </row>
     <row r="4556" spans="1:1">
-      <c r="A4556" s="5" t="s">
-        <v>4554</v>
+      <c r="A4556" s="2" t="s">
+        <v>4555</v>
       </c>
     </row>
     <row r="4557" spans="1:1">
-      <c r="A4557" s="5" t="s">
-        <v>4555</v>
+      <c r="A4557" s="2" t="s">
+        <v>4556</v>
       </c>
     </row>
     <row r="4558" spans="1:1">
-      <c r="A4558" s="5" t="s">
-        <v>4556</v>
+      <c r="A4558" s="2" t="s">
+        <v>4557</v>
       </c>
     </row>
     <row r="4559" spans="1:1">
-      <c r="A4559" s="5" t="s">
-        <v>4557</v>
+      <c r="A4559" s="2" t="s">
+        <v>4558</v>
       </c>
     </row>
     <row r="4560" spans="1:1">
-      <c r="A4560" s="5" t="s">
-        <v>4558</v>
+      <c r="A4560" s="2" t="s">
+        <v>4559</v>
       </c>
     </row>
     <row r="4561" spans="1:1">
-      <c r="A4561" s="5" t="s">
-        <v>4559</v>
+      <c r="A4561" s="2" t="s">
+        <v>4560</v>
       </c>
     </row>
     <row r="4562" spans="1:1">
-      <c r="A4562" s="5" t="s">
-        <v>4560</v>
+      <c r="A4562" s="2" t="s">
+        <v>4561</v>
       </c>
     </row>
     <row r="4563" spans="1:1">
-      <c r="A4563" s="5" t="s">
-        <v>4561</v>
+      <c r="A4563" s="2" t="s">
+        <v>4562</v>
       </c>
     </row>
     <row r="4564" spans="1:1">
-      <c r="A4564" s="5" t="s">
-        <v>4562</v>
+      <c r="A4564" s="2" t="s">
+        <v>4563</v>
       </c>
     </row>
     <row r="4565" spans="1:1">
-      <c r="A4565" s="5" t="s">
-        <v>4563</v>
+      <c r="A4565" s="2" t="s">
+        <v>4564</v>
       </c>
     </row>
     <row r="4566" spans="1:1">
-      <c r="A4566" s="5" t="s">
-        <v>4564</v>
+      <c r="A4566" s="2" t="s">
+        <v>4565</v>
       </c>
     </row>
     <row r="4567" spans="1:1">
-      <c r="A4567" s="5" t="s">
-        <v>4565</v>
+      <c r="A4567" s="2" t="s">
+        <v>4566</v>
       </c>
     </row>
     <row r="4568" spans="1:1">
-      <c r="A4568" s="5" t="s">
-        <v>4566</v>
+      <c r="A4568" s="2" t="s">
+        <v>4567</v>
       </c>
     </row>
     <row r="4569" spans="1:1">
-      <c r="A4569" s="5" t="s">
-        <v>4567</v>
+      <c r="A4569" s="2" t="s">
+        <v>4568</v>
       </c>
     </row>
     <row r="4570" spans="1:1">
-      <c r="A4570" s="5" t="s">
-        <v>4568</v>
+      <c r="A4570" s="2" t="s">
+        <v>4569</v>
       </c>
     </row>
     <row r="4571" spans="1:1">
-      <c r="A4571" s="5" t="s">
-        <v>4569</v>
+      <c r="A4571" s="2" t="s">
+        <v>4570</v>
       </c>
     </row>
     <row r="4572" spans="1:1">
-      <c r="A4572" s="5" t="s">
-        <v>4570</v>
+      <c r="A4572" s="2" t="s">
+        <v>4571</v>
       </c>
     </row>
     <row r="4573" spans="1:1">
-      <c r="A4573" s="5" t="s">
-        <v>4571</v>
+      <c r="A4573" s="2" t="s">
+        <v>4572</v>
       </c>
     </row>
     <row r="4574" spans="1:1">
-      <c r="A4574" s="5" t="s">
-        <v>4572</v>
+      <c r="A4574" s="2" t="s">
+        <v>4573</v>
       </c>
     </row>
     <row r="4575" spans="1:1">
-      <c r="A4575" s="5" t="s">
-        <v>4573</v>
+      <c r="A4575" s="2" t="s">
+        <v>4574</v>
       </c>
     </row>
     <row r="4576" spans="1:1">
-      <c r="A4576" s="5" t="s">
-        <v>4574</v>
+      <c r="A4576" s="2" t="s">
+        <v>4575</v>
       </c>
     </row>
     <row r="4577" spans="1:1">
-      <c r="A4577" s="5" t="s">
-        <v>4575</v>
+      <c r="A4577" s="2" t="s">
+        <v>4576</v>
       </c>
     </row>
     <row r="4578" spans="1:1">
-      <c r="A4578" s="5" t="s">
-        <v>4576</v>
+      <c r="A4578" s="2" t="s">
+        <v>4577</v>
       </c>
     </row>
     <row r="4579" spans="1:1">
-      <c r="A4579" s="5" t="s">
-        <v>4577</v>
+      <c r="A4579" s="2" t="s">
+        <v>4578</v>
       </c>
     </row>
     <row r="4580" spans="1:1">
-      <c r="A4580" s="5" t="s">
-        <v>4578</v>
+      <c r="A4580" s="2" t="s">
+        <v>4579</v>
       </c>
     </row>
     <row r="4581" spans="1:1">
-      <c r="A4581" s="5" t="s">
-        <v>4579</v>
+      <c r="A4581" s="2" t="s">
+        <v>4580</v>
       </c>
     </row>
     <row r="4582" spans="1:1">
-      <c r="A4582" s="5" t="s">
-        <v>4580</v>
+      <c r="A4582" s="2" t="s">
+        <v>4581</v>
       </c>
     </row>
     <row r="4583" spans="1:1">
-      <c r="A4583" s="5" t="s">
-        <v>4581</v>
+      <c r="A4583" s="2" t="s">
+        <v>4582</v>
       </c>
     </row>
     <row r="4584" spans="1:1">
-      <c r="A4584" s="5" t="s">
-        <v>4582</v>
+      <c r="A4584" s="2" t="s">
+        <v>4583</v>
       </c>
     </row>
     <row r="4585" spans="1:1">
-      <c r="A4585" s="5" t="s">
-        <v>4583</v>
+      <c r="A4585" s="2" t="s">
+        <v>4584</v>
       </c>
     </row>
     <row r="4586" spans="1:1">
-      <c r="A4586" s="5" t="s">
-        <v>4584</v>
+      <c r="A4586" s="2" t="s">
+        <v>4585</v>
       </c>
     </row>
     <row r="4587" spans="1:1">
-      <c r="A4587" s="5" t="s">
-        <v>4585</v>
+      <c r="A4587" s="2" t="s">
+        <v>4586</v>
       </c>
     </row>
     <row r="4588" spans="1:1">
-      <c r="A4588" s="5" t="s">
-        <v>4586</v>
+      <c r="A4588" s="2" t="s">
+        <v>4587</v>
       </c>
     </row>
     <row r="4589" spans="1:1">
-      <c r="A4589" s="5" t="s">
-        <v>4587</v>
+      <c r="A4589" s="2" t="s">
+        <v>4588</v>
       </c>
     </row>
     <row r="4590" spans="1:1">
-      <c r="A4590" s="5" t="s">
-        <v>4588</v>
+      <c r="A4590" s="2" t="s">
+        <v>4589</v>
       </c>
     </row>
     <row r="4591" spans="1:1">
-      <c r="A4591" s="5" t="s">
-        <v>4589</v>
+      <c r="A4591" s="2" t="s">
+        <v>4590</v>
       </c>
     </row>
     <row r="4592" spans="1:1">
-      <c r="A4592" s="5" t="s">
-        <v>4590</v>
+      <c r="A4592" s="2" t="s">
+        <v>4591</v>
       </c>
     </row>
     <row r="4593" spans="1:1">
-      <c r="A4593" s="5" t="s">
-        <v>4591</v>
+      <c r="A4593" s="2" t="s">
+        <v>4592</v>
       </c>
     </row>
     <row r="4594" spans="1:1">
-      <c r="A4594" s="5" t="s">
-        <v>4592</v>
+      <c r="A4594" s="2" t="s">
+        <v>4593</v>
       </c>
     </row>
     <row r="4595" spans="1:1">
-      <c r="A4595" s="5" t="s">
-        <v>4593</v>
+      <c r="A4595" s="2" t="s">
+        <v>4594</v>
       </c>
     </row>
     <row r="4596" spans="1:1">
-      <c r="A4596" s="5" t="s">
-        <v>4594</v>
+      <c r="A4596" s="2" t="s">
+        <v>4595</v>
       </c>
     </row>
     <row r="4597" spans="1:1">
-      <c r="A4597" s="5" t="s">
-        <v>4595</v>
+      <c r="A4597" s="2" t="s">
+        <v>4596</v>
       </c>
     </row>
     <row r="4598" spans="1:1">
-      <c r="A4598" s="5" t="s">
-        <v>4596</v>
+      <c r="A4598" s="2" t="s">
+        <v>4597</v>
       </c>
     </row>
     <row r="4599" spans="1:1">
-      <c r="A4599" s="5" t="s">
-        <v>4597</v>
+      <c r="A4599" s="2" t="s">
+        <v>4598</v>
       </c>
     </row>
     <row r="4600" spans="1:1">
-      <c r="A4600" s="5" t="s">
-        <v>4598</v>
+      <c r="A4600" s="2" t="s">
+        <v>4599</v>
       </c>
     </row>
     <row r="4601" spans="1:1">
-      <c r="A4601" s="5" t="s">
-        <v>4599</v>
+      <c r="A4601" s="2" t="s">
+        <v>4600</v>
       </c>
     </row>
     <row r="4602" spans="1:1">
-      <c r="A4602" s="5" t="s">
-        <v>4600</v>
+      <c r="A4602" s="2" t="s">
+        <v>4601</v>
       </c>
     </row>
     <row r="4603" spans="1:1">
-      <c r="A4603" s="5" t="s">
-        <v>4601</v>
+      <c r="A4603" s="2" t="s">
+        <v>4602</v>
       </c>
     </row>
     <row r="4604" spans="1:1">
-      <c r="A4604" s="5" t="s">
-        <v>4602</v>
+      <c r="A4604" s="2" t="s">
+        <v>4603</v>
       </c>
     </row>
     <row r="4605" spans="1:1">
-      <c r="A4605" s="5" t="s">
-        <v>4603</v>
+      <c r="A4605" s="2" t="s">
+        <v>4604</v>
       </c>
     </row>
     <row r="4606" spans="1:1">
-      <c r="A4606" s="5" t="s">
-        <v>4604</v>
+      <c r="A4606" s="2" t="s">
+        <v>4605</v>
       </c>
     </row>
     <row r="4607" spans="1:1">
-      <c r="A4607" s="5" t="s">
-        <v>4605</v>
+      <c r="A4607" s="2" t="s">
+        <v>4606</v>
       </c>
     </row>
     <row r="4608" spans="1:1">
-      <c r="A4608" s="5" t="s">
-        <v>4606</v>
+      <c r="A4608" s="2" t="s">
+        <v>4607</v>
       </c>
     </row>
     <row r="4609" spans="1:1">
-      <c r="A4609" s="5" t="s">
-        <v>4607</v>
+      <c r="A4609" s="2" t="s">
+        <v>4608</v>
       </c>
     </row>
     <row r="4610" spans="1:1">
-      <c r="A4610" s="5" t="s">
-        <v>4608</v>
+      <c r="A4610" s="2" t="s">
+        <v>4609</v>
       </c>
     </row>
     <row r="4611" spans="1:1">
-      <c r="A4611" s="5" t="s">
-        <v>4609</v>
+      <c r="A4611" s="2" t="s">
+        <v>4610</v>
       </c>
     </row>
     <row r="4612" spans="1:1">
-      <c r="A4612" s="5" t="s">
-        <v>4610</v>
+      <c r="A4612" s="2" t="s">
+        <v>4611</v>
       </c>
     </row>
     <row r="4613" spans="1:1">
-      <c r="A4613" s="5" t="s">
-        <v>4611</v>
+      <c r="A4613" s="2" t="s">
+        <v>4612</v>
       </c>
     </row>
     <row r="4614" spans="1:1">
-      <c r="A4614" s="5" t="s">
-        <v>4612</v>
+      <c r="A4614" s="2" t="s">
+        <v>4613</v>
       </c>
     </row>
     <row r="4615" spans="1:1">
-      <c r="A4615" s="5" t="s">
-        <v>4613</v>
+      <c r="A4615" s="2" t="s">
+        <v>4614</v>
       </c>
     </row>
     <row r="4616" spans="1:1">
-      <c r="A4616" s="5" t="s">
-        <v>4614</v>
+      <c r="A4616" s="2" t="s">
+        <v>4615</v>
       </c>
     </row>
     <row r="4617" spans="1:1">
-      <c r="A4617" s="5" t="s">
-        <v>4615</v>
+      <c r="A4617" s="2" t="s">
+        <v>4616</v>
       </c>
     </row>
     <row r="4618" spans="1:1">
-      <c r="A4618" s="5" t="s">
-        <v>4616</v>
+      <c r="A4618" s="2" t="s">
+        <v>4617</v>
       </c>
     </row>
     <row r="4619" spans="1:1">
-      <c r="A4619" s="5" t="s">
-        <v>4617</v>
+      <c r="A4619" s="2" t="s">
+        <v>4618</v>
       </c>
     </row>
     <row r="4620" spans="1:1">
-      <c r="A4620" s="5" t="s">
-        <v>4618</v>
+      <c r="A4620" s="2" t="s">
+        <v>4619</v>
       </c>
     </row>
     <row r="4621" spans="1:1">
-      <c r="A4621" s="5" t="s">
-        <v>4619</v>
+      <c r="A4621" s="2" t="s">
+        <v>4620</v>
       </c>
     </row>
     <row r="4622" spans="1:1">
-      <c r="A4622" s="5" t="s">
-        <v>4620</v>
+      <c r="A4622" s="2" t="s">
+        <v>4621</v>
       </c>
     </row>
     <row r="4623" spans="1:1">
-      <c r="A4623" s="5" t="s">
-        <v>4621</v>
+      <c r="A4623" s="2" t="s">
+        <v>4622</v>
       </c>
     </row>
     <row r="4624" spans="1:1">
-      <c r="A4624" s="5" t="s">
-        <v>4622</v>
+      <c r="A4624" s="2" t="s">
+        <v>4623</v>
       </c>
     </row>
     <row r="4625" spans="1:1">
-      <c r="A4625" s="5" t="s">
-        <v>4623</v>
+      <c r="A4625" s="2" t="s">
+        <v>4624</v>
       </c>
     </row>
     <row r="4626" spans="1:1">
-      <c r="A4626" s="5" t="s">
-        <v>4624</v>
+      <c r="A4626" s="2" t="s">
+        <v>4625</v>
       </c>
     </row>
     <row r="4627" spans="1:1">
-      <c r="A4627" s="5" t="s">
-        <v>4625</v>
+      <c r="A4627" s="2" t="s">
+        <v>4626</v>
       </c>
     </row>
     <row r="4628" spans="1:1">
-      <c r="A4628" s="5" t="s">
-        <v>4626</v>
+      <c r="A4628" s="2" t="s">
+        <v>4627</v>
       </c>
     </row>
     <row r="4629" spans="1:1">
-      <c r="A4629" s="5" t="s">
-        <v>4627</v>
+      <c r="A4629" s="2" t="s">
+        <v>4628</v>
       </c>
     </row>
     <row r="4630" spans="1:1">
-      <c r="A4630" s="5" t="s">
-        <v>4628</v>
+      <c r="A4630" s="2" t="s">
+        <v>4629</v>
       </c>
     </row>
     <row r="4631" spans="1:1">
-      <c r="A4631" s="5" t="s">
-        <v>4629</v>
+      <c r="A4631" s="2" t="s">
+        <v>4630</v>
       </c>
     </row>
     <row r="4632" spans="1:1">
-      <c r="A4632" s="5" t="s">
-        <v>4630</v>
+      <c r="A4632" s="2" t="s">
+        <v>4631</v>
       </c>
     </row>
     <row r="4633" spans="1:1">
-      <c r="A4633" s="5" t="s">
-        <v>4631</v>
+      <c r="A4633" s="2" t="s">
+        <v>4632</v>
       </c>
     </row>
     <row r="4634" spans="1:1">
-      <c r="A4634" s="5" t="s">
-        <v>4632</v>
+      <c r="A4634" s="2" t="s">
+        <v>4633</v>
       </c>
     </row>
     <row r="4635" spans="1:1">
-      <c r="A4635" s="5" t="s">
-        <v>4633</v>
+      <c r="A4635" s="2" t="s">
+        <v>4634</v>
       </c>
     </row>
     <row r="4636" spans="1:1">
-      <c r="A4636" s="5" t="s">
-        <v>4634</v>
+      <c r="A4636" s="2" t="s">
+        <v>4635</v>
       </c>
     </row>
     <row r="4637" spans="1:1">
-      <c r="A4637" s="5" t="s">
-        <v>4635</v>
+      <c r="A4637" s="2" t="s">
+        <v>4636</v>
       </c>
     </row>
     <row r="4638" spans="1:1">
-      <c r="A4638" s="5" t="s">
-        <v>4636</v>
+      <c r="A4638" s="2" t="s">
+        <v>4637</v>
       </c>
     </row>
     <row r="4639" spans="1:1">
-      <c r="A4639" s="5" t="s">
-        <v>4637</v>
+      <c r="A4639" s="2" t="s">
+        <v>4638</v>
       </c>
     </row>
     <row r="4640" spans="1:1">
-      <c r="A4640" s="5" t="s">
-        <v>4638</v>
+      <c r="A4640" s="2" t="s">
+        <v>4639</v>
       </c>
     </row>
     <row r="4641" spans="1:1">
-      <c r="A4641" s="5" t="s">
-        <v>4639</v>
+      <c r="A4641" s="2" t="s">
+        <v>4640</v>
       </c>
     </row>
     <row r="4642" spans="1:1">
-      <c r="A4642" s="5" t="s">
-        <v>4640</v>
+      <c r="A4642" s="2" t="s">
+        <v>4641</v>
       </c>
     </row>
     <row r="4643" spans="1:1">
-      <c r="A4643" s="5" t="s">
-        <v>4641</v>
+      <c r="A4643" s="2" t="s">
+        <v>4642</v>
       </c>
     </row>
     <row r="4644" spans="1:1">
-      <c r="A4644" s="5" t="s">
-        <v>4642</v>
+      <c r="A4644" s="2" t="s">
+        <v>4643</v>
       </c>
     </row>
     <row r="4645" spans="1:1">
-      <c r="A4645" s="5" t="s">
-        <v>4643</v>
+      <c r="A4645" s="2" t="s">
+        <v>4644</v>
       </c>
     </row>
     <row r="4646" spans="1:1">
-      <c r="A4646" s="5" t="s">
-        <v>4644</v>
+      <c r="A4646" s="2" t="s">
+        <v>4645</v>
       </c>
     </row>
     <row r="4647" spans="1:1">
-      <c r="A4647" s="5" t="s">
-        <v>4645</v>
+      <c r="A4647" s="2" t="s">
+        <v>4646</v>
       </c>
     </row>
     <row r="4648" spans="1:1">
-      <c r="A4648" s="5" t="s">
-        <v>4646</v>
+      <c r="A4648" s="2" t="s">
+        <v>4647</v>
       </c>
     </row>
     <row r="4649" spans="1:1">
-      <c r="A4649" s="5" t="s">
-        <v>4647</v>
+      <c r="A4649" s="2" t="s">
+        <v>4648</v>
       </c>
     </row>
     <row r="4650" spans="1:1">
-      <c r="A4650" s="5" t="s">
-        <v>4648</v>
+      <c r="A4650" s="2" t="s">
+        <v>4649</v>
       </c>
     </row>
     <row r="4651" spans="1:1">
-      <c r="A4651" s="5" t="s">
-        <v>4649</v>
+      <c r="A4651" s="2" t="s">
+        <v>4650</v>
       </c>
     </row>
     <row r="4652" spans="1:1">
-      <c r="A4652" s="5" t="s">
-        <v>4650</v>
+      <c r="A4652" s="2" t="s">
+        <v>4651</v>
       </c>
     </row>
     <row r="4653" spans="1:1">
-      <c r="A4653" s="5" t="s">
-        <v>4651</v>
+      <c r="A4653" s="2" t="s">
+        <v>4652</v>
       </c>
     </row>
     <row r="4654" spans="1:1">
-      <c r="A4654" s="5" t="s">
-        <v>4652</v>
+      <c r="A4654" s="2" t="s">
+        <v>4653</v>
       </c>
     </row>
     <row r="4655" spans="1:1">
-      <c r="A4655" s="5" t="s">
-        <v>4653</v>
+      <c r="A4655" s="2" t="s">
+        <v>4654</v>
       </c>
     </row>
     <row r="4656" spans="1:1">
-      <c r="A4656" s="5" t="s">
-        <v>4654</v>
+      <c r="A4656" s="2" t="s">
+        <v>4655</v>
       </c>
     </row>
     <row r="4657" spans="1:1">
-      <c r="A4657" s="5" t="s">
-        <v>4655</v>
+      <c r="A4657" s="2" t="s">
+        <v>4656</v>
       </c>
     </row>
     <row r="4658" spans="1:1">
-      <c r="A4658" s="5" t="s">
-        <v>4656</v>
+      <c r="A4658" s="2" t="s">
+        <v>4657</v>
       </c>
     </row>
     <row r="4659" spans="1:1">
-      <c r="A4659" s="5" t="s">
-        <v>4657</v>
+      <c r="A4659" s="2" t="s">
+        <v>4658</v>
       </c>
     </row>
     <row r="4660" spans="1:1">
-      <c r="A4660" s="5" t="s">
-        <v>4658</v>
+      <c r="A4660" s="2" t="s">
+        <v>4659</v>
       </c>
     </row>
     <row r="4661" spans="1:1">
-      <c r="A4661" s="5" t="s">
-        <v>4659</v>
+      <c r="A4661" s="2" t="s">
+        <v>4660</v>
       </c>
     </row>
     <row r="4662" spans="1:1">
-      <c r="A4662" s="5" t="s">
-        <v>4660</v>
+      <c r="A4662" s="2" t="s">
+        <v>4661</v>
       </c>
     </row>
     <row r="4663" spans="1:1">
-      <c r="A4663" s="5" t="s">
-        <v>4661</v>
+      <c r="A4663" s="2" t="s">
+        <v>4662</v>
       </c>
     </row>
     <row r="4664" spans="1:1">
-      <c r="A4664" s="5" t="s">
-        <v>4662</v>
+      <c r="A4664" s="2" t="s">
+        <v>4663</v>
       </c>
     </row>
     <row r="4665" spans="1:1">
-      <c r="A4665" s="5" t="s">
-        <v>4663</v>
+      <c r="A4665" s="2" t="s">
+        <v>4664</v>
       </c>
     </row>
     <row r="4666" spans="1:1">
-      <c r="A4666" s="5" t="s">
-        <v>4664</v>
+      <c r="A4666" s="2" t="s">
+        <v>4665</v>
       </c>
     </row>
     <row r="4667" spans="1:1">
-      <c r="A4667" s="5" t="s">
-        <v>4665</v>
+      <c r="A4667" s="2" t="s">
+        <v>4666</v>
       </c>
     </row>
     <row r="4668" spans="1:1">
-      <c r="A4668" s="5" t="s">
-        <v>4666</v>
+      <c r="A4668" s="2" t="s">
+        <v>4667</v>
       </c>
     </row>
     <row r="4669" spans="1:1">
-      <c r="A4669" s="5" t="s">
-        <v>4667</v>
+      <c r="A4669" s="2" t="s">
+        <v>4668</v>
       </c>
     </row>
     <row r="4670" spans="1:1">
-      <c r="A4670" s="5" t="s">
-        <v>4668</v>
+      <c r="A4670" s="2" t="s">
+        <v>4669</v>
       </c>
     </row>
     <row r="4671" spans="1:1">
-      <c r="A4671" s="5" t="s">
-        <v>4669</v>
+      <c r="A4671" s="2" t="s">
+        <v>4670</v>
       </c>
     </row>
     <row r="4672" spans="1:1">
-      <c r="A4672" s="5" t="s">
-        <v>4670</v>
+      <c r="A4672" s="2" t="s">
+        <v>4671</v>
       </c>
     </row>
     <row r="4673" spans="1:1">
-      <c r="A4673" s="5" t="s">
-        <v>4671</v>
+      <c r="A4673" s="2" t="s">
+        <v>4672</v>
       </c>
     </row>
     <row r="4674" spans="1:1">
-      <c r="A4674" s="5" t="s">
-        <v>4672</v>
+      <c r="A4674" s="2" t="s">
+        <v>4673</v>
       </c>
     </row>
     <row r="4675" spans="1:1">
-      <c r="A4675" s="5" t="s">
-        <v>4673</v>
+      <c r="A4675" s="2" t="s">
+        <v>4674</v>
       </c>
     </row>
     <row r="4676" spans="1:1">
-      <c r="A4676" s="5" t="s">
-        <v>4674</v>
+      <c r="A4676" s="2" t="s">
+        <v>4675</v>
       </c>
     </row>
     <row r="4677" spans="1:1">
-      <c r="A4677" s="5" t="s">
-        <v>4675</v>
+      <c r="A4677" s="2" t="s">
+        <v>4676</v>
       </c>
     </row>
     <row r="4678" spans="1:1">
-      <c r="A4678" s="5" t="s">
-        <v>4676</v>
+      <c r="A4678" s="2" t="s">
+        <v>4677</v>
       </c>
     </row>
     <row r="4679" spans="1:1">
-      <c r="A4679" s="5" t="s">
-        <v>4677</v>
+      <c r="A4679" s="2" t="s">
+        <v>4678</v>
       </c>
     </row>
     <row r="4680" spans="1:1">
-      <c r="A4680" s="5" t="s">
-        <v>4678</v>
+      <c r="A4680" s="2" t="s">
+        <v>4679</v>
       </c>
     </row>
     <row r="4681" spans="1:1">
-      <c r="A4681" s="5" t="s">
-        <v>4679</v>
+      <c r="A4681" s="2" t="s">
+        <v>4680</v>
       </c>
     </row>
     <row r="4682" spans="1:1">
-      <c r="A4682" s="5" t="s">
-        <v>4680</v>
+      <c r="A4682" s="2" t="s">
+        <v>4681</v>
       </c>
     </row>
     <row r="4683" spans="1:1">
-      <c r="A4683" s="5" t="s">
-        <v>4681</v>
+      <c r="A4683" s="2" t="s">
+        <v>4682</v>
       </c>
     </row>
     <row r="4684" spans="1:1">
-      <c r="A4684" s="5" t="s">
-        <v>4682</v>
+      <c r="A4684" s="2" t="s">
+        <v>4683</v>
       </c>
     </row>
     <row r="4685" spans="1:1">
-      <c r="A4685" s="5" t="s">
-        <v>4683</v>
+      <c r="A4685" s="2" t="s">
+        <v>4684</v>
       </c>
     </row>
     <row r="4686" spans="1:1">
-      <c r="A4686" s="5" t="s">
-        <v>4684</v>
+      <c r="A4686" s="2" t="s">
+        <v>4685</v>
       </c>
     </row>
     <row r="4687" spans="1:1">
-      <c r="A4687" s="5" t="s">
-        <v>4685</v>
+      <c r="A4687" s="2" t="s">
+        <v>4686</v>
       </c>
     </row>
     <row r="4688" spans="1:1">
-      <c r="A4688" s="5" t="s">
-        <v>4686</v>
+      <c r="A4688" s="2" t="s">
+        <v>4687</v>
       </c>
     </row>
     <row r="4689" spans="1:1">
-      <c r="A4689" s="5" t="s">
-        <v>4687</v>
+      <c r="A4689" s="2" t="s">
+        <v>4688</v>
       </c>
     </row>
     <row r="4690" spans="1:1">
-      <c r="A4690" s="5" t="s">
-        <v>4688</v>
+      <c r="A4690" s="2" t="s">
+        <v>4689</v>
       </c>
     </row>
     <row r="4691" spans="1:1">
-      <c r="A4691" s="5" t="s">
-        <v>4689</v>
+      <c r="A4691" s="2" t="s">
+        <v>4690</v>
       </c>
     </row>
     <row r="4692" spans="1:1">
-      <c r="A4692" s="5" t="s">
-        <v>4690</v>
+      <c r="A4692" s="2" t="s">
+        <v>4691</v>
       </c>
     </row>
     <row r="4693" spans="1:1">
-      <c r="A4693" s="5" t="s">
-        <v>4691</v>
+      <c r="A4693" s="2" t="s">
+        <v>4692</v>
       </c>
     </row>
     <row r="4694" spans="1:1">
-      <c r="A4694" s="5" t="s">
-        <v>4692</v>
+      <c r="A4694" s="2" t="s">
+        <v>4693</v>
       </c>
     </row>
     <row r="4695" spans="1:1">
-      <c r="A4695" s="5" t="s">
-        <v>4693</v>
+      <c r="A4695" s="3" t="s">
+        <v>4694</v>
       </c>
     </row>
     <row r="4696" spans="1:1">
-      <c r="A4696"/>
+      <c r="A4696" s="3" t="s">
+        <v>4695</v>
+      </c>
     </row>
     <row r="4697" spans="1:1">
-      <c r="A4697"/>
+      <c r="A4697" s="3" t="s">
+        <v>4696</v>
+      </c>
     </row>
     <row r="4698" spans="1:1">
-      <c r="A4698"/>
+      <c r="A4698" s="3" t="s">
+        <v>4697</v>
+      </c>
     </row>
     <row r="4699" spans="1:1">
-      <c r="A4699"/>
+      <c r="A4699" s="3" t="s">
+        <v>4698</v>
+      </c>
     </row>
     <row r="4700" spans="1:1">
-      <c r="A4700"/>
+      <c r="A4700" s="3" t="s">
+        <v>4699</v>
+      </c>
     </row>
     <row r="4701" spans="1:1">
-      <c r="A4701"/>
+      <c r="A4701" s="3" t="s">
+        <v>4700</v>
+      </c>
     </row>
     <row r="4702" spans="1:1">
-      <c r="A4702"/>
+      <c r="A4702" s="3" t="s">
+        <v>4701</v>
+      </c>
     </row>
     <row r="4703" spans="1:1">
-      <c r="A4703"/>
+      <c r="A4703" s="3" t="s">
+        <v>4702</v>
+      </c>
     </row>
     <row r="4704" spans="1:1">
-      <c r="A4704"/>
+      <c r="A4704" s="3" t="s">
+        <v>4703</v>
+      </c>
     </row>
     <row r="4705" spans="1:1">
-      <c r="A4705"/>
+      <c r="A4705" s="3" t="s">
+        <v>4704</v>
+      </c>
     </row>
     <row r="4706" spans="1:1">
-      <c r="A4706"/>
+      <c r="A4706" s="3" t="s">
+        <v>4705</v>
+      </c>
     </row>
     <row r="4707" spans="1:1">
-      <c r="A4707"/>
+      <c r="A4707" s="3" t="s">
+        <v>4706</v>
+      </c>
     </row>
     <row r="4708" spans="1:1">
-      <c r="A4708"/>
+      <c r="A4708" s="3" t="s">
+        <v>4707</v>
+      </c>
     </row>
     <row r="4709" spans="1:1">
-      <c r="A4709"/>
+      <c r="A4709" s="3" t="s">
+        <v>4708</v>
+      </c>
     </row>
     <row r="4710" spans="1:1">
-      <c r="A4710"/>
+      <c r="A4710" s="3" t="s">
+        <v>4709</v>
+      </c>
     </row>
     <row r="4711" spans="1:1">
-      <c r="A4711"/>
+      <c r="A4711" s="3" t="s">
+        <v>4710</v>
+      </c>
     </row>
     <row r="4712" spans="1:1">
-      <c r="A4712"/>
+      <c r="A4712" s="3" t="s">
+        <v>4711</v>
+      </c>
     </row>
     <row r="4713" spans="1:1">
-      <c r="A4713"/>
+      <c r="A4713" s="3" t="s">
+        <v>4712</v>
+      </c>
     </row>
     <row r="4714" spans="1:1">
-      <c r="A4714"/>
+      <c r="A4714" s="3" t="s">
+        <v>4713</v>
+      </c>
     </row>
     <row r="4715" spans="1:1">
-      <c r="A4715"/>
+      <c r="A4715" s="3" t="s">
+        <v>4714</v>
+      </c>
     </row>
     <row r="4716" spans="1:1">
-      <c r="A4716"/>
+      <c r="A4716" s="3" t="s">
+        <v>4715</v>
+      </c>
     </row>
     <row r="4717" spans="1:1">
-      <c r="A4717"/>
+      <c r="A4717" s="3" t="s">
+        <v>4716</v>
+      </c>
     </row>
     <row r="4718" spans="1:1">
-      <c r="A4718"/>
+      <c r="A4718" s="3" t="s">
+        <v>4717</v>
+      </c>
     </row>
     <row r="4719" spans="1:1">
-      <c r="A4719"/>
+      <c r="A4719" s="3" t="s">
+        <v>4718</v>
+      </c>
     </row>
     <row r="4720" spans="1:1">
-      <c r="A4720"/>
+      <c r="A4720" s="3" t="s">
+        <v>4719</v>
+      </c>
     </row>
     <row r="4721" spans="1:1">
-      <c r="A4721"/>
+      <c r="A4721" s="3" t="s">
+        <v>4720</v>
+      </c>
     </row>
     <row r="4722" spans="1:1">
-      <c r="A4722"/>
+      <c r="A4722" s="3" t="s">
+        <v>4721</v>
+      </c>
     </row>
     <row r="4723" spans="1:1">
-      <c r="A4723"/>
+      <c r="A4723" s="3" t="s">
+        <v>4722</v>
+      </c>
     </row>
     <row r="4724" spans="1:1">
-      <c r="A4724"/>
+      <c r="A4724" s="3" t="s">
+        <v>4723</v>
+      </c>
     </row>
     <row r="4725" spans="1:1">
-      <c r="A4725"/>
+      <c r="A4725" s="3" t="s">
+        <v>4724</v>
+      </c>
     </row>
     <row r="4726" spans="1:1">
-      <c r="A4726"/>
+      <c r="A4726" s="3" t="s">
+        <v>4725</v>
+      </c>
     </row>
     <row r="4727" spans="1:1">
-      <c r="A4727"/>
+      <c r="A4727" s="3" t="s">
+        <v>4726</v>
+      </c>
     </row>
     <row r="4728" spans="1:1">
-      <c r="A4728"/>
+      <c r="A4728" s="3" t="s">
+        <v>4727</v>
+      </c>
     </row>
     <row r="4729" spans="1:1">
-      <c r="A4729"/>
+      <c r="A4729" s="3" t="s">
+        <v>4728</v>
+      </c>
     </row>
     <row r="4730" spans="1:1">
-      <c r="A4730"/>
+      <c r="A4730" s="3" t="s">
+        <v>4729</v>
+      </c>
     </row>
     <row r="4731" spans="1:1">
-      <c r="A4731"/>
+      <c r="A4731" s="3" t="s">
+        <v>4730</v>
+      </c>
     </row>
     <row r="4732" spans="1:1">
-      <c r="A4732"/>
+      <c r="A4732" s="3" t="s">
+        <v>4731</v>
+      </c>
     </row>
     <row r="4733" spans="1:1">
-      <c r="A4733"/>
+      <c r="A4733" s="3" t="s">
+        <v>4732</v>
+      </c>
     </row>
     <row r="4734" spans="1:1">
-      <c r="A4734"/>
+      <c r="A4734" s="3" t="s">
+        <v>4733</v>
+      </c>
     </row>
     <row r="4735" spans="1:1">
-      <c r="A4735"/>
+      <c r="A4735" s="3" t="s">
+        <v>4734</v>
+      </c>
     </row>
     <row r="4736" spans="1:1">
-      <c r="A4736"/>
+      <c r="A4736" s="3" t="s">
+        <v>4735</v>
+      </c>
     </row>
     <row r="4737" spans="1:1">
-      <c r="A4737"/>
+      <c r="A4737" s="3" t="s">
+        <v>4736</v>
+      </c>
     </row>
     <row r="4738" spans="1:1">
-      <c r="A4738"/>
+      <c r="A4738" s="3" t="s">
+        <v>4737</v>
+      </c>
     </row>
     <row r="4739" spans="1:1">
-      <c r="A4739"/>
+      <c r="A4739" s="3" t="s">
+        <v>4738</v>
+      </c>
     </row>
     <row r="4740" spans="1:1">
-      <c r="A4740"/>
+      <c r="A4740" s="3" t="s">
+        <v>4739</v>
+      </c>
     </row>
     <row r="4741" spans="1:1">
-      <c r="A4741"/>
+      <c r="A4741" s="3" t="s">
+        <v>4740</v>
+      </c>
     </row>
     <row r="4742" spans="1:1">
-      <c r="A4742"/>
+      <c r="A4742" s="3" t="s">
+        <v>4741</v>
+      </c>
     </row>
     <row r="4743" spans="1:1">
-      <c r="A4743"/>
+      <c r="A4743" s="3" t="s">
+        <v>4742</v>
+      </c>
     </row>
     <row r="4744" spans="1:1">
-      <c r="A4744"/>
+      <c r="A4744" s="3" t="s">
+        <v>4743</v>
+      </c>
     </row>
     <row r="4745" spans="1:1">
       <c r="A4745"/>
@@ -49805,20 +50049,11 @@
     <row r="8437" spans="1:1">
       <c r="A8437"/>
     </row>
-    <row r="8438" spans="1:1">
-      <c r="A8438"/>
-    </row>
-    <row r="8439" spans="1:1">
-      <c r="A8439"/>
-    </row>
-    <row r="8440" spans="1:1">
-      <c r="A8440"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:A4359" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="A1:A4431 A8441:A1048576">
+  <conditionalFormatting sqref="A1:A4430 A8438:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
